--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="DDR4" sheetId="5" r:id="rId5"/>
     <sheet name="SSD" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="38">
   <si>
     <t>시트구분</t>
   </si>
@@ -138,10 +138,6 @@
   </si>
   <si>
     <t>SSD 단가 변동 및 수량 HISTORY</t>
-  </si>
-  <si>
-    <t>SAPH N97 DP (43A,48A)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -777,885 +773,831 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5">
         <v>45931</v>
       </c>
-      <c r="C4" s="6">
-        <v>800</v>
-      </c>
+      <c r="C4" s="6"/>
       <c r="D4" s="7">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="E4" s="7">
+        <v>72.5</v>
+      </c>
+      <c r="E4" s="7" t="str">
         <f>IF(OR(A4="",SUMIFS(C$4:C4,A$4:A4,A4)=0),"",SUMPRODUCT((A$4:A4=A4)*(C$4:C4)*(D$4:D4))/SUMIFS(C$4:C4,A$4:A4,A4))</f>
-        <v>75.900000000000006</v>
-      </c>
-      <c r="F4" s="6">
-        <v>650</v>
-      </c>
-      <c r="G4" s="6">
-        <f t="shared" ref="G4:G35" si="0">IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
-        <v>150</v>
+        <v/>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6" t="str">
+        <f>IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
+        <v/>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B5" s="5">
         <v>45962</v>
       </c>
-      <c r="C5" s="6">
-        <v>150</v>
-      </c>
+      <c r="C5" s="6"/>
       <c r="D5" s="7">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="E5" s="7">
+        <v>72.5</v>
+      </c>
+      <c r="E5" s="7" t="str">
         <f>IF(OR(A5="",SUMIFS(C$4:C5,A$4:A5,A5)=0),"",SUMPRODUCT((A$4:A5=A5)*(C$4:C5)*(D$4:D5))/SUMIFS(C$4:C5,A$4:A5,A5))</f>
-        <v>75.900000000000006</v>
-      </c>
-      <c r="F5" s="6">
-        <v>150</v>
-      </c>
-      <c r="G5" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6" t="str">
+        <f>IF(C5="","",C5-IF(ISNUMBER(F5),F5,0))</f>
+        <v/>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B6" s="5">
         <v>45992</v>
       </c>
-      <c r="C6" s="6">
-        <v>180</v>
-      </c>
+      <c r="C6" s="6"/>
       <c r="D6" s="7">
-        <v>83.31</v>
-      </c>
-      <c r="E6" s="7">
+        <v>72.5</v>
+      </c>
+      <c r="E6" s="7" t="str">
         <f>IF(OR(A6="",SUMIFS(C$4:C6,A$4:A6,A6)=0),"",SUMPRODUCT((A$4:A6=A6)*(C$4:C6)*(D$4:D6))/SUMIFS(C$4:C6,A$4:A6,A6))</f>
-        <v>77.080353982300892</v>
-      </c>
-      <c r="F6" s="6">
-        <v>180</v>
-      </c>
-      <c r="G6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="str">
+        <f>IF(C6="","",C6-IF(ISNUMBER(F6),F6,0))</f>
+        <v/>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B7" s="5">
         <v>46023</v>
       </c>
-      <c r="C7" s="6">
-        <v>9</v>
-      </c>
+      <c r="C7" s="6"/>
       <c r="D7" s="7">
-        <v>92.21</v>
-      </c>
-      <c r="E7" s="7">
+        <v>72.5</v>
+      </c>
+      <c r="E7" s="7" t="str">
         <f>IF(OR(A7="",SUMIFS(C$4:C7,A$4:A7,A7)=0),"",SUMPRODUCT((A$4:A7=A7)*(C$4:C7)*(D$4:D7))/SUMIFS(C$4:C7,A$4:A7,A7))</f>
-        <v>77.199903424056188</v>
-      </c>
-      <c r="F7" s="6">
-        <v>9</v>
-      </c>
-      <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="str">
+        <f>IF(C7="","",C7-IF(ISNUMBER(F7),F7,0))</f>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5">
         <v>46054</v>
       </c>
-      <c r="C8" s="6">
-        <v>440</v>
-      </c>
+      <c r="C8" s="6"/>
       <c r="D8" s="7">
-        <v>92.9</v>
-      </c>
-      <c r="E8" s="7">
+        <v>72.5</v>
+      </c>
+      <c r="E8" s="7" t="str">
         <f>IF(OR(A8="",SUMIFS(C$4:C8,A$4:A8,A8)=0),"",SUMPRODUCT((A$4:A8=A8)*(C$4:C8)*(D$4:D8))/SUMIFS(C$4:C8,A$4:A8,A8))</f>
-        <v>81.574851171627614</v>
+        <v/>
       </c>
       <c r="F8" s="6">
-        <v>440</v>
-      </c>
-      <c r="G8" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="G8" s="6" t="str">
+        <f>IF(C8="","",C8-IF(ISNUMBER(F8),F8,0))</f>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="C9" s="6">
-        <v>722</v>
+        <v>300</v>
       </c>
       <c r="D9" s="7">
-        <v>92.9</v>
+        <v>89.5</v>
       </c>
       <c r="E9" s="7">
         <f>IF(OR(A9="",SUMIFS(C$4:C9,A$4:A9,A9)=0),"",SUMPRODUCT((A$4:A9=A9)*(C$4:C9)*(D$4:D9))/SUMIFS(C$4:C9,A$4:A9,A9))</f>
-        <v>85.128418079096036</v>
-      </c>
-      <c r="F9" s="6">
-        <v>722</v>
-      </c>
+        <v>89.5</v>
+      </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF(C9="","",C9-IF(ISNUMBER(F9),F9,0))</f>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C10" s="6">
-        <v>670</v>
+        <v>228</v>
       </c>
       <c r="D10" s="7">
-        <v>102.19</v>
+        <v>89.5</v>
       </c>
       <c r="E10" s="7">
         <f>IF(OR(A10="",SUMIFS(C$4:C10,A$4:A10,A10)=0),"",SUMPRODUCT((A$4:A10=A10)*(C$4:C10)*(D$4:D10))/SUMIFS(C$4:C10,A$4:A10,A10))</f>
-        <v>88.976031639178714</v>
+        <v>89.5</v>
       </c>
       <c r="F10" s="6">
-        <v>502</v>
+        <v>197</v>
       </c>
       <c r="G10" s="6">
-        <f t="shared" si="0"/>
-        <v>168</v>
+        <f>IF(C10="","",C10-IF(ISNUMBER(F10),F10,0))</f>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C11" s="6">
-        <v>1168</v>
+        <v>31</v>
       </c>
       <c r="D11" s="7">
-        <v>106.21</v>
+        <v>89.5</v>
       </c>
       <c r="E11" s="7">
         <f>IF(OR(A11="",SUMIFS(C$4:C11,A$4:A11,A11)=0),"",SUMPRODUCT((A$4:A11=A11)*(C$4:C11)*(D$4:D11))/SUMIFS(C$4:C11,A$4:A11,A11))</f>
-        <v>93.839350084561474</v>
+        <v>89.5</v>
       </c>
       <c r="F11" s="6">
-        <v>375</v>
+        <v>31</v>
       </c>
       <c r="G11" s="6">
-        <f t="shared" si="0"/>
-        <v>793</v>
+        <f>IF(C11="","",C11-IF(ISNUMBER(F11),F11,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B12" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C12" s="6">
-        <v>793</v>
+        <v>300</v>
       </c>
       <c r="D12" s="7">
-        <v>106.21</v>
+        <v>104.5</v>
       </c>
       <c r="E12" s="7">
         <f>IF(OR(A12="",SUMIFS(C$4:C12,A$4:A12,A12)=0),"",SUMPRODUCT((A$4:A12=A12)*(C$4:C12)*(D$4:D12))/SUMIFS(C$4:C12,A$4:A12,A12))</f>
-        <v>95.828386050283854</v>
-      </c>
-      <c r="F12" s="6"/>
+        <v>94.738649592549478</v>
+      </c>
+      <c r="F12" s="6">
+        <v>199</v>
+      </c>
       <c r="G12" s="6">
-        <f t="shared" si="0"/>
-        <v>793</v>
+        <f>IF(C12="","",C12-IF(ISNUMBER(F12),F12,0))</f>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B13" s="5">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="C13" s="6">
-        <v>1293</v>
+        <v>101</v>
       </c>
       <c r="D13" s="7">
-        <v>100.87</v>
+        <v>103.1</v>
       </c>
       <c r="E13" s="7">
         <f>IF(OR(A13="",SUMIFS(C$4:C13,A$4:A13,A13)=0),"",SUMPRODUCT((A$4:A13=A13)*(C$4:C13)*(D$4:D13))/SUMIFS(C$4:C13,A$4:A13,A13))</f>
-        <v>96.875583935742966</v>
-      </c>
-      <c r="F13" s="6">
-        <v>560</v>
-      </c>
+        <v>95.618333333333339</v>
+      </c>
+      <c r="F13" s="6"/>
       <c r="G13" s="6">
-        <f t="shared" si="0"/>
-        <v>733</v>
+        <f>IF(C13="","",C13-IF(ISNUMBER(F13),F13,0))</f>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B14" s="5">
-        <v>46235</v>
+        <v>46174</v>
       </c>
       <c r="C14" s="6">
-        <v>733</v>
+        <v>101</v>
       </c>
       <c r="D14" s="7">
-        <v>100.87</v>
+        <v>103.1</v>
       </c>
       <c r="E14" s="7">
         <f>IF(OR(A14="",SUMIFS(C$4:C14,A$4:A14,A14)=0),"",SUMPRODUCT((A$4:A14=A14)*(C$4:C14)*(D$4:D14))/SUMIFS(C$4:C14,A$4:A14,A14))</f>
-        <v>97.296381144006901</v>
+        <v>96.330537229029233</v>
       </c>
       <c r="F14" s="6">
-        <v>618</v>
+        <v>73</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="0"/>
-        <v>115</v>
+        <f>IF(C14="","",C14-IF(ISNUMBER(F14),F14,0))</f>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B15" s="5">
-        <v>46266</v>
+        <v>46204</v>
       </c>
       <c r="C15" s="6">
-        <v>1171</v>
+        <v>28</v>
       </c>
       <c r="D15" s="7">
-        <v>110.04</v>
+        <v>103.1</v>
       </c>
       <c r="E15" s="7">
         <f>IF(OR(A15="",SUMIFS(C$4:C15,A$4:A15,A15)=0),"",SUMPRODUCT((A$4:A15=A15)*(C$4:C15)*(D$4:D15))/SUMIFS(C$4:C15,A$4:A15,A15))</f>
-        <v>99.132126952884732</v>
-      </c>
-      <c r="F15" s="6">
-        <v>30</v>
-      </c>
+        <v>96.50459136822775</v>
+      </c>
+      <c r="F15" s="6"/>
       <c r="G15" s="6">
-        <f t="shared" si="0"/>
-        <v>1141</v>
+        <f>IF(C15="","",C15-IF(ISNUMBER(F15),F15,0))</f>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B16" s="5">
-        <v>46296</v>
+        <v>46235</v>
       </c>
       <c r="C16" s="6">
-        <v>1585</v>
+        <v>28</v>
       </c>
       <c r="D16" s="7">
-        <v>111.24</v>
+        <v>103.1</v>
       </c>
       <c r="E16" s="7">
         <f>IF(OR(A16="",SUMIFS(C$4:C16,A$4:A16,A16)=0),"",SUMPRODUCT((A$4:A16=A16)*(C$4:C16)*(D$4:D16))/SUMIFS(C$4:C16,A$4:A16,A16))</f>
-        <v>101.10772699197035</v>
-      </c>
-      <c r="F16" s="6">
-        <v>70</v>
-      </c>
+        <v>96.669919427036717</v>
+      </c>
+      <c r="F16" s="6"/>
       <c r="G16" s="6">
-        <f t="shared" si="0"/>
-        <v>1515</v>
+        <f>IF(C16="","",C16-IF(ISNUMBER(F16),F16,0))</f>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B17" s="5">
-        <v>45962</v>
+        <v>46266</v>
       </c>
       <c r="C17" s="6">
-        <v>700</v>
+        <v>28</v>
       </c>
       <c r="D17" s="7">
-        <v>84.9</v>
+        <v>103.1</v>
       </c>
       <c r="E17" s="7">
         <f>IF(OR(A17="",SUMIFS(C$4:C17,A$4:A17,A17)=0),"",SUMPRODUCT((A$4:A17=A17)*(C$4:C17)*(D$4:D17))/SUMIFS(C$4:C17,A$4:A17,A17))</f>
-        <v>100.01828884194353</v>
-      </c>
-      <c r="F17" s="6">
-        <v>520</v>
-      </c>
+        <v>96.827161572052418</v>
+      </c>
+      <c r="F17" s="6"/>
       <c r="G17" s="6">
-        <f t="shared" si="0"/>
-        <v>180</v>
+        <f>IF(C17="","",C17-IF(ISNUMBER(F17),F17,0))</f>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B18" s="5">
-        <v>45992</v>
+        <v>46266</v>
       </c>
       <c r="C18" s="6">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="D18" s="7">
-        <v>93.9</v>
+        <v>112.5</v>
       </c>
       <c r="E18" s="7">
         <f>IF(OR(A18="",SUMIFS(C$4:C18,A$4:A18,A18)=0),"",SUMPRODUCT((A$4:A18=A18)*(C$4:C18)*(D$4:D18))/SUMIFS(C$4:C18,A$4:A18,A18))</f>
-        <v>99.931414237031419</v>
-      </c>
-      <c r="F18" s="6">
-        <v>150</v>
-      </c>
+        <v>102.77349593495937</v>
+      </c>
+      <c r="F18" s="6"/>
       <c r="G18" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF(C18="","",C18-IF(ISNUMBER(F18),F18,0))</f>
+        <v>700</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B19" s="5">
-        <v>46023</v>
+        <v>46296</v>
       </c>
       <c r="C19" s="6">
-        <v>1350</v>
+        <v>728</v>
       </c>
       <c r="D19" s="7">
-        <v>92.9</v>
+        <v>112.14</v>
       </c>
       <c r="E19" s="7">
         <f>IF(OR(A19="",SUMIFS(C$4:C19,A$4:A19,A19)=0),"",SUMPRODUCT((A$4:A19=A19)*(C$4:C19)*(D$4:D19))/SUMIFS(C$4:C19,A$4:A19,A19))</f>
-        <v>99.134670135974474</v>
+        <v>105.42363777691412</v>
       </c>
       <c r="F19" s="6">
-        <v>910</v>
+        <v>140</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="0"/>
-        <v>440</v>
+        <f>IF(C19="","",C19-IF(ISNUMBER(F19),F19,0))</f>
+        <v>588</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B20" s="5">
-        <v>46054</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1200</v>
-      </c>
+        <v>45931</v>
+      </c>
+      <c r="C20" s="6"/>
       <c r="D20" s="7">
-        <v>92.9</v>
-      </c>
-      <c r="E20" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E20" s="7" t="str">
         <f>IF(OR(A20="",SUMIFS(C$4:C20,A$4:A20,A20)=0),"",SUMPRODUCT((A$4:A20=A20)*(C$4:C20)*(D$4:D20))/SUMIFS(C$4:C20,A$4:A20,A20))</f>
-        <v>98.564165014488324</v>
-      </c>
-      <c r="F20" s="6">
-        <v>478</v>
-      </c>
-      <c r="G20" s="6">
-        <f t="shared" si="0"/>
-        <v>722</v>
+        <v/>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6" t="str">
+        <f>IF(C20="","",C20-IF(ISNUMBER(F20),F20,0))</f>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B21" s="5">
-        <v>46082</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1000</v>
-      </c>
+        <v>45962</v>
+      </c>
+      <c r="C21" s="6"/>
       <c r="D21" s="7">
-        <v>108.9</v>
-      </c>
-      <c r="E21" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E21" s="7" t="str">
         <f>IF(OR(A21="",SUMIFS(C$4:C21,A$4:A21,A21)=0),"",SUMPRODUCT((A$4:A21=A21)*(C$4:C21)*(D$4:D21))/SUMIFS(C$4:C21,A$4:A21,A21))</f>
-        <v>99.296475839591892</v>
-      </c>
-      <c r="F21" s="6">
-        <v>330</v>
-      </c>
-      <c r="G21" s="6">
-        <f t="shared" si="0"/>
-        <v>670</v>
+        <v/>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6" t="str">
+        <f>IF(C21="","",C21-IF(ISNUMBER(F21),F21,0))</f>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B22" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1000</v>
-      </c>
+        <v>45992</v>
+      </c>
+      <c r="C22" s="6"/>
       <c r="D22" s="7">
-        <v>108.9</v>
-      </c>
-      <c r="E22" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E22" s="7" t="str">
         <f>IF(OR(A22="",SUMIFS(C$4:C22,A$4:A22,A22)=0),"",SUMPRODUCT((A$4:A22=A22)*(C$4:C22)*(D$4:D22))/SUMIFS(C$4:C22,A$4:A22,A22))</f>
-        <v>99.931881699086944</v>
+        <v/>
       </c>
       <c r="F22" s="6"/>
-      <c r="G22" s="6">
-        <f t="shared" si="0"/>
-        <v>1000</v>
+      <c r="G22" s="6" t="str">
+        <f>IF(C22="","",C22-IF(ISNUMBER(F22),F22,0))</f>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B23" s="5">
-        <v>46174</v>
-      </c>
-      <c r="C23" s="6">
-        <v>500</v>
-      </c>
+        <v>46023</v>
+      </c>
+      <c r="C23" s="6"/>
       <c r="D23" s="7">
-        <v>92.4</v>
-      </c>
-      <c r="E23" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E23" s="7" t="str">
         <f>IF(OR(A23="",SUMIFS(C$4:C23,A$4:A23,A23)=0),"",SUMPRODUCT((A$4:A23=A23)*(C$4:C23)*(D$4:D23))/SUMIFS(C$4:C23,A$4:A23,A23))</f>
-        <v>99.690691686947602</v>
+        <v/>
       </c>
       <c r="F23" s="6"/>
-      <c r="G23" s="6">
-        <f t="shared" si="0"/>
-        <v>500</v>
+      <c r="G23" s="6" t="str">
+        <f>IF(C23="","",C23-IF(ISNUMBER(F23),F23,0))</f>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B24" s="5">
-        <v>46235</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1056</v>
-      </c>
+        <v>46054</v>
+      </c>
+      <c r="C24" s="6"/>
       <c r="D24" s="7">
-        <v>116.4</v>
-      </c>
-      <c r="E24" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E24" s="7" t="str">
         <f>IF(OR(A24="",SUMIFS(C$4:C24,A$4:A24,A24)=0),"",SUMPRODUCT((A$4:A24=A24)*(C$4:C24)*(D$4:D24))/SUMIFS(C$4:C24,A$4:A24,A24))</f>
-        <v>100.74918176364726</v>
+        <v/>
       </c>
       <c r="F24" s="6"/>
-      <c r="G24" s="6">
-        <f t="shared" si="0"/>
-        <v>1056</v>
+      <c r="G24" s="6" t="str">
+        <f>IF(C24="","",C24-IF(ISNUMBER(F24),F24,0))</f>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B25" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C25" s="6">
-        <v>444</v>
-      </c>
+        <v>46082</v>
+      </c>
+      <c r="C25" s="6"/>
       <c r="D25" s="7">
-        <v>114.4</v>
-      </c>
-      <c r="E25" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E25" s="7" t="str">
         <f>IF(OR(A25="",SUMIFS(C$4:C25,A$4:A25,A25)=0),"",SUMPRODUCT((A$4:A25=A25)*(C$4:C25)*(D$4:D25))/SUMIFS(C$4:C25,A$4:A25,A25))</f>
-        <v>101.10333411242257</v>
+        <v/>
       </c>
       <c r="F25" s="6"/>
-      <c r="G25" s="6">
-        <f t="shared" si="0"/>
-        <v>444</v>
+      <c r="G25" s="6" t="str">
+        <f>IF(C25="","",C25-IF(ISNUMBER(F25),F25,0))</f>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B26" s="5">
-        <v>45992</v>
-      </c>
-      <c r="C26" s="6">
-        <v>500</v>
-      </c>
+        <v>46113</v>
+      </c>
+      <c r="C26" s="6"/>
       <c r="D26" s="7">
-        <v>94.9</v>
-      </c>
-      <c r="E26" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E26" s="7" t="str">
         <f>IF(OR(A26="",SUMIFS(C$4:C26,A$4:A26,A26)=0),"",SUMPRODUCT((A$4:A26=A26)*(C$4:C26)*(D$4:D26))/SUMIFS(C$4:C26,A$4:A26,A26))</f>
-        <v>100.9272431020779</v>
-      </c>
-      <c r="F26" s="6">
-        <v>491</v>
-      </c>
-      <c r="G26" s="6">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v/>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6" t="str">
+        <f>IF(C26="","",C26-IF(ISNUMBER(F26),F26,0))</f>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B27" s="5">
-        <v>45931</v>
-      </c>
-      <c r="C27" s="6">
-        <v>32</v>
-      </c>
+        <v>46143</v>
+      </c>
+      <c r="C27" s="6"/>
       <c r="D27" s="7">
-        <v>79.2</v>
-      </c>
-      <c r="E27" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E27" s="7" t="str">
         <f>IF(OR(A27="",SUMIFS(C$4:C27,A$4:A27,A27)=0),"",SUMPRODUCT((A$4:A27=A27)*(C$4:C27)*(D$4:D27))/SUMIFS(C$4:C27,A$4:A27,A27))</f>
-        <v>79.2</v>
+        <v/>
       </c>
       <c r="F27" s="6"/>
-      <c r="G27" s="6">
-        <f t="shared" si="0"/>
-        <v>32</v>
+      <c r="G27" s="6" t="str">
+        <f>IF(C27="","",C27-IF(ISNUMBER(F27),F27,0))</f>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B28" s="5">
-        <v>45962</v>
-      </c>
-      <c r="C28" s="6">
-        <v>32</v>
-      </c>
+        <v>46174</v>
+      </c>
+      <c r="C28" s="6"/>
       <c r="D28" s="7">
-        <v>79.2</v>
-      </c>
-      <c r="E28" s="7">
+        <v>73.5</v>
+      </c>
+      <c r="E28" s="7" t="str">
         <f>IF(OR(A28="",SUMIFS(C$4:C28,A$4:A28,A28)=0),"",SUMPRODUCT((A$4:A28=A28)*(C$4:C28)*(D$4:D28))/SUMIFS(C$4:C28,A$4:A28,A28))</f>
-        <v>79.2</v>
+        <v/>
       </c>
       <c r="F28" s="6"/>
-      <c r="G28" s="6">
-        <f t="shared" si="0"/>
-        <v>32</v>
+      <c r="G28" s="6" t="str">
+        <f>IF(C28="","",C28-IF(ISNUMBER(F28),F28,0))</f>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B29" s="5">
-        <v>45992</v>
+        <v>46174</v>
       </c>
       <c r="C29" s="6">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="D29" s="7">
-        <v>79.2</v>
+        <v>91.4</v>
       </c>
       <c r="E29" s="7">
         <f>IF(OR(A29="",SUMIFS(C$4:C29,A$4:A29,A29)=0),"",SUMPRODUCT((A$4:A29=A29)*(C$4:C29)*(D$4:D29))/SUMIFS(C$4:C29,A$4:A29,A29))</f>
-        <v>79.2</v>
-      </c>
-      <c r="F29" s="6"/>
+        <v>91.4</v>
+      </c>
+      <c r="F29" s="6">
+        <v>5</v>
+      </c>
       <c r="G29" s="6">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f>IF(C29="","",C29-IF(ISNUMBER(F29),F29,0))</f>
+        <v>595</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B30" s="5">
-        <v>46023</v>
+        <v>46204</v>
       </c>
       <c r="C30" s="6">
-        <v>32</v>
+        <v>595</v>
       </c>
       <c r="D30" s="7">
-        <v>79.2</v>
+        <v>91.4</v>
       </c>
       <c r="E30" s="7">
         <f>IF(OR(A30="",SUMIFS(C$4:C30,A$4:A30,A30)=0),"",SUMPRODUCT((A$4:A30=A30)*(C$4:C30)*(D$4:D30))/SUMIFS(C$4:C30,A$4:A30,A30))</f>
-        <v>79.2</v>
-      </c>
-      <c r="F30" s="6"/>
+        <v>91.4</v>
+      </c>
+      <c r="F30" s="6">
+        <v>18</v>
+      </c>
       <c r="G30" s="6">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f>IF(C30="","",C30-IF(ISNUMBER(F30),F30,0))</f>
+        <v>577</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B31" s="5">
-        <v>46054</v>
+        <v>46235</v>
       </c>
       <c r="C31" s="6">
-        <v>32</v>
+        <v>577</v>
       </c>
       <c r="D31" s="7">
-        <v>79.2</v>
+        <v>91.4</v>
       </c>
       <c r="E31" s="7">
         <f>IF(OR(A31="",SUMIFS(C$4:C31,A$4:A31,A31)=0),"",SUMPRODUCT((A$4:A31=A31)*(C$4:C31)*(D$4:D31))/SUMIFS(C$4:C31,A$4:A31,A31))</f>
-        <v>79.2</v>
-      </c>
-      <c r="F31" s="6"/>
+        <v>91.399999999999991</v>
+      </c>
+      <c r="F31" s="6">
+        <v>80</v>
+      </c>
       <c r="G31" s="6">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f>IF(C31="","",C31-IF(ISNUMBER(F31),F31,0))</f>
+        <v>497</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B32" s="5">
-        <v>46082</v>
+        <v>46266</v>
       </c>
       <c r="C32" s="6">
-        <v>32</v>
+        <v>497</v>
       </c>
       <c r="D32" s="7">
-        <v>79.2</v>
+        <v>91.4</v>
       </c>
       <c r="E32" s="7">
         <f>IF(OR(A32="",SUMIFS(C$4:C32,A$4:A32,A32)=0),"",SUMPRODUCT((A$4:A32=A32)*(C$4:C32)*(D$4:D32))/SUMIFS(C$4:C32,A$4:A32,A32))</f>
-        <v>79.2</v>
-      </c>
-      <c r="F32" s="6"/>
+        <v>91.399999999999991</v>
+      </c>
+      <c r="F32" s="6">
+        <v>28</v>
+      </c>
       <c r="G32" s="6">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f>IF(C32="","",C32-IF(ISNUMBER(F32),F32,0))</f>
+        <v>469</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B33" s="5">
-        <v>46113</v>
+        <v>46296</v>
       </c>
       <c r="C33" s="6">
-        <v>32</v>
+        <v>469</v>
       </c>
       <c r="D33" s="7">
-        <v>79.2</v>
+        <v>91.4</v>
       </c>
       <c r="E33" s="7">
         <f>IF(OR(A33="",SUMIFS(C$4:C33,A$4:A33,A33)=0),"",SUMPRODUCT((A$4:A33=A33)*(C$4:C33)*(D$4:D33))/SUMIFS(C$4:C33,A$4:A33,A33))</f>
-        <v>79.2</v>
+        <v>91.399999999999991</v>
       </c>
       <c r="F33" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>IF(C33="","",C33-IF(ISNUMBER(F33),F33,0))</f>
+        <v>439</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B34" s="5">
-        <v>46143</v>
-      </c>
-      <c r="C34" s="6">
-        <v>12</v>
-      </c>
+        <v>45931</v>
+      </c>
+      <c r="C34" s="6"/>
       <c r="D34" s="7">
-        <v>79.2</v>
-      </c>
-      <c r="E34" s="7">
+        <v>177.6</v>
+      </c>
+      <c r="E34" s="7" t="str">
         <f>IF(OR(A34="",SUMIFS(C$4:C34,A$4:A34,A34)=0),"",SUMPRODUCT((A$4:A34=A34)*(C$4:C34)*(D$4:D34))/SUMIFS(C$4:C34,A$4:A34,A34))</f>
-        <v>79.2</v>
-      </c>
-      <c r="F34" s="6">
-        <v>12</v>
-      </c>
-      <c r="G34" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6" t="str">
+        <f>IF(C34="","",C34-IF(ISNUMBER(F34),F34,0))</f>
+        <v/>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B35" s="5">
-        <v>46174</v>
-      </c>
-      <c r="C35" s="6">
-        <v>592</v>
-      </c>
+        <v>45962</v>
+      </c>
+      <c r="C35" s="6"/>
       <c r="D35" s="7">
-        <v>91.65</v>
-      </c>
-      <c r="E35" s="7">
+        <v>177.6</v>
+      </c>
+      <c r="E35" s="7" t="str">
         <f>IF(OR(A35="",SUMIFS(C$4:C35,A$4:A35,A35)=0),"",SUMPRODUCT((A$4:A35=A35)*(C$4:C35)*(D$4:D35))/SUMIFS(C$4:C35,A$4:A35,A35))</f>
-        <v>88.101449275362313</v>
-      </c>
-      <c r="F35" s="6">
-        <v>592</v>
-      </c>
-      <c r="G35" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6" t="str">
+        <f>IF(C35="","",C35-IF(ISNUMBER(F35),F35,0))</f>
+        <v/>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B36" s="5">
-        <v>46204</v>
+        <v>45992</v>
       </c>
       <c r="C36" s="6">
-        <v>887</v>
+        <v>27</v>
       </c>
       <c r="D36" s="7">
-        <v>93.67</v>
+        <v>177.6</v>
       </c>
       <c r="E36" s="7">
         <f>IF(OR(A36="",SUMIFS(C$4:C36,A$4:A36,A36)=0),"",SUMPRODUCT((A$4:A36=A36)*(C$4:C36)*(D$4:D36))/SUMIFS(C$4:C36,A$4:A36,A36))</f>
-        <v>90.981510204081644</v>
-      </c>
-      <c r="F36" s="6">
-        <v>190</v>
-      </c>
+        <v>177.6</v>
+      </c>
+      <c r="F36" s="6"/>
       <c r="G36" s="6">
-        <f t="shared" ref="G36:G67" si="1">IF(C36="","",C36-IF(ISNUMBER(F36),F36,0))</f>
-        <v>697</v>
+        <f>IF(C36="","",C36-IF(ISNUMBER(F36),F36,0))</f>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B37" s="5">
-        <v>46235</v>
+        <v>46023</v>
       </c>
       <c r="C37" s="6">
-        <v>697</v>
+        <v>27</v>
       </c>
       <c r="D37" s="7">
-        <v>93.67</v>
+        <v>177.6</v>
       </c>
       <c r="E37" s="7">
         <f>IF(OR(A37="",SUMIFS(C$4:C37,A$4:A37,A37)=0),"",SUMPRODUCT((A$4:A37=A37)*(C$4:C37)*(D$4:D37))/SUMIFS(C$4:C37,A$4:A37,A37))</f>
-        <v>91.758407960199008</v>
+        <v>177.6</v>
       </c>
       <c r="F37" s="6">
-        <v>366</v>
+        <v>27</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" si="1"/>
-        <v>331</v>
+        <f>IF(C37="","",C37-IF(ISNUMBER(F37),F37,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B38" s="5">
-        <v>46266</v>
+        <v>46023</v>
       </c>
       <c r="C38" s="6">
-        <v>331</v>
+        <v>200</v>
       </c>
       <c r="D38" s="7">
-        <v>93.67</v>
+        <v>182.6</v>
       </c>
       <c r="E38" s="7">
         <f>IF(OR(A38="",SUMIFS(C$4:C38,A$4:A38,A38)=0),"",SUMPRODUCT((A$4:A38=A38)*(C$4:C38)*(D$4:D38))/SUMIFS(C$4:C38,A$4:A38,A38))</f>
-        <v>91.989081297849069</v>
+        <v>181.53700787401576</v>
       </c>
       <c r="F38" s="6">
-        <v>570</v>
+        <v>61</v>
       </c>
       <c r="G38" s="6">
-        <f t="shared" si="1"/>
-        <v>-239</v>
+        <f>IF(C38="","",C38-IF(ISNUMBER(F38),F38,0))</f>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B39" s="5">
-        <v>46296</v>
+        <v>46054</v>
       </c>
       <c r="C39" s="6">
-        <v>-239</v>
+        <v>139</v>
       </c>
       <c r="D39" s="7">
-        <v>93.67</v>
+        <v>177.6</v>
       </c>
       <c r="E39" s="7">
         <f>IF(OR(A39="",SUMIFS(C$4:C39,A$4:A39,A39)=0),"",SUMPRODUCT((A$4:A39=A39)*(C$4:C39)*(D$4:D39))/SUMIFS(C$4:C39,A$4:A39,A39))</f>
-        <v>91.828642172523956</v>
+        <v>180.14452926208651</v>
       </c>
       <c r="F39" s="6">
-        <v>580</v>
+        <v>20</v>
       </c>
       <c r="G39" s="6">
-        <f t="shared" si="1"/>
-        <v>-819</v>
+        <f>IF(C39="","",C39-IF(ISNUMBER(F39),F39,0))</f>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B40" s="5">
         <v>46054</v>
@@ -1664,2045 +1606,2117 @@
       <c r="D40" s="7"/>
       <c r="E40" s="7">
         <f>IF(OR(A40="",SUMIFS(C$4:C40,A$4:A40,A40)=0),"",SUMPRODUCT((A$4:A40=A40)*(C$4:C40)*(D$4:D40))/SUMIFS(C$4:C40,A$4:A40,A40))</f>
-        <v>91.828642172523956</v>
+        <v>180.14452926208651</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(C40="","",C40-IF(ISNUMBER(F40),F40,0))</f>
         <v/>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B41" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C41" s="6">
-        <v>1000</v>
+        <v>119</v>
       </c>
       <c r="D41" s="7">
-        <v>91.8</v>
+        <v>177.6</v>
       </c>
       <c r="E41" s="7">
         <f>IF(OR(A41="",SUMIFS(C$4:C41,A$4:A41,A41)=0),"",SUMPRODUCT((A$4:A41=A41)*(C$4:C41)*(D$4:D41))/SUMIFS(C$4:C41,A$4:A41,A41))</f>
-        <v>91.820468036529675</v>
-      </c>
-      <c r="F41" s="6">
-        <v>408</v>
-      </c>
+        <v>179.55312499999999</v>
+      </c>
+      <c r="F41" s="6"/>
       <c r="G41" s="6">
-        <f t="shared" si="1"/>
-        <v>592</v>
+        <f>IF(C41="","",C41-IF(ISNUMBER(F41),F41,0))</f>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B42" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C42" s="6">
-        <v>1000</v>
+        <v>119</v>
       </c>
       <c r="D42" s="7">
-        <v>94.9</v>
+        <v>177.6</v>
       </c>
       <c r="E42" s="7">
         <f>IF(OR(A42="",SUMIFS(C$4:C42,A$4:A42,A42)=0),"",SUMPRODUCT((A$4:A42=A42)*(C$4:C42)*(D$4:D42))/SUMIFS(C$4:C42,A$4:A42,A42))</f>
-        <v>92.504200710479566</v>
+        <v>179.1847860538827</v>
       </c>
       <c r="F42" s="6">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="G42" s="6">
-        <f t="shared" si="1"/>
-        <v>867</v>
+        <f>IF(C42="","",C42-IF(ISNUMBER(F42),F42,0))</f>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B43" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C43" s="6">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D43" s="7">
-        <v>91.8</v>
+        <v>177.6</v>
       </c>
       <c r="E43" s="7">
         <f>IF(OR(A43="",SUMIFS(C$4:C43,A$4:A43,A43)=0),"",SUMPRODUCT((A$4:A43=A43)*(C$4:C43)*(D$4:D43))/SUMIFS(C$4:C43,A$4:A43,A43))</f>
-        <v>92.501087533156493</v>
+        <v>179.02653352353778</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>IF(C43="","",C43-IF(ISNUMBER(F43),F43,0))</f>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B44" s="5">
-        <v>45931</v>
+        <v>46174</v>
       </c>
       <c r="C44" s="6">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="D44" s="7">
-        <v>77.2</v>
+        <v>177.6</v>
       </c>
       <c r="E44" s="7">
         <f>IF(OR(A44="",SUMIFS(C$4:C44,A$4:A44,A44)=0),"",SUMPRODUCT((A$4:A44=A44)*(C$4:C44)*(D$4:D44))/SUMIFS(C$4:C44,A$4:A44,A44))</f>
-        <v>77.2</v>
+        <v>178.89701686121916</v>
       </c>
       <c r="F44" s="6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G44" s="6">
-        <f t="shared" si="1"/>
-        <v>194</v>
+        <f>IF(C44="","",C44-IF(ISNUMBER(F44),F44,0))</f>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B45" s="5">
-        <v>45962</v>
+        <v>46204</v>
       </c>
       <c r="C45" s="6">
-        <v>194</v>
+        <v>55</v>
       </c>
       <c r="D45" s="7">
-        <v>77.2</v>
+        <v>177.6</v>
       </c>
       <c r="E45" s="7">
         <f>IF(OR(A45="",SUMIFS(C$4:C45,A$4:A45,A45)=0),"",SUMPRODUCT((A$4:A45=A45)*(C$4:C45)*(D$4:D45))/SUMIFS(C$4:C45,A$4:A45,A45))</f>
-        <v>77.2</v>
+        <v>178.8106537530266</v>
       </c>
       <c r="F45" s="6">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="G45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(C45="","",C45-IF(ISNUMBER(F45),F45,0))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B46" s="5">
-        <v>45992</v>
+        <v>46204</v>
       </c>
       <c r="C46" s="6">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="D46" s="7">
-        <v>82.67</v>
+        <v>206.9</v>
       </c>
       <c r="E46" s="7">
         <f>IF(OR(A46="",SUMIFS(C$4:C46,A$4:A46,A46)=0),"",SUMPRODUCT((A$4:A46=A46)*(C$4:C46)*(D$4:D46))/SUMIFS(C$4:C46,A$4:A46,A46))</f>
-        <v>77.322158808933011</v>
-      </c>
-      <c r="F46" s="6">
-        <v>9</v>
-      </c>
+        <v>184.28615984405457</v>
+      </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(C46="","",C46-IF(ISNUMBER(F46),F46,0))</f>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B47" s="5">
-        <v>46023</v>
+        <v>46235</v>
       </c>
       <c r="C47" s="6">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="D47" s="7">
-        <v>94.81</v>
+        <v>200.58</v>
       </c>
       <c r="E47" s="7">
         <f>IF(OR(A47="",SUMIFS(C$4:C47,A$4:A47,A47)=0),"",SUMPRODUCT((A$4:A47=A47)*(C$4:C47)*(D$4:D47))/SUMIFS(C$4:C47,A$4:A47,A47))</f>
-        <v>79.97294736842106</v>
+        <v>187.04357894736842</v>
       </c>
       <c r="F47" s="6">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(C47="","",C47-IF(ISNUMBER(F47),F47,0))</f>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B48" s="5">
-        <v>46054</v>
+        <v>46266</v>
       </c>
       <c r="C48" s="6">
-        <v>478</v>
+        <v>133</v>
       </c>
       <c r="D48" s="7">
-        <v>94.28</v>
+        <v>200.58</v>
       </c>
       <c r="E48" s="7">
         <f>IF(OR(A48="",SUMIFS(C$4:C48,A$4:A48,A48)=0),"",SUMPRODUCT((A$4:A48=A48)*(C$4:C48)*(D$4:D48))/SUMIFS(C$4:C48,A$4:A48,A48))</f>
-        <v>87.148992654774403</v>
+        <v>188.35961988304092</v>
       </c>
       <c r="F48" s="6">
-        <v>319</v>
+        <v>60</v>
       </c>
       <c r="G48" s="6">
-        <f t="shared" si="1"/>
-        <v>159</v>
+        <f>IF(C48="","",C48-IF(ISNUMBER(F48),F48,0))</f>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B49" s="5">
-        <v>46082</v>
+        <v>46296</v>
       </c>
       <c r="C49" s="6">
-        <v>475</v>
+        <v>73</v>
       </c>
       <c r="D49" s="7">
-        <v>94.25</v>
+        <v>200.58</v>
       </c>
       <c r="E49" s="7">
         <f>IF(OR(A49="",SUMIFS(C$4:C49,A$4:A49,A49)=0),"",SUMPRODUCT((A$4:A49=A49)*(C$4:C49)*(D$4:D49))/SUMIFS(C$4:C49,A$4:A49,A49))</f>
-        <v>89.511022408963584</v>
+        <v>188.97869535045106</v>
       </c>
       <c r="F49" s="6">
-        <v>453</v>
+        <v>50</v>
       </c>
       <c r="G49" s="6">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <f>IF(C49="","",C49-IF(ISNUMBER(F49),F49,0))</f>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B50" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C50" s="6">
-        <v>22</v>
-      </c>
+        <v>45931</v>
+      </c>
+      <c r="C50" s="6"/>
       <c r="D50" s="7">
-        <v>94.25</v>
-      </c>
-      <c r="E50" s="7">
+        <v>78</v>
+      </c>
+      <c r="E50" s="7" t="str">
         <f>IF(OR(A50="",SUMIFS(C$4:C50,A$4:A50,A50)=0),"",SUMPRODUCT((A$4:A50=A50)*(C$4:C50)*(D$4:D50))/SUMIFS(C$4:C50,A$4:A50,A50))</f>
-        <v>89.582924137931045</v>
-      </c>
-      <c r="F50" s="6">
-        <v>22</v>
-      </c>
-      <c r="G50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6" t="str">
+        <f>IF(C50="","",C50-IF(ISNUMBER(F50),F50,0))</f>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B51" s="5">
-        <v>46143</v>
-      </c>
-      <c r="C51" s="6">
-        <v>5</v>
-      </c>
+        <v>45962</v>
+      </c>
+      <c r="C51" s="6"/>
       <c r="D51" s="7">
-        <v>110.11</v>
-      </c>
-      <c r="E51" s="7">
+        <v>78</v>
+      </c>
+      <c r="E51" s="7" t="str">
         <f>IF(OR(A51="",SUMIFS(C$4:C51,A$4:A51,A51)=0),"",SUMPRODUCT((A$4:A51=A51)*(C$4:C51)*(D$4:D51))/SUMIFS(C$4:C51,A$4:A51,A51))</f>
-        <v>89.653463917525784</v>
-      </c>
-      <c r="F51" s="6">
-        <v>5</v>
-      </c>
-      <c r="G51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6" t="str">
+        <f>IF(C51="","",C51-IF(ISNUMBER(F51),F51,0))</f>
+        <v/>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B52" s="5">
-        <v>46174</v>
+        <v>45992</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="7">
-        <v>110.11</v>
-      </c>
-      <c r="E52" s="7">
+        <v>78</v>
+      </c>
+      <c r="E52" s="7" t="str">
         <f>IF(OR(A52="",SUMIFS(C$4:C52,A$4:A52,A52)=0),"",SUMPRODUCT((A$4:A52=A52)*(C$4:C52)*(D$4:D52))/SUMIFS(C$4:C52,A$4:A52,A52))</f>
-        <v>89.653463917525784</v>
+        <v/>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(C52="","",C52-IF(ISNUMBER(F52),F52,0))</f>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B53" s="5">
-        <v>46204</v>
-      </c>
-      <c r="C53" s="6">
-        <v>500</v>
-      </c>
+        <v>46023</v>
+      </c>
+      <c r="C53" s="6"/>
       <c r="D53" s="7">
-        <v>93.8</v>
-      </c>
-      <c r="E53" s="7">
+        <v>78</v>
+      </c>
+      <c r="E53" s="7" t="str">
         <f>IF(OR(A53="",SUMIFS(C$4:C53,A$4:A53,A53)=0),"",SUMPRODUCT((A$4:A53=A53)*(C$4:C53)*(D$4:D53))/SUMIFS(C$4:C53,A$4:A53,A53))</f>
-        <v>90.713959079283896</v>
-      </c>
-      <c r="F53" s="6">
-        <v>35</v>
-      </c>
-      <c r="G53" s="6">
-        <f t="shared" si="1"/>
-        <v>465</v>
+        <v/>
+      </c>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6" t="str">
+        <f>IF(C53="","",C53-IF(ISNUMBER(F53),F53,0))</f>
+        <v/>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B54" s="5">
-        <v>46235</v>
-      </c>
-      <c r="C54" s="6">
-        <v>465</v>
-      </c>
+        <v>46054</v>
+      </c>
+      <c r="C54" s="6"/>
       <c r="D54" s="7">
-        <v>93.8</v>
-      </c>
-      <c r="E54" s="7">
+        <v>78</v>
+      </c>
+      <c r="E54" s="7" t="str">
         <f>IF(OR(A54="",SUMIFS(C$4:C54,A$4:A54,A54)=0),"",SUMPRODUCT((A$4:A54=A54)*(C$4:C54)*(D$4:D54))/SUMIFS(C$4:C54,A$4:A54,A54))</f>
-        <v>91.306938016528932</v>
-      </c>
-      <c r="F54" s="6">
-        <v>312</v>
-      </c>
-      <c r="G54" s="6">
-        <f t="shared" si="1"/>
-        <v>153</v>
+        <v/>
+      </c>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6" t="str">
+        <f>IF(C54="","",C54-IF(ISNUMBER(F54),F54,0))</f>
+        <v/>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B55" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C55" s="6">
-        <v>653</v>
-      </c>
-      <c r="D55" s="7">
-        <v>106.24</v>
-      </c>
-      <c r="E55" s="7">
+        <v>46054</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7" t="str">
         <f>IF(OR(A55="",SUMIFS(C$4:C55,A$4:A55,A55)=0),"",SUMPRODUCT((A$4:A55=A55)*(C$4:C55)*(D$4:D55))/SUMIFS(C$4:C55,A$4:A55,A55))</f>
-        <v>94.480152945004889</v>
-      </c>
-      <c r="F55" s="6">
-        <v>20</v>
-      </c>
-      <c r="G55" s="6">
-        <f t="shared" si="1"/>
-        <v>633</v>
+        <v/>
+      </c>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6" t="str">
+        <f>IF(C55="","",C55-IF(ISNUMBER(F55),F55,0))</f>
+        <v/>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B56" s="5">
-        <v>46296</v>
+        <v>46082</v>
       </c>
       <c r="C56" s="6">
-        <v>933</v>
+        <v>70</v>
       </c>
       <c r="D56" s="7">
-        <v>109.75</v>
+        <v>89.9</v>
       </c>
       <c r="E56" s="7">
         <f>IF(OR(A56="",SUMIFS(C$4:C56,A$4:A56,A56)=0),"",SUMPRODUCT((A$4:A56=A56)*(C$4:C56)*(D$4:D56))/SUMIFS(C$4:C56,A$4:A56,A56))</f>
-        <v>98.036510234648034</v>
-      </c>
-      <c r="F56" s="6">
-        <v>105</v>
-      </c>
+        <v>89.9</v>
+      </c>
+      <c r="F56" s="6"/>
       <c r="G56" s="6">
-        <f t="shared" si="1"/>
-        <v>828</v>
+        <f>IF(C56="","",C56-IF(ISNUMBER(F56),F56,0))</f>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B57" s="5">
-        <v>45962</v>
+        <v>46113</v>
       </c>
       <c r="C57" s="6">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="D57" s="7">
-        <v>86.2</v>
+        <v>89.9</v>
       </c>
       <c r="E57" s="7">
         <f>IF(OR(A57="",SUMIFS(C$4:C57,A$4:A57,A57)=0),"",SUMPRODUCT((A$4:A57=A57)*(C$4:C57)*(D$4:D57))/SUMIFS(C$4:C57,A$4:A57,A57))</f>
-        <v>97.21185787273572</v>
+        <v>89.9</v>
       </c>
       <c r="F57" s="6">
-        <v>291</v>
+        <v>70</v>
       </c>
       <c r="G57" s="6">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>IF(C57="","",C57-IF(ISNUMBER(F57),F57,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B58" s="5">
-        <v>45992</v>
+        <v>46113</v>
       </c>
       <c r="C58" s="6">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="D58" s="7">
-        <v>95.2</v>
+        <v>98.5</v>
       </c>
       <c r="E58" s="7">
         <f>IF(OR(A58="",SUMIFS(C$4:C58,A$4:A58,A58)=0),"",SUMPRODUCT((A$4:A58=A58)*(C$4:C58)*(D$4:D58))/SUMIFS(C$4:C58,A$4:A58,A58))</f>
-        <v>97.08984729493892</v>
+        <v>95.245945945945948</v>
       </c>
       <c r="F58" s="6">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="G58" s="6">
-        <f t="shared" si="1"/>
-        <v>72</v>
+        <f>IF(C58="","",C58-IF(ISNUMBER(F58),F58,0))</f>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B59" s="5">
-        <v>46023</v>
+        <v>46143</v>
       </c>
       <c r="C59" s="6">
-        <v>506</v>
+        <v>150</v>
       </c>
       <c r="D59" s="7">
-        <v>94.2</v>
+        <v>96.49</v>
       </c>
       <c r="E59" s="7">
         <f>IF(OR(A59="",SUMIFS(C$4:C59,A$4:A59,A59)=0),"",SUMPRODUCT((A$4:A59=A59)*(C$4:C59)*(D$4:D59))/SUMIFS(C$4:C59,A$4:A59,A59))</f>
-        <v>96.802565815324158</v>
-      </c>
-      <c r="F59" s="6">
-        <v>28</v>
-      </c>
+        <v>95.604807692307688</v>
+      </c>
+      <c r="F59" s="6"/>
       <c r="G59" s="6">
-        <f t="shared" si="1"/>
-        <v>478</v>
+        <f>IF(C59="","",C59-IF(ISNUMBER(F59),F59,0))</f>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B60" s="5">
-        <v>46054</v>
+        <v>46174</v>
       </c>
       <c r="C60" s="6">
-        <v>316</v>
+        <v>150</v>
       </c>
       <c r="D60" s="7">
-        <v>94.2</v>
+        <v>96.49</v>
       </c>
       <c r="E60" s="7">
         <f>IF(OR(A60="",SUMIFS(C$4:C60,A$4:A60,A60)=0),"",SUMPRODUCT((A$4:A60=A60)*(C$4:C60)*(D$4:D60))/SUMIFS(C$4:C60,A$4:A60,A60))</f>
-        <v>96.650436551979283</v>
-      </c>
-      <c r="F60" s="6"/>
+        <v>95.802985074626861</v>
+      </c>
+      <c r="F60" s="6">
+        <v>61</v>
+      </c>
       <c r="G60" s="6">
-        <f t="shared" si="1"/>
-        <v>316</v>
+        <f>IF(C60="","",C60-IF(ISNUMBER(F60),F60,0))</f>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B61" s="5">
-        <v>46113</v>
+        <v>46204</v>
       </c>
       <c r="C61" s="6">
-        <v>219</v>
+        <v>89</v>
       </c>
       <c r="D61" s="7">
-        <v>111.7</v>
+        <v>96.49</v>
       </c>
       <c r="E61" s="7">
         <f>IF(OR(A61="",SUMIFS(C$4:C61,A$4:A61,A61)=0),"",SUMPRODUCT((A$4:A61=A61)*(C$4:C61)*(D$4:D61))/SUMIFS(C$4:C61,A$4:A61,A61))</f>
-        <v>97.23636622222223</v>
+        <v>95.883544137022398</v>
       </c>
       <c r="F61" s="6">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="G61" s="6">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f>IF(C61="","",C61-IF(ISNUMBER(F61),F61,0))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B62" s="5">
-        <v>46174</v>
+        <v>46235</v>
       </c>
       <c r="C62" s="6">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="D62" s="7">
-        <v>93.8</v>
+        <v>96.49</v>
       </c>
       <c r="E62" s="7">
         <f>IF(OR(A62="",SUMIFS(C$4:C62,A$4:A62,A62)=0),"",SUMPRODUCT((A$4:A62=A62)*(C$4:C62)*(D$4:D62))/SUMIFS(C$4:C62,A$4:A62,A62))</f>
-        <v>96.955846530612249</v>
-      </c>
-      <c r="F62" s="6"/>
+        <v>95.886723460026218</v>
+      </c>
+      <c r="F62" s="6">
+        <v>30</v>
+      </c>
       <c r="G62" s="6">
-        <f t="shared" si="1"/>
-        <v>500</v>
+        <f>IF(C62="","",C62-IF(ISNUMBER(F62),F62,0))</f>
+        <v>-26</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B63" s="5">
         <v>46235</v>
       </c>
       <c r="C63" s="6">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D63" s="7">
-        <v>117.8</v>
+        <v>106.8</v>
       </c>
       <c r="E63" s="7">
         <f>IF(OR(A63="",SUMIFS(C$4:C63,A$4:A63,A63)=0),"",SUMPRODUCT((A$4:A63=A63)*(C$4:C63)*(D$4:D63))/SUMIFS(C$4:C63,A$4:A63,A63))</f>
-        <v>98.528990188679259</v>
+        <v>98.966669802445921</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6">
-        <f t="shared" si="1"/>
-        <v>500</v>
+        <f>IF(C63="","",C63-IF(ISNUMBER(F63),F63,0))</f>
+        <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B64" s="5">
         <v>46266</v>
       </c>
       <c r="C64" s="6">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="D64" s="7">
-        <v>117.4</v>
+        <v>106.66</v>
       </c>
       <c r="E64" s="7">
         <f>IF(OR(A64="",SUMIFS(C$4:C64,A$4:A64,A64)=0),"",SUMPRODUCT((A$4:A64=A64)*(C$4:C64)*(D$4:D64))/SUMIFS(C$4:C64,A$4:A64,A64))</f>
-        <v>99.346506859205789</v>
-      </c>
-      <c r="F64" s="6"/>
+        <v>100.5433133881825</v>
+      </c>
+      <c r="F64" s="6">
+        <v>30</v>
+      </c>
       <c r="G64" s="6">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <f>IF(C64="","",C64-IF(ISNUMBER(F64),F64,0))</f>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B65" s="5">
-        <v>45931</v>
-      </c>
-      <c r="C65" s="6"/>
+        <v>46266</v>
+      </c>
+      <c r="C65" s="6">
+        <v>200</v>
+      </c>
       <c r="D65" s="7">
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E65" s="7" t="str">
+        <v>104.8</v>
+      </c>
+      <c r="E65" s="7">
         <f>IF(OR(A65="",SUMIFS(C$4:C65,A$4:A65,A65)=0),"",SUMPRODUCT((A$4:A65=A65)*(C$4:C65)*(D$4:D65))/SUMIFS(C$4:C65,A$4:A65,A65))</f>
-        <v/>
+        <v>101.09720884840598</v>
       </c>
       <c r="F65" s="6"/>
-      <c r="G65" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="G65" s="6">
+        <f>IF(C65="","",C65-IF(ISNUMBER(F65),F65,0))</f>
+        <v>200</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B66" s="5">
-        <v>45962</v>
-      </c>
-      <c r="C66" s="6"/>
+        <v>46296</v>
+      </c>
+      <c r="C66" s="6">
+        <v>444</v>
+      </c>
       <c r="D66" s="7">
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E66" s="7" t="str">
+        <v>105.88</v>
+      </c>
+      <c r="E66" s="7">
         <f>IF(OR(A66="",SUMIFS(C$4:C66,A$4:A66,A66)=0),"",SUMPRODUCT((A$4:A66=A66)*(C$4:C66)*(D$4:D66))/SUMIFS(C$4:C66,A$4:A66,A66))</f>
-        <v/>
-      </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>102.16917213528521</v>
+      </c>
+      <c r="F66" s="6">
+        <v>25</v>
+      </c>
+      <c r="G66" s="6">
+        <f>IF(C66="","",C66-IF(ISNUMBER(F66),F66,0))</f>
+        <v>419</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B67" s="5">
-        <v>45992</v>
-      </c>
-      <c r="C67" s="6"/>
+        <v>45931</v>
+      </c>
+      <c r="C67" s="6">
+        <v>800</v>
+      </c>
       <c r="D67" s="7">
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E67" s="7" t="str">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="E67" s="7">
         <f>IF(OR(A67="",SUMIFS(C$4:C67,A$4:A67,A67)=0),"",SUMPRODUCT((A$4:A67=A67)*(C$4:C67)*(D$4:D67))/SUMIFS(C$4:C67,A$4:A67,A67))</f>
-        <v/>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>75.900000000000006</v>
+      </c>
+      <c r="F67" s="6">
+        <v>650</v>
+      </c>
+      <c r="G67" s="6">
+        <f>IF(C67="","",C67-IF(ISNUMBER(F67),F67,0))</f>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B68" s="5">
-        <v>46023</v>
-      </c>
-      <c r="C68" s="6"/>
+        <v>45962</v>
+      </c>
+      <c r="C68" s="6">
+        <v>150</v>
+      </c>
       <c r="D68" s="7">
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E68" s="7" t="str">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="E68" s="7">
         <f>IF(OR(A68="",SUMIFS(C$4:C68,A$4:A68,A68)=0),"",SUMPRODUCT((A$4:A68=A68)*(C$4:C68)*(D$4:D68))/SUMIFS(C$4:C68,A$4:A68,A68))</f>
-        <v/>
-      </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6" t="str">
-        <f t="shared" ref="G68:G99" si="2">IF(C68="","",C68-IF(ISNUMBER(F68),F68,0))</f>
-        <v/>
+        <v>75.900000000000006</v>
+      </c>
+      <c r="F68" s="6">
+        <v>150</v>
+      </c>
+      <c r="G68" s="6">
+        <f>IF(C68="","",C68-IF(ISNUMBER(F68),F68,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B69" s="5">
-        <v>46054</v>
-      </c>
-      <c r="C69" s="6"/>
+        <v>45962</v>
+      </c>
+      <c r="C69" s="6">
+        <v>700</v>
+      </c>
       <c r="D69" s="7">
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E69" s="7" t="str">
+        <v>84.9</v>
+      </c>
+      <c r="E69" s="7">
         <f>IF(OR(A69="",SUMIFS(C$4:C69,A$4:A69,A69)=0),"",SUMPRODUCT((A$4:A69=A69)*(C$4:C69)*(D$4:D69))/SUMIFS(C$4:C69,A$4:A69,A69))</f>
-        <v/>
-      </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>79.718181818181819</v>
+      </c>
+      <c r="F69" s="6">
+        <v>520</v>
+      </c>
+      <c r="G69" s="6">
+        <f>IF(C69="","",C69-IF(ISNUMBER(F69),F69,0))</f>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B70" s="5">
-        <v>46082</v>
-      </c>
-      <c r="C70" s="6"/>
+        <v>45992</v>
+      </c>
+      <c r="C70" s="6">
+        <v>180</v>
+      </c>
       <c r="D70" s="7">
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E70" s="7" t="str">
+        <v>83.31</v>
+      </c>
+      <c r="E70" s="7">
         <f>IF(OR(A70="",SUMIFS(C$4:C70,A$4:A70,A70)=0),"",SUMPRODUCT((A$4:A70=A70)*(C$4:C70)*(D$4:D70))/SUMIFS(C$4:C70,A$4:A70,A70))</f>
-        <v/>
-      </c>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>80.071475409836054</v>
+      </c>
+      <c r="F70" s="6">
+        <v>180</v>
+      </c>
+      <c r="G70" s="6">
+        <f>IF(C70="","",C70-IF(ISNUMBER(F70),F70,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B71" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C71" s="6"/>
+        <v>45992</v>
+      </c>
+      <c r="C71" s="6">
+        <v>150</v>
+      </c>
       <c r="D71" s="7">
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E71" s="7" t="str">
+        <v>93.9</v>
+      </c>
+      <c r="E71" s="7">
         <f>IF(OR(A71="",SUMIFS(C$4:C71,A$4:A71,A71)=0),"",SUMPRODUCT((A$4:A71=A71)*(C$4:C71)*(D$4:D71))/SUMIFS(C$4:C71,A$4:A71,A71))</f>
-        <v/>
-      </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>81.1190909090909</v>
+      </c>
+      <c r="F71" s="6">
+        <v>150</v>
+      </c>
+      <c r="G71" s="6">
+        <f>IF(C71="","",C71-IF(ISNUMBER(F71),F71,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B72" s="5">
-        <v>46143</v>
-      </c>
-      <c r="C72" s="6"/>
+        <v>45992</v>
+      </c>
+      <c r="C72" s="6">
+        <v>500</v>
+      </c>
       <c r="D72" s="7">
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E72" s="7" t="str">
+        <v>94.9</v>
+      </c>
+      <c r="E72" s="7">
         <f>IF(OR(A72="",SUMIFS(C$4:C72,A$4:A72,A72)=0),"",SUMPRODUCT((A$4:A72=A72)*(C$4:C72)*(D$4:D72))/SUMIFS(C$4:C72,A$4:A72,A72))</f>
-        <v/>
-      </c>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>83.897499999999994</v>
+      </c>
+      <c r="F72" s="6">
+        <v>491</v>
+      </c>
+      <c r="G72" s="6">
+        <f>IF(C72="","",C72-IF(ISNUMBER(F72),F72,0))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B73" s="5">
-        <v>46174</v>
+        <v>46023</v>
       </c>
       <c r="C73" s="6">
-        <v>445</v>
+        <v>9</v>
       </c>
       <c r="D73" s="7">
-        <v>93.1</v>
+        <v>92.21</v>
       </c>
       <c r="E73" s="7">
         <f>IF(OR(A73="",SUMIFS(C$4:C73,A$4:A73,A73)=0),"",SUMPRODUCT((A$4:A73=A73)*(C$4:C73)*(D$4:D73))/SUMIFS(C$4:C73,A$4:A73,A73))</f>
-        <v>93.1</v>
+        <v>83.927557251908397</v>
       </c>
       <c r="F73" s="6">
-        <v>445</v>
+        <v>9</v>
       </c>
       <c r="G73" s="6">
-        <f t="shared" si="2"/>
+        <f>IF(C73="","",C73-IF(ISNUMBER(F73),F73,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B74" s="5">
-        <v>46204</v>
+        <v>46023</v>
       </c>
       <c r="C74" s="6">
-        <v>439</v>
+        <v>1350</v>
       </c>
       <c r="D74" s="7">
-        <v>94.79</v>
+        <v>92.9</v>
       </c>
       <c r="E74" s="7">
         <f>IF(OR(A74="",SUMIFS(C$4:C74,A$4:A74,A74)=0),"",SUMPRODUCT((A$4:A74=A74)*(C$4:C74)*(D$4:D74))/SUMIFS(C$4:C74,A$4:A74,A74))</f>
-        <v>93.939264705882351</v>
+        <v>87.082753321177393</v>
       </c>
       <c r="F74" s="6">
-        <v>434</v>
+        <v>910</v>
       </c>
       <c r="G74" s="6">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>IF(C74="","",C74-IF(ISNUMBER(F74),F74,0))</f>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B75" s="5">
-        <v>46235</v>
+        <v>46054</v>
       </c>
       <c r="C75" s="6">
-        <v>5</v>
+        <v>440</v>
       </c>
       <c r="D75" s="7">
-        <v>94.79</v>
+        <v>92.9</v>
       </c>
       <c r="E75" s="7">
         <f>IF(OR(A75="",SUMIFS(C$4:C75,A$4:A75,A75)=0),"",SUMPRODUCT((A$4:A75=A75)*(C$4:C75)*(D$4:D75))/SUMIFS(C$4:C75,A$4:A75,A75))</f>
-        <v>93.944049493813267</v>
-      </c>
-      <c r="F75" s="6"/>
+        <v>87.680927786866093</v>
+      </c>
+      <c r="F75" s="6">
+        <v>440</v>
+      </c>
       <c r="G75" s="6">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>IF(C75="","",C75-IF(ISNUMBER(F75),F75,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B76" s="5">
-        <v>46266</v>
+        <v>46054</v>
       </c>
       <c r="C76" s="6">
-        <v>5</v>
+        <v>1200</v>
       </c>
       <c r="D76" s="7">
-        <v>94.79</v>
+        <v>92.9</v>
       </c>
       <c r="E76" s="7">
         <f>IF(OR(A76="",SUMIFS(C$4:C76,A$4:A76,A76)=0),"",SUMPRODUCT((A$4:A76=A76)*(C$4:C76)*(D$4:D76))/SUMIFS(C$4:C76,A$4:A76,A76))</f>
-        <v>93.948780760626391</v>
+        <v>88.823998904909658</v>
       </c>
       <c r="F76" s="6">
-        <v>310</v>
+        <v>478</v>
       </c>
       <c r="G76" s="6">
-        <f t="shared" si="2"/>
-        <v>-305</v>
+        <f>IF(C76="","",C76-IF(ISNUMBER(F76),F76,0))</f>
+        <v>722</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B77" s="5">
-        <v>46296</v>
+        <v>46082</v>
       </c>
       <c r="C77" s="6">
-        <v>-305</v>
+        <v>722</v>
       </c>
       <c r="D77" s="7">
-        <v>94.79</v>
+        <v>92.9</v>
       </c>
       <c r="E77" s="7">
         <f>IF(OR(A77="",SUMIFS(C$4:C77,A$4:A77,A77)=0),"",SUMPRODUCT((A$4:A77=A77)*(C$4:C77)*(D$4:D77))/SUMIFS(C$4:C77,A$4:A77,A77))</f>
-        <v>93.51317487266553</v>
+        <v>89.298579261409444</v>
       </c>
       <c r="F77" s="6">
-        <v>150</v>
+        <v>722</v>
       </c>
       <c r="G77" s="6">
-        <f t="shared" si="2"/>
-        <v>-455</v>
+        <f>IF(C77="","",C77-IF(ISNUMBER(F77),F77,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B78" s="5">
-        <v>46054</v>
-      </c>
-      <c r="C78" s="6"/>
-      <c r="D78" s="7"/>
+        <v>46082</v>
+      </c>
+      <c r="C78" s="6">
+        <v>1000</v>
+      </c>
+      <c r="D78" s="7">
+        <v>108.9</v>
+      </c>
       <c r="E78" s="7">
         <f>IF(OR(A78="",SUMIFS(C$4:C78,A$4:A78,A78)=0),"",SUMPRODUCT((A$4:A78=A78)*(C$4:C78)*(D$4:D78))/SUMIFS(C$4:C78,A$4:A78,A78))</f>
-        <v>93.51317487266553</v>
-      </c>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>92.020620747118457</v>
+      </c>
+      <c r="F78" s="6">
+        <v>330</v>
+      </c>
+      <c r="G78" s="6">
+        <f>IF(C78="","",C78-IF(ISNUMBER(F78),F78,0))</f>
+        <v>670</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B79" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C79" s="6">
-        <v>1000</v>
+        <v>670</v>
       </c>
       <c r="D79" s="7">
-        <v>93.1</v>
+        <v>102.19</v>
       </c>
       <c r="E79" s="7">
         <f>IF(OR(A79="",SUMIFS(C$4:C79,A$4:A79,A79)=0),"",SUMPRODUCT((A$4:A79=A79)*(C$4:C79)*(D$4:D79))/SUMIFS(C$4:C79,A$4:A79,A79))</f>
-        <v>93.253152926368784</v>
+        <v>92.886264769406694</v>
       </c>
       <c r="F79" s="6">
-        <v>55</v>
+        <v>502</v>
       </c>
       <c r="G79" s="6">
-        <f t="shared" si="2"/>
-        <v>945</v>
+        <f>IF(C79="","",C79-IF(ISNUMBER(F79),F79,0))</f>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B80" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C80" s="6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D80" s="7">
-        <v>96.3</v>
+        <v>108.9</v>
       </c>
       <c r="E80" s="7">
         <f>IF(OR(A80="",SUMIFS(C$4:C80,A$4:A80,A80)=0),"",SUMPRODUCT((A$4:A80=A80)*(C$4:C80)*(D$4:D80))/SUMIFS(C$4:C80,A$4:A80,A80))</f>
-        <v>93.982412637625657</v>
-      </c>
-      <c r="F80" s="6">
-        <v>61</v>
-      </c>
+        <v>94.691442903843992</v>
+      </c>
+      <c r="F80" s="6"/>
       <c r="G80" s="6">
-        <f t="shared" si="2"/>
-        <v>439</v>
+        <f>IF(C80="","",C80-IF(ISNUMBER(F80),F80,0))</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B81" s="5">
-        <v>45931</v>
-      </c>
-      <c r="C81" s="6"/>
+        <v>46143</v>
+      </c>
+      <c r="C81" s="6">
+        <v>1168</v>
+      </c>
       <c r="D81" s="7">
-        <v>72.5</v>
-      </c>
-      <c r="E81" s="7" t="str">
+        <v>106.21</v>
+      </c>
+      <c r="E81" s="7">
         <f>IF(OR(A81="",SUMIFS(C$4:C81,A$4:A81,A81)=0),"",SUMPRODUCT((A$4:A81=A81)*(C$4:C81)*(D$4:D81))/SUMIFS(C$4:C81,A$4:A81,A81))</f>
-        <v/>
-      </c>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>96.03158382308996</v>
+      </c>
+      <c r="F81" s="6">
+        <v>375</v>
+      </c>
+      <c r="G81" s="6">
+        <f>IF(C81="","",C81-IF(ISNUMBER(F81),F81,0))</f>
+        <v>793</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A82" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B82" s="5">
-        <v>45962</v>
-      </c>
-      <c r="C82" s="6"/>
+        <v>46174</v>
+      </c>
+      <c r="C82" s="6">
+        <v>793</v>
+      </c>
       <c r="D82" s="7">
-        <v>72.5</v>
-      </c>
-      <c r="E82" s="7" t="str">
+        <v>106.21</v>
+      </c>
+      <c r="E82" s="7">
         <f>IF(OR(A82="",SUMIFS(C$4:C82,A$4:A82,A82)=0),"",SUMPRODUCT((A$4:A82=A82)*(C$4:C82)*(D$4:D82))/SUMIFS(C$4:C82,A$4:A82,A82))</f>
-        <v/>
+        <v>96.776735598227489</v>
       </c>
       <c r="F82" s="6"/>
-      <c r="G82" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G82" s="6">
+        <f>IF(C82="","",C82-IF(ISNUMBER(F82),F82,0))</f>
+        <v>793</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A83" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B83" s="5">
-        <v>45992</v>
-      </c>
-      <c r="C83" s="6"/>
+        <v>46174</v>
+      </c>
+      <c r="C83" s="6">
+        <v>500</v>
+      </c>
       <c r="D83" s="7">
-        <v>72.5</v>
-      </c>
-      <c r="E83" s="7" t="str">
+        <v>92.4</v>
+      </c>
+      <c r="E83" s="7">
         <f>IF(OR(A83="",SUMIFS(C$4:C83,A$4:A83,A83)=0),"",SUMPRODUCT((A$4:A83=A83)*(C$4:C83)*(D$4:D83))/SUMIFS(C$4:C83,A$4:A83,A83))</f>
-        <v/>
+        <v>96.583621602541484</v>
       </c>
       <c r="F83" s="6"/>
-      <c r="G83" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="G83" s="6">
+        <f>IF(C83="","",C83-IF(ISNUMBER(F83),F83,0))</f>
+        <v>500</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A84" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B84" s="5">
-        <v>46023</v>
-      </c>
-      <c r="C84" s="6"/>
+        <v>46204</v>
+      </c>
+      <c r="C84" s="6">
+        <v>1293</v>
+      </c>
       <c r="D84" s="7">
-        <v>72.5</v>
-      </c>
-      <c r="E84" s="7" t="str">
+        <v>100.87</v>
+      </c>
+      <c r="E84" s="7">
         <f>IF(OR(A84="",SUMIFS(C$4:C84,A$4:A84,A84)=0),"",SUMPRODUCT((A$4:A84=A84)*(C$4:C84)*(D$4:D84))/SUMIFS(C$4:C84,A$4:A84,A84))</f>
-        <v/>
-      </c>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>97.022614653465354</v>
+      </c>
+      <c r="F84" s="6">
+        <v>560</v>
+      </c>
+      <c r="G84" s="6">
+        <f>IF(C84="","",C84-IF(ISNUMBER(F84),F84,0))</f>
+        <v>733</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A85" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B85" s="5">
-        <v>46054</v>
-      </c>
-      <c r="C85" s="6"/>
+        <v>46235</v>
+      </c>
+      <c r="C85" s="6">
+        <v>733</v>
+      </c>
       <c r="D85" s="7">
-        <v>72.5</v>
-      </c>
-      <c r="E85" s="7" t="str">
+        <v>100.87</v>
+      </c>
+      <c r="E85" s="7">
         <f>IF(OR(A85="",SUMIFS(C$4:C85,A$4:A85,A85)=0),"",SUMPRODUCT((A$4:A85=A85)*(C$4:C85)*(D$4:D85))/SUMIFS(C$4:C85,A$4:A85,A85))</f>
-        <v/>
+        <v>97.233734091929932</v>
       </c>
       <c r="F85" s="6">
-        <v>72</v>
-      </c>
-      <c r="G85" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>618</v>
+      </c>
+      <c r="G85" s="6">
+        <f>IF(C85="","",C85-IF(ISNUMBER(F85),F85,0))</f>
+        <v>115</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A86" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B86" s="5">
-        <v>46082</v>
+        <v>46235</v>
       </c>
       <c r="C86" s="6">
-        <v>228</v>
+        <v>1056</v>
       </c>
       <c r="D86" s="7">
-        <v>89.5</v>
+        <v>116.4</v>
       </c>
       <c r="E86" s="7">
         <f>IF(OR(A86="",SUMIFS(C$4:C86,A$4:A86,A86)=0),"",SUMPRODUCT((A$4:A86=A86)*(C$4:C86)*(D$4:D86))/SUMIFS(C$4:C86,A$4:A86,A86))</f>
-        <v>89.5</v>
-      </c>
-      <c r="F86" s="6">
-        <v>197</v>
-      </c>
+        <v>98.637895101984171</v>
+      </c>
+      <c r="F86" s="6"/>
       <c r="G86" s="6">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <f>IF(C86="","",C86-IF(ISNUMBER(F86),F86,0))</f>
+        <v>1056</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A87" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B87" s="5">
-        <v>46113</v>
+        <v>46266</v>
       </c>
       <c r="C87" s="6">
-        <v>31</v>
+        <v>1171</v>
       </c>
       <c r="D87" s="7">
-        <v>89.5</v>
+        <v>110.04</v>
       </c>
       <c r="E87" s="7">
         <f>IF(OR(A87="",SUMIFS(C$4:C87,A$4:A87,A87)=0),"",SUMPRODUCT((A$4:A87=A87)*(C$4:C87)*(D$4:D87))/SUMIFS(C$4:C87,A$4:A87,A87))</f>
-        <v>89.5</v>
+        <v>99.494607635546998</v>
       </c>
       <c r="F87" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G87" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF(C87="","",C87-IF(ISNUMBER(F87),F87,0))</f>
+        <v>1141</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A88" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B88" s="5">
-        <v>46143</v>
+        <v>46266</v>
       </c>
       <c r="C88" s="6">
-        <v>101</v>
+        <v>444</v>
       </c>
       <c r="D88" s="7">
-        <v>103.1</v>
+        <v>114.4</v>
       </c>
       <c r="E88" s="7">
         <f>IF(OR(A88="",SUMIFS(C$4:C88,A$4:A88,A88)=0),"",SUMPRODUCT((A$4:A88=A88)*(C$4:C88)*(D$4:D88))/SUMIFS(C$4:C88,A$4:A88,A88))</f>
-        <v>93.315555555555548</v>
+        <v>99.907483935367154</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6">
-        <f t="shared" si="2"/>
-        <v>101</v>
+        <f>IF(C88="","",C88-IF(ISNUMBER(F88),F88,0))</f>
+        <v>444</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A89" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B89" s="5">
-        <v>46174</v>
+        <v>46296</v>
       </c>
       <c r="C89" s="6">
-        <v>101</v>
+        <v>1585</v>
       </c>
       <c r="D89" s="7">
-        <v>103.1</v>
+        <v>111.24</v>
       </c>
       <c r="E89" s="7">
         <f>IF(OR(A89="",SUMIFS(C$4:C89,A$4:A89,A89)=0),"",SUMPRODUCT((A$4:A89=A89)*(C$4:C89)*(D$4:D89))/SUMIFS(C$4:C89,A$4:A89,A89))</f>
-        <v>95.45921908893709</v>
+        <v>100.9272431020779</v>
       </c>
       <c r="F89" s="6">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G89" s="6">
-        <f t="shared" si="2"/>
-        <v>28</v>
+        <f>IF(C89="","",C89-IF(ISNUMBER(F89),F89,0))</f>
+        <v>1515</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A90" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B90" s="5">
-        <v>46204</v>
+        <v>45931</v>
       </c>
       <c r="C90" s="6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D90" s="7">
-        <v>103.1</v>
+        <v>79.2</v>
       </c>
       <c r="E90" s="7">
         <f>IF(OR(A90="",SUMIFS(C$4:C90,A$4:A90,A90)=0),"",SUMPRODUCT((A$4:A90=A90)*(C$4:C90)*(D$4:D90))/SUMIFS(C$4:C90,A$4:A90,A90))</f>
-        <v>95.896728016359916</v>
+        <v>79.2</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6">
-        <f t="shared" si="2"/>
-        <v>28</v>
+        <f>IF(C90="","",C90-IF(ISNUMBER(F90),F90,0))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A91" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B91" s="5">
-        <v>46235</v>
+        <v>45962</v>
       </c>
       <c r="C91" s="6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D91" s="7">
-        <v>103.1</v>
+        <v>79.2</v>
       </c>
       <c r="E91" s="7">
         <f>IF(OR(A91="",SUMIFS(C$4:C91,A$4:A91,A91)=0),"",SUMPRODUCT((A$4:A91=A91)*(C$4:C91)*(D$4:D91))/SUMIFS(C$4:C91,A$4:A91,A91))</f>
-        <v>96.286847195357836</v>
+        <v>79.2</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="6">
-        <f t="shared" si="2"/>
-        <v>28</v>
+        <f>IF(C91="","",C91-IF(ISNUMBER(F91),F91,0))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A92" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B92" s="5">
-        <v>46266</v>
+        <v>45992</v>
       </c>
       <c r="C92" s="6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D92" s="7">
-        <v>103.1</v>
+        <v>79.2</v>
       </c>
       <c r="E92" s="7">
         <f>IF(OR(A92="",SUMIFS(C$4:C92,A$4:A92,A92)=0),"",SUMPRODUCT((A$4:A92=A92)*(C$4:C92)*(D$4:D92))/SUMIFS(C$4:C92,A$4:A92,A92))</f>
-        <v>96.636880733944963</v>
+        <v>79.2</v>
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="6">
-        <f t="shared" si="2"/>
-        <v>28</v>
+        <f>IF(C92="","",C92-IF(ISNUMBER(F92),F92,0))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A93" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B93" s="5">
-        <v>46296</v>
+        <v>46023</v>
       </c>
       <c r="C93" s="6">
-        <v>728</v>
+        <v>32</v>
       </c>
       <c r="D93" s="7">
-        <v>112.14</v>
+        <v>79.2</v>
       </c>
       <c r="E93" s="7">
         <f>IF(OR(A93="",SUMIFS(C$4:C93,A$4:A93,A93)=0),"",SUMPRODUCT((A$4:A93=A93)*(C$4:C93)*(D$4:D93))/SUMIFS(C$4:C93,A$4:A93,A93))</f>
-        <v>105.50276512175964</v>
-      </c>
-      <c r="F93" s="6">
-        <v>140</v>
-      </c>
+        <v>79.2</v>
+      </c>
+      <c r="F93" s="6"/>
       <c r="G93" s="6">
-        <f t="shared" si="2"/>
-        <v>588</v>
+        <f>IF(C93="","",C93-IF(ISNUMBER(F93),F93,0))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A94" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B94" s="5">
         <v>46054</v>
       </c>
       <c r="C94" s="6">
-        <v>300</v>
+        <v>32</v>
       </c>
       <c r="D94" s="7">
-        <v>89.5</v>
+        <v>79.2</v>
       </c>
       <c r="E94" s="7">
         <f>IF(OR(A94="",SUMIFS(C$4:C94,A$4:A94,A94)=0),"",SUMPRODUCT((A$4:A94=A94)*(C$4:C94)*(D$4:D94))/SUMIFS(C$4:C94,A$4:A94,A94))</f>
-        <v>102.45074380165291</v>
+        <v>79.2</v>
       </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6">
-        <f t="shared" si="2"/>
-        <v>300</v>
+        <f>IF(C94="","",C94-IF(ISNUMBER(F94),F94,0))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A95" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B95" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C95" s="6">
-        <v>300</v>
-      </c>
-      <c r="D95" s="7">
-        <v>104.5</v>
-      </c>
+        <v>46054</v>
+      </c>
+      <c r="C95" s="6"/>
+      <c r="D95" s="7"/>
       <c r="E95" s="7">
         <f>IF(OR(A95="",SUMIFS(C$4:C95,A$4:A95,A95)=0),"",SUMPRODUCT((A$4:A95=A95)*(C$4:C95)*(D$4:D95))/SUMIFS(C$4:C95,A$4:A95,A95))</f>
-        <v>102.77897490656702</v>
-      </c>
-      <c r="F95" s="6">
-        <v>199</v>
-      </c>
-      <c r="G95" s="6">
-        <f t="shared" si="2"/>
-        <v>101</v>
+        <v>79.2</v>
+      </c>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6" t="str">
+        <f>IF(C95="","",C95-IF(ISNUMBER(F95),F95,0))</f>
+        <v/>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A96" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B96" s="5">
-        <v>46266</v>
+        <v>46082</v>
       </c>
       <c r="C96" s="6">
-        <v>700</v>
+        <v>32</v>
       </c>
       <c r="D96" s="7">
-        <v>112.5</v>
+        <v>79.2</v>
       </c>
       <c r="E96" s="7">
         <f>IF(OR(A96="",SUMIFS(C$4:C96,A$4:A96,A96)=0),"",SUMPRODUCT((A$4:A96=A96)*(C$4:C96)*(D$4:D96))/SUMIFS(C$4:C96,A$4:A96,A96))</f>
-        <v>105.42363777691412</v>
+        <v>79.2</v>
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="6">
-        <f t="shared" si="2"/>
-        <v>700</v>
+        <f>IF(C96="","",C96-IF(ISNUMBER(F96),F96,0))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A97" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B97" s="5">
-        <v>45931</v>
-      </c>
-      <c r="C97" s="6"/>
+        <v>46113</v>
+      </c>
+      <c r="C97" s="6">
+        <v>32</v>
+      </c>
       <c r="D97" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E97" s="7" t="str">
+        <v>79.2</v>
+      </c>
+      <c r="E97" s="7">
         <f>IF(OR(A97="",SUMIFS(C$4:C97,A$4:A97,A97)=0),"",SUMPRODUCT((A$4:A97=A97)*(C$4:C97)*(D$4:D97))/SUMIFS(C$4:C97,A$4:A97,A97))</f>
-        <v/>
-      </c>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>79.2</v>
+      </c>
+      <c r="F97" s="6">
+        <v>20</v>
+      </c>
+      <c r="G97" s="6">
+        <f>IF(C97="","",C97-IF(ISNUMBER(F97),F97,0))</f>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A98" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B98" s="5">
-        <v>45962</v>
-      </c>
-      <c r="C98" s="6"/>
+        <v>46143</v>
+      </c>
+      <c r="C98" s="6">
+        <v>12</v>
+      </c>
       <c r="D98" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E98" s="7" t="str">
+        <v>79.2</v>
+      </c>
+      <c r="E98" s="7">
         <f>IF(OR(A98="",SUMIFS(C$4:C98,A$4:A98,A98)=0),"",SUMPRODUCT((A$4:A98=A98)*(C$4:C98)*(D$4:D98))/SUMIFS(C$4:C98,A$4:A98,A98))</f>
-        <v/>
-      </c>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>79.2</v>
+      </c>
+      <c r="F98" s="6">
+        <v>12</v>
+      </c>
+      <c r="G98" s="6">
+        <f>IF(C98="","",C98-IF(ISNUMBER(F98),F98,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A99" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B99" s="5">
-        <v>45992</v>
-      </c>
-      <c r="C99" s="6"/>
+        <v>46143</v>
+      </c>
+      <c r="C99" s="6">
+        <v>1000</v>
+      </c>
       <c r="D99" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E99" s="7" t="str">
+        <v>91.8</v>
+      </c>
+      <c r="E99" s="7">
         <f>IF(OR(A99="",SUMIFS(C$4:C99,A$4:A99,A99)=0),"",SUMPRODUCT((A$4:A99=A99)*(C$4:C99)*(D$4:D99))/SUMIFS(C$4:C99,A$4:A99,A99))</f>
-        <v/>
-      </c>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>89.394174757281547</v>
+      </c>
+      <c r="F99" s="6">
+        <v>408</v>
+      </c>
+      <c r="G99" s="6">
+        <f>IF(C99="","",C99-IF(ISNUMBER(F99),F99,0))</f>
+        <v>592</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A100" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B100" s="5">
-        <v>46023</v>
-      </c>
-      <c r="C100" s="6"/>
+        <v>46174</v>
+      </c>
+      <c r="C100" s="6">
+        <v>592</v>
+      </c>
       <c r="D100" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E100" s="7" t="str">
+        <v>91.65</v>
+      </c>
+      <c r="E100" s="7">
         <f>IF(OR(A100="",SUMIFS(C$4:C100,A$4:A100,A100)=0),"",SUMPRODUCT((A$4:A100=A100)*(C$4:C100)*(D$4:D100))/SUMIFS(C$4:C100,A$4:A100,A100))</f>
-        <v/>
-      </c>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6" t="str">
-        <f t="shared" ref="G100:G131" si="3">IF(C100="","",C100-IF(ISNUMBER(F100),F100,0))</f>
-        <v/>
+        <v>90.124726477024069</v>
+      </c>
+      <c r="F100" s="6">
+        <v>592</v>
+      </c>
+      <c r="G100" s="6">
+        <f>IF(C100="","",C100-IF(ISNUMBER(F100),F100,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A101" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B101" s="5">
-        <v>46054</v>
-      </c>
-      <c r="C101" s="6"/>
+        <v>46174</v>
+      </c>
+      <c r="C101" s="6">
+        <v>1000</v>
+      </c>
       <c r="D101" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E101" s="7" t="str">
+        <v>94.9</v>
+      </c>
+      <c r="E101" s="7">
         <f>IF(OR(A101="",SUMIFS(C$4:C101,A$4:A101,A101)=0),"",SUMPRODUCT((A$4:A101=A101)*(C$4:C101)*(D$4:D101))/SUMIFS(C$4:C101,A$4:A101,A101))</f>
-        <v/>
-      </c>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>91.81329561527582</v>
+      </c>
+      <c r="F101" s="6">
+        <v>133</v>
+      </c>
+      <c r="G101" s="6">
+        <f>IF(C101="","",C101-IF(ISNUMBER(F101),F101,0))</f>
+        <v>867</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A102" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B102" s="5">
-        <v>46082</v>
-      </c>
-      <c r="C102" s="6"/>
+        <v>46174</v>
+      </c>
+      <c r="C102" s="6">
+        <v>20</v>
+      </c>
       <c r="D102" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E102" s="7" t="str">
+        <v>91.8</v>
+      </c>
+      <c r="E102" s="7">
         <f>IF(OR(A102="",SUMIFS(C$4:C102,A$4:A102,A102)=0),"",SUMPRODUCT((A$4:A102=A102)*(C$4:C102)*(D$4:D102))/SUMIFS(C$4:C102,A$4:A102,A102))</f>
-        <v/>
+        <v>91.813202247191015</v>
       </c>
       <c r="F102" s="6"/>
-      <c r="G102" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="G102" s="6">
+        <f>IF(C102="","",C102-IF(ISNUMBER(F102),F102,0))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A103" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B103" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C103" s="6"/>
+        <v>46204</v>
+      </c>
+      <c r="C103" s="6">
+        <v>887</v>
+      </c>
       <c r="D103" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E103" s="7" t="str">
+        <v>93.67</v>
+      </c>
+      <c r="E103" s="7">
         <f>IF(OR(A103="",SUMIFS(C$4:C103,A$4:A103,A103)=0),"",SUMPRODUCT((A$4:A103=A103)*(C$4:C103)*(D$4:D103))/SUMIFS(C$4:C103,A$4:A103,A103))</f>
-        <v/>
-      </c>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>92.254160642570298</v>
+      </c>
+      <c r="F103" s="6">
+        <v>190</v>
+      </c>
+      <c r="G103" s="6">
+        <f>IF(C103="","",C103-IF(ISNUMBER(F103),F103,0))</f>
+        <v>697</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A104" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B104" s="5">
-        <v>46143</v>
-      </c>
-      <c r="C104" s="6"/>
+        <v>46235</v>
+      </c>
+      <c r="C104" s="6">
+        <v>697</v>
+      </c>
       <c r="D104" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E104" s="7" t="str">
+        <v>93.67</v>
+      </c>
+      <c r="E104" s="7">
         <f>IF(OR(A104="",SUMIFS(C$4:C104,A$4:A104,A104)=0),"",SUMPRODUCT((A$4:A104=A104)*(C$4:C104)*(D$4:D104))/SUMIFS(C$4:C104,A$4:A104,A104))</f>
-        <v/>
-      </c>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>92.476823104693153</v>
+      </c>
+      <c r="F104" s="6">
+        <v>366</v>
+      </c>
+      <c r="G104" s="6">
+        <f>IF(C104="","",C104-IF(ISNUMBER(F104),F104,0))</f>
+        <v>331</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A105" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B105" s="5">
-        <v>46174</v>
-      </c>
-      <c r="C105" s="6"/>
+        <v>46266</v>
+      </c>
+      <c r="C105" s="6">
+        <v>331</v>
+      </c>
       <c r="D105" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="E105" s="7" t="str">
+        <v>93.67</v>
+      </c>
+      <c r="E105" s="7">
         <f>IF(OR(A105="",SUMIFS(C$4:C105,A$4:A105,A105)=0),"",SUMPRODUCT((A$4:A105=A105)*(C$4:C105)*(D$4:D105))/SUMIFS(C$4:C105,A$4:A105,A105))</f>
-        <v/>
-      </c>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>92.559741759395351</v>
+      </c>
+      <c r="F105" s="6">
+        <v>570</v>
+      </c>
+      <c r="G105" s="6">
+        <f>IF(C105="","",C105-IF(ISNUMBER(F105),F105,0))</f>
+        <v>-239</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A106" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B106" s="5">
-        <v>46204</v>
+        <v>46296</v>
       </c>
       <c r="C106" s="6">
-        <v>595</v>
+        <v>-239</v>
       </c>
       <c r="D106" s="7">
-        <v>91.4</v>
+        <v>93.67</v>
       </c>
       <c r="E106" s="7">
         <f>IF(OR(A106="",SUMIFS(C$4:C106,A$4:A106,A106)=0),"",SUMPRODUCT((A$4:A106=A106)*(C$4:C106)*(D$4:D106))/SUMIFS(C$4:C106,A$4:A106,A106))</f>
-        <v>91.4</v>
+        <v>92.501087533156507</v>
       </c>
       <c r="F106" s="6">
-        <v>18</v>
+        <v>580</v>
       </c>
       <c r="G106" s="6">
-        <f t="shared" si="3"/>
-        <v>577</v>
+        <f>IF(C106="","",C106-IF(ISNUMBER(F106),F106,0))</f>
+        <v>-819</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A107" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B107" s="5">
-        <v>46235</v>
+        <v>45931</v>
       </c>
       <c r="C107" s="6">
-        <v>577</v>
+        <v>200</v>
       </c>
       <c r="D107" s="7">
-        <v>91.4</v>
+        <v>77.2</v>
       </c>
       <c r="E107" s="7">
         <f>IF(OR(A107="",SUMIFS(C$4:C107,A$4:A107,A107)=0),"",SUMPRODUCT((A$4:A107=A107)*(C$4:C107)*(D$4:D107))/SUMIFS(C$4:C107,A$4:A107,A107))</f>
-        <v>91.4</v>
+        <v>77.2</v>
       </c>
       <c r="F107" s="6">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="G107" s="6">
-        <f t="shared" si="3"/>
-        <v>497</v>
+        <f>IF(C107="","",C107-IF(ISNUMBER(F107),F107,0))</f>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A108" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B108" s="5">
-        <v>46266</v>
+        <v>45962</v>
       </c>
       <c r="C108" s="6">
-        <v>497</v>
+        <v>194</v>
       </c>
       <c r="D108" s="7">
-        <v>91.4</v>
+        <v>77.2</v>
       </c>
       <c r="E108" s="7">
         <f>IF(OR(A108="",SUMIFS(C$4:C108,A$4:A108,A108)=0),"",SUMPRODUCT((A$4:A108=A108)*(C$4:C108)*(D$4:D108))/SUMIFS(C$4:C108,A$4:A108,A108))</f>
-        <v>91.4</v>
+        <v>77.2</v>
       </c>
       <c r="F108" s="6">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="G108" s="6">
-        <f t="shared" si="3"/>
-        <v>469</v>
+        <f>IF(C108="","",C108-IF(ISNUMBER(F108),F108,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A109" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B109" s="5">
-        <v>46296</v>
+        <v>45992</v>
       </c>
       <c r="C109" s="6">
-        <v>469</v>
+        <v>9</v>
       </c>
       <c r="D109" s="7">
-        <v>91.4</v>
+        <v>82.67</v>
       </c>
       <c r="E109" s="7">
         <f>IF(OR(A109="",SUMIFS(C$4:C109,A$4:A109,A109)=0),"",SUMPRODUCT((A$4:A109=A109)*(C$4:C109)*(D$4:D109))/SUMIFS(C$4:C109,A$4:A109,A109))</f>
-        <v>91.4</v>
+        <v>77.322158808933011</v>
       </c>
       <c r="F109" s="6">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G109" s="6">
-        <f t="shared" si="3"/>
-        <v>439</v>
+        <f>IF(C109="","",C109-IF(ISNUMBER(F109),F109,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A110" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B110" s="5">
-        <v>46174</v>
+        <v>46023</v>
       </c>
       <c r="C110" s="6">
-        <v>600</v>
+        <v>72</v>
       </c>
       <c r="D110" s="7">
-        <v>91.4</v>
+        <v>94.81</v>
       </c>
       <c r="E110" s="7">
         <f>IF(OR(A110="",SUMIFS(C$4:C110,A$4:A110,A110)=0),"",SUMPRODUCT((A$4:A110=A110)*(C$4:C110)*(D$4:D110))/SUMIFS(C$4:C110,A$4:A110,A110))</f>
-        <v>91.4</v>
+        <v>79.97294736842106</v>
       </c>
       <c r="F110" s="6">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="G110" s="6">
-        <f t="shared" si="3"/>
-        <v>595</v>
+        <f>IF(C110="","",C110-IF(ISNUMBER(F110),F110,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A111" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B111" s="5">
-        <v>45931</v>
-      </c>
-      <c r="C111" s="6"/>
+        <v>46054</v>
+      </c>
+      <c r="C111" s="6">
+        <v>478</v>
+      </c>
       <c r="D111" s="7">
-        <v>78</v>
-      </c>
-      <c r="E111" s="7" t="str">
+        <v>94.28</v>
+      </c>
+      <c r="E111" s="7">
         <f>IF(OR(A111="",SUMIFS(C$4:C111,A$4:A111,A111)=0),"",SUMPRODUCT((A$4:A111=A111)*(C$4:C111)*(D$4:D111))/SUMIFS(C$4:C111,A$4:A111,A111))</f>
-        <v/>
-      </c>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>87.148992654774403</v>
+      </c>
+      <c r="F111" s="6">
+        <v>319</v>
+      </c>
+      <c r="G111" s="6">
+        <f>IF(C111="","",C111-IF(ISNUMBER(F111),F111,0))</f>
+        <v>159</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A112" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B112" s="5">
-        <v>45962</v>
-      </c>
-      <c r="C112" s="6"/>
+        <v>46082</v>
+      </c>
+      <c r="C112" s="6">
+        <v>475</v>
+      </c>
       <c r="D112" s="7">
-        <v>78</v>
-      </c>
-      <c r="E112" s="7" t="str">
+        <v>94.25</v>
+      </c>
+      <c r="E112" s="7">
         <f>IF(OR(A112="",SUMIFS(C$4:C112,A$4:A112,A112)=0),"",SUMPRODUCT((A$4:A112=A112)*(C$4:C112)*(D$4:D112))/SUMIFS(C$4:C112,A$4:A112,A112))</f>
-        <v/>
-      </c>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>89.511022408963584</v>
+      </c>
+      <c r="F112" s="6">
+        <v>453</v>
+      </c>
+      <c r="G112" s="6">
+        <f>IF(C112="","",C112-IF(ISNUMBER(F112),F112,0))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A113" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B113" s="5">
-        <v>45992</v>
-      </c>
-      <c r="C113" s="6"/>
+        <v>46113</v>
+      </c>
+      <c r="C113" s="6">
+        <v>22</v>
+      </c>
       <c r="D113" s="7">
-        <v>78</v>
-      </c>
-      <c r="E113" s="7" t="str">
+        <v>94.25</v>
+      </c>
+      <c r="E113" s="7">
         <f>IF(OR(A113="",SUMIFS(C$4:C113,A$4:A113,A113)=0),"",SUMPRODUCT((A$4:A113=A113)*(C$4:C113)*(D$4:D113))/SUMIFS(C$4:C113,A$4:A113,A113))</f>
-        <v/>
-      </c>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>89.582924137931045</v>
+      </c>
+      <c r="F113" s="6">
+        <v>22</v>
+      </c>
+      <c r="G113" s="6">
+        <f>IF(C113="","",C113-IF(ISNUMBER(F113),F113,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A114" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B114" s="5">
-        <v>46023</v>
-      </c>
-      <c r="C114" s="6"/>
+        <v>46113</v>
+      </c>
+      <c r="C114" s="6">
+        <v>219</v>
+      </c>
       <c r="D114" s="7">
-        <v>78</v>
-      </c>
-      <c r="E114" s="7" t="str">
+        <v>111.7</v>
+      </c>
+      <c r="E114" s="7">
         <f>IF(OR(A114="",SUMIFS(C$4:C114,A$4:A114,A114)=0),"",SUMPRODUCT((A$4:A114=A114)*(C$4:C114)*(D$4:D114))/SUMIFS(C$4:C114,A$4:A114,A114))</f>
-        <v/>
-      </c>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>92.485044937088077</v>
+      </c>
+      <c r="F114" s="6">
+        <v>214</v>
+      </c>
+      <c r="G114" s="6">
+        <f>IF(C114="","",C114-IF(ISNUMBER(F114),F114,0))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A115" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B115" s="5">
-        <v>46054</v>
-      </c>
-      <c r="C115" s="6"/>
+        <v>46143</v>
+      </c>
+      <c r="C115" s="6">
+        <v>5</v>
+      </c>
       <c r="D115" s="7">
-        <v>78</v>
-      </c>
-      <c r="E115" s="7" t="str">
+        <v>110.11</v>
+      </c>
+      <c r="E115" s="7">
         <f>IF(OR(A115="",SUMIFS(C$4:C115,A$4:A115,A115)=0),"",SUMPRODUCT((A$4:A115=A115)*(C$4:C115)*(D$4:D115))/SUMIFS(C$4:C115,A$4:A115,A115))</f>
-        <v/>
-      </c>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>92.537688172043005</v>
+      </c>
+      <c r="F115" s="6">
+        <v>5</v>
+      </c>
+      <c r="G115" s="6">
+        <f>IF(C115="","",C115-IF(ISNUMBER(F115),F115,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A116" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B116" s="5">
-        <v>46082</v>
-      </c>
-      <c r="C116" s="6">
-        <v>70</v>
-      </c>
+        <v>46174</v>
+      </c>
+      <c r="C116" s="6"/>
       <c r="D116" s="7">
-        <v>89.9</v>
+        <v>110.11</v>
       </c>
       <c r="E116" s="7">
         <f>IF(OR(A116="",SUMIFS(C$4:C116,A$4:A116,A116)=0),"",SUMPRODUCT((A$4:A116=A116)*(C$4:C116)*(D$4:D116))/SUMIFS(C$4:C116,A$4:A116,A116))</f>
-        <v>89.9</v>
+        <v>92.537688172043005</v>
       </c>
       <c r="F116" s="6"/>
-      <c r="G116" s="6">
-        <f t="shared" si="3"/>
-        <v>70</v>
+      <c r="G116" s="6" t="str">
+        <f>IF(C116="","",C116-IF(ISNUMBER(F116),F116,0))</f>
+        <v/>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A117" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B117" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C117" s="6">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="D117" s="7">
-        <v>89.9</v>
+        <v>93.8</v>
       </c>
       <c r="E117" s="7">
         <f>IF(OR(A117="",SUMIFS(C$4:C117,A$4:A117,A117)=0),"",SUMPRODUCT((A$4:A117=A117)*(C$4:C117)*(D$4:D117))/SUMIFS(C$4:C117,A$4:A117,A117))</f>
-        <v>89.9</v>
-      </c>
-      <c r="F117" s="6">
-        <v>70</v>
-      </c>
+        <v>92.828008279668808</v>
+      </c>
+      <c r="F117" s="6"/>
       <c r="G117" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>IF(C117="","",C117-IF(ISNUMBER(F117),F117,0))</f>
+        <v>500</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A118" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B118" s="5">
-        <v>46143</v>
+        <v>46204</v>
       </c>
       <c r="C118" s="6">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="D118" s="7">
-        <v>96.49</v>
+        <v>93.8</v>
       </c>
       <c r="E118" s="7">
         <f>IF(OR(A118="",SUMIFS(C$4:C118,A$4:A118,A118)=0),"",SUMPRODUCT((A$4:A118=A118)*(C$4:C118)*(D$4:D118))/SUMIFS(C$4:C118,A$4:A118,A118))</f>
-        <v>93.308620689655172</v>
-      </c>
-      <c r="F118" s="6"/>
+        <v>93.009756918474196</v>
+      </c>
+      <c r="F118" s="6">
+        <v>35</v>
+      </c>
       <c r="G118" s="6">
-        <f t="shared" si="3"/>
-        <v>150</v>
+        <f>IF(C118="","",C118-IF(ISNUMBER(F118),F118,0))</f>
+        <v>465</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A119" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B119" s="5">
-        <v>46174</v>
+        <v>46235</v>
       </c>
       <c r="C119" s="6">
-        <v>150</v>
+        <v>465</v>
       </c>
       <c r="D119" s="7">
-        <v>96.49</v>
+        <v>93.8</v>
       </c>
       <c r="E119" s="7">
         <f>IF(OR(A119="",SUMIFS(C$4:C119,A$4:A119,A119)=0),"",SUMPRODUCT((A$4:A119=A119)*(C$4:C119)*(D$4:D119))/SUMIFS(C$4:C119,A$4:A119,A119))</f>
-        <v>94.393181818181816</v>
+        <v>93.126820643517036</v>
       </c>
       <c r="F119" s="6">
-        <v>61</v>
+        <v>312</v>
       </c>
       <c r="G119" s="6">
-        <f t="shared" si="3"/>
-        <v>89</v>
+        <f>IF(C119="","",C119-IF(ISNUMBER(F119),F119,0))</f>
+        <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A120" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B120" s="5">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="C120" s="6">
-        <v>89</v>
+        <v>500</v>
       </c>
       <c r="D120" s="7">
-        <v>96.49</v>
+        <v>117.8</v>
       </c>
       <c r="E120" s="7">
         <f>IF(OR(A120="",SUMIFS(C$4:C120,A$4:A120,A120)=0),"",SUMPRODUCT((A$4:A120=A120)*(C$4:C120)*(D$4:D120))/SUMIFS(C$4:C120,A$4:A120,A120))</f>
-        <v>94.745954631379959</v>
-      </c>
-      <c r="F120" s="6">
-        <v>85</v>
-      </c>
+        <v>96.516924979389927</v>
+      </c>
+      <c r="F120" s="6"/>
       <c r="G120" s="6">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f>IF(C120="","",C120-IF(ISNUMBER(F120),F120,0))</f>
+        <v>500</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A121" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B121" s="5">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="C121" s="6">
-        <v>4</v>
+        <v>653</v>
       </c>
       <c r="D121" s="7">
-        <v>96.49</v>
+        <v>106.24</v>
       </c>
       <c r="E121" s="7">
         <f>IF(OR(A121="",SUMIFS(C$4:C121,A$4:A121,A121)=0),"",SUMPRODUCT((A$4:A121=A121)*(C$4:C121)*(D$4:D121))/SUMIFS(C$4:C121,A$4:A121,A121))</f>
-        <v>94.759043151969976</v>
+        <v>97.996227865796811</v>
       </c>
       <c r="F121" s="6">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G121" s="6">
-        <f t="shared" si="3"/>
-        <v>-26</v>
+        <f>IF(C121="","",C121-IF(ISNUMBER(F121),F121,0))</f>
+        <v>633</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A122" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B122" s="5">
         <v>46266</v>
       </c>
       <c r="C122" s="6">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="D122" s="7">
-        <v>106.66</v>
+        <v>117.4</v>
       </c>
       <c r="E122" s="7">
         <f>IF(OR(A122="",SUMIFS(C$4:C122,A$4:A122,A122)=0),"",SUMPRODUCT((A$4:A122=A122)*(C$4:C122)*(D$4:D122))/SUMIFS(C$4:C122,A$4:A122,A122))</f>
-        <v>98.799764560099135</v>
-      </c>
-      <c r="F122" s="6">
-        <v>30</v>
-      </c>
+        <v>99.263895905923334</v>
+      </c>
+      <c r="F122" s="6"/>
       <c r="G122" s="6">
-        <f t="shared" si="3"/>
-        <v>244</v>
+        <f>IF(C122="","",C122-IF(ISNUMBER(F122),F122,0))</f>
+        <v>300</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A123" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B123" s="5">
         <v>46296</v>
       </c>
       <c r="C123" s="6">
-        <v>444</v>
+        <v>933</v>
       </c>
       <c r="D123" s="7">
-        <v>105.88</v>
+        <v>109.75</v>
       </c>
       <c r="E123" s="7">
         <f>IF(OR(A123="",SUMIFS(C$4:C123,A$4:A123,A123)=0),"",SUMPRODUCT((A$4:A123=A123)*(C$4:C123)*(D$4:D123))/SUMIFS(C$4:C123,A$4:A123,A123))</f>
-        <v>101.31265387689848</v>
+        <v>101.03467149321266</v>
       </c>
       <c r="F123" s="6">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="G123" s="6">
-        <f t="shared" si="3"/>
-        <v>419</v>
+        <f>IF(C123="","",C123-IF(ISNUMBER(F123),F123,0))</f>
+        <v>828</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A124" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B124" s="5">
-        <v>46054</v>
-      </c>
-      <c r="C124" s="6"/>
-      <c r="D124" s="7"/>
+        <v>46327</v>
+      </c>
+      <c r="C124" s="6">
+        <v>300</v>
+      </c>
+      <c r="D124" s="7">
+        <v>86.2</v>
+      </c>
       <c r="E124" s="7">
         <f>IF(OR(A124="",SUMIFS(C$4:C124,A$4:A124,A124)=0),"",SUMPRODUCT((A$4:A124=A124)*(C$4:C124)*(D$4:D124))/SUMIFS(C$4:C124,A$4:A124,A124))</f>
-        <v>101.31265387689848</v>
-      </c>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>100.27065407725321</v>
+      </c>
+      <c r="F124" s="6">
+        <v>291</v>
+      </c>
+      <c r="G124" s="6">
+        <f>IF(C124="","",C124-IF(ISNUMBER(F124),F124,0))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A125" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B125" s="5">
-        <v>46113</v>
+        <v>46357</v>
       </c>
       <c r="C125" s="6">
-        <v>230</v>
+        <v>278</v>
       </c>
       <c r="D125" s="7">
-        <v>98.5</v>
+        <v>95.2</v>
       </c>
       <c r="E125" s="7">
         <f>IF(OR(A125="",SUMIFS(C$4:C125,A$4:A125,A125)=0),"",SUMPRODUCT((A$4:A125=A125)*(C$4:C125)*(D$4:D125))/SUMIFS(C$4:C125,A$4:A125,A125))</f>
-        <v>100.87584740040514</v>
+        <v>100.03967884646893</v>
       </c>
       <c r="F125" s="6">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="G125" s="6">
-        <f t="shared" si="3"/>
-        <v>150</v>
+        <f>IF(C125="","",C125-IF(ISNUMBER(F125),F125,0))</f>
+        <v>72</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A126" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B126" s="5">
-        <v>46235</v>
+        <v>46388</v>
       </c>
       <c r="C126" s="6">
-        <v>300</v>
+        <v>506</v>
       </c>
       <c r="D126" s="7">
-        <v>106.8</v>
+        <v>94.2</v>
       </c>
       <c r="E126" s="7">
         <f>IF(OR(A126="",SUMIFS(C$4:C126,A$4:A126,A126)=0),"",SUMPRODUCT((A$4:A126=A126)*(C$4:C126)*(D$4:D126))/SUMIFS(C$4:C126,A$4:A126,A126))</f>
-        <v>101.87373947220662</v>
-      </c>
-      <c r="F126" s="6"/>
+        <v>99.592579815403212</v>
+      </c>
+      <c r="F126" s="6">
+        <v>28</v>
+      </c>
       <c r="G126" s="6">
-        <f t="shared" si="3"/>
-        <v>300</v>
+        <f>IF(C126="","",C126-IF(ISNUMBER(F126),F126,0))</f>
+        <v>478</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A127" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B127" s="5">
-        <v>46266</v>
+        <v>46419</v>
       </c>
       <c r="C127" s="6">
-        <v>200</v>
+        <v>316</v>
       </c>
       <c r="D127" s="7">
-        <v>104.8</v>
+        <v>94.2</v>
       </c>
       <c r="E127" s="7">
         <f>IF(OR(A127="",SUMIFS(C$4:C127,A$4:A127,A127)=0),"",SUMPRODUCT((A$4:A127=A127)*(C$4:C127)*(D$4:D127))/SUMIFS(C$4:C127,A$4:A127,A127))</f>
-        <v>102.16917213528521</v>
+        <v>99.346506859205746</v>
       </c>
       <c r="F127" s="6"/>
       <c r="G127" s="6">
-        <f t="shared" si="3"/>
-        <v>200</v>
+        <f>IF(C127="","",C127-IF(ISNUMBER(F127),F127,0))</f>
+        <v>316</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A128" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B128" s="5">
         <v>45931</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="7">
-        <v>177.6</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="E128" s="7" t="str">
         <f>IF(OR(A128="",SUMIFS(C$4:C128,A$4:A128,A128)=0),"",SUMPRODUCT((A$4:A128=A128)*(C$4:C128)*(D$4:D128))/SUMIFS(C$4:C128,A$4:A128,A128))</f>
@@ -3710,20 +3724,20 @@
       </c>
       <c r="F128" s="6"/>
       <c r="G128" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(C128="","",C128-IF(ISNUMBER(F128),F128,0))</f>
         <v/>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A129" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B129" s="5">
         <v>45962</v>
       </c>
       <c r="C129" s="6"/>
       <c r="D129" s="7">
-        <v>177.6</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="E129" s="7" t="str">
         <f>IF(OR(A129="",SUMIFS(C$4:C129,A$4:A129,A129)=0),"",SUMPRODUCT((A$4:A129=A129)*(C$4:C129)*(D$4:D129))/SUMIFS(C$4:C129,A$4:A129,A129))</f>
@@ -3731,344 +3745,326 @@
       </c>
       <c r="F129" s="6"/>
       <c r="G129" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(C129="","",C129-IF(ISNUMBER(F129),F129,0))</f>
         <v/>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A130" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B130" s="5">
         <v>45992</v>
       </c>
-      <c r="C130" s="6">
-        <v>27</v>
-      </c>
+      <c r="C130" s="6"/>
       <c r="D130" s="7">
-        <v>177.6</v>
-      </c>
-      <c r="E130" s="7">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="E130" s="7" t="str">
         <f>IF(OR(A130="",SUMIFS(C$4:C130,A$4:A130,A130)=0),"",SUMPRODUCT((A$4:A130=A130)*(C$4:C130)*(D$4:D130))/SUMIFS(C$4:C130,A$4:A130,A130))</f>
-        <v>177.6</v>
+        <v/>
       </c>
       <c r="F130" s="6"/>
-      <c r="G130" s="6">
-        <f t="shared" si="3"/>
-        <v>27</v>
+      <c r="G130" s="6" t="str">
+        <f>IF(C130="","",C130-IF(ISNUMBER(F130),F130,0))</f>
+        <v/>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A131" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B131" s="5">
         <v>46023</v>
       </c>
-      <c r="C131" s="6">
-        <v>27</v>
-      </c>
+      <c r="C131" s="6"/>
       <c r="D131" s="7">
-        <v>177.6</v>
-      </c>
-      <c r="E131" s="7">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="E131" s="7" t="str">
         <f>IF(OR(A131="",SUMIFS(C$4:C131,A$4:A131,A131)=0),"",SUMPRODUCT((A$4:A131=A131)*(C$4:C131)*(D$4:D131))/SUMIFS(C$4:C131,A$4:A131,A131))</f>
-        <v>177.6</v>
-      </c>
-      <c r="F131" s="6">
-        <v>27</v>
-      </c>
-      <c r="G131" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="F131" s="6"/>
+      <c r="G131" s="6" t="str">
+        <f>IF(C131="","",C131-IF(ISNUMBER(F131),F131,0))</f>
+        <v/>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A132" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B132" s="5">
         <v>46054</v>
       </c>
-      <c r="C132" s="6">
-        <v>139</v>
-      </c>
+      <c r="C132" s="6"/>
       <c r="D132" s="7">
-        <v>177.6</v>
-      </c>
-      <c r="E132" s="7">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="E132" s="7" t="str">
         <f>IF(OR(A132="",SUMIFS(C$4:C132,A$4:A132,A132)=0),"",SUMPRODUCT((A$4:A132=A132)*(C$4:C132)*(D$4:D132))/SUMIFS(C$4:C132,A$4:A132,A132))</f>
-        <v>177.59999999999997</v>
-      </c>
-      <c r="F132" s="6">
-        <v>20</v>
-      </c>
-      <c r="G132" s="6">
-        <f t="shared" ref="G132:G163" si="4">IF(C132="","",C132-IF(ISNUMBER(F132),F132,0))</f>
-        <v>119</v>
+        <v/>
+      </c>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6" t="str">
+        <f>IF(C132="","",C132-IF(ISNUMBER(F132),F132,0))</f>
+        <v/>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A133" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B133" s="5">
-        <v>46082</v>
-      </c>
-      <c r="C133" s="6">
-        <v>119</v>
-      </c>
-      <c r="D133" s="7">
-        <v>177.6</v>
-      </c>
-      <c r="E133" s="7">
+        <v>46054</v>
+      </c>
+      <c r="C133" s="6"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7" t="str">
         <f>IF(OR(A133="",SUMIFS(C$4:C133,A$4:A133,A133)=0),"",SUMPRODUCT((A$4:A133=A133)*(C$4:C133)*(D$4:D133))/SUMIFS(C$4:C133,A$4:A133,A133))</f>
-        <v>177.6</v>
+        <v/>
       </c>
       <c r="F133" s="6"/>
-      <c r="G133" s="6">
-        <f t="shared" si="4"/>
-        <v>119</v>
+      <c r="G133" s="6" t="str">
+        <f>IF(C133="","",C133-IF(ISNUMBER(F133),F133,0))</f>
+        <v/>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A134" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B134" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C134" s="6">
-        <v>119</v>
-      </c>
+        <v>46082</v>
+      </c>
+      <c r="C134" s="6"/>
       <c r="D134" s="7">
-        <v>177.6</v>
-      </c>
-      <c r="E134" s="7">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="E134" s="7" t="str">
         <f>IF(OR(A134="",SUMIFS(C$4:C134,A$4:A134,A134)=0),"",SUMPRODUCT((A$4:A134=A134)*(C$4:C134)*(D$4:D134))/SUMIFS(C$4:C134,A$4:A134,A134))</f>
-        <v>177.59999999999997</v>
-      </c>
-      <c r="F134" s="6">
-        <v>49</v>
-      </c>
-      <c r="G134" s="6">
-        <f t="shared" si="4"/>
-        <v>70</v>
+        <v/>
+      </c>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6" t="str">
+        <f>IF(C134="","",C134-IF(ISNUMBER(F134),F134,0))</f>
+        <v/>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A135" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B135" s="5">
-        <v>46143</v>
-      </c>
-      <c r="C135" s="6">
-        <v>70</v>
-      </c>
+        <v>46113</v>
+      </c>
+      <c r="C135" s="6"/>
       <c r="D135" s="7">
-        <v>177.6</v>
-      </c>
-      <c r="E135" s="7">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="E135" s="7" t="str">
         <f>IF(OR(A135="",SUMIFS(C$4:C135,A$4:A135,A135)=0),"",SUMPRODUCT((A$4:A135=A135)*(C$4:C135)*(D$4:D135))/SUMIFS(C$4:C135,A$4:A135,A135))</f>
-        <v>177.6</v>
+        <v/>
       </c>
       <c r="F135" s="6"/>
-      <c r="G135" s="6">
-        <f t="shared" si="4"/>
-        <v>70</v>
+      <c r="G135" s="6" t="str">
+        <f>IF(C135="","",C135-IF(ISNUMBER(F135),F135,0))</f>
+        <v/>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A136" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B136" s="5">
-        <v>46174</v>
-      </c>
-      <c r="C136" s="6">
-        <v>70</v>
-      </c>
+        <v>46143</v>
+      </c>
+      <c r="C136" s="6"/>
       <c r="D136" s="7">
-        <v>177.6</v>
-      </c>
-      <c r="E136" s="7">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="E136" s="7" t="str">
         <f>IF(OR(A136="",SUMIFS(C$4:C136,A$4:A136,A136)=0),"",SUMPRODUCT((A$4:A136=A136)*(C$4:C136)*(D$4:D136))/SUMIFS(C$4:C136,A$4:A136,A136))</f>
-        <v>177.6</v>
-      </c>
-      <c r="F136" s="6">
-        <v>15</v>
-      </c>
-      <c r="G136" s="6">
-        <f t="shared" si="4"/>
-        <v>55</v>
+        <v/>
+      </c>
+      <c r="F136" s="6"/>
+      <c r="G136" s="6" t="str">
+        <f>IF(C136="","",C136-IF(ISNUMBER(F136),F136,0))</f>
+        <v/>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A137" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B137" s="5">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="C137" s="6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="D137" s="7">
-        <v>177.6</v>
+        <v>93.1</v>
       </c>
       <c r="E137" s="7">
         <f>IF(OR(A137="",SUMIFS(C$4:C137,A$4:A137,A137)=0),"",SUMPRODUCT((A$4:A137=A137)*(C$4:C137)*(D$4:D137))/SUMIFS(C$4:C137,A$4:A137,A137))</f>
-        <v>177.6</v>
+        <v>93.1</v>
       </c>
       <c r="F137" s="6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G137" s="6">
-        <f t="shared" si="4"/>
-        <v>9</v>
+        <f>IF(C137="","",C137-IF(ISNUMBER(F137),F137,0))</f>
+        <v>945</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A138" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B138" s="5">
-        <v>46235</v>
+        <v>46174</v>
       </c>
       <c r="C138" s="6">
-        <v>209</v>
+        <v>445</v>
       </c>
       <c r="D138" s="7">
-        <v>200.58</v>
+        <v>93.1</v>
       </c>
       <c r="E138" s="7">
         <f>IF(OR(A138="",SUMIFS(C$4:C138,A$4:A138,A138)=0),"",SUMPRODUCT((A$4:A138=A138)*(C$4:C138)*(D$4:D138))/SUMIFS(C$4:C138,A$4:A138,A138))</f>
-        <v>183.35188023952097</v>
+        <v>93.1</v>
       </c>
       <c r="F138" s="6">
-        <v>76</v>
+        <v>445</v>
       </c>
       <c r="G138" s="6">
-        <f t="shared" si="4"/>
-        <v>133</v>
+        <f>IF(C138="","",C138-IF(ISNUMBER(F138),F138,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A139" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B139" s="5">
-        <v>46266</v>
+        <v>46174</v>
       </c>
       <c r="C139" s="6">
-        <v>133</v>
+        <v>500</v>
       </c>
       <c r="D139" s="7">
-        <v>200.58</v>
+        <v>96.3</v>
       </c>
       <c r="E139" s="7">
         <f>IF(OR(A139="",SUMIFS(C$4:C139,A$4:A139,A139)=0),"",SUMPRODUCT((A$4:A139=A139)*(C$4:C139)*(D$4:D139))/SUMIFS(C$4:C139,A$4:A139,A139))</f>
-        <v>185.71896694214877</v>
+        <v>93.922622107969147</v>
       </c>
       <c r="F139" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G139" s="6">
-        <f t="shared" si="4"/>
-        <v>73</v>
+        <f>IF(C139="","",C139-IF(ISNUMBER(F139),F139,0))</f>
+        <v>439</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A140" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B140" s="5">
-        <v>46296</v>
+        <v>46204</v>
       </c>
       <c r="C140" s="6">
-        <v>73</v>
+        <v>439</v>
       </c>
       <c r="D140" s="7">
-        <v>200.58</v>
+        <v>94.79</v>
       </c>
       <c r="E140" s="7">
         <f>IF(OR(A140="",SUMIFS(C$4:C140,A$4:A140,A140)=0),"",SUMPRODUCT((A$4:A140=A140)*(C$4:C140)*(D$4:D140))/SUMIFS(C$4:C140,A$4:A140,A140))</f>
-        <v>186.76109510086457</v>
+        <v>94.082344798657715</v>
       </c>
       <c r="F140" s="6">
-        <v>50</v>
+        <v>434</v>
       </c>
       <c r="G140" s="6">
-        <f t="shared" si="4"/>
-        <v>23</v>
+        <f>IF(C140="","",C140-IF(ISNUMBER(F140),F140,0))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A141" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B141" s="5">
-        <v>46023</v>
+        <v>46235</v>
       </c>
       <c r="C141" s="6">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="D141" s="7">
-        <v>182.6</v>
+        <v>94.79</v>
       </c>
       <c r="E141" s="7">
         <f>IF(OR(A141="",SUMIFS(C$4:C141,A$4:A141,A141)=0),"",SUMPRODUCT((A$4:A141=A141)*(C$4:C141)*(D$4:D141))/SUMIFS(C$4:C141,A$4:A141,A141))</f>
-        <v>186.0904915390814</v>
-      </c>
-      <c r="F141" s="6">
-        <v>61</v>
-      </c>
+        <v>94.083825868564261</v>
+      </c>
+      <c r="F141" s="6"/>
       <c r="G141" s="6">
-        <f t="shared" si="4"/>
-        <v>139</v>
+        <f>IF(C141="","",C141-IF(ISNUMBER(F141),F141,0))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A142" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B142" s="5">
-        <v>46054</v>
-      </c>
-      <c r="C142" s="6"/>
-      <c r="D142" s="7"/>
+        <v>46266</v>
+      </c>
+      <c r="C142" s="6">
+        <v>5</v>
+      </c>
+      <c r="D142" s="7">
+        <v>94.79</v>
+      </c>
       <c r="E142" s="7">
         <f>IF(OR(A142="",SUMIFS(C$4:C142,A$4:A142,A142)=0),"",SUMPRODUCT((A$4:A142=A142)*(C$4:C142)*(D$4:D142))/SUMIFS(C$4:C142,A$4:A142,A142))</f>
-        <v>186.0904915390814</v>
-      </c>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <v>94.085300751879714</v>
+      </c>
+      <c r="F142" s="6">
+        <v>310</v>
+      </c>
+      <c r="G142" s="6">
+        <f>IF(C142="","",C142-IF(ISNUMBER(F142),F142,0))</f>
+        <v>-305</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A143" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B143" s="5">
-        <v>46204</v>
+        <v>46296</v>
       </c>
       <c r="C143" s="6">
-        <v>200</v>
+        <v>-305</v>
       </c>
       <c r="D143" s="7">
-        <v>206.9</v>
+        <v>94.79</v>
       </c>
       <c r="E143" s="7">
         <f>IF(OR(A143="",SUMIFS(C$4:C143,A$4:A143,A143)=0),"",SUMPRODUCT((A$4:A143=A143)*(C$4:C143)*(D$4:D143))/SUMIFS(C$4:C143,A$4:A143,A143))</f>
-        <v>188.97869535045112</v>
-      </c>
-      <c r="F143" s="6"/>
+        <v>93.982412637625657</v>
+      </c>
+      <c r="F143" s="6">
+        <v>150</v>
+      </c>
       <c r="G143" s="6">
-        <f t="shared" si="4"/>
-        <v>200</v>
+        <f>IF(C143="","",C143-IF(ISNUMBER(F143),F143,0))</f>
+        <v>-455</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.4">
@@ -4082,7 +4078,7 @@
       </c>
       <c r="F144" s="6"/>
       <c r="G144" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="G132:G163" si="0">IF(C144="","",C144-IF(ISNUMBER(F144),F144,0))</f>
         <v/>
       </c>
     </row>
@@ -4097,7 +4093,7 @@
       </c>
       <c r="F145" s="6"/>
       <c r="G145" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4112,7 +4108,7 @@
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4127,7 +4123,7 @@
       </c>
       <c r="F147" s="6"/>
       <c r="G147" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4142,7 +4138,7 @@
       </c>
       <c r="F148" s="6"/>
       <c r="G148" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4157,7 +4153,7 @@
       </c>
       <c r="F149" s="6"/>
       <c r="G149" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4172,7 +4168,7 @@
       </c>
       <c r="F150" s="6"/>
       <c r="G150" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4187,7 +4183,7 @@
       </c>
       <c r="F151" s="6"/>
       <c r="G151" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4202,7 +4198,7 @@
       </c>
       <c r="F152" s="6"/>
       <c r="G152" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4217,7 +4213,7 @@
       </c>
       <c r="F153" s="6"/>
       <c r="G153" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4232,7 +4228,7 @@
       </c>
       <c r="F154" s="6"/>
       <c r="G154" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4247,7 +4243,7 @@
       </c>
       <c r="F155" s="6"/>
       <c r="G155" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4262,7 +4258,7 @@
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4277,7 +4273,7 @@
       </c>
       <c r="F157" s="6"/>
       <c r="G157" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4292,7 +4288,7 @@
       </c>
       <c r="F158" s="6"/>
       <c r="G158" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4307,7 +4303,7 @@
       </c>
       <c r="F159" s="6"/>
       <c r="G159" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4322,7 +4318,7 @@
       </c>
       <c r="F160" s="6"/>
       <c r="G160" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4337,7 +4333,7 @@
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4352,7 +4348,7 @@
       </c>
       <c r="F162" s="6"/>
       <c r="G162" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4367,7 +4363,7 @@
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4382,7 +4378,7 @@
       </c>
       <c r="F164" s="6"/>
       <c r="G164" s="6" t="str">
-        <f t="shared" ref="G164:G195" si="5">IF(C164="","",C164-IF(ISNUMBER(F164),F164,0))</f>
+        <f t="shared" ref="G164:G195" si="1">IF(C164="","",C164-IF(ISNUMBER(F164),F164,0))</f>
         <v/>
       </c>
     </row>
@@ -4397,7 +4393,7 @@
       </c>
       <c r="F165" s="6"/>
       <c r="G165" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4412,7 +4408,7 @@
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4427,7 +4423,7 @@
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4442,7 +4438,7 @@
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4457,7 +4453,7 @@
       </c>
       <c r="F169" s="6"/>
       <c r="G169" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4472,7 +4468,7 @@
       </c>
       <c r="F170" s="6"/>
       <c r="G170" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4487,7 +4483,7 @@
       </c>
       <c r="F171" s="6"/>
       <c r="G171" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4502,7 +4498,7 @@
       </c>
       <c r="F172" s="6"/>
       <c r="G172" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4517,7 +4513,7 @@
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4532,11 +4528,11 @@
       </c>
       <c r="D174" s="10">
         <f>IF(SUM(C4:C173)=0,0,SUMPRODUCT(C4:C173,D4:D173)/SUM(C4:C173))</f>
-        <v>102.21223141531901</v>
+        <v>102.21223141531902</v>
       </c>
       <c r="E174" s="10">
         <f>AVERAGEIF(E4:E173,"&lt;&gt;0")</f>
-        <v>103.54768031412334</v>
+        <v>102.92481427162295</v>
       </c>
       <c r="F174" s="9">
         <f>SUM(F4:F173)</f>
@@ -4548,6 +4544,10 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A4:G143">
+    <sortCondition ref="A4:A143"/>
+    <sortCondition ref="B4:B143"/>
+  </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="7">
-        <v>149.4</v>
+        <v>149.9</v>
       </c>
       <c r="E4" s="7" t="str">
         <f>IF(OR(A4="",SUMIFS(C$4:C4,A$4:A4,A4)=0),"",SUMPRODUCT((A$4:A4=A4)*(C$4:C4)*(D$4:D4))/SUMIFS(C$4:C4,A$4:A4,A4))</f>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6" t="str">
-        <f t="shared" ref="G4:G41" si="0">IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
+        <f>IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
         <v/>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
         <v>37</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C5="","",C5-IF(ISNUMBER(F5),F5,0))</f>
         <v>47</v>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C6="","",C6-IF(ISNUMBER(F6),F6,0))</f>
         <v>250</v>
       </c>
     </row>
@@ -4681,24 +4681,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="5">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="C7" s="6">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="D7" s="7">
-        <v>215.12</v>
+        <v>227</v>
       </c>
       <c r="E7" s="7">
         <f>IF(OR(A7="",SUMIFS(C$4:C7,A$4:A7,A7)=0),"",SUMPRODUCT((A$4:A7=A7)*(C$4:C7)*(D$4:D7))/SUMIFS(C$4:C7,A$4:A7,A7))</f>
-        <v>211.32642745709828</v>
-      </c>
-      <c r="F7" s="6">
-        <v>10</v>
-      </c>
+        <v>216.20794701986756</v>
+      </c>
+      <c r="F7" s="6"/>
       <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>287</v>
+        <f>IF(C7="","",C7-IF(ISNUMBER(F7),F7,0))</f>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -4706,21 +4704,23 @@
         <v>12</v>
       </c>
       <c r="B8" s="5">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="C8" s="6">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D8" s="7">
         <v>215.12</v>
       </c>
       <c r="E8" s="7">
         <f>IF(OR(A8="",SUMIFS(C$4:C8,A$4:A8,A8)=0),"",SUMPRODUCT((A$4:A8=A8)*(C$4:C8)*(D$4:D8))/SUMIFS(C$4:C8,A$4:A8,A8))</f>
-        <v>212.49965517241378</v>
-      </c>
-      <c r="F8" s="6"/>
+        <v>215.84932297447278</v>
+      </c>
+      <c r="F8" s="6">
+        <v>10</v>
+      </c>
       <c r="G8" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C8="","",C8-IF(ISNUMBER(F8),F8,0))</f>
         <v>287</v>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="5">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="C9" s="6">
         <v>287</v>
@@ -4739,11 +4739,11 @@
       </c>
       <c r="E9" s="7">
         <f>IF(OR(A9="",SUMIFS(C$4:C9,A$4:A9,A9)=0),"",SUMPRODUCT((A$4:A9=A9)*(C$4:C9)*(D$4:D9))/SUMIFS(C$4:C9,A$4:A9,A9))</f>
-        <v>213.11861728395061</v>
+        <v>215.67313131313131</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C9="","",C9-IF(ISNUMBER(F9),F9,0))</f>
         <v>287</v>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="5">
-        <v>46327</v>
+        <v>46296</v>
       </c>
       <c r="C10" s="6">
         <v>287</v>
@@ -4762,11 +4762,11 @@
       </c>
       <c r="E10" s="7">
         <f>IF(OR(A10="",SUMIFS(C$4:C10,A$4:A10,A10)=0),"",SUMPRODUCT((A$4:A10=A10)*(C$4:C10)*(D$4:D10))/SUMIFS(C$4:C10,A$4:A10,A10))</f>
-        <v>213.50103861517977</v>
+        <v>215.56550508474575</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C10="","",C10-IF(ISNUMBER(F10),F10,0))</f>
         <v>287</v>
       </c>
     </row>
@@ -4775,13 +4775,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="5">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C11" s="6">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="D11" s="7">
-        <v>227</v>
+        <v>215.12</v>
       </c>
       <c r="E11" s="7">
         <f>IF(OR(A11="",SUMIFS(C$4:C11,A$4:A11,A11)=0),"",SUMPRODUCT((A$4:A11=A11)*(C$4:C11)*(D$4:D11))/SUMIFS(C$4:C11,A$4:A11,A11))</f>
@@ -4789,8 +4789,8 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6">
-        <f t="shared" si="0"/>
-        <v>260</v>
+        <f>IF(C11="","",C11-IF(ISNUMBER(F11),F11,0))</f>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G4:G41" si="0">IF(C12="","",C12-IF(ISNUMBER(F12),F12,0))</f>
         <v/>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="E42" s="10">
         <f>AVERAGEIF(E4:E41,"&lt;&gt;0")</f>
-        <v>203.34140588006139</v>
+        <v>205.17714414628639</v>
       </c>
       <c r="F42" s="9">
         <f>SUM(F4:F41)</f>
@@ -5270,6 +5270,10 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A4:G11">
+    <sortCondition ref="A4:A11"/>
+    <sortCondition ref="B4:B11"/>
+  </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -5348,7 +5352,7 @@
         <v>196</v>
       </c>
       <c r="G4" s="6">
-        <f t="shared" ref="G4:G35" si="0">IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
+        <f>IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
         <v>4</v>
       </c>
     </row>
@@ -5357,24 +5361,24 @@
         <v>14</v>
       </c>
       <c r="B5" s="5">
-        <v>46235</v>
+        <v>45931</v>
       </c>
       <c r="C5" s="6">
-        <v>4</v>
+        <v>413</v>
       </c>
       <c r="D5" s="7">
-        <v>85</v>
+        <v>187.96</v>
       </c>
       <c r="E5" s="7">
         <f>IF(OR(A5="",SUMIFS(C$4:C5,A$4:A5,A5)=0),"",SUMPRODUCT((A$4:A5=A5)*(C$4:C5)*(D$4:D5))/SUMIFS(C$4:C5,A$4:A5,A5))</f>
-        <v>85</v>
+        <v>154.36783034257749</v>
       </c>
       <c r="F5" s="6">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF(C5="","",C5-IF(ISNUMBER(F5),F5,0))</f>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
@@ -5382,23 +5386,23 @@
         <v>14</v>
       </c>
       <c r="B6" s="5">
-        <v>46266</v>
+        <v>45992</v>
       </c>
       <c r="C6" s="6">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="D6" s="7">
-        <v>92.4</v>
+        <v>97.27</v>
       </c>
       <c r="E6" s="7">
         <f>IF(OR(A6="",SUMIFS(C$4:C6,A$4:A6,A6)=0),"",SUMPRODUCT((A$4:A6=A6)*(C$4:C6)*(D$4:D6))/SUMIFS(C$4:C6,A$4:A6,A6))</f>
-        <v>87.726315789473674</v>
+        <v>137.08907849829353</v>
       </c>
       <c r="F6" s="6">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C6="","",C6-IF(ISNUMBER(F6),F6,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -5410,21 +5414,19 @@
         <v>45992</v>
       </c>
       <c r="C7" s="6">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="D7" s="7">
-        <v>97.27</v>
+        <v>115</v>
       </c>
       <c r="E7" s="7">
         <f>IF(OR(A7="",SUMIFS(C$4:C7,A$4:A7,A7)=0),"",SUMPRODUCT((A$4:A7=A7)*(C$4:C7)*(D$4:D7))/SUMIFS(C$4:C7,A$4:A7,A7))</f>
-        <v>92.036366723259761</v>
-      </c>
-      <c r="F7" s="6">
-        <v>266</v>
-      </c>
+        <v>131.46844783715014</v>
+      </c>
+      <c r="F7" s="6"/>
       <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF(C7="","",C7-IF(ISNUMBER(F7),F7,0))</f>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -5442,13 +5444,13 @@
       </c>
       <c r="E8" s="7">
         <f>IF(OR(A8="",SUMIFS(C$4:C8,A$4:A8,A8)=0),"",SUMPRODUCT((A$4:A8=A8)*(C$4:C8)*(D$4:D8))/SUMIFS(C$4:C8,A$4:A8,A8))</f>
-        <v>96.974600674915635</v>
+        <v>126.43833671399595</v>
       </c>
       <c r="F8" s="6">
         <v>56</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C8="","",C8-IF(ISNUMBER(F8),F8,0))</f>
         <v>244</v>
       </c>
     </row>
@@ -5467,13 +5469,13 @@
       </c>
       <c r="E9" s="7">
         <f>IF(OR(A9="",SUMIFS(C$4:C9,A$4:A9,A9)=0),"",SUMPRODUCT((A$4:A9=A9)*(C$4:C9)*(D$4:D9))/SUMIFS(C$4:C9,A$4:A9,A9))</f>
-        <v>99.062577228596638</v>
+        <v>123.63887405687755</v>
       </c>
       <c r="F9" s="6">
         <v>68</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C9="","",C9-IF(ISNUMBER(F9),F9,0))</f>
         <v>176</v>
       </c>
     </row>
@@ -5492,11 +5494,11 @@
       </c>
       <c r="E10" s="7">
         <f>IF(OR(A10="",SUMIFS(C$4:C10,A$4:A10,A10)=0),"",SUMPRODUCT((A$4:A10=A10)*(C$4:C10)*(D$4:D10))/SUMIFS(C$4:C10,A$4:A10,A10))</f>
-        <v>100.08542398777692</v>
+        <v>122.0661927330174</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C10="","",C10-IF(ISNUMBER(F10),F10,0))</f>
         <v>176</v>
       </c>
     </row>
@@ -5515,13 +5517,13 @@
       </c>
       <c r="E11" s="7">
         <f>IF(OR(A11="",SUMIFS(C$4:C11,A$4:A11,A11)=0),"",SUMPRODUCT((A$4:A11=A11)*(C$4:C11)*(D$4:D11))/SUMIFS(C$4:C11,A$4:A11,A11))</f>
-        <v>100.86581818181817</v>
+        <v>120.76029879518074</v>
       </c>
       <c r="F11" s="6">
         <v>161</v>
       </c>
       <c r="G11" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C11="","",C11-IF(ISNUMBER(F11),F11,0))</f>
         <v>15</v>
       </c>
     </row>
@@ -5540,13 +5542,13 @@
       </c>
       <c r="E12" s="7">
         <f>IF(OR(A12="",SUMIFS(C$4:C12,A$4:A12,A12)=0),"",SUMPRODUCT((A$4:A12=A12)*(C$4:C12)*(D$4:D12))/SUMIFS(C$4:C12,A$4:A12,A12))</f>
-        <v>100.92385999999999</v>
+        <v>120.65917224880384</v>
       </c>
       <c r="F12" s="6">
         <v>15</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C12="","",C12-IF(ISNUMBER(F12),F12,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -5555,24 +5557,24 @@
         <v>14</v>
       </c>
       <c r="B13" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C13" s="6">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="D13" s="7">
-        <v>174.46</v>
+        <v>177</v>
       </c>
       <c r="E13" s="7">
         <f>IF(OR(A13="",SUMIFS(C$4:C13,A$4:A13,A13)=0),"",SUMPRODUCT((A$4:A13=A13)*(C$4:C13)*(D$4:D13))/SUMIFS(C$4:C13,A$4:A13,A13))</f>
-        <v>111.42902285714284</v>
+        <v>129.70990763052211</v>
       </c>
       <c r="F13" s="6">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" si="0"/>
-        <v>178</v>
+        <f>IF(C13="","",C13-IF(ISNUMBER(F13),F13,0))</f>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -5580,24 +5582,24 @@
         <v>14</v>
       </c>
       <c r="B14" s="5">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="C14" s="6">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="D14" s="7">
         <v>174.46</v>
       </c>
       <c r="E14" s="7">
         <f>IF(OR(A14="",SUMIFS(C$4:C14,A$4:A14,A14)=0),"",SUMPRODUCT((A$4:A14=A14)*(C$4:C14)*(D$4:D14))/SUMIFS(C$4:C14,A$4:A14,A14))</f>
-        <v>117.24827282157675</v>
+        <v>133.79294525547448</v>
       </c>
       <c r="F14" s="6">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="0"/>
-        <v>168</v>
+        <f>IF(C14="","",C14-IF(ISNUMBER(F14),F14,0))</f>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
@@ -5605,24 +5607,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="5">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="C15" s="6">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D15" s="7">
         <v>174.46</v>
       </c>
       <c r="E15" s="7">
         <f>IF(OR(A15="",SUMIFS(C$4:C15,A$4:A15,A15)=0),"",SUMPRODUCT((A$4:A15=A15)*(C$4:C15)*(D$4:D15))/SUMIFS(C$4:C15,A$4:A15,A15))</f>
-        <v>121.83394561068701</v>
+        <v>136.27366346812886</v>
       </c>
       <c r="F15" s="6">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>IF(C15="","",C15-IF(ISNUMBER(F15),F15,0))</f>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
@@ -5630,22 +5632,24 @@
         <v>14</v>
       </c>
       <c r="B16" s="5">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="C16" s="6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D16" s="7">
-        <v>174.46</v>
+        <v>85</v>
       </c>
       <c r="E16" s="7">
         <f>IF(OR(A16="",SUMIFS(C$4:C16,A$4:A16,A16)=0),"",SUMPRODUCT((A$4:A16=A16)*(C$4:C16)*(D$4:D16))/SUMIFS(C$4:C16,A$4:A16,A16))</f>
-        <v>122.15833570412518</v>
-      </c>
-      <c r="F16" s="6"/>
+        <v>136.20347364818619</v>
+      </c>
+      <c r="F16" s="6">
+        <v>4</v>
+      </c>
       <c r="G16" s="6">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>IF(C16="","",C16-IF(ISNUMBER(F16),F16,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -5653,24 +5657,24 @@
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>45931</v>
+        <v>46235</v>
       </c>
       <c r="C17" s="6">
-        <v>413</v>
+        <v>168</v>
       </c>
       <c r="D17" s="7">
-        <v>187.96</v>
+        <v>174.46</v>
       </c>
       <c r="E17" s="7">
         <f>IF(OR(A17="",SUMIFS(C$4:C17,A$4:A17,A17)=0),"",SUMPRODUCT((A$4:A17=A17)*(C$4:C17)*(D$4:D17))/SUMIFS(C$4:C17,A$4:A17,A17))</f>
-        <v>132.93394528152263</v>
+        <v>138.28344012944987</v>
       </c>
       <c r="F17" s="6">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="0"/>
-        <v>353</v>
+        <f>IF(C17="","",C17-IF(ISNUMBER(F17),F17,0))</f>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -5688,13 +5692,13 @@
       </c>
       <c r="E18" s="7">
         <f>IF(OR(A18="",SUMIFS(C$4:C18,A$4:A18,A18)=0),"",SUMPRODUCT((A$4:A18=A18)*(C$4:C18)*(D$4:D18))/SUMIFS(C$4:C18,A$4:A18,A18))</f>
-        <v>128.63551027639974</v>
+        <v>134.23180825958704</v>
       </c>
       <c r="F18" s="6">
         <v>181</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C18="","",C18-IF(ISNUMBER(F18),F18,0))</f>
         <v>119</v>
       </c>
     </row>
@@ -5706,21 +5710,21 @@
         <v>46266</v>
       </c>
       <c r="C19" s="6">
-        <v>300</v>
+        <v>119</v>
       </c>
       <c r="D19" s="7">
-        <v>99.2</v>
+        <v>92.4</v>
       </c>
       <c r="E19" s="7">
         <f>IF(OR(A19="",SUMIFS(C$4:C19,A$4:A19,A19)=0),"",SUMPRODUCT((A$4:A19=A19)*(C$4:C19)*(D$4:D19))/SUMIFS(C$4:C19,A$4:A19,A19))</f>
-        <v>125.80698590647022</v>
+        <v>132.81317469364492</v>
       </c>
       <c r="F19" s="6">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="0"/>
-        <v>266</v>
+        <f>IF(C19="","",C19-IF(ISNUMBER(F19),F19,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -5728,22 +5732,22 @@
         <v>14</v>
       </c>
       <c r="B20" s="5">
-        <v>45992</v>
+        <v>46266</v>
       </c>
       <c r="C20" s="6">
-        <v>300</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7">
-        <v>115</v>
+        <v>174.46</v>
       </c>
       <c r="E20" s="7">
         <f>IF(OR(A20="",SUMIFS(C$4:C20,A$4:A20,A20)=0),"",SUMPRODUCT((A$4:A20=A20)*(C$4:C20)*(D$4:D20))/SUMIFS(C$4:C20,A$4:A20,A20))</f>
-        <v>124.85955873758037</v>
+        <v>132.96689664963091</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <f>IF(C20="","",C20-IF(ISNUMBER(F20),F20,0))</f>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
@@ -5751,24 +5755,24 @@
         <v>14</v>
       </c>
       <c r="B21" s="5">
-        <v>46143</v>
+        <v>46266</v>
       </c>
       <c r="C21" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D21" s="7">
-        <v>177</v>
+        <v>99.2</v>
       </c>
       <c r="E21" s="7">
         <f>IF(OR(A21="",SUMIFS(C$4:C21,A$4:A21,A21)=0),"",SUMPRODUCT((A$4:A21=A21)*(C$4:C21)*(D$4:D21))/SUMIFS(C$4:C21,A$4:A21,A21))</f>
         <v>130.31643380429097</v>
       </c>
       <c r="F21" s="6">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="0"/>
-        <v>250</v>
+        <f>IF(C21="","",C21-IF(ISNUMBER(F21),F21,0))</f>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
@@ -5790,7 +5794,7 @@
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C22="","",C22-IF(ISNUMBER(F22),F22,0))</f>
         <v>400</v>
       </c>
     </row>
@@ -5805,7 +5809,7 @@
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G4:G35" si="0">IF(C23="","",C23-IF(ISNUMBER(F23),F23,0))</f>
         <v/>
       </c>
     </row>
@@ -6259,7 +6263,7 @@
       </c>
       <c r="E53" s="10">
         <f>AVERAGEIF(E4:E52,"&lt;&gt;0")</f>
-        <v>110.45875529779548</v>
+        <v>129.57365009669948</v>
       </c>
       <c r="F53" s="9">
         <f>SUM(F4:F52)</f>
@@ -6271,6 +6275,10 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A4:G22">
+    <sortCondition ref="A4:A22"/>
+    <sortCondition ref="B4:B22"/>
+  </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -6330,298 +6338,298 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="5">
         <v>45992</v>
       </c>
       <c r="C4" s="6">
-        <v>1749</v>
+        <v>968</v>
       </c>
       <c r="D4" s="7">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="E4" s="7">
         <f>IF(OR(A4="",SUMIFS(C$4:C4,A$4:A4,A4)=0),"",SUMPRODUCT((A$4:A4=A4)*(C$4:C4)*(D$4:D4))/SUMIFS(C$4:C4,A$4:A4,A4))</f>
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="F4" s="6">
-        <v>634</v>
+        <v>240</v>
       </c>
       <c r="G4" s="6">
-        <f t="shared" ref="G4:G35" si="0">IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
-        <v>1115</v>
+        <f>IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5">
         <v>46023</v>
       </c>
       <c r="C5" s="6">
-        <v>1115</v>
+        <v>728</v>
       </c>
       <c r="D5" s="7">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="E5" s="7">
         <f>IF(OR(A5="",SUMIFS(C$4:C5,A$4:A5,A5)=0),"",SUMPRODUCT((A$4:A5=A5)*(C$4:C5)*(D$4:D5))/SUMIFS(C$4:C5,A$4:A5,A5))</f>
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="F5" s="6">
-        <v>954</v>
+        <v>366</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="0"/>
-        <v>161</v>
+        <f>IF(C5="","",C5-IF(ISNUMBER(F5),F5,0))</f>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5">
         <v>46054</v>
       </c>
       <c r="C6" s="6">
-        <v>161</v>
+        <v>362</v>
       </c>
       <c r="D6" s="7">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="E6" s="7">
         <f>IF(OR(A6="",SUMIFS(C$4:C6,A$4:A6,A6)=0),"",SUMPRODUCT((A$4:A6=A6)*(C$4:C6)*(D$4:D6))/SUMIFS(C$4:C6,A$4:A6,A6))</f>
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="F6" s="6">
-        <v>350</v>
+        <v>165</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="0"/>
-        <v>-189</v>
+        <f>IF(C6="","",C6-IF(ISNUMBER(F6),F6,0))</f>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="5">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="C7" s="6">
-        <v>1580</v>
+        <v>1000</v>
       </c>
       <c r="D7" s="7">
-        <v>47.43</v>
+        <v>27</v>
       </c>
       <c r="E7" s="7">
         <f>IF(OR(A7="",SUMIFS(C$4:C7,A$4:A7,A7)=0),"",SUMPRODUCT((A$4:A7=A7)*(C$4:C7)*(D$4:D7))/SUMIFS(C$4:C7,A$4:A7,A7))</f>
-        <v>26.455352877307273</v>
+        <v>15.89568345323741</v>
       </c>
       <c r="F7" s="6">
-        <v>1048</v>
+        <v>104</v>
       </c>
       <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>532</v>
+        <f>IF(C7="","",C7-IF(ISNUMBER(F7),F7,0))</f>
+        <v>896</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C8" s="6">
-        <v>2032</v>
+        <v>1093</v>
       </c>
       <c r="D8" s="7">
-        <v>53.39</v>
+        <v>22.61</v>
       </c>
       <c r="E8" s="7">
         <f>IF(OR(A8="",SUMIFS(C$4:C8,A$4:A8,A8)=0),"",SUMPRODUCT((A$4:A8=A8)*(C$4:C8)*(D$4:D8))/SUMIFS(C$4:C8,A$4:A8,A8))</f>
-        <v>34.701729697152331</v>
+        <v>17.663630450493855</v>
       </c>
       <c r="F8" s="6">
-        <v>869</v>
+        <v>268</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="0"/>
-        <v>1163</v>
+        <f>IF(C8="","",C8-IF(ISNUMBER(F8),F8,0))</f>
+        <v>825</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C9" s="6">
-        <v>3163</v>
+        <v>825</v>
       </c>
       <c r="D9" s="7">
-        <v>60.64</v>
+        <v>22.61</v>
       </c>
       <c r="E9" s="7">
         <f>IF(OR(A9="",SUMIFS(C$4:C9,A$4:A9,A9)=0),"",SUMPRODUCT((A$4:A9=A9)*(C$4:C9)*(D$4:D9))/SUMIFS(C$4:C9,A$4:A9,A9))</f>
-        <v>43.073438775510205</v>
+        <v>18.483717845659164</v>
       </c>
       <c r="F9" s="6">
-        <v>623</v>
+        <v>280</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="0"/>
-        <v>2540</v>
+        <f>IF(C9="","",C9-IF(ISNUMBER(F9),F9,0))</f>
+        <v>545</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C10" s="6">
-        <v>4540</v>
+        <v>545</v>
       </c>
       <c r="D10" s="7">
-        <v>63.1</v>
+        <v>22.61</v>
       </c>
       <c r="E10" s="7">
         <f>IF(OR(A10="",SUMIFS(C$4:C10,A$4:A10,A10)=0),"",SUMPRODUCT((A$4:A10=A10)*(C$4:C10)*(D$4:D10))/SUMIFS(C$4:C10,A$4:A10,A10))</f>
-        <v>49.41378661087866</v>
+        <v>18.891039666727043</v>
       </c>
       <c r="F10" s="6">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="G10" s="6">
-        <f t="shared" si="0"/>
-        <v>4271</v>
+        <f>IF(C10="","",C10-IF(ISNUMBER(F10),F10,0))</f>
+        <v>316</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="C11" s="6">
-        <v>4271</v>
+        <v>1500</v>
       </c>
       <c r="D11" s="7">
-        <v>63.1</v>
+        <v>38</v>
       </c>
       <c r="E11" s="7">
         <f>IF(OR(A11="",SUMIFS(C$4:C11,A$4:A11,A11)=0),"",SUMPRODUCT((A$4:A11=A11)*(C$4:C11)*(D$4:D11))/SUMIFS(C$4:C11,A$4:A11,A11))</f>
-        <v>52.554607490193973</v>
-      </c>
-      <c r="F11" s="6">
-        <v>282</v>
-      </c>
+        <v>22.973569292123628</v>
+      </c>
+      <c r="F11" s="6"/>
       <c r="G11" s="6">
-        <f t="shared" si="0"/>
-        <v>3989</v>
+        <f>IF(C11="","",C11-IF(ISNUMBER(F11),F11,0))</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5">
-        <v>46235</v>
+        <v>46174</v>
       </c>
       <c r="C12" s="6">
-        <v>3989</v>
+        <v>1816</v>
       </c>
       <c r="D12" s="7">
-        <v>63.1</v>
+        <v>33.9</v>
       </c>
       <c r="E12" s="7">
         <f>IF(OR(A12="",SUMIFS(C$4:C12,A$4:A12,A12)=0),"",SUMPRODUCT((A$4:A12=A12)*(C$4:C12)*(D$4:D12))/SUMIFS(C$4:C12,A$4:A12,A12))</f>
-        <v>54.415915929203535</v>
+        <v>25.218946475048092</v>
       </c>
       <c r="F12" s="6">
-        <v>435</v>
+        <v>531</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" si="0"/>
-        <v>3554</v>
+        <f>IF(C12="","",C12-IF(ISNUMBER(F12),F12,0))</f>
+        <v>1285</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="5">
-        <v>46266</v>
+        <v>46204</v>
       </c>
       <c r="C13" s="6">
-        <v>3554</v>
+        <v>1041</v>
       </c>
       <c r="D13" s="7">
-        <v>63.1</v>
+        <v>33.9</v>
       </c>
       <c r="E13" s="7">
         <f>IF(OR(A13="",SUMIFS(C$4:C13,A$4:A13,A13)=0),"",SUMPRODUCT((A$4:A13=A13)*(C$4:C13)*(D$4:D13))/SUMIFS(C$4:C13,A$4:A13,A13))</f>
-        <v>55.595973847212662</v>
-      </c>
-      <c r="F13" s="6"/>
+        <v>26.133805426199633</v>
+      </c>
+      <c r="F13" s="6">
+        <v>245</v>
+      </c>
       <c r="G13" s="6">
-        <f t="shared" si="0"/>
-        <v>3554</v>
+        <f>IF(C13="","",C13-IF(ISNUMBER(F13),F13,0))</f>
+        <v>796</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="5">
-        <v>46054</v>
+        <v>46235</v>
       </c>
       <c r="C14" s="6">
-        <v>2000</v>
+        <v>796</v>
       </c>
       <c r="D14" s="7">
-        <v>50</v>
+        <v>33.9</v>
       </c>
       <c r="E14" s="7">
         <f>IF(OR(A14="",SUMIFS(C$4:C14,A$4:A14,A14)=0),"",SUMPRODUCT((A$4:A14=A14)*(C$4:C14)*(D$4:D14))/SUMIFS(C$4:C14,A$4:A14,A14))</f>
-        <v>55.198447822689488</v>
+        <v>26.712959527824619</v>
       </c>
       <c r="F14" s="6">
-        <v>231</v>
+        <v>455</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="0"/>
-        <v>1769</v>
+        <f>IF(C14="","",C14-IF(ISNUMBER(F14),F14,0))</f>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="5">
-        <v>46082</v>
+        <v>46266</v>
       </c>
       <c r="C15" s="6">
-        <v>500</v>
+        <v>341</v>
       </c>
       <c r="D15" s="7">
-        <v>63</v>
+        <v>33.9</v>
       </c>
       <c r="E15" s="7">
         <f>IF(OR(A15="",SUMIFS(C$4:C15,A$4:A15,A15)=0),"",SUMPRODUCT((A$4:A15=A15)*(C$4:C15)*(D$4:D15))/SUMIFS(C$4:C15,A$4:A15,A15))</f>
-        <v>55.334581559293639</v>
+        <v>26.935454380390379</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <f>IF(C15="","",C15-IF(ISNUMBER(F15),F15,0))</f>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
@@ -6629,22 +6637,24 @@
         <v>16</v>
       </c>
       <c r="B16" s="5">
-        <v>46113</v>
+        <v>45992</v>
       </c>
       <c r="C16" s="6">
-        <v>2000</v>
+        <v>1749</v>
       </c>
       <c r="D16" s="7">
-        <v>68</v>
+        <v>15.5</v>
       </c>
       <c r="E16" s="7">
         <f>IF(OR(A16="",SUMIFS(C$4:C16,A$4:A16,A16)=0),"",SUMPRODUCT((A$4:A16=A16)*(C$4:C16)*(D$4:D16))/SUMIFS(C$4:C16,A$4:A16,A16))</f>
-        <v>56.160928426958954</v>
-      </c>
-      <c r="F16" s="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="F16" s="6">
+        <v>634</v>
+      </c>
       <c r="G16" s="6">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <f>IF(C16="","",C16-IF(ISNUMBER(F16),F16,0))</f>
+        <v>1115</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -6652,22 +6662,24 @@
         <v>16</v>
       </c>
       <c r="B17" s="5">
-        <v>46143</v>
+        <v>46023</v>
       </c>
       <c r="C17" s="6">
-        <v>2000</v>
+        <v>1115</v>
       </c>
       <c r="D17" s="7">
-        <v>67</v>
+        <v>15.5</v>
       </c>
       <c r="E17" s="7">
         <f>IF(OR(A17="",SUMIFS(C$4:C17,A$4:A17,A17)=0),"",SUMPRODUCT((A$4:A17=A17)*(C$4:C17)*(D$4:D17))/SUMIFS(C$4:C17,A$4:A17,A17))</f>
-        <v>56.824802474428857</v>
-      </c>
-      <c r="F17" s="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="F17" s="6">
+        <v>954</v>
+      </c>
       <c r="G17" s="6">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <f>IF(C17="","",C17-IF(ISNUMBER(F17),F17,0))</f>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -6675,318 +6687,314 @@
         <v>16</v>
       </c>
       <c r="B18" s="5">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="C18" s="6">
-        <v>1000</v>
+        <v>161</v>
       </c>
       <c r="D18" s="7">
-        <v>58</v>
+        <v>15.5</v>
       </c>
       <c r="E18" s="7">
         <f>IF(OR(A18="",SUMIFS(C$4:C18,A$4:A18,A18)=0),"",SUMPRODUCT((A$4:A18=A18)*(C$4:C18)*(D$4:D18))/SUMIFS(C$4:C18,A$4:A18,A18))</f>
-        <v>56.859722469840136</v>
-      </c>
-      <c r="F18" s="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="F18" s="6">
+        <v>350</v>
+      </c>
       <c r="G18" s="6">
-        <f t="shared" si="0"/>
-        <v>1000</v>
+        <f>IF(C18="","",C18-IF(ISNUMBER(F18),F18,0))</f>
+        <v>-189</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="5">
-        <v>45992</v>
+        <v>46054</v>
       </c>
       <c r="C19" s="6">
-        <v>968</v>
+        <v>2000</v>
       </c>
       <c r="D19" s="7">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="E19" s="7">
         <f>IF(OR(A19="",SUMIFS(C$4:C19,A$4:A19,A19)=0),"",SUMPRODUCT((A$4:A19=A19)*(C$4:C19)*(D$4:D19))/SUMIFS(C$4:C19,A$4:A19,A19))</f>
-        <v>10.5</v>
+        <v>29.231343283582088</v>
       </c>
       <c r="F19" s="6">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="0"/>
-        <v>728</v>
+        <f>IF(C19="","",C19-IF(ISNUMBER(F19),F19,0))</f>
+        <v>1769</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46023</v>
+        <v>46082</v>
       </c>
       <c r="C20" s="6">
-        <v>728</v>
+        <v>1580</v>
       </c>
       <c r="D20" s="7">
-        <v>10.5</v>
+        <v>47.43</v>
       </c>
       <c r="E20" s="7">
         <f>IF(OR(A20="",SUMIFS(C$4:C20,A$4:A20,A20)=0),"",SUMPRODUCT((A$4:A20=A20)*(C$4:C20)*(D$4:D20))/SUMIFS(C$4:C20,A$4:A20,A20))</f>
-        <v>10.5</v>
+        <v>33.584693414080242</v>
       </c>
       <c r="F20" s="6">
-        <v>366</v>
+        <v>1048</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="0"/>
-        <v>362</v>
+        <f>IF(C20="","",C20-IF(ISNUMBER(F20),F20,0))</f>
+        <v>532</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="5">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C21" s="6">
-        <v>362</v>
+        <v>500</v>
       </c>
       <c r="D21" s="7">
-        <v>10.5</v>
+        <v>63</v>
       </c>
       <c r="E21" s="7">
         <f>IF(OR(A21="",SUMIFS(C$4:C21,A$4:A21,A21)=0),"",SUMPRODUCT((A$4:A21=A21)*(C$4:C21)*(D$4:D21))/SUMIFS(C$4:C21,A$4:A21,A21))</f>
-        <v>10.5</v>
-      </c>
-      <c r="F21" s="6">
-        <v>165</v>
-      </c>
+        <v>35.654736101337086</v>
+      </c>
+      <c r="F21" s="6"/>
       <c r="G21" s="6">
-        <f t="shared" si="0"/>
-        <v>197</v>
+        <f>IF(C21="","",C21-IF(ISNUMBER(F21),F21,0))</f>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="5">
         <v>46082</v>
       </c>
       <c r="C22" s="6">
-        <v>1093</v>
+        <v>1000</v>
       </c>
       <c r="D22" s="7">
-        <v>22.61</v>
+        <v>58</v>
       </c>
       <c r="E22" s="7">
         <f>IF(OR(A22="",SUMIFS(C$4:C22,A$4:A22,A22)=0),"",SUMPRODUCT((A$4:A22=A22)*(C$4:C22)*(D$4:D22))/SUMIFS(C$4:C22,A$4:A22,A22))</f>
-        <v>14.700644239923832</v>
-      </c>
-      <c r="F22" s="6">
-        <v>268</v>
-      </c>
+        <v>38.411708821714996</v>
+      </c>
+      <c r="F22" s="6"/>
       <c r="G22" s="6">
-        <f t="shared" si="0"/>
-        <v>825</v>
+        <f>IF(C22="","",C22-IF(ISNUMBER(F22),F22,0))</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="5">
         <v>46113</v>
       </c>
       <c r="C23" s="6">
-        <v>825</v>
+        <v>2032</v>
       </c>
       <c r="D23" s="7">
-        <v>22.61</v>
+        <v>53.39</v>
       </c>
       <c r="E23" s="7">
         <f>IF(OR(A23="",SUMIFS(C$4:C23,A$4:A23,A23)=0),"",SUMPRODUCT((A$4:A23=A23)*(C$4:C23)*(D$4:D23))/SUMIFS(C$4:C23,A$4:A23,A23))</f>
-        <v>16.341795774647885</v>
+        <v>41.414163953832492</v>
       </c>
       <c r="F23" s="6">
-        <v>280</v>
+        <v>869</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="0"/>
-        <v>545</v>
+        <f>IF(C23="","",C23-IF(ISNUMBER(F23),F23,0))</f>
+        <v>1163</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C24" s="6">
-        <v>545</v>
+        <v>2000</v>
       </c>
       <c r="D24" s="7">
-        <v>22.61</v>
+        <v>68</v>
       </c>
       <c r="E24" s="7">
         <f>IF(OR(A24="",SUMIFS(C$4:C24,A$4:A24,A24)=0),"",SUMPRODUCT((A$4:A24=A24)*(C$4:C24)*(D$4:D24))/SUMIFS(C$4:C24,A$4:A24,A24))</f>
-        <v>17.097418712674184</v>
-      </c>
-      <c r="F24" s="6">
-        <v>229</v>
-      </c>
+        <v>45.79512070528137</v>
+      </c>
+      <c r="F24" s="6"/>
       <c r="G24" s="6">
-        <f t="shared" si="0"/>
-        <v>316</v>
+        <f>IF(C24="","",C24-IF(ISNUMBER(F24),F24,0))</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C25" s="6">
-        <v>1816</v>
+        <v>3163</v>
       </c>
       <c r="D25" s="7">
-        <v>33.9</v>
+        <v>60.64</v>
       </c>
       <c r="E25" s="7">
         <f>IF(OR(A25="",SUMIFS(C$4:C25,A$4:A25,A25)=0),"",SUMPRODUCT((A$4:A25=A25)*(C$4:C25)*(D$4:D25))/SUMIFS(C$4:C25,A$4:A25,A25))</f>
-        <v>21.912550102572194</v>
+        <v>48.864032679738557</v>
       </c>
       <c r="F25" s="6">
-        <v>531</v>
+        <v>623</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="0"/>
-        <v>1285</v>
+        <f>IF(C25="","",C25-IF(ISNUMBER(F25),F25,0))</f>
+        <v>2540</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="C26" s="6">
-        <v>1041</v>
+        <v>2000</v>
       </c>
       <c r="D26" s="7">
-        <v>33.9</v>
+        <v>67</v>
       </c>
       <c r="E26" s="7">
         <f>IF(OR(A26="",SUMIFS(C$4:C26,A$4:A26,A26)=0),"",SUMPRODUCT((A$4:A26=A26)*(C$4:C26)*(D$4:D26))/SUMIFS(C$4:C26,A$4:A26,A26))</f>
-        <v>23.603921116833828</v>
-      </c>
-      <c r="F26" s="6">
-        <v>245</v>
-      </c>
+        <v>50.960676300578029</v>
+      </c>
+      <c r="F26" s="6"/>
       <c r="G26" s="6">
-        <f t="shared" si="0"/>
-        <v>796</v>
+        <f>IF(C26="","",C26-IF(ISNUMBER(F26),F26,0))</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="5">
-        <v>46235</v>
+        <v>46174</v>
       </c>
       <c r="C27" s="6">
-        <v>796</v>
+        <v>4540</v>
       </c>
       <c r="D27" s="7">
-        <v>33.9</v>
+        <v>63.1</v>
       </c>
       <c r="E27" s="7">
         <f>IF(OR(A27="",SUMIFS(C$4:C27,A$4:A27,A27)=0),"",SUMPRODUCT((A$4:A27=A27)*(C$4:C27)*(D$4:D27))/SUMIFS(C$4:C27,A$4:A27,A27))</f>
-        <v>24.606573281135304</v>
+        <v>53.484143772893773</v>
       </c>
       <c r="F27" s="6">
-        <v>455</v>
+        <v>269</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="0"/>
-        <v>341</v>
+        <f>IF(C27="","",C27-IF(ISNUMBER(F27),F27,0))</f>
+        <v>4271</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46266</v>
+        <v>46204</v>
       </c>
       <c r="C28" s="6">
-        <v>341</v>
+        <v>4271</v>
       </c>
       <c r="D28" s="7">
-        <v>33.9</v>
+        <v>63.1</v>
       </c>
       <c r="E28" s="7">
         <f>IF(OR(A28="",SUMIFS(C$4:C28,A$4:A28,A28)=0),"",SUMPRODUCT((A$4:A28=A28)*(C$4:C28)*(D$4:D28))/SUMIFS(C$4:C28,A$4:A28,A28))</f>
-        <v>24.97874691720493</v>
-      </c>
-      <c r="F28" s="6"/>
+        <v>55.057018114970703</v>
+      </c>
+      <c r="F28" s="6">
+        <v>282</v>
+      </c>
       <c r="G28" s="6">
-        <f t="shared" si="0"/>
-        <v>341</v>
+        <f>IF(C28="","",C28-IF(ISNUMBER(F28),F28,0))</f>
+        <v>3989</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="5">
-        <v>46054</v>
+        <v>46235</v>
       </c>
       <c r="C29" s="6">
-        <v>1000</v>
+        <v>3989</v>
       </c>
       <c r="D29" s="7">
-        <v>27</v>
+        <v>63.1</v>
       </c>
       <c r="E29" s="7">
         <f>IF(OR(A29="",SUMIFS(C$4:C29,A$4:A29,A29)=0),"",SUMPRODUCT((A$4:A29=A29)*(C$4:C29)*(D$4:D29))/SUMIFS(C$4:C29,A$4:A29,A29))</f>
-        <v>25.191174986862844</v>
+        <v>56.122913621262455</v>
       </c>
       <c r="F29" s="6">
-        <v>104</v>
+        <v>435</v>
       </c>
       <c r="G29" s="6">
-        <f t="shared" si="0"/>
-        <v>896</v>
+        <f>IF(C29="","",C29-IF(ISNUMBER(F29),F29,0))</f>
+        <v>3554</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46143</v>
+        <v>46266</v>
       </c>
       <c r="C30" s="6">
-        <v>1500</v>
+        <v>3554</v>
       </c>
       <c r="D30" s="7">
-        <v>38</v>
+        <v>63.1</v>
       </c>
       <c r="E30" s="7">
         <f>IF(OR(A30="",SUMIFS(C$4:C30,A$4:A30,A30)=0),"",SUMPRODUCT((A$4:A30=A30)*(C$4:C30)*(D$4:D30))/SUMIFS(C$4:C30,A$4:A30,A30))</f>
-        <v>26.935454380390375</v>
+        <v>56.859722469840136</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6">
-        <f t="shared" si="0"/>
-        <v>1500</v>
+        <f>IF(C30="","",C30-IF(ISNUMBER(F30),F30,0))</f>
+        <v>3554</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
@@ -7000,7 +7008,7 @@
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G4:G35" si="0">IF(C31="","",C31-IF(ISNUMBER(F31),F31,0))</f>
         <v/>
       </c>
     </row>
@@ -7450,11 +7458,11 @@
       </c>
       <c r="D61" s="10">
         <f>IF(SUM(C4:C60)=0,0,SUMPRODUCT(C4:C60,D4:D60)/SUM(C4:C60))</f>
-        <v>49.480649443685763</v>
+        <v>49.480649443685778</v>
       </c>
       <c r="E61" s="10">
         <f>AVERAGEIF(E4:E60,"&lt;&gt;0")</f>
-        <v>32.220650647885748</v>
+        <v>30.457373324326507</v>
       </c>
       <c r="F61" s="9">
         <f>SUM(F4:F60)</f>
@@ -7466,6 +7474,10 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A4:G30">
+    <sortCondition ref="A4:A30"/>
+    <sortCondition ref="B4:B30"/>
+  </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -7544,7 +7556,7 @@
         <v>762</v>
       </c>
       <c r="G4" s="6">
-        <f t="shared" ref="G4:G35" si="0">IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
+        <f>IF(C4="","",C4-IF(ISNUMBER(F4),F4,0))</f>
         <v>174</v>
       </c>
     </row>
@@ -7569,7 +7581,7 @@
         <v>174</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C5="","",C5-IF(ISNUMBER(F5),F5,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -7578,24 +7590,24 @@
         <v>19</v>
       </c>
       <c r="B6" s="5">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="C6" s="6">
-        <v>3100</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="7">
-        <v>33.770000000000003</v>
+        <v>34</v>
       </c>
       <c r="E6" s="7">
         <f>IF(OR(A6="",SUMIFS(C$4:C6,A$4:A6,A6)=0),"",SUMPRODUCT((A$4:A6=A6)*(C$4:C6)*(D$4:D6))/SUMIFS(C$4:C6,A$4:A6,A6))</f>
-        <v>29.322090261282664</v>
+        <v>25.0042654028436</v>
       </c>
       <c r="F6" s="6">
-        <v>410</v>
+        <v>800</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="0"/>
-        <v>2690</v>
+        <f>IF(C6="","",C6-IF(ISNUMBER(F6),F6,0))</f>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -7603,24 +7615,22 @@
         <v>19</v>
       </c>
       <c r="B7" s="5">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="C7" s="6">
-        <v>4179</v>
+        <v>2000</v>
       </c>
       <c r="D7" s="7">
-        <v>35.43</v>
+        <v>33</v>
       </c>
       <c r="E7" s="7">
         <f>IF(OR(A7="",SUMIFS(C$4:C7,A$4:A7,A7)=0),"",SUMPRODUCT((A$4:A7=A7)*(C$4:C7)*(D$4:D7))/SUMIFS(C$4:C7,A$4:A7,A7))</f>
-        <v>32.364759804505901</v>
-      </c>
-      <c r="F7" s="6">
-        <v>810</v>
-      </c>
+        <v>28.895133819951337</v>
+      </c>
+      <c r="F7" s="6"/>
       <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>3369</v>
+        <f>IF(C7="","",C7-IF(ISNUMBER(F7),F7,0))</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -7628,24 +7638,22 @@
         <v>19</v>
       </c>
       <c r="B8" s="5">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="C8" s="6">
-        <v>2169</v>
+        <v>900</v>
       </c>
       <c r="D8" s="7">
-        <v>36.409999999999997</v>
+        <v>38.5</v>
       </c>
       <c r="E8" s="7">
         <f>IF(OR(A8="",SUMIFS(C$4:C8,A$4:A8,A8)=0),"",SUMPRODUCT((A$4:A8=A8)*(C$4:C8)*(D$4:D8))/SUMIFS(C$4:C8,A$4:A8,A8))</f>
-        <v>33.195800340973669</v>
-      </c>
-      <c r="F8" s="6">
-        <v>495</v>
-      </c>
+        <v>30.620558882235528</v>
+      </c>
+      <c r="F8" s="6"/>
       <c r="G8" s="6">
-        <f t="shared" si="0"/>
-        <v>1674</v>
+        <f>IF(C8="","",C8-IF(ISNUMBER(F8),F8,0))</f>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
@@ -7653,24 +7661,24 @@
         <v>19</v>
       </c>
       <c r="B9" s="5">
-        <v>46143</v>
+        <v>46054</v>
       </c>
       <c r="C9" s="6">
-        <v>3674</v>
+        <v>3100</v>
       </c>
       <c r="D9" s="7">
-        <v>46.29</v>
+        <v>33.770000000000003</v>
       </c>
       <c r="E9" s="7">
         <f>IF(OR(A9="",SUMIFS(C$4:C9,A$4:A9,A9)=0),"",SUMPRODUCT((A$4:A9=A9)*(C$4:C9)*(D$4:D9))/SUMIFS(C$4:C9,A$4:A9,A9))</f>
-        <v>36.576076447442382</v>
+        <v>31.824414303329224</v>
       </c>
       <c r="F9" s="6">
-        <v>540</v>
+        <v>410</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="0"/>
-        <v>3134</v>
+        <f>IF(C9="","",C9-IF(ISNUMBER(F9),F9,0))</f>
+        <v>2690</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -7678,24 +7686,24 @@
         <v>19</v>
       </c>
       <c r="B10" s="5">
-        <v>46174</v>
+        <v>46054</v>
       </c>
       <c r="C10" s="6">
-        <v>3134</v>
+        <v>2000</v>
       </c>
       <c r="D10" s="7">
-        <v>46.29</v>
+        <v>38</v>
       </c>
       <c r="E10" s="7">
         <f>IF(OR(A10="",SUMIFS(C$4:C10,A$4:A10,A10)=0),"",SUMPRODUCT((A$4:A10=A10)*(C$4:C10)*(D$4:D10))/SUMIFS(C$4:C10,A$4:A10,A10))</f>
-        <v>38.329124726477019</v>
+        <v>33.046092977250247</v>
       </c>
       <c r="F10" s="6">
-        <v>130</v>
+        <v>511</v>
       </c>
       <c r="G10" s="6">
-        <f t="shared" si="0"/>
-        <v>3004</v>
+        <f>IF(C10="","",C10-IF(ISNUMBER(F10),F10,0))</f>
+        <v>1489</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -7703,24 +7711,24 @@
         <v>19</v>
       </c>
       <c r="B11" s="5">
-        <v>46204</v>
+        <v>46082</v>
       </c>
       <c r="C11" s="6">
-        <v>3004</v>
+        <v>4179</v>
       </c>
       <c r="D11" s="7">
-        <v>46.29</v>
+        <v>35.43</v>
       </c>
       <c r="E11" s="7">
         <f>IF(OR(A11="",SUMIFS(C$4:C11,A$4:A11,A11)=0),"",SUMPRODUCT((A$4:A11=A11)*(C$4:C11)*(D$4:D11))/SUMIFS(C$4:C11,A$4:A11,A11))</f>
-        <v>39.50312911143839</v>
+        <v>33.743296941703406</v>
       </c>
       <c r="F11" s="6">
-        <v>90</v>
+        <v>810</v>
       </c>
       <c r="G11" s="6">
-        <f t="shared" si="0"/>
-        <v>2914</v>
+        <f>IF(C11="","",C11-IF(ISNUMBER(F11),F11,0))</f>
+        <v>3369</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
@@ -7728,24 +7736,22 @@
         <v>19</v>
       </c>
       <c r="B12" s="5">
-        <v>46235</v>
+        <v>46082</v>
       </c>
       <c r="C12" s="6">
-        <v>2914</v>
+        <v>3000</v>
       </c>
       <c r="D12" s="7">
-        <v>46.29</v>
+        <v>45.5</v>
       </c>
       <c r="E12" s="7">
         <f>IF(OR(A12="",SUMIFS(C$4:C12,A$4:A12,A12)=0),"",SUMPRODUCT((A$4:A12=A12)*(C$4:C12)*(D$4:D12))/SUMIFS(C$4:C12,A$4:A12,A12))</f>
-        <v>40.352508160109949</v>
-      </c>
-      <c r="F12" s="6">
-        <v>110</v>
-      </c>
+        <v>35.783328706113714</v>
+      </c>
+      <c r="F12" s="6"/>
       <c r="G12" s="6">
-        <f t="shared" si="0"/>
-        <v>2804</v>
+        <f>IF(C12="","",C12-IF(ISNUMBER(F12),F12,0))</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
@@ -7753,22 +7759,22 @@
         <v>19</v>
       </c>
       <c r="B13" s="5">
-        <v>46266</v>
+        <v>46082</v>
       </c>
       <c r="C13" s="6">
-        <v>2804</v>
+        <v>-3000</v>
       </c>
       <c r="D13" s="7">
-        <v>46.29</v>
+        <v>45.5</v>
       </c>
       <c r="E13" s="7">
         <f>IF(OR(A13="",SUMIFS(C$4:C13,A$4:A13,A13)=0),"",SUMPRODUCT((A$4:A13=A13)*(C$4:C13)*(D$4:D13))/SUMIFS(C$4:C13,A$4:A13,A13))</f>
-        <v>40.990683839313093</v>
+        <v>33.743296941703406</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6">
-        <f t="shared" si="0"/>
-        <v>2804</v>
+        <f>IF(C13="","",C13-IF(ISNUMBER(F13),F13,0))</f>
+        <v>-3000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -7776,24 +7782,22 @@
         <v>19</v>
       </c>
       <c r="B14" s="5">
-        <v>46023</v>
+        <v>46082</v>
       </c>
       <c r="C14" s="6">
-        <v>1000</v>
+        <v>-1200</v>
       </c>
       <c r="D14" s="7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" s="7">
         <f>IF(OR(A14="",SUMIFS(C$4:C14,A$4:A14,A14)=0),"",SUMPRODUCT((A$4:A14=A14)*(C$4:C14)*(D$4:D14))/SUMIFS(C$4:C14,A$4:A14,A14))</f>
-        <v>40.732610750147664</v>
-      </c>
-      <c r="F14" s="6">
-        <v>800</v>
-      </c>
+        <v>33.811442432576968</v>
+      </c>
+      <c r="F14" s="6"/>
       <c r="G14" s="6">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <f>IF(C14="","",C14-IF(ISNUMBER(F14),F14,0))</f>
+        <v>-1200</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
@@ -7801,24 +7805,24 @@
         <v>19</v>
       </c>
       <c r="B15" s="5">
-        <v>46054</v>
+        <v>46113</v>
       </c>
       <c r="C15" s="6">
-        <v>2000</v>
+        <v>2169</v>
       </c>
       <c r="D15" s="7">
-        <v>38</v>
+        <v>36.409999999999997</v>
       </c>
       <c r="E15" s="7">
         <f>IF(OR(A15="",SUMIFS(C$4:C15,A$4:A15,A15)=0),"",SUMPRODUCT((A$4:A15=A15)*(C$4:C15)*(D$4:D15))/SUMIFS(C$4:C15,A$4:A15,A15))</f>
-        <v>40.544724972497249</v>
+        <v>34.180840214969194</v>
       </c>
       <c r="F15" s="6">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="0"/>
-        <v>1489</v>
+        <f>IF(C15="","",C15-IF(ISNUMBER(F15),F15,0))</f>
+        <v>1674</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
@@ -7826,22 +7830,22 @@
         <v>19</v>
       </c>
       <c r="B16" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C16" s="6">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="D16" s="7">
-        <v>45.5</v>
+        <v>57</v>
       </c>
       <c r="E16" s="7">
         <f>IF(OR(A16="",SUMIFS(C$4:C16,A$4:A16,A16)=0),"",SUMPRODUCT((A$4:A16=A16)*(C$4:C16)*(D$4:D16))/SUMIFS(C$4:C16,A$4:A16,A16))</f>
-        <v>41.008007978060334</v>
+        <v>36.825313477807391</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
-        <f t="shared" si="0"/>
-        <v>3000</v>
+        <f>IF(C16="","",C16-IF(ISNUMBER(F16),F16,0))</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -7849,22 +7853,24 @@
         <v>19</v>
       </c>
       <c r="B17" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C17" s="6">
-        <v>2000</v>
+        <v>3674</v>
       </c>
       <c r="D17" s="7">
-        <v>57</v>
+        <v>46.29</v>
       </c>
       <c r="E17" s="7">
         <f>IF(OR(A17="",SUMIFS(C$4:C17,A$4:A17,A17)=0),"",SUMPRODUCT((A$4:A17=A17)*(C$4:C17)*(D$4:D17))/SUMIFS(C$4:C17,A$4:A17,A17))</f>
-        <v>41.94628490964562</v>
-      </c>
-      <c r="F17" s="6"/>
+        <v>38.486562201414102</v>
+      </c>
+      <c r="F17" s="6">
+        <v>540</v>
+      </c>
       <c r="G17" s="6">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <f>IF(C17="","",C17-IF(ISNUMBER(F17),F17,0))</f>
+        <v>3134</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -7872,22 +7878,24 @@
         <v>19</v>
       </c>
       <c r="B18" s="5">
-        <v>46023</v>
+        <v>46174</v>
       </c>
       <c r="C18" s="6">
-        <v>2000</v>
+        <v>3134</v>
       </c>
       <c r="D18" s="7">
-        <v>33</v>
+        <v>46.29</v>
       </c>
       <c r="E18" s="7">
         <f>IF(OR(A18="",SUMIFS(C$4:C18,A$4:A18,A18)=0),"",SUMPRODUCT((A$4:A18=A18)*(C$4:C18)*(D$4:D18))/SUMIFS(C$4:C18,A$4:A18,A18))</f>
-        <v>41.450481046331191</v>
-      </c>
-      <c r="F18" s="6"/>
+        <v>39.502766558630434</v>
+      </c>
+      <c r="F18" s="6">
+        <v>130</v>
+      </c>
       <c r="G18" s="6">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <f>IF(C18="","",C18-IF(ISNUMBER(F18),F18,0))</f>
+        <v>3004</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
@@ -7895,22 +7903,24 @@
         <v>19</v>
       </c>
       <c r="B19" s="5">
-        <v>46082</v>
+        <v>46204</v>
       </c>
       <c r="C19" s="6">
-        <v>-3000</v>
+        <v>3004</v>
       </c>
       <c r="D19" s="7">
-        <v>45.5</v>
+        <v>46.29</v>
       </c>
       <c r="E19" s="7">
         <f>IF(OR(A19="",SUMIFS(C$4:C19,A$4:A19,A19)=0),"",SUMPRODUCT((A$4:A19=A19)*(C$4:C19)*(D$4:D19))/SUMIFS(C$4:C19,A$4:A19,A19))</f>
-        <v>41.083322050290136</v>
-      </c>
-      <c r="F19" s="6"/>
+        <v>40.255956409309199</v>
+      </c>
+      <c r="F19" s="6">
+        <v>90</v>
+      </c>
       <c r="G19" s="6">
-        <f t="shared" si="0"/>
-        <v>-3000</v>
+        <f>IF(C19="","",C19-IF(ISNUMBER(F19),F19,0))</f>
+        <v>2914</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -7918,22 +7928,24 @@
         <v>19</v>
       </c>
       <c r="B20" s="5">
-        <v>46023</v>
+        <v>46235</v>
       </c>
       <c r="C20" s="6">
-        <v>900</v>
+        <v>2914</v>
       </c>
       <c r="D20" s="7">
-        <v>38.5</v>
+        <v>46.29</v>
       </c>
       <c r="E20" s="7">
         <f>IF(OR(A20="",SUMIFS(C$4:C20,A$4:A20,A20)=0),"",SUMPRODUCT((A$4:A20=A20)*(C$4:C20)*(D$4:D20))/SUMIFS(C$4:C20,A$4:A20,A20))</f>
-        <v>41.014915852653878</v>
-      </c>
-      <c r="F20" s="6"/>
+        <v>40.842375933831377</v>
+      </c>
+      <c r="F20" s="6">
+        <v>110</v>
+      </c>
       <c r="G20" s="6">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <f>IF(C20="","",C20-IF(ISNUMBER(F20),F20,0))</f>
+        <v>2804</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
@@ -7941,13 +7953,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="5">
-        <v>46082</v>
+        <v>46266</v>
       </c>
       <c r="C21" s="6">
-        <v>-1200</v>
+        <v>2804</v>
       </c>
       <c r="D21" s="7">
-        <v>33</v>
+        <v>46.29</v>
       </c>
       <c r="E21" s="7">
         <f>IF(OR(A21="",SUMIFS(C$4:C21,A$4:A21,A21)=0),"",SUMPRODUCT((A$4:A21=A21)*(C$4:C21)*(D$4:D21))/SUMIFS(C$4:C21,A$4:A21,A21))</f>
@@ -7955,8 +7967,8 @@
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6">
-        <f t="shared" si="0"/>
-        <v>-1200</v>
+        <f>IF(C21="","",C21-IF(ISNUMBER(F21),F21,0))</f>
+        <v>2804</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
@@ -7980,7 +7992,7 @@
         <v>31</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C22="","",C22-IF(ISNUMBER(F22),F22,0))</f>
         <v>538</v>
       </c>
     </row>
@@ -8005,7 +8017,7 @@
         <v>42</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C23="","",C23-IF(ISNUMBER(F23),F23,0))</f>
         <v>496</v>
       </c>
     </row>
@@ -8030,7 +8042,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C24="","",C24-IF(ISNUMBER(F24),F24,0))</f>
         <v>476</v>
       </c>
     </row>
@@ -8055,7 +8067,7 @@
         <v>212</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="0"/>
+        <f>IF(C25="","",C25-IF(ISNUMBER(F25),F25,0))</f>
         <v>239</v>
       </c>
     </row>
@@ -8064,24 +8076,22 @@
         <v>20</v>
       </c>
       <c r="B26" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C26" s="6">
-        <v>789</v>
+        <v>550</v>
       </c>
       <c r="D26" s="7">
-        <v>29.59</v>
+        <v>40</v>
       </c>
       <c r="E26" s="7">
         <f>IF(OR(A26="",SUMIFS(C$4:C26,A$4:A26,A26)=0),"",SUMPRODUCT((A$4:A26=A26)*(C$4:C26)*(D$4:D26))/SUMIFS(C$4:C26,A$4:A26,A26))</f>
-        <v>20.421776292648612</v>
-      </c>
-      <c r="F26" s="6">
-        <v>474</v>
-      </c>
+        <v>21.779032258064515</v>
+      </c>
+      <c r="F26" s="6"/>
       <c r="G26" s="6">
-        <f t="shared" si="0"/>
-        <v>315</v>
+        <f>IF(C26="","",C26-IF(ISNUMBER(F26),F26,0))</f>
+        <v>550</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
@@ -8089,24 +8099,24 @@
         <v>20</v>
       </c>
       <c r="B27" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C27" s="6">
-        <v>324</v>
+        <v>789</v>
       </c>
       <c r="D27" s="7">
-        <v>29.52</v>
+        <v>29.59</v>
       </c>
       <c r="E27" s="7">
         <f>IF(OR(A27="",SUMIFS(C$4:C27,A$4:A27,A27)=0),"",SUMPRODUCT((A$4:A27=A27)*(C$4:C27)*(D$4:D27))/SUMIFS(C$4:C27,A$4:A27,A27))</f>
-        <v>21.352570255762551</v>
+        <v>23.595375773651636</v>
       </c>
       <c r="F27" s="6">
-        <v>38</v>
+        <v>474</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="0"/>
-        <v>286</v>
+        <f>IF(C27="","",C27-IF(ISNUMBER(F27),F27,0))</f>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
@@ -8114,24 +8124,22 @@
         <v>20</v>
       </c>
       <c r="B28" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C28" s="6">
-        <v>286</v>
+        <v>9</v>
       </c>
       <c r="D28" s="7">
-        <v>29.52</v>
+        <v>23</v>
       </c>
       <c r="E28" s="7">
         <f>IF(OR(A28="",SUMIFS(C$4:C28,A$4:A28,A28)=0),"",SUMPRODUCT((A$4:A28=A28)*(C$4:C28)*(D$4:D28))/SUMIFS(C$4:C28,A$4:A28,A28))</f>
-        <v>22.029050101361136</v>
-      </c>
-      <c r="F28" s="6">
-        <v>37</v>
-      </c>
+        <v>23.593800705467373</v>
+      </c>
+      <c r="F28" s="6"/>
       <c r="G28" s="6">
-        <f t="shared" si="0"/>
-        <v>249</v>
+        <f>IF(C28="","",C28-IF(ISNUMBER(F28),F28,0))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
@@ -8139,24 +8147,24 @@
         <v>20</v>
       </c>
       <c r="B29" s="5">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="C29" s="6">
-        <v>749</v>
+        <v>324</v>
       </c>
       <c r="D29" s="7">
-        <v>36.630000000000003</v>
+        <v>29.52</v>
       </c>
       <c r="E29" s="7">
         <f>IF(OR(A29="",SUMIFS(C$4:C29,A$4:A29,A29)=0),"",SUMPRODUCT((A$4:A29=A29)*(C$4:C29)*(D$4:D29))/SUMIFS(C$4:C29,A$4:A29,A29))</f>
-        <v>24.631646834840552</v>
+        <v>24.109122383252817</v>
       </c>
       <c r="F29" s="6">
-        <v>200</v>
+        <v>38</v>
       </c>
       <c r="G29" s="6">
-        <f t="shared" si="0"/>
-        <v>549</v>
+        <f>IF(C29="","",C29-IF(ISNUMBER(F29),F29,0))</f>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
@@ -8164,24 +8172,24 @@
         <v>20</v>
       </c>
       <c r="B30" s="5">
-        <v>46235</v>
+        <v>46174</v>
       </c>
       <c r="C30" s="6">
-        <v>1049</v>
+        <v>286</v>
       </c>
       <c r="D30" s="7">
-        <v>38.86</v>
+        <v>29.52</v>
       </c>
       <c r="E30" s="7">
         <f>IF(OR(A30="",SUMIFS(C$4:C30,A$4:A30,A30)=0),"",SUMPRODUCT((A$4:A30=A30)*(C$4:C30)*(D$4:D30))/SUMIFS(C$4:C30,A$4:A30,A30))</f>
-        <v>27.474065892211009</v>
+        <v>24.49484297108674</v>
       </c>
       <c r="F30" s="6">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" si="0"/>
-        <v>909</v>
+        <f>IF(C30="","",C30-IF(ISNUMBER(F30),F30,0))</f>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
@@ -8189,22 +8197,22 @@
         <v>20</v>
       </c>
       <c r="B31" s="5">
-        <v>46266</v>
+        <v>46174</v>
       </c>
       <c r="C31" s="6">
-        <v>909</v>
+        <v>500</v>
       </c>
       <c r="D31" s="7">
-        <v>38.86</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="E31" s="7">
         <f>IF(OR(A31="",SUMIFS(C$4:C31,A$4:A31,A31)=0),"",SUMPRODUCT((A$4:A31=A31)*(C$4:C31)*(D$4:D31))/SUMIFS(C$4:C31,A$4:A31,A31))</f>
-        <v>29.154230519480517</v>
+        <v>26.290627216312057</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6">
-        <f t="shared" si="0"/>
-        <v>909</v>
+        <f>IF(C31="","",C31-IF(ISNUMBER(F31),F31,0))</f>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -8212,22 +8220,24 @@
         <v>20</v>
       </c>
       <c r="B32" s="5">
-        <v>46082</v>
+        <v>46204</v>
       </c>
       <c r="C32" s="6">
-        <v>550</v>
+        <v>749</v>
       </c>
       <c r="D32" s="7">
-        <v>40</v>
+        <v>36.630000000000003</v>
       </c>
       <c r="E32" s="7">
         <f>IF(OR(A32="",SUMIFS(C$4:C32,A$4:A32,A32)=0),"",SUMPRODUCT((A$4:A32=A32)*(C$4:C32)*(D$4:D32))/SUMIFS(C$4:C32,A$4:A32,A32))</f>
-        <v>30.043228017883756</v>
-      </c>
-      <c r="F32" s="6"/>
+        <v>27.762626877019578</v>
+      </c>
+      <c r="F32" s="6">
+        <v>200</v>
+      </c>
       <c r="G32" s="6">
-        <f t="shared" si="0"/>
-        <v>550</v>
+        <f>IF(C32="","",C32-IF(ISNUMBER(F32),F32,0))</f>
+        <v>549</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
@@ -8235,22 +8245,22 @@
         <v>20</v>
       </c>
       <c r="B33" s="5">
-        <v>46113</v>
+        <v>46204</v>
       </c>
       <c r="C33" s="6">
-        <v>9</v>
+        <v>500</v>
       </c>
       <c r="D33" s="7">
-        <v>23</v>
+        <v>42.2</v>
       </c>
       <c r="E33" s="7">
         <f>IF(OR(A33="",SUMIFS(C$4:C33,A$4:A33,A33)=0),"",SUMPRODUCT((A$4:A33=A33)*(C$4:C33)*(D$4:D33))/SUMIFS(C$4:C33,A$4:A33,A33))</f>
-        <v>30.033793719303468</v>
+        <v>29.015653532372852</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>IF(C33="","",C33-IF(ISNUMBER(F33),F33,0))</f>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
@@ -8258,22 +8268,24 @@
         <v>20</v>
       </c>
       <c r="B34" s="5">
-        <v>46174</v>
+        <v>46235</v>
       </c>
       <c r="C34" s="6">
-        <v>500</v>
+        <v>1049</v>
       </c>
       <c r="D34" s="7">
-        <v>40.700000000000003</v>
+        <v>38.86</v>
       </c>
       <c r="E34" s="7">
         <f>IF(OR(A34="",SUMIFS(C$4:C34,A$4:A34,A34)=0),"",SUMPRODUCT((A$4:A34=A34)*(C$4:C34)*(D$4:D34))/SUMIFS(C$4:C34,A$4:A34,A34))</f>
-        <v>30.772552985178002</v>
-      </c>
-      <c r="F34" s="6"/>
+        <v>30.53205873715125</v>
+      </c>
+      <c r="F34" s="6">
+        <v>140</v>
+      </c>
       <c r="G34" s="6">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <f>IF(C34="","",C34-IF(ISNUMBER(F34),F34,0))</f>
+        <v>909</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
@@ -8281,13 +8293,13 @@
         <v>20</v>
       </c>
       <c r="B35" s="5">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C35" s="6">
-        <v>500</v>
+        <v>909</v>
       </c>
       <c r="D35" s="7">
-        <v>42.2</v>
+        <v>38.86</v>
       </c>
       <c r="E35" s="7">
         <f>IF(OR(A35="",SUMIFS(C$4:C35,A$4:A35,A35)=0),"",SUMPRODUCT((A$4:A35=A35)*(C$4:C35)*(D$4:D35))/SUMIFS(C$4:C35,A$4:A35,A35))</f>
@@ -8295,244 +8307,244 @@
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <f>IF(C35="","",C35-IF(ISNUMBER(F35),F35,0))</f>
+        <v>909</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B36" s="5">
         <v>45992</v>
       </c>
       <c r="C36" s="6">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="D36" s="7">
-        <v>24.5</v>
+        <v>42</v>
       </c>
       <c r="E36" s="7">
         <f>IF(OR(A36="",SUMIFS(C$4:C36,A$4:A36,A36)=0),"",SUMPRODUCT((A$4:A36=A36)*(C$4:C36)*(D$4:D36))/SUMIFS(C$4:C36,A$4:A36,A36))</f>
-        <v>24.5</v>
-      </c>
-      <c r="F36" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="F36" s="6">
+        <v>2</v>
+      </c>
       <c r="G36" s="6">
-        <f t="shared" ref="G36:G67" si="1">IF(C36="","",C36-IF(ISNUMBER(F36),F36,0))</f>
-        <v>70</v>
+        <f>IF(C36="","",C36-IF(ISNUMBER(F36),F36,0))</f>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B37" s="5">
         <v>46023</v>
       </c>
       <c r="C37" s="6">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="D37" s="7">
-        <v>24.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E37" s="7">
         <f>IF(OR(A37="",SUMIFS(C$4:C37,A$4:A37,A37)=0),"",SUMPRODUCT((A$4:A37=A37)*(C$4:C37)*(D$4:D37))/SUMIFS(C$4:C37,A$4:A37,A37))</f>
-        <v>24.5</v>
+        <v>29.567289719626167</v>
       </c>
       <c r="F37" s="6">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>IF(C37="","",C37-IF(ISNUMBER(F37),F37,0))</f>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B38" s="5">
         <v>46054</v>
       </c>
       <c r="C38" s="6">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D38" s="7">
-        <v>24.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E38" s="7">
         <f>IF(OR(A38="",SUMIFS(C$4:C38,A$4:A38,A38)=0),"",SUMPRODUCT((A$4:A38=A38)*(C$4:C38)*(D$4:D38))/SUMIFS(C$4:C38,A$4:A38,A38))</f>
-        <v>24.5</v>
+        <v>25.817105263157895</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>IF(C38="","",C38-IF(ISNUMBER(F38),F38,0))</f>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B39" s="5">
         <v>46082</v>
       </c>
       <c r="C39" s="6">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D39" s="7">
-        <v>24.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E39" s="7">
         <f>IF(OR(A39="",SUMIFS(C$4:C39,A$4:A39,A39)=0),"",SUMPRODUCT((A$4:A39=A39)*(C$4:C39)*(D$4:D39))/SUMIFS(C$4:C39,A$4:A39,A39))</f>
-        <v>24.5</v>
+        <v>23.78020304568528</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>IF(C39="","",C39-IF(ISNUMBER(F39),F39,0))</f>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B40" s="5">
         <v>46113</v>
       </c>
       <c r="C40" s="6">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D40" s="7">
-        <v>24.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E40" s="7">
         <f>IF(OR(A40="",SUMIFS(C$4:C40,A$4:A40,A40)=0),"",SUMPRODUCT((A$4:A40=A40)*(C$4:C40)*(D$4:D40))/SUMIFS(C$4:C40,A$4:A40,A40))</f>
-        <v>24.5</v>
+        <v>22.500826446280993</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>IF(C40="","",C40-IF(ISNUMBER(F40),F40,0))</f>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B41" s="5">
         <v>46143</v>
       </c>
       <c r="C41" s="6">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D41" s="7">
-        <v>24.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E41" s="7">
         <f>IF(OR(A41="",SUMIFS(C$4:C41,A$4:A41,A41)=0),"",SUMPRODUCT((A$4:A41=A41)*(C$4:C41)*(D$4:D41))/SUMIFS(C$4:C41,A$4:A41,A41))</f>
-        <v>24.5</v>
-      </c>
-      <c r="F41" s="6"/>
+        <v>21.622648083623695</v>
+      </c>
+      <c r="F41" s="6">
+        <v>18</v>
+      </c>
       <c r="G41" s="6">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>IF(C41="","",C41-IF(ISNUMBER(F41),F41,0))</f>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B42" s="5">
         <v>46174</v>
       </c>
       <c r="C42" s="6">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D42" s="7">
-        <v>24.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E42" s="7">
         <f>IF(OR(A42="",SUMIFS(C$4:C42,A$4:A42,A42)=0),"",SUMPRODUCT((A$4:A42=A42)*(C$4:C42)*(D$4:D42))/SUMIFS(C$4:C42,A$4:A42,A42))</f>
-        <v>24.5</v>
-      </c>
-      <c r="F42" s="6">
-        <v>30</v>
-      </c>
+        <v>21.096284829721359</v>
+      </c>
+      <c r="F42" s="6"/>
       <c r="G42" s="6">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>IF(C42="","",C42-IF(ISNUMBER(F42),F42,0))</f>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B43" s="5">
         <v>46204</v>
       </c>
       <c r="C43" s="6">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D43" s="7">
-        <v>24.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E43" s="7">
         <f>IF(OR(A43="",SUMIFS(C$4:C43,A$4:A43,A43)=0),"",SUMPRODUCT((A$4:A43=A43)*(C$4:C43)*(D$4:D43))/SUMIFS(C$4:C43,A$4:A43,A43))</f>
-        <v>24.5</v>
-      </c>
-      <c r="F43" s="6">
-        <v>12</v>
-      </c>
+        <v>20.675487465181057</v>
+      </c>
+      <c r="F43" s="6"/>
       <c r="G43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(C43="","",C43-IF(ISNUMBER(F43),F43,0))</f>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B44" s="5">
         <v>46235</v>
       </c>
       <c r="C44" s="6">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D44" s="7">
-        <v>59.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E44" s="7">
         <f>IF(OR(A44="",SUMIFS(C$4:C44,A$4:A44,A44)=0),"",SUMPRODUCT((A$4:A44=A44)*(C$4:C44)*(D$4:D44))/SUMIFS(C$4:C44,A$4:A44,A44))</f>
-        <v>26.505208333333332</v>
+        <v>20.331392405063287</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <f>IF(C44="","",C44-IF(ISNUMBER(F44),F44,0))</f>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B45" s="5">
         <v>46266</v>
       </c>
       <c r="C45" s="6">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D45" s="7">
-        <v>59.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E45" s="7">
         <f>IF(OR(A45="",SUMIFS(C$4:C45,A$4:A45,A45)=0),"",SUMPRODUCT((A$4:A45=A45)*(C$4:C45)*(D$4:D45))/SUMIFS(C$4:C45,A$4:A45,A45))</f>
-        <v>28.293103448275861</v>
+        <v>20.044779582366587</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <f>IF(C45="","",C45-IF(ISNUMBER(F45),F45,0))</f>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
@@ -8540,24 +8552,22 @@
         <v>21</v>
       </c>
       <c r="B46" s="5">
-        <v>46204</v>
+        <v>45992</v>
       </c>
       <c r="C46" s="6">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D46" s="7">
-        <v>73.5</v>
+        <v>24.5</v>
       </c>
       <c r="E46" s="7">
         <f>IF(OR(A46="",SUMIFS(C$4:C46,A$4:A46,A46)=0),"",SUMPRODUCT((A$4:A46=A46)*(C$4:C46)*(D$4:D46))/SUMIFS(C$4:C46,A$4:A46,A46))</f>
-        <v>31.403669724770641</v>
-      </c>
-      <c r="F46" s="6">
-        <v>8</v>
-      </c>
+        <v>24.5</v>
+      </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="6">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <f>IF(C46="","",C46-IF(ISNUMBER(F46),F46,0))</f>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
@@ -8565,20 +8575,24 @@
         <v>21</v>
       </c>
       <c r="B47" s="5">
-        <v>46235</v>
-      </c>
-      <c r="C47" s="6"/>
+        <v>46023</v>
+      </c>
+      <c r="C47" s="6">
+        <v>70</v>
+      </c>
       <c r="D47" s="7">
-        <v>73.5</v>
+        <v>24.5</v>
       </c>
       <c r="E47" s="7">
         <f>IF(OR(A47="",SUMIFS(C$4:C47,A$4:A47,A47)=0),"",SUMPRODUCT((A$4:A47=A47)*(C$4:C47)*(D$4:D47))/SUMIFS(C$4:C47,A$4:A47,A47))</f>
-        <v>31.403669724770641</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>24.5</v>
+      </c>
+      <c r="F47" s="6">
+        <v>28</v>
+      </c>
+      <c r="G47" s="6">
+        <f>IF(C47="","",C47-IF(ISNUMBER(F47),F47,0))</f>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
@@ -8586,31 +8600,33 @@
         <v>21</v>
       </c>
       <c r="B48" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C48" s="6"/>
+        <v>46054</v>
+      </c>
+      <c r="C48" s="6">
+        <v>42</v>
+      </c>
       <c r="D48" s="7">
-        <v>73.5</v>
+        <v>24.5</v>
       </c>
       <c r="E48" s="7">
         <f>IF(OR(A48="",SUMIFS(C$4:C48,A$4:A48,A48)=0),"",SUMPRODUCT((A$4:A48=A48)*(C$4:C48)*(D$4:D48))/SUMIFS(C$4:C48,A$4:A48,A48))</f>
-        <v>31.403669724770641</v>
+        <v>24.5</v>
       </c>
       <c r="F48" s="6"/>
-      <c r="G48" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="G48" s="6">
+        <f>IF(C48="","",C48-IF(ISNUMBER(F48),F48,0))</f>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" s="5">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="C49" s="6">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="D49" s="7">
         <v>24.5</v>
@@ -8621,19 +8637,19 @@
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6">
-        <f t="shared" si="1"/>
-        <v>165</v>
+        <f>IF(C49="","",C49-IF(ISNUMBER(F49),F49,0))</f>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" s="5">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="C50" s="6">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="D50" s="7">
         <v>24.5</v>
@@ -8642,23 +8658,21 @@
         <f>IF(OR(A50="",SUMIFS(C$4:C50,A$4:A50,A50)=0),"",SUMPRODUCT((A$4:A50=A50)*(C$4:C50)*(D$4:D50))/SUMIFS(C$4:C50,A$4:A50,A50))</f>
         <v>24.5</v>
       </c>
-      <c r="F50" s="6">
-        <v>1</v>
-      </c>
+      <c r="F50" s="6"/>
       <c r="G50" s="6">
-        <f t="shared" si="1"/>
-        <v>164</v>
+        <f>IF(C50="","",C50-IF(ISNUMBER(F50),F50,0))</f>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" s="5">
-        <v>46054</v>
+        <v>46143</v>
       </c>
       <c r="C51" s="6">
-        <v>164</v>
+        <v>42</v>
       </c>
       <c r="D51" s="7">
         <v>24.5</v>
@@ -8667,23 +8681,21 @@
         <f>IF(OR(A51="",SUMIFS(C$4:C51,A$4:A51,A51)=0),"",SUMPRODUCT((A$4:A51=A51)*(C$4:C51)*(D$4:D51))/SUMIFS(C$4:C51,A$4:A51,A51))</f>
         <v>24.5</v>
       </c>
-      <c r="F51" s="6">
-        <v>125</v>
-      </c>
+      <c r="F51" s="6"/>
       <c r="G51" s="6">
-        <f t="shared" si="1"/>
-        <v>39</v>
+        <f>IF(C51="","",C51-IF(ISNUMBER(F51),F51,0))</f>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B52" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C52" s="6">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D52" s="7">
         <v>24.5</v>
@@ -8692,154 +8704,150 @@
         <f>IF(OR(A52="",SUMIFS(C$4:C52,A$4:A52,A52)=0),"",SUMPRODUCT((A$4:A52=A52)*(C$4:C52)*(D$4:D52))/SUMIFS(C$4:C52,A$4:A52,A52))</f>
         <v>24.5</v>
       </c>
-      <c r="F52" s="6"/>
+      <c r="F52" s="6">
+        <v>30</v>
+      </c>
       <c r="G52" s="6">
-        <f t="shared" si="1"/>
-        <v>39</v>
+        <f>IF(C52="","",C52-IF(ISNUMBER(F52),F52,0))</f>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B53" s="5">
-        <v>46113</v>
+        <v>46204</v>
       </c>
       <c r="C53" s="6">
-        <v>289</v>
+        <v>12</v>
       </c>
       <c r="D53" s="7">
-        <v>63.86</v>
+        <v>24.5</v>
       </c>
       <c r="E53" s="7">
         <f>IF(OR(A53="",SUMIFS(C$4:C53,A$4:A53,A53)=0),"",SUMPRODUCT((A$4:A53=A53)*(C$4:C53)*(D$4:D53))/SUMIFS(C$4:C53,A$4:A53,A53))</f>
-        <v>38.338248175182486</v>
+        <v>24.5</v>
       </c>
       <c r="F53" s="6">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="G53" s="6">
-        <f t="shared" si="1"/>
-        <v>209</v>
+        <f>IF(C53="","",C53-IF(ISNUMBER(F53),F53,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B54" s="5">
-        <v>46143</v>
+        <v>46204</v>
       </c>
       <c r="C54" s="6">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="D54" s="7">
-        <v>63.86</v>
+        <v>73.5</v>
       </c>
       <c r="E54" s="7">
         <f>IF(OR(A54="",SUMIFS(C$4:C54,A$4:A54,A54)=0),"",SUMPRODUCT((A$4:A54=A54)*(C$4:C54)*(D$4:D54))/SUMIFS(C$4:C54,A$4:A54,A54))</f>
-        <v>43.511910766246359</v>
+        <v>28.25</v>
       </c>
       <c r="F54" s="6">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="G54" s="6">
-        <f t="shared" si="1"/>
-        <v>134</v>
+        <f>IF(C54="","",C54-IF(ISNUMBER(F54),F54,0))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C55" s="6">
         <v>22</v>
       </c>
-      <c r="B55" s="5">
-        <v>46174</v>
-      </c>
-      <c r="C55" s="6">
-        <v>134</v>
-      </c>
       <c r="D55" s="7">
-        <v>63.86</v>
+        <v>59.5</v>
       </c>
       <c r="E55" s="7">
         <f>IF(OR(A55="",SUMIFS(C$4:C55,A$4:A55,A55)=0),"",SUMPRODUCT((A$4:A55=A55)*(C$4:C55)*(D$4:D55))/SUMIFS(C$4:C55,A$4:A55,A55))</f>
-        <v>45.852377682403429</v>
+        <v>29.910628019323671</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6">
-        <f t="shared" si="1"/>
-        <v>134</v>
+        <f>IF(C55="","",C55-IF(ISNUMBER(F55),F55,0))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B56" s="5">
-        <v>46204</v>
-      </c>
-      <c r="C56" s="6">
-        <v>134</v>
-      </c>
+        <v>46235</v>
+      </c>
+      <c r="C56" s="6"/>
       <c r="D56" s="7">
-        <v>63.86</v>
+        <v>73.5</v>
       </c>
       <c r="E56" s="7">
         <f>IF(OR(A56="",SUMIFS(C$4:C56,A$4:A56,A56)=0),"",SUMPRODUCT((A$4:A56=A56)*(C$4:C56)*(D$4:D56))/SUMIFS(C$4:C56,A$4:A56,A56))</f>
-        <v>47.709976905311777</v>
+        <v>29.910628019323671</v>
       </c>
       <c r="F56" s="6"/>
-      <c r="G56" s="6">
-        <f t="shared" si="1"/>
-        <v>134</v>
+      <c r="G56" s="6" t="str">
+        <f>IF(C56="","",C56-IF(ISNUMBER(F56),F56,0))</f>
+        <v/>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="6">
         <v>22</v>
       </c>
-      <c r="B57" s="5">
-        <v>46235</v>
-      </c>
-      <c r="C57" s="6">
-        <v>234</v>
-      </c>
       <c r="D57" s="7">
-        <v>68.62</v>
+        <v>59.5</v>
       </c>
       <c r="E57" s="7">
         <f>IF(OR(A57="",SUMIFS(C$4:C57,A$4:A57,A57)=0),"",SUMPRODUCT((A$4:A57=A57)*(C$4:C57)*(D$4:D57))/SUMIFS(C$4:C57,A$4:A57,A57))</f>
-        <v>50.901722113502935</v>
-      </c>
-      <c r="F57" s="6">
-        <v>185</v>
-      </c>
+        <v>31.403669724770641</v>
+      </c>
+      <c r="F57" s="6"/>
       <c r="G57" s="6">
-        <f t="shared" si="1"/>
-        <v>49</v>
+        <f>IF(C57="","",C57-IF(ISNUMBER(F57),F57,0))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B58" s="5">
         <v>46266</v>
       </c>
-      <c r="C58" s="6">
-        <v>49</v>
-      </c>
+      <c r="C58" s="6"/>
       <c r="D58" s="7">
-        <v>68.62</v>
+        <v>73.5</v>
       </c>
       <c r="E58" s="7">
         <f>IF(OR(A58="",SUMIFS(C$4:C58,A$4:A58,A58)=0),"",SUMPRODUCT((A$4:A58=A58)*(C$4:C58)*(D$4:D58))/SUMIFS(C$4:C58,A$4:A58,A58))</f>
-        <v>51.450518331226299</v>
+        <v>31.403669724770641</v>
       </c>
       <c r="F58" s="6"/>
-      <c r="G58" s="6">
-        <f t="shared" si="1"/>
-        <v>49</v>
+      <c r="G58" s="6" t="str">
+        <f>IF(C58="","",C58-IF(ISNUMBER(F58),F58,0))</f>
+        <v/>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
@@ -8847,22 +8855,22 @@
         <v>22</v>
       </c>
       <c r="B59" s="5">
-        <v>46082</v>
+        <v>45992</v>
       </c>
       <c r="C59" s="6">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="D59" s="7">
-        <v>70</v>
+        <v>24.5</v>
       </c>
       <c r="E59" s="7">
         <f>IF(OR(A59="",SUMIFS(C$4:C59,A$4:A59,A59)=0),"",SUMPRODUCT((A$4:A59=A59)*(C$4:C59)*(D$4:D59))/SUMIFS(C$4:C59,A$4:A59,A59))</f>
-        <v>53.981834061135373</v>
+        <v>24.5</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6">
-        <f t="shared" si="1"/>
-        <v>250</v>
+        <f>IF(C59="","",C59-IF(ISNUMBER(F59),F59,0))</f>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
@@ -8870,252 +8878,262 @@
         <v>22</v>
       </c>
       <c r="B60" s="5">
-        <v>46204</v>
+        <v>46023</v>
       </c>
       <c r="C60" s="6">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="D60" s="7">
-        <v>75</v>
+        <v>24.5</v>
       </c>
       <c r="E60" s="7">
         <f>IF(OR(A60="",SUMIFS(C$4:C60,A$4:A60,A60)=0),"",SUMPRODUCT((A$4:A60=A60)*(C$4:C60)*(D$4:D60))/SUMIFS(C$4:C60,A$4:A60,A60))</f>
-        <v>55.069730848861283</v>
-      </c>
-      <c r="F60" s="6"/>
+        <v>24.5</v>
+      </c>
+      <c r="F60" s="6">
+        <v>1</v>
+      </c>
       <c r="G60" s="6">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>IF(C60="","",C60-IF(ISNUMBER(F60),F60,0))</f>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B61" s="5">
-        <v>45992</v>
+        <v>46054</v>
       </c>
       <c r="C61" s="6">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="D61" s="7">
-        <v>42</v>
+        <v>24.5</v>
       </c>
       <c r="E61" s="7">
         <f>IF(OR(A61="",SUMIFS(C$4:C61,A$4:A61,A61)=0),"",SUMPRODUCT((A$4:A61=A61)*(C$4:C61)*(D$4:D61))/SUMIFS(C$4:C61,A$4:A61,A61))</f>
-        <v>42</v>
-      </c>
-      <c r="F61" s="6"/>
+        <v>24.5</v>
+      </c>
+      <c r="F61" s="6">
+        <v>125</v>
+      </c>
       <c r="G61" s="6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>IF(C61="","",C61-IF(ISNUMBER(F61),F61,0))</f>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B62" s="5">
-        <v>46023</v>
+        <v>46082</v>
       </c>
       <c r="C62" s="6">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D62" s="7">
-        <v>42</v>
+        <v>24.5</v>
       </c>
       <c r="E62" s="7">
         <f>IF(OR(A62="",SUMIFS(C$4:C62,A$4:A62,A62)=0),"",SUMPRODUCT((A$4:A62=A62)*(C$4:C62)*(D$4:D62))/SUMIFS(C$4:C62,A$4:A62,A62))</f>
-        <v>42</v>
+        <v>24.5</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>IF(C62="","",C62-IF(ISNUMBER(F62),F62,0))</f>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B63" s="5">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C63" s="6">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="D63" s="7">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="E63" s="7">
         <f>IF(OR(A63="",SUMIFS(C$4:C63,A$4:A63,A63)=0),"",SUMPRODUCT((A$4:A63=A63)*(C$4:C63)*(D$4:D63))/SUMIFS(C$4:C63,A$4:A63,A63))</f>
-        <v>42</v>
+        <v>39.027458492975732</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>IF(C63="","",C63-IF(ISNUMBER(F63),F63,0))</f>
+        <v>250</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B64" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C64" s="6">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="D64" s="7">
-        <v>42</v>
+        <v>63.86</v>
       </c>
       <c r="E64" s="7">
         <f>IF(OR(A64="",SUMIFS(C$4:C64,A$4:A64,A64)=0),"",SUMPRODUCT((A$4:A64=A64)*(C$4:C64)*(D$4:D64))/SUMIFS(C$4:C64,A$4:A64,A64))</f>
-        <v>42</v>
-      </c>
-      <c r="F64" s="6"/>
+        <v>45.722052238805972</v>
+      </c>
+      <c r="F64" s="6">
+        <v>80</v>
+      </c>
       <c r="G64" s="6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>IF(C64="","",C64-IF(ISNUMBER(F64),F64,0))</f>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B65" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C65" s="6">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="D65" s="7">
-        <v>42</v>
+        <v>63.86</v>
       </c>
       <c r="E65" s="7">
         <f>IF(OR(A65="",SUMIFS(C$4:C65,A$4:A65,A65)=0),"",SUMPRODUCT((A$4:A65=A65)*(C$4:C65)*(D$4:D65))/SUMIFS(C$4:C65,A$4:A65,A65))</f>
-        <v>42</v>
-      </c>
-      <c r="F65" s="6"/>
+        <v>48.681327088212335</v>
+      </c>
+      <c r="F65" s="6">
+        <v>75</v>
+      </c>
       <c r="G65" s="6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>IF(C65="","",C65-IF(ISNUMBER(F65),F65,0))</f>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B66" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C66" s="6">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="D66" s="7">
-        <v>42</v>
+        <v>63.86</v>
       </c>
       <c r="E66" s="7">
         <f>IF(OR(A66="",SUMIFS(C$4:C66,A$4:A66,A66)=0),"",SUMPRODUCT((A$4:A66=A66)*(C$4:C66)*(D$4:D66))/SUMIFS(C$4:C66,A$4:A66,A66))</f>
-        <v>42</v>
+        <v>50.118742049469965</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>IF(C66="","",C66-IF(ISNUMBER(F66),F66,0))</f>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B67" s="5">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="C67" s="6">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="D67" s="7">
-        <v>42</v>
+        <v>63.86</v>
       </c>
       <c r="E67" s="7">
         <f>IF(OR(A67="",SUMIFS(C$4:C67,A$4:A67,A67)=0),"",SUMPRODUCT((A$4:A67=A67)*(C$4:C67)*(D$4:D67))/SUMIFS(C$4:C67,A$4:A67,A67))</f>
-        <v>42</v>
+        <v>51.307462879276962</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f>IF(C67="","",C67-IF(ISNUMBER(F67),F67,0))</f>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B68" s="5">
         <v>46204</v>
       </c>
       <c r="C68" s="6">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D68" s="7">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="E68" s="7">
         <f>IF(OR(A68="",SUMIFS(C$4:C68,A$4:A68,A68)=0),"",SUMPRODUCT((A$4:A68=A68)*(C$4:C68)*(D$4:D68))/SUMIFS(C$4:C68,A$4:A68,A68))</f>
-        <v>42</v>
+        <v>52.744244996967865</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6">
-        <f t="shared" ref="G68:G99" si="2">IF(C68="","",C68-IF(ISNUMBER(F68),F68,0))</f>
-        <v>30</v>
+        <f>IF(C68="","",C68-IF(ISNUMBER(F68),F68,0))</f>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B69" s="5">
         <v>46235</v>
       </c>
       <c r="C69" s="6">
-        <v>30</v>
+        <v>234</v>
       </c>
       <c r="D69" s="7">
-        <v>42</v>
+        <v>68.62</v>
       </c>
       <c r="E69" s="7">
         <f>IF(OR(A69="",SUMIFS(C$4:C69,A$4:A69,A69)=0),"",SUMPRODUCT((A$4:A69=A69)*(C$4:C69)*(D$4:D69))/SUMIFS(C$4:C69,A$4:A69,A69))</f>
-        <v>42</v>
-      </c>
-      <c r="F69" s="6"/>
+        <v>54.717121614445041</v>
+      </c>
+      <c r="F69" s="6">
+        <v>185</v>
+      </c>
       <c r="G69" s="6">
-        <f t="shared" si="2"/>
-        <v>30</v>
+        <f>IF(C69="","",C69-IF(ISNUMBER(F69),F69,0))</f>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B70" s="5">
         <v>46266</v>
       </c>
       <c r="C70" s="6">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D70" s="7">
-        <v>42</v>
+        <v>68.62</v>
       </c>
       <c r="E70" s="7">
         <f>IF(OR(A70="",SUMIFS(C$4:C70,A$4:A70,A70)=0),"",SUMPRODUCT((A$4:A70=A70)*(C$4:C70)*(D$4:D70))/SUMIFS(C$4:C70,A$4:A70,A70))</f>
-        <v>42</v>
+        <v>55.06973084886129</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="6">
-        <f t="shared" si="2"/>
-        <v>30</v>
+        <f>IF(C70="","",C70-IF(ISNUMBER(F70),F70,0))</f>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
@@ -9123,10 +9141,10 @@
         <v>23</v>
       </c>
       <c r="B71" s="5">
-        <v>46143</v>
+        <v>45992</v>
       </c>
       <c r="C71" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D71" s="7">
         <v>42</v>
@@ -9137,19 +9155,19 @@
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="6">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <f>IF(C71="","",C71-IF(ISNUMBER(F71),F71,0))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B72" s="5">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="C72" s="6">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D72" s="7">
         <v>42</v>
@@ -9158,223 +9176,217 @@
         <f>IF(OR(A72="",SUMIFS(C$4:C72,A$4:A72,A72)=0),"",SUMPRODUCT((A$4:A72=A72)*(C$4:C72)*(D$4:D72))/SUMIFS(C$4:C72,A$4:A72,A72))</f>
         <v>42</v>
       </c>
-      <c r="F72" s="6">
-        <v>2</v>
-      </c>
+      <c r="F72" s="6"/>
       <c r="G72" s="6">
-        <f t="shared" si="2"/>
-        <v>106</v>
+        <f>IF(C72="","",C72-IF(ISNUMBER(F72),F72,0))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B73" s="5">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C73" s="6">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="D73" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E73" s="7">
         <f>IF(OR(A73="",SUMIFS(C$4:C73,A$4:A73,A73)=0),"",SUMPRODUCT((A$4:A73=A73)*(C$4:C73)*(D$4:D73))/SUMIFS(C$4:C73,A$4:A73,A73))</f>
-        <v>29.567289719626167</v>
-      </c>
-      <c r="F73" s="6">
-        <v>16</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F73" s="6"/>
       <c r="G73" s="6">
-        <f t="shared" si="2"/>
-        <v>90</v>
+        <f>IF(C73="","",C73-IF(ISNUMBER(F73),F73,0))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B74" s="5">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C74" s="6">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D74" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E74" s="7">
         <f>IF(OR(A74="",SUMIFS(C$4:C74,A$4:A74,A74)=0),"",SUMPRODUCT((A$4:A74=A74)*(C$4:C74)*(D$4:D74))/SUMIFS(C$4:C74,A$4:A74,A74))</f>
-        <v>25.817105263157895</v>
+        <v>42</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="6">
-        <f t="shared" si="2"/>
-        <v>90</v>
+        <f>IF(C74="","",C74-IF(ISNUMBER(F74),F74,0))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B75" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C75" s="6">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D75" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E75" s="7">
         <f>IF(OR(A75="",SUMIFS(C$4:C75,A$4:A75,A75)=0),"",SUMPRODUCT((A$4:A75=A75)*(C$4:C75)*(D$4:D75))/SUMIFS(C$4:C75,A$4:A75,A75))</f>
-        <v>23.78020304568528</v>
+        <v>42</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="6">
-        <f t="shared" si="2"/>
-        <v>90</v>
+        <f>IF(C75="","",C75-IF(ISNUMBER(F75),F75,0))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B76" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C76" s="6">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D76" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E76" s="7">
         <f>IF(OR(A76="",SUMIFS(C$4:C76,A$4:A76,A76)=0),"",SUMPRODUCT((A$4:A76=A76)*(C$4:C76)*(D$4:D76))/SUMIFS(C$4:C76,A$4:A76,A76))</f>
-        <v>22.500826446280993</v>
+        <v>42</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="6">
-        <f t="shared" si="2"/>
-        <v>90</v>
+        <f>IF(C76="","",C76-IF(ISNUMBER(F76),F76,0))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B77" s="5">
         <v>46143</v>
       </c>
       <c r="C77" s="6">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D77" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E77" s="7">
         <f>IF(OR(A77="",SUMIFS(C$4:C77,A$4:A77,A77)=0),"",SUMPRODUCT((A$4:A77=A77)*(C$4:C77)*(D$4:D77))/SUMIFS(C$4:C77,A$4:A77,A77))</f>
-        <v>21.622648083623695</v>
-      </c>
-      <c r="F77" s="6">
-        <v>18</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F77" s="6"/>
       <c r="G77" s="6">
-        <f t="shared" si="2"/>
-        <v>72</v>
+        <f>IF(C77="","",C77-IF(ISNUMBER(F77),F77,0))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B78" s="5">
         <v>46174</v>
       </c>
       <c r="C78" s="6">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D78" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E78" s="7">
         <f>IF(OR(A78="",SUMIFS(C$4:C78,A$4:A78,A78)=0),"",SUMPRODUCT((A$4:A78=A78)*(C$4:C78)*(D$4:D78))/SUMIFS(C$4:C78,A$4:A78,A78))</f>
-        <v>21.096284829721359</v>
+        <v>42</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="6">
-        <f t="shared" si="2"/>
-        <v>72</v>
+        <f>IF(C78="","",C78-IF(ISNUMBER(F78),F78,0))</f>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B79" s="5">
         <v>46204</v>
       </c>
       <c r="C79" s="6">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D79" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E79" s="7">
         <f>IF(OR(A79="",SUMIFS(C$4:C79,A$4:A79,A79)=0),"",SUMPRODUCT((A$4:A79=A79)*(C$4:C79)*(D$4:D79))/SUMIFS(C$4:C79,A$4:A79,A79))</f>
-        <v>20.675487465181057</v>
+        <v>42</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6">
-        <f t="shared" si="2"/>
-        <v>72</v>
+        <f>IF(C79="","",C79-IF(ISNUMBER(F79),F79,0))</f>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B80" s="5">
         <v>46235</v>
       </c>
       <c r="C80" s="6">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D80" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E80" s="7">
         <f>IF(OR(A80="",SUMIFS(C$4:C80,A$4:A80,A80)=0),"",SUMPRODUCT((A$4:A80=A80)*(C$4:C80)*(D$4:D80))/SUMIFS(C$4:C80,A$4:A80,A80))</f>
-        <v>20.331392405063287</v>
+        <v>42</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="6">
-        <f t="shared" si="2"/>
-        <v>72</v>
+        <f>IF(C80="","",C80-IF(ISNUMBER(F80),F80,0))</f>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B81" s="5">
         <v>46266</v>
       </c>
       <c r="C81" s="6">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D81" s="7">
-        <v>16.899999999999999</v>
+        <v>42</v>
       </c>
       <c r="E81" s="7">
         <f>IF(OR(A81="",SUMIFS(C$4:C81,A$4:A81,A81)=0),"",SUMPRODUCT((A$4:A81=A81)*(C$4:C81)*(D$4:D81))/SUMIFS(C$4:C81,A$4:A81,A81))</f>
-        <v>20.044779582366587</v>
+        <v>42</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="6">
-        <f t="shared" si="2"/>
-        <v>72</v>
+        <f>IF(C81="","",C81-IF(ISNUMBER(F81),F81,0))</f>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.4">
@@ -9388,7 +9400,7 @@
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G68:G99" si="0">IF(C82="","",C82-IF(ISNUMBER(F82),F82,0))</f>
         <v/>
       </c>
     </row>
@@ -9403,7 +9415,7 @@
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9418,7 +9430,7 @@
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9433,7 +9445,7 @@
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9448,7 +9460,7 @@
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9463,7 +9475,7 @@
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9478,7 +9490,7 @@
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9493,7 +9505,7 @@
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9508,7 +9520,7 @@
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9523,7 +9535,7 @@
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9538,7 +9550,7 @@
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9553,7 +9565,7 @@
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9568,7 +9580,7 @@
       </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9583,7 +9595,7 @@
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9598,7 +9610,7 @@
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9613,7 +9625,7 @@
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9628,7 +9640,7 @@
       </c>
       <c r="F98" s="6"/>
       <c r="G98" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9643,7 +9655,7 @@
       </c>
       <c r="F99" s="6"/>
       <c r="G99" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9658,7 +9670,7 @@
       </c>
       <c r="F100" s="6"/>
       <c r="G100" s="6" t="str">
-        <f t="shared" ref="G100:G131" si="3">IF(C100="","",C100-IF(ISNUMBER(F100),F100,0))</f>
+        <f t="shared" ref="G100:G131" si="1">IF(C100="","",C100-IF(ISNUMBER(F100),F100,0))</f>
         <v/>
       </c>
     </row>
@@ -9673,7 +9685,7 @@
       </c>
       <c r="F101" s="6"/>
       <c r="G101" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9688,7 +9700,7 @@
       </c>
       <c r="F102" s="6"/>
       <c r="G102" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9703,7 +9715,7 @@
       </c>
       <c r="F103" s="6"/>
       <c r="G103" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9718,7 +9730,7 @@
       </c>
       <c r="F104" s="6"/>
       <c r="G104" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9733,7 +9745,7 @@
       </c>
       <c r="F105" s="6"/>
       <c r="G105" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9748,7 +9760,7 @@
       </c>
       <c r="F106" s="6"/>
       <c r="G106" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9763,7 +9775,7 @@
       </c>
       <c r="F107" s="6"/>
       <c r="G107" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9778,7 +9790,7 @@
       </c>
       <c r="F108" s="6"/>
       <c r="G108" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9793,7 +9805,7 @@
       </c>
       <c r="F109" s="6"/>
       <c r="G109" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9808,7 +9820,7 @@
       </c>
       <c r="F110" s="6"/>
       <c r="G110" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9823,7 +9835,7 @@
       </c>
       <c r="F111" s="6"/>
       <c r="G111" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9842,7 +9854,7 @@
       </c>
       <c r="E112" s="10">
         <f>AVERAGEIF(E4:E111,"&lt;&gt;0")</f>
-        <v>32.407821946706441</v>
+        <v>31.713622544727247</v>
       </c>
       <c r="F112" s="9">
         <f>SUM(F4:F111)</f>
@@ -9854,6 +9866,10 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A4:G81">
+    <sortCondition ref="A4:A81"/>
+    <sortCondition ref="B4:B81"/>
+  </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>

--- a/data.xlsx
+++ b/data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="38">
   <si>
     <t>시트구분</t>
   </si>
@@ -189,7 +189,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,6 +206,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -236,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -265,6 +271,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -927,17 +945,17 @@
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="13">
         <v>46082</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7">
+      <c r="C10" s="14"/>
+      <c r="D10" s="15">
         <v>89.5</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="14">
         <v>197</v>
       </c>
       <c r="F10" s="6">
@@ -951,19 +969,19 @@
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="13">
         <v>46113</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="14">
         <v>300</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="15">
         <v>104.5</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="14">
         <v>199</v>
       </c>
       <c r="F11" s="6">
@@ -977,17 +995,17 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="13">
         <v>46113</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7">
+      <c r="C12" s="14"/>
+      <c r="D12" s="15">
         <v>89.5</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="14">
         <v>31</v>
       </c>
       <c r="F12" s="6">
@@ -1001,17 +1019,17 @@
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="13">
         <v>46143</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7">
+      <c r="C13" s="14"/>
+      <c r="D13" s="15">
         <v>103.1</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="6">
         <f>IF(A13="","",IFERROR(LOOKUP(2,1/(A$4:A12=A13),F$4:F12),0)+IF(ISNUMBER(C13),C13,0)-IF(ISNUMBER(E13),E13,0))</f>
         <v>101</v>
@@ -1023,17 +1041,17 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="13">
         <v>46174</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7">
+      <c r="C14" s="14"/>
+      <c r="D14" s="15">
         <v>103.1</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="14">
         <v>73</v>
       </c>
       <c r="F14" s="6">
@@ -1047,17 +1065,17 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="13">
         <v>46204</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7">
+      <c r="C15" s="14"/>
+      <c r="D15" s="15">
         <v>103.1</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="6">
         <f>IF(A15="","",IFERROR(LOOKUP(2,1/(A$4:A14=A15),F$4:F14),0)+IF(ISNUMBER(C15),C15,0)-IF(ISNUMBER(E15),E15,0))</f>
         <v>28</v>
@@ -1069,17 +1087,17 @@
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="13">
         <v>46235</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7">
+      <c r="C16" s="14"/>
+      <c r="D16" s="15">
         <v>103.1</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="14"/>
       <c r="F16" s="6">
         <f>IF(A16="","",IFERROR(LOOKUP(2,1/(A$4:A15=A16),F$4:F15),0)+IF(ISNUMBER(C16),C16,0)-IF(ISNUMBER(E16),E16,0))</f>
         <v>28</v>
@@ -1091,19 +1109,19 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="13">
         <v>46266</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="14">
         <v>672</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="15">
         <v>112.5</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="14"/>
       <c r="F17" s="6">
         <f>IF(A17="","",IFERROR(LOOKUP(2,1/(A$4:A16=A17),F$4:F16),0)+IF(ISNUMBER(C17),C17,0)-IF(ISNUMBER(E17),E17,0))</f>
         <v>700</v>
@@ -1115,17 +1133,17 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="13">
         <v>46266</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7">
+      <c r="C18" s="14"/>
+      <c r="D18" s="15">
         <v>103.1</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="14"/>
       <c r="F18" s="6">
         <f>IF(A18="","",IFERROR(LOOKUP(2,1/(A$4:A17=A18),F$4:F17),0)+IF(ISNUMBER(C18),C18,0)-IF(ISNUMBER(E18),E18,0))</f>
         <v>700</v>
@@ -1137,17 +1155,17 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="13">
         <v>46296</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7">
+      <c r="C19" s="14"/>
+      <c r="D19" s="15">
         <v>112.14</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="14">
         <v>140</v>
       </c>
       <c r="F19" s="6">
@@ -1161,17 +1179,17 @@
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="13">
         <v>45931</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7">
+      <c r="C20" s="14"/>
+      <c r="D20" s="15">
         <v>73.5</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="6">
         <f>IF(A20="","",IFERROR(LOOKUP(2,1/(A$4:A19=A20),F$4:F19),0)+IF(ISNUMBER(C20),C20,0)-IF(ISNUMBER(E20),E20,0))</f>
         <v>0</v>
@@ -1183,17 +1201,17 @@
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="13">
         <v>45962</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7">
+      <c r="C21" s="14"/>
+      <c r="D21" s="15">
         <v>73.5</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="6">
         <f>IF(A21="","",IFERROR(LOOKUP(2,1/(A$4:A20=A21),F$4:F20),0)+IF(ISNUMBER(C21),C21,0)-IF(ISNUMBER(E21),E21,0))</f>
         <v>0</v>
@@ -1205,17 +1223,17 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="13">
         <v>45992</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7">
+      <c r="C22" s="14"/>
+      <c r="D22" s="15">
         <v>73.5</v>
       </c>
-      <c r="E22" s="6"/>
+      <c r="E22" s="14"/>
       <c r="F22" s="6">
         <f>IF(A22="","",IFERROR(LOOKUP(2,1/(A$4:A21=A22),F$4:F21),0)+IF(ISNUMBER(C22),C22,0)-IF(ISNUMBER(E22),E22,0))</f>
         <v>0</v>
@@ -1227,17 +1245,17 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="13">
         <v>46023</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7">
+      <c r="C23" s="14"/>
+      <c r="D23" s="15">
         <v>73.5</v>
       </c>
-      <c r="E23" s="6"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="6">
         <f>IF(A23="","",IFERROR(LOOKUP(2,1/(A$4:A22=A23),F$4:F22),0)+IF(ISNUMBER(C23),C23,0)-IF(ISNUMBER(E23),E23,0))</f>
         <v>0</v>
@@ -1249,17 +1267,17 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="13">
         <v>46054</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7">
+      <c r="C24" s="14"/>
+      <c r="D24" s="15">
         <v>73.5</v>
       </c>
-      <c r="E24" s="6"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="6">
         <f>IF(A24="","",IFERROR(LOOKUP(2,1/(A$4:A23=A24),F$4:F23),0)+IF(ISNUMBER(C24),C24,0)-IF(ISNUMBER(E24),E24,0))</f>
         <v>0</v>
@@ -1271,17 +1289,17 @@
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="13">
         <v>46082</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7">
+      <c r="C25" s="14"/>
+      <c r="D25" s="15">
         <v>73.5</v>
       </c>
-      <c r="E25" s="6"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="6">
         <f>IF(A25="","",IFERROR(LOOKUP(2,1/(A$4:A24=A25),F$4:F24),0)+IF(ISNUMBER(C25),C25,0)-IF(ISNUMBER(E25),E25,0))</f>
         <v>0</v>
@@ -1293,17 +1311,17 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="13">
         <v>46113</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7">
+      <c r="C26" s="14"/>
+      <c r="D26" s="15">
         <v>73.5</v>
       </c>
-      <c r="E26" s="6"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="6">
         <f>IF(A26="","",IFERROR(LOOKUP(2,1/(A$4:A25=A26),F$4:F25),0)+IF(ISNUMBER(C26),C26,0)-IF(ISNUMBER(E26),E26,0))</f>
         <v>0</v>
@@ -1315,17 +1333,17 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="13">
         <v>46143</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7">
+      <c r="C27" s="14"/>
+      <c r="D27" s="15">
         <v>73.5</v>
       </c>
-      <c r="E27" s="6"/>
+      <c r="E27" s="14"/>
       <c r="F27" s="6">
         <f>IF(A27="","",IFERROR(LOOKUP(2,1/(A$4:A26=A27),F$4:F26),0)+IF(ISNUMBER(C27),C27,0)-IF(ISNUMBER(E27),E27,0))</f>
         <v>0</v>
@@ -1337,19 +1355,19 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="13">
         <v>46174</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="14">
         <v>600</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="15">
         <v>91.4</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="14">
         <v>5</v>
       </c>
       <c r="F28" s="6">
@@ -1363,17 +1381,17 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="13">
         <v>46174</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7">
+      <c r="C29" s="14"/>
+      <c r="D29" s="15">
         <v>73.5</v>
       </c>
-      <c r="E29" s="6"/>
+      <c r="E29" s="14"/>
       <c r="F29" s="6">
         <f>IF(A29="","",IFERROR(LOOKUP(2,1/(A$4:A28=A29),F$4:F28),0)+IF(ISNUMBER(C29),C29,0)-IF(ISNUMBER(E29),E29,0))</f>
         <v>595</v>
@@ -1385,17 +1403,17 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="13">
         <v>46204</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7">
+      <c r="C30" s="14"/>
+      <c r="D30" s="15">
         <v>91.4</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="14">
         <v>18</v>
       </c>
       <c r="F30" s="6">
@@ -1409,17 +1427,17 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="13">
         <v>46235</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7">
+      <c r="C31" s="14"/>
+      <c r="D31" s="15">
         <v>91.4</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="14">
         <v>80</v>
       </c>
       <c r="F31" s="6">
@@ -1433,17 +1451,17 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="13">
         <v>46266</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7">
+      <c r="C32" s="14"/>
+      <c r="D32" s="15">
         <v>91.4</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="14">
         <v>28</v>
       </c>
       <c r="F32" s="6">
@@ -1457,17 +1475,17 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="13">
         <v>46296</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7">
+      <c r="C33" s="14"/>
+      <c r="D33" s="15">
         <v>91.4</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="14">
         <v>30</v>
       </c>
       <c r="F33" s="6">
@@ -1481,17 +1499,17 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="13">
         <v>45931</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7">
+      <c r="C34" s="14"/>
+      <c r="D34" s="15">
         <v>177.6</v>
       </c>
-      <c r="E34" s="6"/>
+      <c r="E34" s="14"/>
       <c r="F34" s="6">
         <f>IF(A34="","",IFERROR(LOOKUP(2,1/(A$4:A33=A34),F$4:F33),0)+IF(ISNUMBER(C34),C34,0)-IF(ISNUMBER(E34),E34,0))</f>
         <v>0</v>
@@ -1503,17 +1521,17 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="13">
         <v>45962</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7">
+      <c r="C35" s="14"/>
+      <c r="D35" s="15">
         <v>177.6</v>
       </c>
-      <c r="E35" s="6"/>
+      <c r="E35" s="14"/>
       <c r="F35" s="6">
         <f>IF(A35="","",IFERROR(LOOKUP(2,1/(A$4:A34=A35),F$4:F34),0)+IF(ISNUMBER(C35),C35,0)-IF(ISNUMBER(E35),E35,0))</f>
         <v>0</v>
@@ -1525,19 +1543,19 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="13">
         <v>45992</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="14">
         <v>27</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="15">
         <v>177.6</v>
       </c>
-      <c r="E36" s="6"/>
+      <c r="E36" s="14"/>
       <c r="F36" s="6">
         <f>IF(A36="","",IFERROR(LOOKUP(2,1/(A$4:A35=A36),F$4:F35),0)+IF(ISNUMBER(C36),C36,0)-IF(ISNUMBER(E36),E36,0))</f>
         <v>27</v>
@@ -1549,19 +1567,19 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="13">
         <v>46023</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="14">
         <v>200</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="15">
         <v>182.6</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="14">
         <v>61</v>
       </c>
       <c r="F37" s="6">
@@ -1575,17 +1593,17 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="13">
         <v>46023</v>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7">
+      <c r="C38" s="14"/>
+      <c r="D38" s="15">
         <v>177.6</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="14">
         <v>27</v>
       </c>
       <c r="F38" s="6">
@@ -1599,17 +1617,17 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="13">
         <v>46054</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7">
+      <c r="C39" s="14"/>
+      <c r="D39" s="15">
         <v>177.6</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="14">
         <v>20</v>
       </c>
       <c r="F39" s="6">
@@ -1623,17 +1641,17 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="13">
         <v>46082</v>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7">
+      <c r="C40" s="14"/>
+      <c r="D40" s="15">
         <v>177.6</v>
       </c>
-      <c r="E40" s="6"/>
+      <c r="E40" s="14"/>
       <c r="F40" s="6">
         <f>IF(A40="","",IFERROR(LOOKUP(2,1/(A$4:A39=A40),F$4:F39),0)+IF(ISNUMBER(C40),C40,0)-IF(ISNUMBER(E40),E40,0))</f>
         <v>119</v>
@@ -1645,17 +1663,17 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="13">
         <v>46113</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7">
+      <c r="C41" s="14"/>
+      <c r="D41" s="15">
         <v>177.6</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="14">
         <v>49</v>
       </c>
       <c r="F41" s="6">
@@ -1669,17 +1687,17 @@
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="13">
         <v>46143</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7">
+      <c r="C42" s="14"/>
+      <c r="D42" s="15">
         <v>177.6</v>
       </c>
-      <c r="E42" s="6"/>
+      <c r="E42" s="14"/>
       <c r="F42" s="6">
         <f>IF(A42="","",IFERROR(LOOKUP(2,1/(A$4:A41=A42),F$4:F41),0)+IF(ISNUMBER(C42),C42,0)-IF(ISNUMBER(E42),E42,0))</f>
         <v>70</v>
@@ -1691,17 +1709,17 @@
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="13">
         <v>46174</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7">
+      <c r="C43" s="14"/>
+      <c r="D43" s="15">
         <v>177.6</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="14">
         <v>15</v>
       </c>
       <c r="F43" s="6">
@@ -1715,19 +1733,19 @@
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="13">
         <v>46204</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="14">
         <v>200</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="15">
         <v>206.9</v>
       </c>
-      <c r="E44" s="6"/>
+      <c r="E44" s="14"/>
       <c r="F44" s="6">
         <f>IF(A44="","",IFERROR(LOOKUP(2,1/(A$4:A43=A44),F$4:F43),0)+IF(ISNUMBER(C44),C44,0)-IF(ISNUMBER(E44),E44,0))</f>
         <v>255</v>
@@ -1739,17 +1757,17 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="13">
         <v>46204</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7">
+      <c r="C45" s="14"/>
+      <c r="D45" s="15">
         <v>177.6</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="14">
         <v>46</v>
       </c>
       <c r="F45" s="6">
@@ -1763,17 +1781,17 @@
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="13">
         <v>46235</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7">
+      <c r="C46" s="14"/>
+      <c r="D46" s="15">
         <v>206.9</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="14">
         <v>67</v>
       </c>
       <c r="F46" s="6">
@@ -1787,17 +1805,17 @@
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="13">
         <v>46235</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7">
+      <c r="C47" s="14"/>
+      <c r="D47" s="15">
         <v>177.6</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="14">
         <v>9</v>
       </c>
       <c r="F47" s="6">
@@ -1811,17 +1829,17 @@
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="13">
         <v>46266</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7">
+      <c r="C48" s="14"/>
+      <c r="D48" s="15">
         <v>200.58</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="14">
         <v>60</v>
       </c>
       <c r="F48" s="6">
@@ -1835,17 +1853,17 @@
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="13">
         <v>46296</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7">
+      <c r="C49" s="14"/>
+      <c r="D49" s="15">
         <v>200.58</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="14">
         <v>50</v>
       </c>
       <c r="F49" s="6">
@@ -1859,17 +1877,17 @@
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="13">
         <v>45931</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7">
+      <c r="C50" s="14"/>
+      <c r="D50" s="15">
         <v>78</v>
       </c>
-      <c r="E50" s="6"/>
+      <c r="E50" s="14"/>
       <c r="F50" s="6">
         <f>IF(A50="","",IFERROR(LOOKUP(2,1/(A$4:A49=A50),F$4:F49),0)+IF(ISNUMBER(C50),C50,0)-IF(ISNUMBER(E50),E50,0))</f>
         <v>0</v>
@@ -1881,17 +1899,17 @@
       <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="13">
         <v>45962</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7">
+      <c r="C51" s="14"/>
+      <c r="D51" s="15">
         <v>78</v>
       </c>
-      <c r="E51" s="6"/>
+      <c r="E51" s="14"/>
       <c r="F51" s="6">
         <f>IF(A51="","",IFERROR(LOOKUP(2,1/(A$4:A50=A51),F$4:F50),0)+IF(ISNUMBER(C51),C51,0)-IF(ISNUMBER(E51),E51,0))</f>
         <v>0</v>
@@ -1903,17 +1921,17 @@
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="13">
         <v>45992</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7">
+      <c r="C52" s="14"/>
+      <c r="D52" s="15">
         <v>78</v>
       </c>
-      <c r="E52" s="6"/>
+      <c r="E52" s="14"/>
       <c r="F52" s="6">
         <f>IF(A52="","",IFERROR(LOOKUP(2,1/(A$4:A51=A52),F$4:F51),0)+IF(ISNUMBER(C52),C52,0)-IF(ISNUMBER(E52),E52,0))</f>
         <v>0</v>
@@ -1925,17 +1943,17 @@
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="13">
         <v>46023</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7">
+      <c r="C53" s="14"/>
+      <c r="D53" s="15">
         <v>78</v>
       </c>
-      <c r="E53" s="6"/>
+      <c r="E53" s="14"/>
       <c r="F53" s="6">
         <f>IF(A53="","",IFERROR(LOOKUP(2,1/(A$4:A52=A53),F$4:F52),0)+IF(ISNUMBER(C53),C53,0)-IF(ISNUMBER(E53),E53,0))</f>
         <v>0</v>
@@ -1947,17 +1965,17 @@
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="13">
         <v>46054</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="7">
+      <c r="C54" s="14"/>
+      <c r="D54" s="15">
         <v>78</v>
       </c>
-      <c r="E54" s="6"/>
+      <c r="E54" s="14"/>
       <c r="F54" s="6">
         <f>IF(A54="","",IFERROR(LOOKUP(2,1/(A$4:A53=A54),F$4:F53),0)+IF(ISNUMBER(C54),C54,0)-IF(ISNUMBER(E54),E54,0))</f>
         <v>0</v>
@@ -1969,15 +1987,15 @@
       <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="13">
         <v>46054</v>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="6"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="14"/>
       <c r="F55" s="6">
         <f>IF(A55="","",IFERROR(LOOKUP(2,1/(A$4:A54=A55),F$4:F54),0)+IF(ISNUMBER(C55),C55,0)-IF(ISNUMBER(E55),E55,0))</f>
         <v>0</v>
@@ -1989,19 +2007,19 @@
       <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="13">
         <v>46082</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="14">
         <v>70</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="15">
         <v>89.9</v>
       </c>
-      <c r="E56" s="6"/>
+      <c r="E56" s="14"/>
       <c r="F56" s="6">
         <f>IF(A56="","",IFERROR(LOOKUP(2,1/(A$4:A55=A56),F$4:F55),0)+IF(ISNUMBER(C56),C56,0)-IF(ISNUMBER(E56),E56,0))</f>
         <v>70</v>
@@ -2013,19 +2031,19 @@
       <c r="I56" s="7"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="13">
         <v>46113</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="14">
         <v>230</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="15">
         <v>98.5</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E57" s="14">
         <v>80</v>
       </c>
       <c r="F57" s="6">
@@ -2039,17 +2057,17 @@
       <c r="I57" s="7"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58" s="13">
         <v>46113</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="7">
+      <c r="C58" s="14"/>
+      <c r="D58" s="15">
         <v>89.9</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="14">
         <v>70</v>
       </c>
       <c r="F58" s="6">
@@ -2063,17 +2081,17 @@
       <c r="I58" s="7"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="13">
         <v>46143</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="7">
+      <c r="C59" s="14"/>
+      <c r="D59" s="15">
         <v>96.49</v>
       </c>
-      <c r="E59" s="6"/>
+      <c r="E59" s="14"/>
       <c r="F59" s="6">
         <f>IF(A59="","",IFERROR(LOOKUP(2,1/(A$4:A58=A59),F$4:F58),0)+IF(ISNUMBER(C59),C59,0)-IF(ISNUMBER(E59),E59,0))</f>
         <v>150</v>
@@ -2085,17 +2103,17 @@
       <c r="I59" s="7"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60" s="13">
         <v>46174</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="7">
+      <c r="C60" s="14"/>
+      <c r="D60" s="15">
         <v>96.49</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E60" s="14">
         <v>61</v>
       </c>
       <c r="F60" s="6">
@@ -2109,17 +2127,17 @@
       <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61" s="13">
         <v>46204</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="7">
+      <c r="C61" s="14"/>
+      <c r="D61" s="15">
         <v>96.49</v>
       </c>
-      <c r="E61" s="6">
+      <c r="E61" s="14">
         <v>85</v>
       </c>
       <c r="F61" s="6">
@@ -2133,19 +2151,19 @@
       <c r="I61" s="7"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62" s="13">
         <v>46235</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="14">
         <v>300</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="15">
         <v>106.8</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E62" s="14">
         <v>26</v>
       </c>
       <c r="F62" s="6">
@@ -2159,17 +2177,17 @@
       <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63" s="13">
         <v>46235</v>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="7">
+      <c r="C63" s="14"/>
+      <c r="D63" s="15">
         <v>96.49</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E63" s="14">
         <v>4</v>
       </c>
       <c r="F63" s="6">
@@ -2183,17 +2201,17 @@
       <c r="I63" s="7"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64" s="13">
         <v>46266</v>
       </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="7">
+      <c r="C64" s="14"/>
+      <c r="D64" s="15">
         <v>106.66</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E64" s="14">
         <v>30</v>
       </c>
       <c r="F64" s="6">
@@ -2207,19 +2225,19 @@
       <c r="I64" s="7"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="13">
         <v>46266</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="14">
         <v>200</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="15">
         <v>104.8</v>
       </c>
-      <c r="E65" s="6"/>
+      <c r="E65" s="14"/>
       <c r="F65" s="6">
         <f>IF(A65="","",IFERROR(LOOKUP(2,1/(A$4:A64=A65),F$4:F64),0)+IF(ISNUMBER(C65),C65,0)-IF(ISNUMBER(E65),E65,0))</f>
         <v>444</v>
@@ -2231,17 +2249,17 @@
       <c r="I65" s="7"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B66" s="13">
         <v>46296</v>
       </c>
-      <c r="C66" s="6"/>
-      <c r="D66" s="7">
+      <c r="C66" s="14"/>
+      <c r="D66" s="15">
         <v>105.88</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="14">
         <v>25</v>
       </c>
       <c r="F66" s="6">
@@ -2255,19 +2273,19 @@
       <c r="I66" s="7"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B67" s="13">
         <v>45931</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="14">
         <v>800</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="15">
         <v>75.900000000000006</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E67" s="14">
         <v>650</v>
       </c>
       <c r="F67" s="6">
@@ -2281,19 +2299,19 @@
       <c r="I67" s="7"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68" s="13">
         <v>45962</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="14">
         <v>700</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="15">
         <v>84.9</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68" s="14">
         <v>520</v>
       </c>
       <c r="F68" s="6">
@@ -2307,17 +2325,17 @@
       <c r="I68" s="7"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69" s="13">
         <v>45962</v>
       </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="7">
+      <c r="C69" s="14"/>
+      <c r="D69" s="15">
         <v>75.900000000000006</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E69" s="14">
         <v>150</v>
       </c>
       <c r="F69" s="6">
@@ -2331,19 +2349,19 @@
       <c r="I69" s="7"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B70" s="13">
         <v>45992</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="14">
         <v>150</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="15">
         <v>93.9</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E70" s="14">
         <v>150</v>
       </c>
       <c r="F70" s="6">
@@ -2357,19 +2375,19 @@
       <c r="I70" s="7"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B71" s="13">
         <v>45992</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="14">
         <v>500</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="15">
         <v>94.9</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E71" s="14">
         <v>491</v>
       </c>
       <c r="F71" s="6">
@@ -2383,17 +2401,17 @@
       <c r="I71" s="7"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B72" s="13">
         <v>45992</v>
       </c>
-      <c r="C72" s="6"/>
-      <c r="D72" s="7">
+      <c r="C72" s="14"/>
+      <c r="D72" s="15">
         <v>83.31</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72" s="14">
         <v>180</v>
       </c>
       <c r="F72" s="6">
@@ -2407,19 +2425,19 @@
       <c r="I72" s="7"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B73" s="13">
         <v>46023</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="14">
         <v>1350</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="15">
         <v>92.9</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E73" s="14">
         <v>910</v>
       </c>
       <c r="F73" s="6">
@@ -2433,17 +2451,17 @@
       <c r="I73" s="7"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B74" s="13">
         <v>46023</v>
       </c>
-      <c r="C74" s="6"/>
-      <c r="D74" s="7">
+      <c r="C74" s="14"/>
+      <c r="D74" s="15">
         <v>92.21</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E74" s="14">
         <v>9</v>
       </c>
       <c r="F74" s="6">
@@ -2457,19 +2475,19 @@
       <c r="I74" s="7"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B75" s="5">
+      <c r="B75" s="13">
         <v>46054</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="14">
         <v>1200</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="15">
         <v>92.9</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E75" s="14">
         <v>478</v>
       </c>
       <c r="F75" s="6">
@@ -2483,17 +2501,17 @@
       <c r="I75" s="7"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B76" s="5">
+      <c r="B76" s="13">
         <v>46054</v>
       </c>
-      <c r="C76" s="6"/>
-      <c r="D76" s="7">
+      <c r="C76" s="14"/>
+      <c r="D76" s="15">
         <v>92.9</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E76" s="14">
         <v>440</v>
       </c>
       <c r="F76" s="6">
@@ -2507,19 +2525,19 @@
       <c r="I76" s="7"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B77" s="5">
+      <c r="B77" s="13">
         <v>46082</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="14">
         <v>1000</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="15">
         <v>108.9</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E77" s="14">
         <v>330</v>
       </c>
       <c r="F77" s="6">
@@ -2533,17 +2551,17 @@
       <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B78" s="5">
+      <c r="B78" s="13">
         <v>46082</v>
       </c>
-      <c r="C78" s="6"/>
-      <c r="D78" s="7">
+      <c r="C78" s="14"/>
+      <c r="D78" s="15">
         <v>92.9</v>
       </c>
-      <c r="E78" s="6">
+      <c r="E78" s="14">
         <v>722</v>
       </c>
       <c r="F78" s="6">
@@ -2557,19 +2575,19 @@
       <c r="I78" s="7"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B79" s="5">
+      <c r="B79" s="13">
         <v>46113</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="14">
         <v>1000</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="15">
         <v>108.9</v>
       </c>
-      <c r="E79" s="6"/>
+      <c r="E79" s="14"/>
       <c r="F79" s="6">
         <f>IF(A79="","",IFERROR(LOOKUP(2,1/(A$4:A78=A79),F$4:F78),0)+IF(ISNUMBER(C79),C79,0)-IF(ISNUMBER(E79),E79,0))</f>
         <v>1670</v>
@@ -2581,17 +2599,17 @@
       <c r="I79" s="7"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B80" s="5">
+      <c r="B80" s="13">
         <v>46113</v>
       </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="7">
+      <c r="C80" s="14"/>
+      <c r="D80" s="15">
         <v>102.19</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E80" s="14">
         <v>502</v>
       </c>
       <c r="F80" s="6">
@@ -2605,17 +2623,17 @@
       <c r="I80" s="7"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B81" s="5">
+      <c r="B81" s="13">
         <v>46143</v>
       </c>
-      <c r="C81" s="6"/>
-      <c r="D81" s="7">
+      <c r="C81" s="14"/>
+      <c r="D81" s="15">
         <v>106.21</v>
       </c>
-      <c r="E81" s="6">
+      <c r="E81" s="14">
         <v>375</v>
       </c>
       <c r="F81" s="6">
@@ -2629,19 +2647,19 @@
       <c r="I81" s="7"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B82" s="5">
+      <c r="B82" s="13">
         <v>46174</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="14">
         <v>500</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="15">
         <v>92.4</v>
       </c>
-      <c r="E82" s="6"/>
+      <c r="E82" s="14"/>
       <c r="F82" s="6">
         <f>IF(A82="","",IFERROR(LOOKUP(2,1/(A$4:A81=A82),F$4:F81),0)+IF(ISNUMBER(C82),C82,0)-IF(ISNUMBER(E82),E82,0))</f>
         <v>1293</v>
@@ -2653,17 +2671,17 @@
       <c r="I82" s="7"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B83" s="5">
+      <c r="B83" s="13">
         <v>46174</v>
       </c>
-      <c r="C83" s="6"/>
-      <c r="D83" s="7">
+      <c r="C83" s="14"/>
+      <c r="D83" s="15">
         <v>92.4</v>
       </c>
-      <c r="E83" s="6"/>
+      <c r="E83" s="14"/>
       <c r="F83" s="6">
         <f>IF(A83="","",IFERROR(LOOKUP(2,1/(A$4:A82=A83),F$4:F82),0)+IF(ISNUMBER(C83),C83,0)-IF(ISNUMBER(E83),E83,0))</f>
         <v>1293</v>
@@ -2675,17 +2693,17 @@
       <c r="I83" s="7"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B84" s="5">
+      <c r="B84" s="13">
         <v>46204</v>
       </c>
-      <c r="C84" s="6"/>
-      <c r="D84" s="7">
+      <c r="C84" s="14"/>
+      <c r="D84" s="15">
         <v>100.87</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E84" s="14">
         <v>560</v>
       </c>
       <c r="F84" s="6">
@@ -2699,19 +2717,19 @@
       <c r="I84" s="7"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B85" s="5">
+      <c r="B85" s="13">
         <v>46235</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="14">
         <v>1056</v>
       </c>
-      <c r="D85" s="7">
+      <c r="D85" s="15">
         <v>116.4</v>
       </c>
-      <c r="E85" s="6"/>
+      <c r="E85" s="14"/>
       <c r="F85" s="6">
         <f>IF(A85="","",IFERROR(LOOKUP(2,1/(A$4:A84=A85),F$4:F84),0)+IF(ISNUMBER(C85),C85,0)-IF(ISNUMBER(E85),E85,0))</f>
         <v>1789</v>
@@ -2723,17 +2741,17 @@
       <c r="I85" s="7"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B86" s="5">
+      <c r="B86" s="13">
         <v>46235</v>
       </c>
-      <c r="C86" s="6"/>
-      <c r="D86" s="7">
+      <c r="C86" s="14"/>
+      <c r="D86" s="15">
         <v>100.87</v>
       </c>
-      <c r="E86" s="6">
+      <c r="E86" s="14">
         <v>618</v>
       </c>
       <c r="F86" s="6">
@@ -2747,17 +2765,17 @@
       <c r="I86" s="7"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B87" s="5">
+      <c r="B87" s="13">
         <v>46266</v>
       </c>
-      <c r="C87" s="6"/>
-      <c r="D87" s="7">
+      <c r="C87" s="14"/>
+      <c r="D87" s="15">
         <v>110.04</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="14">
         <v>30</v>
       </c>
       <c r="F87" s="6">
@@ -2771,19 +2789,19 @@
       <c r="I87" s="7"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B88" s="5">
+      <c r="B88" s="13">
         <v>46266</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="14">
         <v>444</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="15">
         <v>114.4</v>
       </c>
-      <c r="E88" s="6"/>
+      <c r="E88" s="14"/>
       <c r="F88" s="6">
         <f>IF(A88="","",IFERROR(LOOKUP(2,1/(A$4:A87=A88),F$4:F87),0)+IF(ISNUMBER(C88),C88,0)-IF(ISNUMBER(E88),E88,0))</f>
         <v>1585</v>
@@ -2795,17 +2813,17 @@
       <c r="I88" s="7"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B89" s="5">
+      <c r="B89" s="13">
         <v>46296</v>
       </c>
-      <c r="C89" s="6"/>
-      <c r="D89" s="7">
+      <c r="C89" s="14"/>
+      <c r="D89" s="15">
         <v>111.24</v>
       </c>
-      <c r="E89" s="6">
+      <c r="E89" s="14">
         <v>70</v>
       </c>
       <c r="F89" s="6">
@@ -2819,19 +2837,19 @@
       <c r="I89" s="7"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B90" s="5">
+      <c r="B90" s="13">
         <v>45931</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="14">
         <v>32</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="15">
         <v>79.2</v>
       </c>
-      <c r="E90" s="6"/>
+      <c r="E90" s="14"/>
       <c r="F90" s="6">
         <f>IF(A90="","",IFERROR(LOOKUP(2,1/(A$4:A89=A90),F$4:F89),0)+IF(ISNUMBER(C90),C90,0)-IF(ISNUMBER(E90),E90,0))</f>
         <v>32</v>
@@ -2843,17 +2861,17 @@
       <c r="I90" s="7"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B91" s="5">
+      <c r="B91" s="13">
         <v>45962</v>
       </c>
-      <c r="C91" s="6"/>
-      <c r="D91" s="7">
+      <c r="C91" s="14"/>
+      <c r="D91" s="15">
         <v>79.2</v>
       </c>
-      <c r="E91" s="6"/>
+      <c r="E91" s="14"/>
       <c r="F91" s="6">
         <f>IF(A91="","",IFERROR(LOOKUP(2,1/(A$4:A90=A91),F$4:F90),0)+IF(ISNUMBER(C91),C91,0)-IF(ISNUMBER(E91),E91,0))</f>
         <v>32</v>
@@ -2865,17 +2883,17 @@
       <c r="I91" s="7"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B92" s="5">
+      <c r="B92" s="13">
         <v>45992</v>
       </c>
-      <c r="C92" s="6"/>
-      <c r="D92" s="7">
+      <c r="C92" s="14"/>
+      <c r="D92" s="15">
         <v>79.2</v>
       </c>
-      <c r="E92" s="6"/>
+      <c r="E92" s="14"/>
       <c r="F92" s="6">
         <f>IF(A92="","",IFERROR(LOOKUP(2,1/(A$4:A91=A92),F$4:F91),0)+IF(ISNUMBER(C92),C92,0)-IF(ISNUMBER(E92),E92,0))</f>
         <v>32</v>
@@ -2887,17 +2905,17 @@
       <c r="I92" s="7"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B93" s="5">
+      <c r="B93" s="13">
         <v>46023</v>
       </c>
-      <c r="C93" s="6"/>
-      <c r="D93" s="7">
+      <c r="C93" s="14"/>
+      <c r="D93" s="15">
         <v>79.2</v>
       </c>
-      <c r="E93" s="6"/>
+      <c r="E93" s="14"/>
       <c r="F93" s="6">
         <f>IF(A93="","",IFERROR(LOOKUP(2,1/(A$4:A92=A93),F$4:F92),0)+IF(ISNUMBER(C93),C93,0)-IF(ISNUMBER(E93),E93,0))</f>
         <v>32</v>
@@ -2909,17 +2927,17 @@
       <c r="I93" s="7"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B94" s="5">
+      <c r="B94" s="13">
         <v>46054</v>
       </c>
-      <c r="C94" s="6"/>
-      <c r="D94" s="7">
+      <c r="C94" s="14"/>
+      <c r="D94" s="15">
         <v>79.2</v>
       </c>
-      <c r="E94" s="6"/>
+      <c r="E94" s="14"/>
       <c r="F94" s="6">
         <f>IF(A94="","",IFERROR(LOOKUP(2,1/(A$4:A93=A94),F$4:F93),0)+IF(ISNUMBER(C94),C94,0)-IF(ISNUMBER(E94),E94,0))</f>
         <v>32</v>
@@ -2931,17 +2949,17 @@
       <c r="I94" s="7"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B95" s="5">
+      <c r="B95" s="13">
         <v>46054</v>
       </c>
-      <c r="C95" s="6"/>
-      <c r="D95" s="7">
+      <c r="C95" s="14"/>
+      <c r="D95" s="15">
         <v>79.2</v>
       </c>
-      <c r="E95" s="6"/>
+      <c r="E95" s="14"/>
       <c r="F95" s="6">
         <f>IF(A95="","",IFERROR(LOOKUP(2,1/(A$4:A94=A95),F$4:F94),0)+IF(ISNUMBER(C95),C95,0)-IF(ISNUMBER(E95),E95,0))</f>
         <v>32</v>
@@ -2953,17 +2971,17 @@
       <c r="I95" s="7"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B96" s="5">
+      <c r="B96" s="13">
         <v>46082</v>
       </c>
-      <c r="C96" s="6"/>
-      <c r="D96" s="7">
+      <c r="C96" s="14"/>
+      <c r="D96" s="15">
         <v>79.2</v>
       </c>
-      <c r="E96" s="6"/>
+      <c r="E96" s="14"/>
       <c r="F96" s="6">
         <f>IF(A96="","",IFERROR(LOOKUP(2,1/(A$4:A95=A96),F$4:F95),0)+IF(ISNUMBER(C96),C96,0)-IF(ISNUMBER(E96),E96,0))</f>
         <v>32</v>
@@ -2975,17 +2993,17 @@
       <c r="I96" s="7"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B97" s="5">
+      <c r="B97" s="13">
         <v>46113</v>
       </c>
-      <c r="C97" s="6"/>
-      <c r="D97" s="7">
+      <c r="C97" s="14"/>
+      <c r="D97" s="15">
         <v>79.2</v>
       </c>
-      <c r="E97" s="6">
+      <c r="E97" s="14">
         <v>20</v>
       </c>
       <c r="F97" s="6">
@@ -2999,19 +3017,19 @@
       <c r="I97" s="7"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B98" s="5">
+      <c r="B98" s="13">
         <v>46143</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="14">
         <v>1000</v>
       </c>
-      <c r="D98" s="7">
+      <c r="D98" s="15">
         <v>91.8</v>
       </c>
-      <c r="E98" s="6">
+      <c r="E98" s="14">
         <v>408</v>
       </c>
       <c r="F98" s="6">
@@ -3025,17 +3043,17 @@
       <c r="I98" s="7"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B99" s="5">
+      <c r="B99" s="13">
         <v>46143</v>
       </c>
-      <c r="C99" s="6"/>
-      <c r="D99" s="7">
+      <c r="C99" s="14"/>
+      <c r="D99" s="15">
         <v>79.2</v>
       </c>
-      <c r="E99" s="6">
+      <c r="E99" s="14">
         <v>12</v>
       </c>
       <c r="F99" s="6">
@@ -3049,19 +3067,19 @@
       <c r="I99" s="7"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B100" s="5">
+      <c r="B100" s="13">
         <v>46174</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="14">
         <v>1000</v>
       </c>
-      <c r="D100" s="7">
+      <c r="D100" s="15">
         <v>94.9</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E100" s="14">
         <v>133</v>
       </c>
       <c r="F100" s="6">
@@ -3075,17 +3093,17 @@
       <c r="I100" s="7"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B101" s="5">
+      <c r="B101" s="13">
         <v>46174</v>
       </c>
-      <c r="C101" s="6"/>
-      <c r="D101" s="7">
+      <c r="C101" s="14"/>
+      <c r="D101" s="15">
         <v>91.65</v>
       </c>
-      <c r="E101" s="6">
+      <c r="E101" s="14">
         <v>592</v>
       </c>
       <c r="F101" s="6">
@@ -3099,19 +3117,19 @@
       <c r="I101" s="7"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B102" s="5">
+      <c r="B102" s="13">
         <v>46174</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="14">
         <v>20</v>
       </c>
-      <c r="D102" s="7">
+      <c r="D102" s="15">
         <v>91.8</v>
       </c>
-      <c r="E102" s="6"/>
+      <c r="E102" s="14"/>
       <c r="F102" s="6">
         <f>IF(A102="","",IFERROR(LOOKUP(2,1/(A$4:A101=A102),F$4:F101),0)+IF(ISNUMBER(C102),C102,0)-IF(ISNUMBER(E102),E102,0))</f>
         <v>887</v>
@@ -3123,17 +3141,17 @@
       <c r="I102" s="7"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B103" s="5">
+      <c r="B103" s="13">
         <v>46204</v>
       </c>
-      <c r="C103" s="6"/>
-      <c r="D103" s="7">
+      <c r="C103" s="14"/>
+      <c r="D103" s="15">
         <v>93.67</v>
       </c>
-      <c r="E103" s="6">
+      <c r="E103" s="14">
         <v>190</v>
       </c>
       <c r="F103" s="6">
@@ -3147,17 +3165,17 @@
       <c r="I103" s="7"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B104" s="5">
+      <c r="B104" s="13">
         <v>46235</v>
       </c>
-      <c r="C104" s="6"/>
-      <c r="D104" s="7">
+      <c r="C104" s="14"/>
+      <c r="D104" s="15">
         <v>93.67</v>
       </c>
-      <c r="E104" s="6">
+      <c r="E104" s="14">
         <v>366</v>
       </c>
       <c r="F104" s="6">
@@ -3171,17 +3189,17 @@
       <c r="I104" s="7"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B105" s="5">
+      <c r="B105" s="13">
         <v>46266</v>
       </c>
-      <c r="C105" s="6"/>
-      <c r="D105" s="7">
+      <c r="C105" s="14"/>
+      <c r="D105" s="15">
         <v>93.67</v>
       </c>
-      <c r="E105" s="6">
+      <c r="E105" s="14">
         <v>570</v>
       </c>
       <c r="F105" s="6">
@@ -3195,17 +3213,17 @@
       <c r="I105" s="7"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B106" s="5">
+      <c r="B106" s="13">
         <v>46296</v>
       </c>
-      <c r="C106" s="6"/>
-      <c r="D106" s="7">
+      <c r="C106" s="14"/>
+      <c r="D106" s="15">
         <v>93.67</v>
       </c>
-      <c r="E106" s="6">
+      <c r="E106" s="14">
         <v>580</v>
       </c>
       <c r="F106" s="6">
@@ -3219,19 +3237,19 @@
       <c r="I106" s="7"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B107" s="5">
+      <c r="B107" s="13">
         <v>45931</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="14">
         <v>200</v>
       </c>
-      <c r="D107" s="7">
+      <c r="D107" s="15">
         <v>77.2</v>
       </c>
-      <c r="E107" s="6">
+      <c r="E107" s="14">
         <v>6</v>
       </c>
       <c r="F107" s="6">
@@ -3245,19 +3263,19 @@
       <c r="I107" s="7"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B108" s="5">
+      <c r="B108" s="13">
         <v>45962</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="14">
         <v>300</v>
       </c>
-      <c r="D108" s="7">
+      <c r="D108" s="15">
         <v>86.2</v>
       </c>
-      <c r="E108" s="6">
+      <c r="E108" s="14">
         <v>291</v>
       </c>
       <c r="F108" s="6">
@@ -3271,17 +3289,17 @@
       <c r="I108" s="7"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B109" s="5">
+      <c r="B109" s="13">
         <v>45962</v>
       </c>
-      <c r="C109" s="6"/>
-      <c r="D109" s="7">
+      <c r="C109" s="14"/>
+      <c r="D109" s="15">
         <v>77.2</v>
       </c>
-      <c r="E109" s="6">
+      <c r="E109" s="14">
         <v>194</v>
       </c>
       <c r="F109" s="6">
@@ -3295,19 +3313,19 @@
       <c r="I109" s="7"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B110" s="5">
+      <c r="B110" s="13">
         <v>45992</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="14">
         <v>278</v>
       </c>
-      <c r="D110" s="7">
+      <c r="D110" s="15">
         <v>95.2</v>
       </c>
-      <c r="E110" s="6">
+      <c r="E110" s="14">
         <v>206</v>
       </c>
       <c r="F110" s="6">
@@ -3321,17 +3339,17 @@
       <c r="I110" s="7"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B111" s="5">
+      <c r="B111" s="13">
         <v>45992</v>
       </c>
-      <c r="C111" s="6"/>
-      <c r="D111" s="7">
+      <c r="C111" s="14"/>
+      <c r="D111" s="15">
         <v>82.67</v>
       </c>
-      <c r="E111" s="6">
+      <c r="E111" s="14">
         <v>9</v>
       </c>
       <c r="F111" s="6">
@@ -3345,19 +3363,19 @@
       <c r="I111" s="7"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B112" s="5">
+      <c r="B112" s="13">
         <v>46023</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="14">
         <v>506</v>
       </c>
-      <c r="D112" s="7">
+      <c r="D112" s="15">
         <v>94.2</v>
       </c>
-      <c r="E112" s="6">
+      <c r="E112" s="14">
         <v>28</v>
       </c>
       <c r="F112" s="6">
@@ -3371,17 +3389,17 @@
       <c r="I112" s="7"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B113" s="5">
+      <c r="B113" s="13">
         <v>46023</v>
       </c>
-      <c r="C113" s="6"/>
-      <c r="D113" s="7">
+      <c r="C113" s="14"/>
+      <c r="D113" s="15">
         <v>94.81</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E113" s="14">
         <v>72</v>
       </c>
       <c r="F113" s="6">
@@ -3395,19 +3413,19 @@
       <c r="I113" s="7"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B114" s="5">
+      <c r="B114" s="13">
         <v>46082</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="14">
         <v>316</v>
       </c>
-      <c r="D114" s="7">
+      <c r="D114" s="15">
         <v>94.2</v>
       </c>
-      <c r="E114" s="6">
+      <c r="E114" s="14">
         <v>453</v>
       </c>
       <c r="F114" s="6">
@@ -3421,17 +3439,17 @@
       <c r="I114" s="7"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B115" s="5">
+      <c r="B115" s="13">
         <v>46082</v>
       </c>
-      <c r="C115" s="6"/>
-      <c r="D115" s="7">
+      <c r="C115" s="14"/>
+      <c r="D115" s="15">
         <v>92.28</v>
       </c>
-      <c r="E115" s="6">
+      <c r="E115" s="14">
         <v>319</v>
       </c>
       <c r="F115" s="6">
@@ -3445,19 +3463,19 @@
       <c r="I115" s="7"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B116" s="5">
+      <c r="B116" s="13">
         <v>46113</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="14">
         <v>219</v>
       </c>
-      <c r="D116" s="7">
+      <c r="D116" s="15">
         <v>111.7</v>
       </c>
-      <c r="E116" s="6">
+      <c r="E116" s="14">
         <v>214</v>
       </c>
       <c r="F116" s="6">
@@ -3471,17 +3489,17 @@
       <c r="I116" s="7"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B117" s="5">
+      <c r="B117" s="13">
         <v>46113</v>
       </c>
-      <c r="C117" s="6"/>
-      <c r="D117" s="7">
+      <c r="C117" s="14"/>
+      <c r="D117" s="15">
         <v>94.25</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E117" s="14">
         <v>22</v>
       </c>
       <c r="F117" s="6">
@@ -3495,17 +3513,17 @@
       <c r="I117" s="7"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B118" s="5">
+      <c r="B118" s="13">
         <v>46143</v>
       </c>
-      <c r="C118" s="6"/>
-      <c r="D118" s="7">
+      <c r="C118" s="14"/>
+      <c r="D118" s="15">
         <v>110.11</v>
       </c>
-      <c r="E118" s="6">
+      <c r="E118" s="14">
         <v>5</v>
       </c>
       <c r="F118" s="6">
@@ -3519,19 +3537,19 @@
       <c r="I118" s="7"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B119" s="5">
+      <c r="B119" s="13">
         <v>46174</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="14">
         <v>500</v>
       </c>
-      <c r="D119" s="7">
+      <c r="D119" s="15">
         <v>93.8</v>
       </c>
-      <c r="E119" s="6"/>
+      <c r="E119" s="14"/>
       <c r="F119" s="6">
         <f>IF(A119="","",IFERROR(LOOKUP(2,1/(A$4:A118=A119),F$4:F118),0)+IF(ISNUMBER(C119),C119,0)-IF(ISNUMBER(E119),E119,0))</f>
         <v>500</v>
@@ -3543,17 +3561,17 @@
       <c r="I119" s="7"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B120" s="5">
+      <c r="B120" s="13">
         <v>46174</v>
       </c>
-      <c r="C120" s="6"/>
-      <c r="D120" s="7">
+      <c r="C120" s="14"/>
+      <c r="D120" s="15">
         <v>93.8</v>
       </c>
-      <c r="E120" s="6"/>
+      <c r="E120" s="14"/>
       <c r="F120" s="6">
         <f>IF(A120="","",IFERROR(LOOKUP(2,1/(A$4:A119=A120),F$4:F119),0)+IF(ISNUMBER(C120),C120,0)-IF(ISNUMBER(E120),E120,0))</f>
         <v>500</v>
@@ -3565,17 +3583,17 @@
       <c r="I120" s="7"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B121" s="5">
+      <c r="B121" s="13">
         <v>46204</v>
       </c>
-      <c r="C121" s="6"/>
-      <c r="D121" s="7">
+      <c r="C121" s="14"/>
+      <c r="D121" s="15">
         <v>93.8</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E121" s="14">
         <v>35</v>
       </c>
       <c r="F121" s="6">
@@ -3589,19 +3607,19 @@
       <c r="I121" s="7"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B122" s="5">
+      <c r="B122" s="13">
         <v>46235</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="14">
         <v>500</v>
       </c>
-      <c r="D122" s="7">
+      <c r="D122" s="15">
         <v>117.8</v>
       </c>
-      <c r="E122" s="6"/>
+      <c r="E122" s="14"/>
       <c r="F122" s="6">
         <f>IF(A122="","",IFERROR(LOOKUP(2,1/(A$4:A121=A122),F$4:F121),0)+IF(ISNUMBER(C122),C122,0)-IF(ISNUMBER(E122),E122,0))</f>
         <v>965</v>
@@ -3613,17 +3631,17 @@
       <c r="I122" s="7"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B123" s="5">
+      <c r="B123" s="13">
         <v>46235</v>
       </c>
-      <c r="C123" s="6"/>
-      <c r="D123" s="7">
+      <c r="C123" s="14"/>
+      <c r="D123" s="15">
         <v>93.8</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E123" s="14">
         <v>312</v>
       </c>
       <c r="F123" s="6">
@@ -3637,17 +3655,17 @@
       <c r="I123" s="7"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B124" s="5">
+      <c r="B124" s="13">
         <v>46266</v>
       </c>
-      <c r="C124" s="6"/>
-      <c r="D124" s="7">
+      <c r="C124" s="14"/>
+      <c r="D124" s="15">
         <v>106.24</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E124" s="14">
         <v>20</v>
       </c>
       <c r="F124" s="6">
@@ -3661,19 +3679,19 @@
       <c r="I124" s="7"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B125" s="5">
+      <c r="B125" s="13">
         <v>46266</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="14">
         <v>300</v>
       </c>
-      <c r="D125" s="7">
+      <c r="D125" s="15">
         <v>117.4</v>
       </c>
-      <c r="E125" s="6"/>
+      <c r="E125" s="14"/>
       <c r="F125" s="6">
         <f>IF(A125="","",IFERROR(LOOKUP(2,1/(A$4:A124=A125),F$4:F124),0)+IF(ISNUMBER(C125),C125,0)-IF(ISNUMBER(E125),E125,0))</f>
         <v>933</v>
@@ -3685,17 +3703,17 @@
       <c r="I125" s="7"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B126" s="5">
+      <c r="B126" s="13">
         <v>46296</v>
       </c>
-      <c r="C126" s="6"/>
-      <c r="D126" s="7">
+      <c r="C126" s="14"/>
+      <c r="D126" s="15">
         <v>109.75</v>
       </c>
-      <c r="E126" s="6">
+      <c r="E126" s="14">
         <v>105</v>
       </c>
       <c r="F126" s="6">
@@ -3709,17 +3727,17 @@
       <c r="I126" s="7"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B127" s="5">
+      <c r="B127" s="13">
         <v>46419</v>
       </c>
-      <c r="C127" s="6"/>
-      <c r="D127" s="7">
+      <c r="C127" s="14"/>
+      <c r="D127" s="15">
         <v>94.2</v>
       </c>
-      <c r="E127" s="6"/>
+      <c r="E127" s="14"/>
       <c r="F127" s="6">
         <f>IF(A127="","",IFERROR(LOOKUP(2,1/(A$4:A126=A127),F$4:F126),0)+IF(ISNUMBER(C127),C127,0)-IF(ISNUMBER(E127),E127,0))</f>
         <v>828</v>
@@ -3731,17 +3749,17 @@
       <c r="I127" s="7"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B128" s="5">
+      <c r="B128" s="13">
         <v>45931</v>
       </c>
-      <c r="C128" s="6"/>
-      <c r="D128" s="7">
+      <c r="C128" s="14"/>
+      <c r="D128" s="15">
         <v>77.900000000000006</v>
       </c>
-      <c r="E128" s="6"/>
+      <c r="E128" s="14"/>
       <c r="F128" s="6">
         <f>IF(A128="","",IFERROR(LOOKUP(2,1/(A$4:A127=A128),F$4:F127),0)+IF(ISNUMBER(C128),C128,0)-IF(ISNUMBER(E128),E128,0))</f>
         <v>0</v>
@@ -3753,17 +3771,17 @@
       <c r="I128" s="7"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B129" s="5">
+      <c r="B129" s="13">
         <v>45962</v>
       </c>
-      <c r="C129" s="6"/>
-      <c r="D129" s="7">
+      <c r="C129" s="14"/>
+      <c r="D129" s="15">
         <v>77.900000000000006</v>
       </c>
-      <c r="E129" s="6"/>
+      <c r="E129" s="14"/>
       <c r="F129" s="6">
         <f>IF(A129="","",IFERROR(LOOKUP(2,1/(A$4:A128=A129),F$4:F128),0)+IF(ISNUMBER(C129),C129,0)-IF(ISNUMBER(E129),E129,0))</f>
         <v>0</v>
@@ -3775,17 +3793,17 @@
       <c r="I129" s="7"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B130" s="5">
+      <c r="B130" s="13">
         <v>45992</v>
       </c>
-      <c r="C130" s="6"/>
-      <c r="D130" s="7">
+      <c r="C130" s="14"/>
+      <c r="D130" s="15">
         <v>77.900000000000006</v>
       </c>
-      <c r="E130" s="6"/>
+      <c r="E130" s="14"/>
       <c r="F130" s="6">
         <f>IF(A130="","",IFERROR(LOOKUP(2,1/(A$4:A129=A130),F$4:F129),0)+IF(ISNUMBER(C130),C130,0)-IF(ISNUMBER(E130),E130,0))</f>
         <v>0</v>
@@ -3797,17 +3815,17 @@
       <c r="I130" s="7"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B131" s="5">
+      <c r="B131" s="13">
         <v>46023</v>
       </c>
-      <c r="C131" s="6"/>
-      <c r="D131" s="7">
+      <c r="C131" s="14"/>
+      <c r="D131" s="15">
         <v>77.900000000000006</v>
       </c>
-      <c r="E131" s="6"/>
+      <c r="E131" s="14"/>
       <c r="F131" s="6">
         <f>IF(A131="","",IFERROR(LOOKUP(2,1/(A$4:A130=A131),F$4:F130),0)+IF(ISNUMBER(C131),C131,0)-IF(ISNUMBER(E131),E131,0))</f>
         <v>0</v>
@@ -3819,17 +3837,17 @@
       <c r="I131" s="7"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B132" s="5">
+      <c r="B132" s="13">
         <v>46054</v>
       </c>
-      <c r="C132" s="6"/>
-      <c r="D132" s="7">
+      <c r="C132" s="14"/>
+      <c r="D132" s="15">
         <v>77.900000000000006</v>
       </c>
-      <c r="E132" s="6"/>
+      <c r="E132" s="14"/>
       <c r="F132" s="6">
         <f>IF(A132="","",IFERROR(LOOKUP(2,1/(A$4:A131=A132),F$4:F131),0)+IF(ISNUMBER(C132),C132,0)-IF(ISNUMBER(E132),E132,0))</f>
         <v>0</v>
@@ -3841,15 +3859,15 @@
       <c r="I132" s="7"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B133" s="5">
+      <c r="B133" s="13">
         <v>46054</v>
       </c>
-      <c r="C133" s="6"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="6"/>
+      <c r="C133" s="14"/>
+      <c r="D133" s="15"/>
+      <c r="E133" s="14"/>
       <c r="F133" s="6">
         <f>IF(A133="","",IFERROR(LOOKUP(2,1/(A$4:A132=A133),F$4:F132),0)+IF(ISNUMBER(C133),C133,0)-IF(ISNUMBER(E133),E133,0))</f>
         <v>0</v>
@@ -3861,17 +3879,17 @@
       <c r="I133" s="7"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B134" s="5">
+      <c r="B134" s="13">
         <v>46082</v>
       </c>
-      <c r="C134" s="6"/>
-      <c r="D134" s="7">
+      <c r="C134" s="14"/>
+      <c r="D134" s="15">
         <v>77.900000000000006</v>
       </c>
-      <c r="E134" s="6"/>
+      <c r="E134" s="14"/>
       <c r="F134" s="6">
         <f>IF(A134="","",IFERROR(LOOKUP(2,1/(A$4:A133=A134),F$4:F133),0)+IF(ISNUMBER(C134),C134,0)-IF(ISNUMBER(E134),E134,0))</f>
         <v>0</v>
@@ -3883,17 +3901,17 @@
       <c r="I134" s="7"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B135" s="5">
+      <c r="B135" s="13">
         <v>46113</v>
       </c>
-      <c r="C135" s="6"/>
-      <c r="D135" s="7">
+      <c r="C135" s="14"/>
+      <c r="D135" s="15">
         <v>77.900000000000006</v>
       </c>
-      <c r="E135" s="6"/>
+      <c r="E135" s="14"/>
       <c r="F135" s="6">
         <f>IF(A135="","",IFERROR(LOOKUP(2,1/(A$4:A134=A135),F$4:F134),0)+IF(ISNUMBER(C135),C135,0)-IF(ISNUMBER(E135),E135,0))</f>
         <v>0</v>
@@ -3905,19 +3923,19 @@
       <c r="I135" s="7"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B136" s="5">
+      <c r="B136" s="13">
         <v>46143</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="14">
         <v>500</v>
       </c>
-      <c r="D136" s="7">
+      <c r="D136" s="15">
         <v>93.1</v>
       </c>
-      <c r="E136" s="6">
+      <c r="E136" s="14">
         <v>55</v>
       </c>
       <c r="F136" s="6">
@@ -3931,17 +3949,17 @@
       <c r="I136" s="7"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B137" s="5">
+      <c r="B137" s="13">
         <v>46143</v>
       </c>
-      <c r="C137" s="6"/>
-      <c r="D137" s="7">
+      <c r="C137" s="14"/>
+      <c r="D137" s="15">
         <v>93.1</v>
       </c>
-      <c r="E137" s="6"/>
+      <c r="E137" s="14"/>
       <c r="F137" s="6">
         <f>IF(A137="","",IFERROR(LOOKUP(2,1/(A$4:A136=A137),F$4:F136),0)+IF(ISNUMBER(C137),C137,0)-IF(ISNUMBER(E137),E137,0))</f>
         <v>445</v>
@@ -3953,19 +3971,19 @@
       <c r="I137" s="7"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B138" s="5">
+      <c r="B138" s="13">
         <v>46174</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="14">
         <v>500</v>
       </c>
-      <c r="D138" s="7">
+      <c r="D138" s="15">
         <v>96.3</v>
       </c>
-      <c r="E138" s="6">
+      <c r="E138" s="14">
         <v>61</v>
       </c>
       <c r="F138" s="6">
@@ -3979,17 +3997,17 @@
       <c r="I138" s="7"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B139" s="5">
+      <c r="B139" s="13">
         <v>46143</v>
       </c>
-      <c r="C139" s="6"/>
-      <c r="D139" s="7">
+      <c r="C139" s="14"/>
+      <c r="D139" s="15">
         <v>93.1</v>
       </c>
-      <c r="E139" s="6">
+      <c r="E139" s="14">
         <v>445</v>
       </c>
       <c r="F139" s="6">
@@ -4003,17 +4021,17 @@
       <c r="I139" s="7"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B140" s="5">
+      <c r="B140" s="13">
         <v>46204</v>
       </c>
-      <c r="C140" s="6"/>
-      <c r="D140" s="7">
+      <c r="C140" s="14"/>
+      <c r="D140" s="15">
         <v>94.79</v>
       </c>
-      <c r="E140" s="6">
+      <c r="E140" s="14">
         <v>434</v>
       </c>
       <c r="F140" s="6">
@@ -4027,17 +4045,17 @@
       <c r="I140" s="7"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B141" s="5">
+      <c r="B141" s="13">
         <v>46235</v>
       </c>
-      <c r="C141" s="6"/>
-      <c r="D141" s="7">
+      <c r="C141" s="14"/>
+      <c r="D141" s="15">
         <v>94.79</v>
       </c>
-      <c r="E141" s="6"/>
+      <c r="E141" s="14"/>
       <c r="F141" s="6">
         <f>IF(A141="","",IFERROR(LOOKUP(2,1/(A$4:A140=A141),F$4:F140),0)+IF(ISNUMBER(C141),C141,0)-IF(ISNUMBER(E141),E141,0))</f>
         <v>5</v>
@@ -4049,17 +4067,17 @@
       <c r="I141" s="7"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B142" s="5">
+      <c r="B142" s="13">
         <v>46266</v>
       </c>
-      <c r="C142" s="6"/>
-      <c r="D142" s="7">
+      <c r="C142" s="14"/>
+      <c r="D142" s="15">
         <v>94.79</v>
       </c>
-      <c r="E142" s="6">
+      <c r="E142" s="14">
         <v>310</v>
       </c>
       <c r="F142" s="6">
@@ -4073,17 +4091,17 @@
       <c r="I142" s="7"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B143" s="5">
+      <c r="B143" s="13">
         <v>46296</v>
       </c>
-      <c r="C143" s="6"/>
-      <c r="D143" s="7">
+      <c r="C143" s="14"/>
+      <c r="D143" s="15">
         <v>94.79</v>
       </c>
-      <c r="E143" s="6">
+      <c r="E143" s="14">
         <v>150</v>
       </c>
       <c r="F143" s="6">
@@ -4097,11 +4115,11 @@
       <c r="I143" s="7"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A144" s="4"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="6"/>
+      <c r="A144" s="12"/>
+      <c r="B144" s="13"/>
+      <c r="C144" s="14"/>
+      <c r="D144" s="15"/>
+      <c r="E144" s="14"/>
       <c r="F144" s="6" t="str">
         <f>IF(A144="","",IFERROR(LOOKUP(2,1/(A$4:A143=A144),F$4:F143),0)+IF(ISNUMBER(C144),C144,0)-IF(ISNUMBER(E144),E144,0))</f>
         <v/>
@@ -4113,11 +4131,11 @@
       <c r="I144" s="7"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A145" s="4"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="6"/>
+      <c r="A145" s="12"/>
+      <c r="B145" s="13"/>
+      <c r="C145" s="14"/>
+      <c r="D145" s="15"/>
+      <c r="E145" s="14"/>
       <c r="F145" s="6" t="str">
         <f>IF(A145="","",IFERROR(LOOKUP(2,1/(A$4:A144=A145),F$4:F144),0)+IF(ISNUMBER(C145),C145,0)-IF(ISNUMBER(E145),E145,0))</f>
         <v/>
@@ -4129,11 +4147,11 @@
       <c r="I145" s="7"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A146" s="4"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="6"/>
+      <c r="A146" s="12"/>
+      <c r="B146" s="13"/>
+      <c r="C146" s="14"/>
+      <c r="D146" s="15"/>
+      <c r="E146" s="14"/>
       <c r="F146" s="6" t="str">
         <f>IF(A146="","",IFERROR(LOOKUP(2,1/(A$4:A145=A146),F$4:F145),0)+IF(ISNUMBER(C146),C146,0)-IF(ISNUMBER(E146),E146,0))</f>
         <v/>
@@ -4145,11 +4163,11 @@
       <c r="I146" s="7"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A147" s="4"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="6"/>
+      <c r="A147" s="12"/>
+      <c r="B147" s="13"/>
+      <c r="C147" s="14"/>
+      <c r="D147" s="15"/>
+      <c r="E147" s="14"/>
       <c r="F147" s="6" t="str">
         <f>IF(A147="","",IFERROR(LOOKUP(2,1/(A$4:A146=A147),F$4:F146),0)+IF(ISNUMBER(C147),C147,0)-IF(ISNUMBER(E147),E147,0))</f>
         <v/>
@@ -4161,11 +4179,11 @@
       <c r="I147" s="7"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A148" s="4"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="6"/>
+      <c r="A148" s="12"/>
+      <c r="B148" s="13"/>
+      <c r="C148" s="14"/>
+      <c r="D148" s="15"/>
+      <c r="E148" s="14"/>
       <c r="F148" s="6" t="str">
         <f>IF(A148="","",IFERROR(LOOKUP(2,1/(A$4:A147=A148),F$4:F147),0)+IF(ISNUMBER(C148),C148,0)-IF(ISNUMBER(E148),E148,0))</f>
         <v/>
@@ -4177,11 +4195,11 @@
       <c r="I148" s="7"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A149" s="4"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="6"/>
+      <c r="A149" s="12"/>
+      <c r="B149" s="13"/>
+      <c r="C149" s="14"/>
+      <c r="D149" s="15"/>
+      <c r="E149" s="14"/>
       <c r="F149" s="6" t="str">
         <f>IF(A149="","",IFERROR(LOOKUP(2,1/(A$4:A148=A149),F$4:F148),0)+IF(ISNUMBER(C149),C149,0)-IF(ISNUMBER(E149),E149,0))</f>
         <v/>
@@ -4193,11 +4211,11 @@
       <c r="I149" s="7"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A150" s="4"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="6"/>
+      <c r="A150" s="12"/>
+      <c r="B150" s="13"/>
+      <c r="C150" s="14"/>
+      <c r="D150" s="15"/>
+      <c r="E150" s="14"/>
       <c r="F150" s="6" t="str">
         <f>IF(A150="","",IFERROR(LOOKUP(2,1/(A$4:A149=A150),F$4:F149),0)+IF(ISNUMBER(C150),C150,0)-IF(ISNUMBER(E150),E150,0))</f>
         <v/>
@@ -4209,11 +4227,11 @@
       <c r="I150" s="7"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A151" s="4"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="6"/>
+      <c r="A151" s="12"/>
+      <c r="B151" s="13"/>
+      <c r="C151" s="14"/>
+      <c r="D151" s="15"/>
+      <c r="E151" s="14"/>
       <c r="F151" s="6" t="str">
         <f>IF(A151="","",IFERROR(LOOKUP(2,1/(A$4:A150=A151),F$4:F150),0)+IF(ISNUMBER(C151),C151,0)-IF(ISNUMBER(E151),E151,0))</f>
         <v/>
@@ -4225,11 +4243,11 @@
       <c r="I151" s="7"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A152" s="4"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="6"/>
+      <c r="A152" s="12"/>
+      <c r="B152" s="13"/>
+      <c r="C152" s="14"/>
+      <c r="D152" s="15"/>
+      <c r="E152" s="14"/>
       <c r="F152" s="6" t="str">
         <f>IF(A152="","",IFERROR(LOOKUP(2,1/(A$4:A151=A152),F$4:F151),0)+IF(ISNUMBER(C152),C152,0)-IF(ISNUMBER(E152),E152,0))</f>
         <v/>
@@ -4241,11 +4259,11 @@
       <c r="I152" s="7"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A153" s="4"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="6"/>
+      <c r="A153" s="12"/>
+      <c r="B153" s="13"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="15"/>
+      <c r="E153" s="14"/>
       <c r="F153" s="6" t="str">
         <f>IF(A153="","",IFERROR(LOOKUP(2,1/(A$4:A152=A153),F$4:F152),0)+IF(ISNUMBER(C153),C153,0)-IF(ISNUMBER(E153),E153,0))</f>
         <v/>
@@ -4257,11 +4275,11 @@
       <c r="I153" s="7"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A154" s="4"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="6"/>
+      <c r="A154" s="12"/>
+      <c r="B154" s="13"/>
+      <c r="C154" s="14"/>
+      <c r="D154" s="15"/>
+      <c r="E154" s="14"/>
       <c r="F154" s="6" t="str">
         <f>IF(A154="","",IFERROR(LOOKUP(2,1/(A$4:A153=A154),F$4:F153),0)+IF(ISNUMBER(C154),C154,0)-IF(ISNUMBER(E154),E154,0))</f>
         <v/>
@@ -4273,11 +4291,11 @@
       <c r="I154" s="7"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A155" s="4"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="6"/>
+      <c r="A155" s="12"/>
+      <c r="B155" s="13"/>
+      <c r="C155" s="14"/>
+      <c r="D155" s="15"/>
+      <c r="E155" s="14"/>
       <c r="F155" s="6" t="str">
         <f>IF(A155="","",IFERROR(LOOKUP(2,1/(A$4:A154=A155),F$4:F154),0)+IF(ISNUMBER(C155),C155,0)-IF(ISNUMBER(E155),E155,0))</f>
         <v/>
@@ -4289,11 +4307,11 @@
       <c r="I155" s="7"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A156" s="4"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="6"/>
+      <c r="A156" s="12"/>
+      <c r="B156" s="13"/>
+      <c r="C156" s="14"/>
+      <c r="D156" s="15"/>
+      <c r="E156" s="14"/>
       <c r="F156" s="6" t="str">
         <f>IF(A156="","",IFERROR(LOOKUP(2,1/(A$4:A155=A156),F$4:F155),0)+IF(ISNUMBER(C156),C156,0)-IF(ISNUMBER(E156),E156,0))</f>
         <v/>
@@ -4305,11 +4323,11 @@
       <c r="I156" s="7"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A157" s="4"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="6"/>
+      <c r="A157" s="12"/>
+      <c r="B157" s="13"/>
+      <c r="C157" s="14"/>
+      <c r="D157" s="15"/>
+      <c r="E157" s="14"/>
       <c r="F157" s="6" t="str">
         <f>IF(A157="","",IFERROR(LOOKUP(2,1/(A$4:A156=A157),F$4:F156),0)+IF(ISNUMBER(C157),C157,0)-IF(ISNUMBER(E157),E157,0))</f>
         <v/>
@@ -4321,11 +4339,11 @@
       <c r="I157" s="7"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A158" s="4"/>
-      <c r="B158" s="5"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="6"/>
+      <c r="A158" s="12"/>
+      <c r="B158" s="13"/>
+      <c r="C158" s="14"/>
+      <c r="D158" s="15"/>
+      <c r="E158" s="14"/>
       <c r="F158" s="6" t="str">
         <f>IF(A158="","",IFERROR(LOOKUP(2,1/(A$4:A157=A158),F$4:F157),0)+IF(ISNUMBER(C158),C158,0)-IF(ISNUMBER(E158),E158,0))</f>
         <v/>
@@ -4337,11 +4355,11 @@
       <c r="I158" s="7"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A159" s="4"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="6"/>
+      <c r="A159" s="12"/>
+      <c r="B159" s="13"/>
+      <c r="C159" s="14"/>
+      <c r="D159" s="15"/>
+      <c r="E159" s="14"/>
       <c r="F159" s="6" t="str">
         <f>IF(A159="","",IFERROR(LOOKUP(2,1/(A$4:A158=A159),F$4:F158),0)+IF(ISNUMBER(C159),C159,0)-IF(ISNUMBER(E159),E159,0))</f>
         <v/>
@@ -4353,11 +4371,11 @@
       <c r="I159" s="7"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A160" s="4"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="6"/>
+      <c r="A160" s="12"/>
+      <c r="B160" s="13"/>
+      <c r="C160" s="14"/>
+      <c r="D160" s="15"/>
+      <c r="E160" s="14"/>
       <c r="F160" s="6" t="str">
         <f>IF(A160="","",IFERROR(LOOKUP(2,1/(A$4:A159=A160),F$4:F159),0)+IF(ISNUMBER(C160),C160,0)-IF(ISNUMBER(E160),E160,0))</f>
         <v/>
@@ -4369,11 +4387,11 @@
       <c r="I160" s="7"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A161" s="4"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="6"/>
+      <c r="A161" s="12"/>
+      <c r="B161" s="13"/>
+      <c r="C161" s="14"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="14"/>
       <c r="F161" s="6" t="str">
         <f>IF(A161="","",IFERROR(LOOKUP(2,1/(A$4:A160=A161),F$4:F160),0)+IF(ISNUMBER(C161),C161,0)-IF(ISNUMBER(E161),E161,0))</f>
         <v/>
@@ -4385,11 +4403,11 @@
       <c r="I161" s="7"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A162" s="4"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="6"/>
+      <c r="A162" s="12"/>
+      <c r="B162" s="13"/>
+      <c r="C162" s="14"/>
+      <c r="D162" s="15"/>
+      <c r="E162" s="14"/>
       <c r="F162" s="6" t="str">
         <f>IF(A162="","",IFERROR(LOOKUP(2,1/(A$4:A161=A162),F$4:F161),0)+IF(ISNUMBER(C162),C162,0)-IF(ISNUMBER(E162),E162,0))</f>
         <v/>
@@ -4401,11 +4419,11 @@
       <c r="I162" s="7"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A163" s="4"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="6"/>
+      <c r="A163" s="12"/>
+      <c r="B163" s="13"/>
+      <c r="C163" s="14"/>
+      <c r="D163" s="15"/>
+      <c r="E163" s="14"/>
       <c r="F163" s="6" t="str">
         <f>IF(A163="","",IFERROR(LOOKUP(2,1/(A$4:A162=A163),F$4:F162),0)+IF(ISNUMBER(C163),C163,0)-IF(ISNUMBER(E163),E163,0))</f>
         <v/>
@@ -4417,11 +4435,11 @@
       <c r="I163" s="7"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A164" s="4"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="6"/>
+      <c r="A164" s="12"/>
+      <c r="B164" s="13"/>
+      <c r="C164" s="14"/>
+      <c r="D164" s="15"/>
+      <c r="E164" s="14"/>
       <c r="F164" s="6" t="str">
         <f>IF(A164="","",IFERROR(LOOKUP(2,1/(A$4:A163=A164),F$4:F163),0)+IF(ISNUMBER(C164),C164,0)-IF(ISNUMBER(E164),E164,0))</f>
         <v/>
@@ -4433,11 +4451,11 @@
       <c r="I164" s="7"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A165" s="4"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="6"/>
+      <c r="A165" s="12"/>
+      <c r="B165" s="13"/>
+      <c r="C165" s="14"/>
+      <c r="D165" s="15"/>
+      <c r="E165" s="14"/>
       <c r="F165" s="6" t="str">
         <f>IF(A165="","",IFERROR(LOOKUP(2,1/(A$4:A164=A165),F$4:F164),0)+IF(ISNUMBER(C165),C165,0)-IF(ISNUMBER(E165),E165,0))</f>
         <v/>
@@ -4449,11 +4467,11 @@
       <c r="I165" s="7"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A166" s="4"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="6"/>
+      <c r="A166" s="12"/>
+      <c r="B166" s="13"/>
+      <c r="C166" s="14"/>
+      <c r="D166" s="15"/>
+      <c r="E166" s="14"/>
       <c r="F166" s="6" t="str">
         <f>IF(A166="","",IFERROR(LOOKUP(2,1/(A$4:A165=A166),F$4:F165),0)+IF(ISNUMBER(C166),C166,0)-IF(ISNUMBER(E166),E166,0))</f>
         <v/>
@@ -4465,11 +4483,11 @@
       <c r="I166" s="7"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A167" s="4"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="6"/>
+      <c r="A167" s="12"/>
+      <c r="B167" s="13"/>
+      <c r="C167" s="14"/>
+      <c r="D167" s="15"/>
+      <c r="E167" s="14"/>
       <c r="F167" s="6" t="str">
         <f>IF(A167="","",IFERROR(LOOKUP(2,1/(A$4:A166=A167),F$4:F166),0)+IF(ISNUMBER(C167),C167,0)-IF(ISNUMBER(E167),E167,0))</f>
         <v/>
@@ -4481,11 +4499,11 @@
       <c r="I167" s="7"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A168" s="4"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="6"/>
+      <c r="A168" s="12"/>
+      <c r="B168" s="13"/>
+      <c r="C168" s="14"/>
+      <c r="D168" s="15"/>
+      <c r="E168" s="14"/>
       <c r="F168" s="6" t="str">
         <f>IF(A168="","",IFERROR(LOOKUP(2,1/(A$4:A167=A168),F$4:F167),0)+IF(ISNUMBER(C168),C168,0)-IF(ISNUMBER(E168),E168,0))</f>
         <v/>
@@ -4497,11 +4515,11 @@
       <c r="I168" s="7"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A169" s="4"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="6"/>
+      <c r="A169" s="12"/>
+      <c r="B169" s="13"/>
+      <c r="C169" s="14"/>
+      <c r="D169" s="15"/>
+      <c r="E169" s="14"/>
       <c r="F169" s="6" t="str">
         <f>IF(A169="","",IFERROR(LOOKUP(2,1/(A$4:A168=A169),F$4:F168),0)+IF(ISNUMBER(C169),C169,0)-IF(ISNUMBER(E169),E169,0))</f>
         <v/>
@@ -4513,11 +4531,11 @@
       <c r="I169" s="7"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A170" s="4"/>
-      <c r="B170" s="5"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="6"/>
+      <c r="A170" s="12"/>
+      <c r="B170" s="13"/>
+      <c r="C170" s="14"/>
+      <c r="D170" s="15"/>
+      <c r="E170" s="14"/>
       <c r="F170" s="6" t="str">
         <f>IF(A170="","",IFERROR(LOOKUP(2,1/(A$4:A169=A170),F$4:F169),0)+IF(ISNUMBER(C170),C170,0)-IF(ISNUMBER(E170),E170,0))</f>
         <v/>
@@ -4529,11 +4547,11 @@
       <c r="I170" s="7"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A171" s="4"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="7"/>
-      <c r="E171" s="6"/>
+      <c r="A171" s="12"/>
+      <c r="B171" s="13"/>
+      <c r="C171" s="14"/>
+      <c r="D171" s="15"/>
+      <c r="E171" s="14"/>
       <c r="F171" s="6" t="str">
         <f>IF(A171="","",IFERROR(LOOKUP(2,1/(A$4:A170=A171),F$4:F170),0)+IF(ISNUMBER(C171),C171,0)-IF(ISNUMBER(E171),E171,0))</f>
         <v/>
@@ -4545,11 +4563,11 @@
       <c r="I171" s="7"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A172" s="4"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="6"/>
+      <c r="A172" s="12"/>
+      <c r="B172" s="13"/>
+      <c r="C172" s="14"/>
+      <c r="D172" s="15"/>
+      <c r="E172" s="14"/>
       <c r="F172" s="6" t="str">
         <f>IF(A172="","",IFERROR(LOOKUP(2,1/(A$4:A171=A172),F$4:F171),0)+IF(ISNUMBER(C172),C172,0)-IF(ISNUMBER(E172),E172,0))</f>
         <v/>
@@ -4561,11 +4579,11 @@
       <c r="I172" s="7"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A173" s="4"/>
-      <c r="B173" s="5"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="6"/>
+      <c r="A173" s="12"/>
+      <c r="B173" s="13"/>
+      <c r="C173" s="14"/>
+      <c r="D173" s="15"/>
+      <c r="E173" s="14"/>
       <c r="F173" s="6" t="str">
         <f>IF(A173="","",IFERROR(LOOKUP(2,1/(A$4:A172=A173),F$4:F172),0)+IF(ISNUMBER(C173),C173,0)-IF(ISNUMBER(E173),E173,0))</f>
         <v/>
@@ -4577,11 +4595,11 @@
       <c r="I173" s="7"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A174" s="4"/>
-      <c r="B174" s="5"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="6"/>
+      <c r="A174" s="12"/>
+      <c r="B174" s="13"/>
+      <c r="C174" s="14"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="14"/>
       <c r="F174" s="6" t="str">
         <f>IF(A174="","",IFERROR(LOOKUP(2,1/(A$4:A173=A174),F$4:F173),0)+IF(ISNUMBER(C174),C174,0)-IF(ISNUMBER(E174),E174,0))</f>
         <v/>
@@ -4593,11 +4611,11 @@
       <c r="I174" s="7"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A175" s="4"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="6"/>
+      <c r="A175" s="12"/>
+      <c r="B175" s="13"/>
+      <c r="C175" s="14"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="14"/>
       <c r="F175" s="6" t="str">
         <f>IF(A175="","",IFERROR(LOOKUP(2,1/(A$4:A174=A175),F$4:F174),0)+IF(ISNUMBER(C175),C175,0)-IF(ISNUMBER(E175),E175,0))</f>
         <v/>
@@ -4609,11 +4627,11 @@
       <c r="I175" s="7"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A176" s="4"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="7"/>
-      <c r="E176" s="6"/>
+      <c r="A176" s="12"/>
+      <c r="B176" s="13"/>
+      <c r="C176" s="14"/>
+      <c r="D176" s="15"/>
+      <c r="E176" s="14"/>
       <c r="F176" s="6" t="str">
         <f>IF(A176="","",IFERROR(LOOKUP(2,1/(A$4:A175=A176),F$4:F175),0)+IF(ISNUMBER(C176),C176,0)-IF(ISNUMBER(E176),E176,0))</f>
         <v/>
@@ -4625,11 +4643,11 @@
       <c r="I176" s="7"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A177" s="4"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="7"/>
-      <c r="E177" s="6"/>
+      <c r="A177" s="12"/>
+      <c r="B177" s="13"/>
+      <c r="C177" s="14"/>
+      <c r="D177" s="15"/>
+      <c r="E177" s="14"/>
       <c r="F177" s="6" t="str">
         <f>IF(A177="","",IFERROR(LOOKUP(2,1/(A$4:A176=A177),F$4:F176),0)+IF(ISNUMBER(C177),C177,0)-IF(ISNUMBER(E177),E177,0))</f>
         <v/>
@@ -4641,11 +4659,11 @@
       <c r="I177" s="7"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A178" s="4"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="7"/>
-      <c r="E178" s="6"/>
+      <c r="A178" s="12"/>
+      <c r="B178" s="13"/>
+      <c r="C178" s="14"/>
+      <c r="D178" s="15"/>
+      <c r="E178" s="14"/>
       <c r="F178" s="6" t="str">
         <f>IF(A178="","",IFERROR(LOOKUP(2,1/(A$4:A177=A178),F$4:F177),0)+IF(ISNUMBER(C178),C178,0)-IF(ISNUMBER(E178),E178,0))</f>
         <v/>
@@ -4657,11 +4675,11 @@
       <c r="I178" s="7"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A179" s="4"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="6"/>
+      <c r="A179" s="12"/>
+      <c r="B179" s="13"/>
+      <c r="C179" s="14"/>
+      <c r="D179" s="15"/>
+      <c r="E179" s="14"/>
       <c r="F179" s="6" t="str">
         <f>IF(A179="","",IFERROR(LOOKUP(2,1/(A$4:A178=A179),F$4:F178),0)+IF(ISNUMBER(C179),C179,0)-IF(ISNUMBER(E179),E179,0))</f>
         <v/>
@@ -4673,11 +4691,11 @@
       <c r="I179" s="7"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A180" s="4"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="7"/>
-      <c r="E180" s="6"/>
+      <c r="A180" s="12"/>
+      <c r="B180" s="13"/>
+      <c r="C180" s="14"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="14"/>
       <c r="F180" s="6" t="str">
         <f>IF(A180="","",IFERROR(LOOKUP(2,1/(A$4:A179=A180),F$4:F179),0)+IF(ISNUMBER(C180),C180,0)-IF(ISNUMBER(E180),E180,0))</f>
         <v/>
@@ -4689,11 +4707,11 @@
       <c r="I180" s="7"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A181" s="4"/>
-      <c r="B181" s="5"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="7"/>
-      <c r="E181" s="6"/>
+      <c r="A181" s="12"/>
+      <c r="B181" s="13"/>
+      <c r="C181" s="14"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="14"/>
       <c r="F181" s="6" t="str">
         <f>IF(A181="","",IFERROR(LOOKUP(2,1/(A$4:A180=A181),F$4:F180),0)+IF(ISNUMBER(C181),C181,0)-IF(ISNUMBER(E181),E181,0))</f>
         <v/>
@@ -4705,11 +4723,11 @@
       <c r="I181" s="7"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A182" s="4"/>
-      <c r="B182" s="5"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="7"/>
-      <c r="E182" s="6"/>
+      <c r="A182" s="12"/>
+      <c r="B182" s="13"/>
+      <c r="C182" s="14"/>
+      <c r="D182" s="15"/>
+      <c r="E182" s="14"/>
       <c r="F182" s="6" t="str">
         <f>IF(A182="","",IFERROR(LOOKUP(2,1/(A$4:A181=A182),F$4:F181),0)+IF(ISNUMBER(C182),C182,0)-IF(ISNUMBER(E182),E182,0))</f>
         <v/>
@@ -4721,11 +4739,11 @@
       <c r="I182" s="7"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A183" s="4"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="7"/>
-      <c r="E183" s="6"/>
+      <c r="A183" s="12"/>
+      <c r="B183" s="13"/>
+      <c r="C183" s="14"/>
+      <c r="D183" s="15"/>
+      <c r="E183" s="14"/>
       <c r="F183" s="6" t="str">
         <f>IF(A183="","",IFERROR(LOOKUP(2,1/(A$4:A182=A183),F$4:F182),0)+IF(ISNUMBER(C183),C183,0)-IF(ISNUMBER(E183),E183,0))</f>
         <v/>
@@ -4737,11 +4755,11 @@
       <c r="I183" s="7"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A184" s="4"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="6"/>
+      <c r="A184" s="12"/>
+      <c r="B184" s="13"/>
+      <c r="C184" s="14"/>
+      <c r="D184" s="15"/>
+      <c r="E184" s="14"/>
       <c r="F184" s="6" t="str">
         <f>IF(A184="","",IFERROR(LOOKUP(2,1/(A$4:A183=A184),F$4:F183),0)+IF(ISNUMBER(C184),C184,0)-IF(ISNUMBER(E184),E184,0))</f>
         <v/>
@@ -4753,11 +4771,11 @@
       <c r="I184" s="7"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A185" s="4"/>
-      <c r="B185" s="5"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="7"/>
-      <c r="E185" s="6"/>
+      <c r="A185" s="12"/>
+      <c r="B185" s="13"/>
+      <c r="C185" s="14"/>
+      <c r="D185" s="15"/>
+      <c r="E185" s="14"/>
       <c r="F185" s="6" t="str">
         <f>IF(A185="","",IFERROR(LOOKUP(2,1/(A$4:A184=A185),F$4:F184),0)+IF(ISNUMBER(C185),C185,0)-IF(ISNUMBER(E185),E185,0))</f>
         <v/>
@@ -4769,11 +4787,11 @@
       <c r="I185" s="7"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A186" s="4"/>
-      <c r="B186" s="5"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="7"/>
-      <c r="E186" s="6"/>
+      <c r="A186" s="12"/>
+      <c r="B186" s="13"/>
+      <c r="C186" s="14"/>
+      <c r="D186" s="15"/>
+      <c r="E186" s="14"/>
       <c r="F186" s="6" t="str">
         <f>IF(A186="","",IFERROR(LOOKUP(2,1/(A$4:A185=A186),F$4:F185),0)+IF(ISNUMBER(C186),C186,0)-IF(ISNUMBER(E186),E186,0))</f>
         <v/>
@@ -4785,11 +4803,11 @@
       <c r="I186" s="7"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A187" s="4"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="7"/>
-      <c r="E187" s="6"/>
+      <c r="A187" s="12"/>
+      <c r="B187" s="13"/>
+      <c r="C187" s="14"/>
+      <c r="D187" s="15"/>
+      <c r="E187" s="14"/>
       <c r="F187" s="6" t="str">
         <f>IF(A187="","",IFERROR(LOOKUP(2,1/(A$4:A186=A187),F$4:F186),0)+IF(ISNUMBER(C187),C187,0)-IF(ISNUMBER(E187),E187,0))</f>
         <v/>
@@ -4801,11 +4819,11 @@
       <c r="I187" s="7"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A188" s="4"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="7"/>
-      <c r="E188" s="6"/>
+      <c r="A188" s="12"/>
+      <c r="B188" s="13"/>
+      <c r="C188" s="14"/>
+      <c r="D188" s="15"/>
+      <c r="E188" s="14"/>
       <c r="F188" s="6" t="str">
         <f>IF(A188="","",IFERROR(LOOKUP(2,1/(A$4:A187=A188),F$4:F187),0)+IF(ISNUMBER(C188),C188,0)-IF(ISNUMBER(E188),E188,0))</f>
         <v/>
@@ -4817,11 +4835,11 @@
       <c r="I188" s="7"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A189" s="4"/>
-      <c r="B189" s="5"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="6"/>
+      <c r="A189" s="12"/>
+      <c r="B189" s="13"/>
+      <c r="C189" s="14"/>
+      <c r="D189" s="15"/>
+      <c r="E189" s="14"/>
       <c r="F189" s="6" t="str">
         <f>IF(A189="","",IFERROR(LOOKUP(2,1/(A$4:A188=A189),F$4:F188),0)+IF(ISNUMBER(C189),C189,0)-IF(ISNUMBER(E189),E189,0))</f>
         <v/>
@@ -4833,11 +4851,11 @@
       <c r="I189" s="7"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A190" s="4"/>
-      <c r="B190" s="5"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="7"/>
-      <c r="E190" s="6"/>
+      <c r="A190" s="12"/>
+      <c r="B190" s="13"/>
+      <c r="C190" s="14"/>
+      <c r="D190" s="15"/>
+      <c r="E190" s="14"/>
       <c r="F190" s="6" t="str">
         <f>IF(A190="","",IFERROR(LOOKUP(2,1/(A$4:A189=A190),F$4:F189),0)+IF(ISNUMBER(C190),C190,0)-IF(ISNUMBER(E190),E190,0))</f>
         <v/>
@@ -4849,11 +4867,11 @@
       <c r="I190" s="7"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A191" s="4"/>
-      <c r="B191" s="5"/>
-      <c r="C191" s="6"/>
-      <c r="D191" s="7"/>
-      <c r="E191" s="6"/>
+      <c r="A191" s="12"/>
+      <c r="B191" s="13"/>
+      <c r="C191" s="14"/>
+      <c r="D191" s="15"/>
+      <c r="E191" s="14"/>
       <c r="F191" s="6" t="str">
         <f>IF(A191="","",IFERROR(LOOKUP(2,1/(A$4:A190=A191),F$4:F190),0)+IF(ISNUMBER(C191),C191,0)-IF(ISNUMBER(E191),E191,0))</f>
         <v/>
@@ -4865,11 +4883,11 @@
       <c r="I191" s="7"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A192" s="4"/>
-      <c r="B192" s="5"/>
-      <c r="C192" s="6"/>
-      <c r="D192" s="7"/>
-      <c r="E192" s="6"/>
+      <c r="A192" s="12"/>
+      <c r="B192" s="13"/>
+      <c r="C192" s="14"/>
+      <c r="D192" s="15"/>
+      <c r="E192" s="14"/>
       <c r="F192" s="6" t="str">
         <f>IF(A192="","",IFERROR(LOOKUP(2,1/(A$4:A191=A192),F$4:F191),0)+IF(ISNUMBER(C192),C192,0)-IF(ISNUMBER(E192),E192,0))</f>
         <v/>
@@ -4881,11 +4899,11 @@
       <c r="I192" s="7"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A193" s="4"/>
-      <c r="B193" s="5"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="6"/>
+      <c r="A193" s="12"/>
+      <c r="B193" s="13"/>
+      <c r="C193" s="14"/>
+      <c r="D193" s="15"/>
+      <c r="E193" s="14"/>
       <c r="F193" s="6" t="str">
         <f>IF(A193="","",IFERROR(LOOKUP(2,1/(A$4:A192=A193),F$4:F192),0)+IF(ISNUMBER(C193),C193,0)-IF(ISNUMBER(E193),E193,0))</f>
         <v/>
@@ -4897,11 +4915,11 @@
       <c r="I193" s="7"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A194" s="4"/>
-      <c r="B194" s="5"/>
-      <c r="C194" s="6"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="6"/>
+      <c r="A194" s="12"/>
+      <c r="B194" s="13"/>
+      <c r="C194" s="14"/>
+      <c r="D194" s="15"/>
+      <c r="E194" s="14"/>
       <c r="F194" s="6" t="str">
         <f>IF(A194="","",IFERROR(LOOKUP(2,1/(A$4:A193=A194),F$4:F193),0)+IF(ISNUMBER(C194),C194,0)-IF(ISNUMBER(E194),E194,0))</f>
         <v/>
@@ -4913,11 +4931,11 @@
       <c r="I194" s="7"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A195" s="4"/>
-      <c r="B195" s="5"/>
-      <c r="C195" s="6"/>
-      <c r="D195" s="7"/>
-      <c r="E195" s="6"/>
+      <c r="A195" s="12"/>
+      <c r="B195" s="13"/>
+      <c r="C195" s="14"/>
+      <c r="D195" s="15"/>
+      <c r="E195" s="14"/>
       <c r="F195" s="6" t="str">
         <f>IF(A195="","",IFERROR(LOOKUP(2,1/(A$4:A194=A195),F$4:F194),0)+IF(ISNUMBER(C195),C195,0)-IF(ISNUMBER(E195),E195,0))</f>
         <v/>
@@ -4929,11 +4947,11 @@
       <c r="I195" s="7"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A196" s="4"/>
-      <c r="B196" s="5"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="6"/>
+      <c r="A196" s="12"/>
+      <c r="B196" s="13"/>
+      <c r="C196" s="14"/>
+      <c r="D196" s="15"/>
+      <c r="E196" s="14"/>
       <c r="F196" s="6" t="str">
         <f>IF(A196="","",IFERROR(LOOKUP(2,1/(A$4:A195=A196),F$4:F195),0)+IF(ISNUMBER(C196),C196,0)-IF(ISNUMBER(E196),E196,0))</f>
         <v/>
@@ -4945,11 +4963,11 @@
       <c r="I196" s="7"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A197" s="4"/>
-      <c r="B197" s="5"/>
-      <c r="C197" s="6"/>
-      <c r="D197" s="7"/>
-      <c r="E197" s="6"/>
+      <c r="A197" s="12"/>
+      <c r="B197" s="13"/>
+      <c r="C197" s="14"/>
+      <c r="D197" s="15"/>
+      <c r="E197" s="14"/>
       <c r="F197" s="6" t="str">
         <f>IF(A197="","",IFERROR(LOOKUP(2,1/(A$4:A196=A197),F$4:F196),0)+IF(ISNUMBER(C197),C197,0)-IF(ISNUMBER(E197),E197,0))</f>
         <v/>
@@ -4961,11 +4979,11 @@
       <c r="I197" s="7"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A198" s="4"/>
-      <c r="B198" s="5"/>
-      <c r="C198" s="6"/>
-      <c r="D198" s="7"/>
-      <c r="E198" s="6"/>
+      <c r="A198" s="12"/>
+      <c r="B198" s="13"/>
+      <c r="C198" s="14"/>
+      <c r="D198" s="15"/>
+      <c r="E198" s="14"/>
       <c r="F198" s="6" t="str">
         <f>IF(A198="","",IFERROR(LOOKUP(2,1/(A$4:A197=A198),F$4:F197),0)+IF(ISNUMBER(C198),C198,0)-IF(ISNUMBER(E198),E198,0))</f>
         <v/>
@@ -4977,11 +4995,11 @@
       <c r="I198" s="7"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A199" s="4"/>
-      <c r="B199" s="5"/>
-      <c r="C199" s="6"/>
-      <c r="D199" s="7"/>
-      <c r="E199" s="6"/>
+      <c r="A199" s="12"/>
+      <c r="B199" s="13"/>
+      <c r="C199" s="14"/>
+      <c r="D199" s="15"/>
+      <c r="E199" s="14"/>
       <c r="F199" s="6" t="str">
         <f>IF(A199="","",IFERROR(LOOKUP(2,1/(A$4:A198=A199),F$4:F198),0)+IF(ISNUMBER(C199),C199,0)-IF(ISNUMBER(E199),E199,0))</f>
         <v/>
@@ -4993,11 +5011,11 @@
       <c r="I199" s="7"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A200" s="4"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="6"/>
-      <c r="D200" s="7"/>
-      <c r="E200" s="6"/>
+      <c r="A200" s="12"/>
+      <c r="B200" s="13"/>
+      <c r="C200" s="14"/>
+      <c r="D200" s="15"/>
+      <c r="E200" s="14"/>
       <c r="F200" s="6" t="str">
         <f>IF(A200="","",IFERROR(LOOKUP(2,1/(A$4:A199=A200),F$4:F199),0)+IF(ISNUMBER(C200),C200,0)-IF(ISNUMBER(E200),E200,0))</f>
         <v/>
@@ -5009,11 +5027,11 @@
       <c r="I200" s="7"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A201" s="4"/>
-      <c r="B201" s="5"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="7"/>
-      <c r="E201" s="6"/>
+      <c r="A201" s="12"/>
+      <c r="B201" s="13"/>
+      <c r="C201" s="14"/>
+      <c r="D201" s="15"/>
+      <c r="E201" s="14"/>
       <c r="F201" s="6" t="str">
         <f>IF(A201="","",IFERROR(LOOKUP(2,1/(A$4:A200=A201),F$4:F200),0)+IF(ISNUMBER(C201),C201,0)-IF(ISNUMBER(E201),E201,0))</f>
         <v/>
@@ -5025,11 +5043,11 @@
       <c r="I201" s="7"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A202" s="4"/>
-      <c r="B202" s="5"/>
-      <c r="C202" s="6"/>
-      <c r="D202" s="7"/>
-      <c r="E202" s="6"/>
+      <c r="A202" s="12"/>
+      <c r="B202" s="13"/>
+      <c r="C202" s="14"/>
+      <c r="D202" s="15"/>
+      <c r="E202" s="14"/>
       <c r="F202" s="6" t="str">
         <f>IF(A202="","",IFERROR(LOOKUP(2,1/(A$4:A201=A202),F$4:F201),0)+IF(ISNUMBER(C202),C202,0)-IF(ISNUMBER(E202),E202,0))</f>
         <v/>
@@ -5041,11 +5059,11 @@
       <c r="I202" s="7"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A203" s="4"/>
-      <c r="B203" s="5"/>
-      <c r="C203" s="6"/>
-      <c r="D203" s="7"/>
-      <c r="E203" s="6"/>
+      <c r="A203" s="12"/>
+      <c r="B203" s="13"/>
+      <c r="C203" s="14"/>
+      <c r="D203" s="15"/>
+      <c r="E203" s="14"/>
       <c r="F203" s="6" t="str">
         <f>IF(A203="","",IFERROR(LOOKUP(2,1/(A$4:A202=A203),F$4:F202),0)+IF(ISNUMBER(C203),C203,0)-IF(ISNUMBER(E203),E203,0))</f>
         <v/>
@@ -5057,11 +5075,11 @@
       <c r="I203" s="7"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A204" s="4"/>
-      <c r="B204" s="5"/>
-      <c r="C204" s="6"/>
-      <c r="D204" s="7"/>
-      <c r="E204" s="6"/>
+      <c r="A204" s="12"/>
+      <c r="B204" s="13"/>
+      <c r="C204" s="14"/>
+      <c r="D204" s="15"/>
+      <c r="E204" s="14"/>
       <c r="F204" s="6" t="str">
         <f>IF(A204="","",IFERROR(LOOKUP(2,1/(A$4:A203=A204),F$4:F203),0)+IF(ISNUMBER(C204),C204,0)-IF(ISNUMBER(E204),E204,0))</f>
         <v/>
@@ -5073,11 +5091,11 @@
       <c r="I204" s="7"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A205" s="4"/>
-      <c r="B205" s="5"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="7"/>
-      <c r="E205" s="6"/>
+      <c r="A205" s="12"/>
+      <c r="B205" s="13"/>
+      <c r="C205" s="14"/>
+      <c r="D205" s="15"/>
+      <c r="E205" s="14"/>
       <c r="F205" s="6" t="str">
         <f>IF(A205="","",IFERROR(LOOKUP(2,1/(A$4:A204=A205),F$4:F204),0)+IF(ISNUMBER(C205),C205,0)-IF(ISNUMBER(E205),E205,0))</f>
         <v/>
@@ -5089,11 +5107,11 @@
       <c r="I205" s="7"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A206" s="4"/>
-      <c r="B206" s="5"/>
-      <c r="C206" s="6"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="6"/>
+      <c r="A206" s="12"/>
+      <c r="B206" s="13"/>
+      <c r="C206" s="14"/>
+      <c r="D206" s="15"/>
+      <c r="E206" s="14"/>
       <c r="F206" s="6" t="str">
         <f>IF(A206="","",IFERROR(LOOKUP(2,1/(A$4:A205=A206),F$4:F205),0)+IF(ISNUMBER(C206),C206,0)-IF(ISNUMBER(E206),E206,0))</f>
         <v/>
@@ -5105,11 +5123,11 @@
       <c r="I206" s="7"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A207" s="4"/>
-      <c r="B207" s="5"/>
-      <c r="C207" s="6"/>
-      <c r="D207" s="7"/>
-      <c r="E207" s="6"/>
+      <c r="A207" s="12"/>
+      <c r="B207" s="13"/>
+      <c r="C207" s="14"/>
+      <c r="D207" s="15"/>
+      <c r="E207" s="14"/>
       <c r="F207" s="6" t="str">
         <f>IF(A207="","",IFERROR(LOOKUP(2,1/(A$4:A206=A207),F$4:F206),0)+IF(ISNUMBER(C207),C207,0)-IF(ISNUMBER(E207),E207,0))</f>
         <v/>
@@ -5121,11 +5139,11 @@
       <c r="I207" s="7"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A208" s="4"/>
-      <c r="B208" s="5"/>
-      <c r="C208" s="6"/>
-      <c r="D208" s="7"/>
-      <c r="E208" s="6"/>
+      <c r="A208" s="12"/>
+      <c r="B208" s="13"/>
+      <c r="C208" s="14"/>
+      <c r="D208" s="15"/>
+      <c r="E208" s="14"/>
       <c r="F208" s="6" t="str">
         <f>IF(A208="","",IFERROR(LOOKUP(2,1/(A$4:A207=A208),F$4:F207),0)+IF(ISNUMBER(C208),C208,0)-IF(ISNUMBER(E208),E208,0))</f>
         <v/>
@@ -5137,11 +5155,11 @@
       <c r="I208" s="7"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A209" s="4"/>
-      <c r="B209" s="5"/>
-      <c r="C209" s="6"/>
-      <c r="D209" s="7"/>
-      <c r="E209" s="6"/>
+      <c r="A209" s="12"/>
+      <c r="B209" s="13"/>
+      <c r="C209" s="14"/>
+      <c r="D209" s="15"/>
+      <c r="E209" s="14"/>
       <c r="F209" s="6" t="str">
         <f>IF(A209="","",IFERROR(LOOKUP(2,1/(A$4:A208=A209),F$4:F208),0)+IF(ISNUMBER(C209),C209,0)-IF(ISNUMBER(E209),E209,0))</f>
         <v/>
@@ -5153,11 +5171,11 @@
       <c r="I209" s="7"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A210" s="4"/>
-      <c r="B210" s="5"/>
-      <c r="C210" s="6"/>
-      <c r="D210" s="7"/>
-      <c r="E210" s="6"/>
+      <c r="A210" s="12"/>
+      <c r="B210" s="13"/>
+      <c r="C210" s="14"/>
+      <c r="D210" s="15"/>
+      <c r="E210" s="14"/>
       <c r="F210" s="6" t="str">
         <f>IF(A210="","",IFERROR(LOOKUP(2,1/(A$4:A209=A210),F$4:F209),0)+IF(ISNUMBER(C210),C210,0)-IF(ISNUMBER(E210),E210,0))</f>
         <v/>
@@ -5169,11 +5187,11 @@
       <c r="I210" s="7"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A211" s="4"/>
-      <c r="B211" s="5"/>
-      <c r="C211" s="6"/>
-      <c r="D211" s="7"/>
-      <c r="E211" s="6"/>
+      <c r="A211" s="12"/>
+      <c r="B211" s="13"/>
+      <c r="C211" s="14"/>
+      <c r="D211" s="15"/>
+      <c r="E211" s="14"/>
       <c r="F211" s="6" t="str">
         <f>IF(A211="","",IFERROR(LOOKUP(2,1/(A$4:A210=A211),F$4:F210),0)+IF(ISNUMBER(C211),C211,0)-IF(ISNUMBER(E211),E211,0))</f>
         <v/>
@@ -5185,11 +5203,11 @@
       <c r="I211" s="7"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A212" s="4"/>
-      <c r="B212" s="5"/>
-      <c r="C212" s="6"/>
-      <c r="D212" s="7"/>
-      <c r="E212" s="6"/>
+      <c r="A212" s="12"/>
+      <c r="B212" s="13"/>
+      <c r="C212" s="14"/>
+      <c r="D212" s="15"/>
+      <c r="E212" s="14"/>
       <c r="F212" s="6" t="str">
         <f>IF(A212="","",IFERROR(LOOKUP(2,1/(A$4:A211=A212),F$4:F211),0)+IF(ISNUMBER(C212),C212,0)-IF(ISNUMBER(E212),E212,0))</f>
         <v/>
@@ -5201,11 +5219,11 @@
       <c r="I212" s="7"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A213" s="4"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="6"/>
-      <c r="D213" s="7"/>
-      <c r="E213" s="6"/>
+      <c r="A213" s="12"/>
+      <c r="B213" s="13"/>
+      <c r="C213" s="14"/>
+      <c r="D213" s="15"/>
+      <c r="E213" s="14"/>
       <c r="F213" s="6" t="str">
         <f>IF(A213="","",IFERROR(LOOKUP(2,1/(A$4:A212=A213),F$4:F212),0)+IF(ISNUMBER(C213),C213,0)-IF(ISNUMBER(E213),E213,0))</f>
         <v/>
@@ -5217,11 +5235,11 @@
       <c r="I213" s="7"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A214" s="4"/>
-      <c r="B214" s="5"/>
-      <c r="C214" s="6"/>
-      <c r="D214" s="7"/>
-      <c r="E214" s="6"/>
+      <c r="A214" s="12"/>
+      <c r="B214" s="13"/>
+      <c r="C214" s="14"/>
+      <c r="D214" s="15"/>
+      <c r="E214" s="14"/>
       <c r="F214" s="6" t="str">
         <f>IF(A214="","",IFERROR(LOOKUP(2,1/(A$4:A213=A214),F$4:F213),0)+IF(ISNUMBER(C214),C214,0)-IF(ISNUMBER(E214),E214,0))</f>
         <v/>
@@ -5233,11 +5251,11 @@
       <c r="I214" s="7"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A215" s="4"/>
-      <c r="B215" s="5"/>
-      <c r="C215" s="6"/>
-      <c r="D215" s="7"/>
-      <c r="E215" s="6"/>
+      <c r="A215" s="12"/>
+      <c r="B215" s="13"/>
+      <c r="C215" s="14"/>
+      <c r="D215" s="15"/>
+      <c r="E215" s="14"/>
       <c r="F215" s="6" t="str">
         <f>IF(A215="","",IFERROR(LOOKUP(2,1/(A$4:A214=A215),F$4:F214),0)+IF(ISNUMBER(C215),C215,0)-IF(ISNUMBER(E215),E215,0))</f>
         <v/>
@@ -5249,11 +5267,11 @@
       <c r="I215" s="7"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A216" s="4"/>
-      <c r="B216" s="5"/>
-      <c r="C216" s="6"/>
-      <c r="D216" s="7"/>
-      <c r="E216" s="6"/>
+      <c r="A216" s="12"/>
+      <c r="B216" s="13"/>
+      <c r="C216" s="14"/>
+      <c r="D216" s="15"/>
+      <c r="E216" s="14"/>
       <c r="F216" s="6" t="str">
         <f>IF(A216="","",IFERROR(LOOKUP(2,1/(A$4:A215=A216),F$4:F215),0)+IF(ISNUMBER(C216),C216,0)-IF(ISNUMBER(E216),E216,0))</f>
         <v/>
@@ -5265,11 +5283,11 @@
       <c r="I216" s="7"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A217" s="4"/>
-      <c r="B217" s="5"/>
-      <c r="C217" s="6"/>
-      <c r="D217" s="7"/>
-      <c r="E217" s="6"/>
+      <c r="A217" s="12"/>
+      <c r="B217" s="13"/>
+      <c r="C217" s="14"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="14"/>
       <c r="F217" s="6" t="str">
         <f>IF(A217="","",IFERROR(LOOKUP(2,1/(A$4:A216=A217),F$4:F216),0)+IF(ISNUMBER(C217),C217,0)-IF(ISNUMBER(E217),E217,0))</f>
         <v/>
@@ -5281,11 +5299,11 @@
       <c r="I217" s="7"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A218" s="4"/>
-      <c r="B218" s="5"/>
-      <c r="C218" s="6"/>
-      <c r="D218" s="7"/>
-      <c r="E218" s="6"/>
+      <c r="A218" s="12"/>
+      <c r="B218" s="13"/>
+      <c r="C218" s="14"/>
+      <c r="D218" s="15"/>
+      <c r="E218" s="14"/>
       <c r="F218" s="6" t="str">
         <f>IF(A218="","",IFERROR(LOOKUP(2,1/(A$4:A217=A218),F$4:F217),0)+IF(ISNUMBER(C218),C218,0)-IF(ISNUMBER(E218),E218,0))</f>
         <v/>
@@ -5297,11 +5315,11 @@
       <c r="I218" s="7"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A219" s="4"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="6"/>
-      <c r="D219" s="7"/>
-      <c r="E219" s="6"/>
+      <c r="A219" s="12"/>
+      <c r="B219" s="13"/>
+      <c r="C219" s="14"/>
+      <c r="D219" s="15"/>
+      <c r="E219" s="14"/>
       <c r="F219" s="6" t="str">
         <f>IF(A219="","",IFERROR(LOOKUP(2,1/(A$4:A218=A219),F$4:F218),0)+IF(ISNUMBER(C219),C219,0)-IF(ISNUMBER(E219),E219,0))</f>
         <v/>
@@ -5313,11 +5331,11 @@
       <c r="I219" s="7"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A220" s="4"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="6"/>
-      <c r="D220" s="7"/>
-      <c r="E220" s="6"/>
+      <c r="A220" s="12"/>
+      <c r="B220" s="13"/>
+      <c r="C220" s="14"/>
+      <c r="D220" s="15"/>
+      <c r="E220" s="14"/>
       <c r="F220" s="6" t="str">
         <f>IF(A220="","",IFERROR(LOOKUP(2,1/(A$4:A219=A220),F$4:F219),0)+IF(ISNUMBER(C220),C220,0)-IF(ISNUMBER(E220),E220,0))</f>
         <v/>
@@ -5329,11 +5347,11 @@
       <c r="I220" s="7"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A221" s="4"/>
-      <c r="B221" s="5"/>
-      <c r="C221" s="6"/>
-      <c r="D221" s="7"/>
-      <c r="E221" s="6"/>
+      <c r="A221" s="12"/>
+      <c r="B221" s="13"/>
+      <c r="C221" s="14"/>
+      <c r="D221" s="15"/>
+      <c r="E221" s="14"/>
       <c r="F221" s="6" t="str">
         <f>IF(A221="","",IFERROR(LOOKUP(2,1/(A$4:A220=A221),F$4:F220),0)+IF(ISNUMBER(C221),C221,0)-IF(ISNUMBER(E221),E221,0))</f>
         <v/>
@@ -5345,11 +5363,11 @@
       <c r="I221" s="7"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A222" s="4"/>
-      <c r="B222" s="5"/>
-      <c r="C222" s="6"/>
-      <c r="D222" s="7"/>
-      <c r="E222" s="6"/>
+      <c r="A222" s="12"/>
+      <c r="B222" s="13"/>
+      <c r="C222" s="14"/>
+      <c r="D222" s="15"/>
+      <c r="E222" s="14"/>
       <c r="F222" s="6" t="str">
         <f>IF(A222="","",IFERROR(LOOKUP(2,1/(A$4:A221=A222),F$4:F221),0)+IF(ISNUMBER(C222),C222,0)-IF(ISNUMBER(E222),E222,0))</f>
         <v/>
@@ -5361,11 +5379,11 @@
       <c r="I222" s="7"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A223" s="4"/>
-      <c r="B223" s="5"/>
-      <c r="C223" s="6"/>
-      <c r="D223" s="7"/>
-      <c r="E223" s="6"/>
+      <c r="A223" s="12"/>
+      <c r="B223" s="13"/>
+      <c r="C223" s="14"/>
+      <c r="D223" s="15"/>
+      <c r="E223" s="14"/>
       <c r="F223" s="6" t="str">
         <f>IF(A223="","",IFERROR(LOOKUP(2,1/(A$4:A222=A223),F$4:F222),0)+IF(ISNUMBER(C223),C223,0)-IF(ISNUMBER(E223),E223,0))</f>
         <v/>
@@ -5377,11 +5395,11 @@
       <c r="I223" s="7"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A224" s="4"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="6"/>
-      <c r="D224" s="7"/>
-      <c r="E224" s="6"/>
+      <c r="A224" s="12"/>
+      <c r="B224" s="13"/>
+      <c r="C224" s="14"/>
+      <c r="D224" s="15"/>
+      <c r="E224" s="14"/>
       <c r="F224" s="6" t="str">
         <f>IF(A224="","",IFERROR(LOOKUP(2,1/(A$4:A223=A224),F$4:F223),0)+IF(ISNUMBER(C224),C224,0)-IF(ISNUMBER(E224),E224,0))</f>
         <v/>
@@ -5393,11 +5411,11 @@
       <c r="I224" s="7"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A225" s="4"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="6"/>
-      <c r="D225" s="7"/>
-      <c r="E225" s="6"/>
+      <c r="A225" s="12"/>
+      <c r="B225" s="13"/>
+      <c r="C225" s="14"/>
+      <c r="D225" s="15"/>
+      <c r="E225" s="14"/>
       <c r="F225" s="6" t="str">
         <f>IF(A225="","",IFERROR(LOOKUP(2,1/(A$4:A224=A225),F$4:F224),0)+IF(ISNUMBER(C225),C225,0)-IF(ISNUMBER(E225),E225,0))</f>
         <v/>
@@ -5409,11 +5427,11 @@
       <c r="I225" s="7"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A226" s="4"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="6"/>
-      <c r="D226" s="7"/>
-      <c r="E226" s="6"/>
+      <c r="A226" s="12"/>
+      <c r="B226" s="13"/>
+      <c r="C226" s="14"/>
+      <c r="D226" s="15"/>
+      <c r="E226" s="14"/>
       <c r="F226" s="6" t="str">
         <f>IF(A226="","",IFERROR(LOOKUP(2,1/(A$4:A225=A226),F$4:F225),0)+IF(ISNUMBER(C226),C226,0)-IF(ISNUMBER(E226),E226,0))</f>
         <v/>
@@ -5425,11 +5443,11 @@
       <c r="I226" s="7"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A227" s="4"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="6"/>
-      <c r="D227" s="7"/>
-      <c r="E227" s="6"/>
+      <c r="A227" s="12"/>
+      <c r="B227" s="13"/>
+      <c r="C227" s="14"/>
+      <c r="D227" s="15"/>
+      <c r="E227" s="14"/>
       <c r="F227" s="6" t="str">
         <f>IF(A227="","",IFERROR(LOOKUP(2,1/(A$4:A226=A227),F$4:F226),0)+IF(ISNUMBER(C227),C227,0)-IF(ISNUMBER(E227),E227,0))</f>
         <v/>
@@ -5441,11 +5459,11 @@
       <c r="I227" s="7"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A228" s="4"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="6"/>
-      <c r="D228" s="7"/>
-      <c r="E228" s="6"/>
+      <c r="A228" s="12"/>
+      <c r="B228" s="13"/>
+      <c r="C228" s="14"/>
+      <c r="D228" s="15"/>
+      <c r="E228" s="14"/>
       <c r="F228" s="6" t="str">
         <f>IF(A228="","",IFERROR(LOOKUP(2,1/(A$4:A227=A228),F$4:F227),0)+IF(ISNUMBER(C228),C228,0)-IF(ISNUMBER(E228),E228,0))</f>
         <v/>
@@ -5457,11 +5475,11 @@
       <c r="I228" s="7"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A229" s="4"/>
-      <c r="B229" s="5"/>
-      <c r="C229" s="6"/>
-      <c r="D229" s="7"/>
-      <c r="E229" s="6"/>
+      <c r="A229" s="12"/>
+      <c r="B229" s="13"/>
+      <c r="C229" s="14"/>
+      <c r="D229" s="15"/>
+      <c r="E229" s="14"/>
       <c r="F229" s="6" t="str">
         <f>IF(A229="","",IFERROR(LOOKUP(2,1/(A$4:A228=A229),F$4:F228),0)+IF(ISNUMBER(C229),C229,0)-IF(ISNUMBER(E229),E229,0))</f>
         <v/>
@@ -5473,11 +5491,11 @@
       <c r="I229" s="7"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A230" s="4"/>
-      <c r="B230" s="5"/>
-      <c r="C230" s="6"/>
-      <c r="D230" s="7"/>
-      <c r="E230" s="6"/>
+      <c r="A230" s="12"/>
+      <c r="B230" s="13"/>
+      <c r="C230" s="14"/>
+      <c r="D230" s="15"/>
+      <c r="E230" s="14"/>
       <c r="F230" s="6" t="str">
         <f>IF(A230="","",IFERROR(LOOKUP(2,1/(A$4:A229=A230),F$4:F229),0)+IF(ISNUMBER(C230),C230,0)-IF(ISNUMBER(E230),E230,0))</f>
         <v/>
@@ -5489,11 +5507,11 @@
       <c r="I230" s="7"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A231" s="4"/>
-      <c r="B231" s="5"/>
-      <c r="C231" s="6"/>
-      <c r="D231" s="7"/>
-      <c r="E231" s="6"/>
+      <c r="A231" s="12"/>
+      <c r="B231" s="13"/>
+      <c r="C231" s="14"/>
+      <c r="D231" s="15"/>
+      <c r="E231" s="14"/>
       <c r="F231" s="6" t="str">
         <f>IF(A231="","",IFERROR(LOOKUP(2,1/(A$4:A230=A231),F$4:F230),0)+IF(ISNUMBER(C231),C231,0)-IF(ISNUMBER(E231),E231,0))</f>
         <v/>
@@ -5505,11 +5523,11 @@
       <c r="I231" s="7"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A232" s="4"/>
-      <c r="B232" s="5"/>
-      <c r="C232" s="6"/>
-      <c r="D232" s="7"/>
-      <c r="E232" s="6"/>
+      <c r="A232" s="12"/>
+      <c r="B232" s="13"/>
+      <c r="C232" s="14"/>
+      <c r="D232" s="15"/>
+      <c r="E232" s="14"/>
       <c r="F232" s="6" t="str">
         <f>IF(A232="","",IFERROR(LOOKUP(2,1/(A$4:A231=A232),F$4:F231),0)+IF(ISNUMBER(C232),C232,0)-IF(ISNUMBER(E232),E232,0))</f>
         <v/>
@@ -5521,11 +5539,11 @@
       <c r="I232" s="7"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A233" s="4"/>
-      <c r="B233" s="5"/>
-      <c r="C233" s="6"/>
-      <c r="D233" s="7"/>
-      <c r="E233" s="6"/>
+      <c r="A233" s="12"/>
+      <c r="B233" s="13"/>
+      <c r="C233" s="14"/>
+      <c r="D233" s="15"/>
+      <c r="E233" s="14"/>
       <c r="F233" s="6" t="str">
         <f>IF(A233="","",IFERROR(LOOKUP(2,1/(A$4:A232=A233),F$4:F232),0)+IF(ISNUMBER(C233),C233,0)-IF(ISNUMBER(E233),E233,0))</f>
         <v/>
@@ -5537,11 +5555,11 @@
       <c r="I233" s="7"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A234" s="4"/>
-      <c r="B234" s="5"/>
-      <c r="C234" s="6"/>
-      <c r="D234" s="7"/>
-      <c r="E234" s="6"/>
+      <c r="A234" s="12"/>
+      <c r="B234" s="13"/>
+      <c r="C234" s="14"/>
+      <c r="D234" s="15"/>
+      <c r="E234" s="14"/>
       <c r="F234" s="6" t="str">
         <f>IF(A234="","",IFERROR(LOOKUP(2,1/(A$4:A233=A234),F$4:F233),0)+IF(ISNUMBER(C234),C234,0)-IF(ISNUMBER(E234),E234,0))</f>
         <v/>
@@ -5553,11 +5571,11 @@
       <c r="I234" s="7"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A235" s="4"/>
-      <c r="B235" s="5"/>
-      <c r="C235" s="6"/>
-      <c r="D235" s="7"/>
-      <c r="E235" s="6"/>
+      <c r="A235" s="12"/>
+      <c r="B235" s="13"/>
+      <c r="C235" s="14"/>
+      <c r="D235" s="15"/>
+      <c r="E235" s="14"/>
       <c r="F235" s="6" t="str">
         <f>IF(A235="","",IFERROR(LOOKUP(2,1/(A$4:A234=A235),F$4:F234),0)+IF(ISNUMBER(C235),C235,0)-IF(ISNUMBER(E235),E235,0))</f>
         <v/>
@@ -5569,11 +5587,11 @@
       <c r="I235" s="7"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A236" s="4"/>
-      <c r="B236" s="5"/>
-      <c r="C236" s="6"/>
-      <c r="D236" s="7"/>
-      <c r="E236" s="6"/>
+      <c r="A236" s="12"/>
+      <c r="B236" s="13"/>
+      <c r="C236" s="14"/>
+      <c r="D236" s="15"/>
+      <c r="E236" s="14"/>
       <c r="F236" s="6" t="str">
         <f>IF(A236="","",IFERROR(LOOKUP(2,1/(A$4:A235=A236),F$4:F235),0)+IF(ISNUMBER(C236),C236,0)-IF(ISNUMBER(E236),E236,0))</f>
         <v/>
@@ -5585,11 +5603,11 @@
       <c r="I236" s="7"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A237" s="4"/>
-      <c r="B237" s="5"/>
-      <c r="C237" s="6"/>
-      <c r="D237" s="7"/>
-      <c r="E237" s="6"/>
+      <c r="A237" s="12"/>
+      <c r="B237" s="13"/>
+      <c r="C237" s="14"/>
+      <c r="D237" s="15"/>
+      <c r="E237" s="14"/>
       <c r="F237" s="6" t="str">
         <f>IF(A237="","",IFERROR(LOOKUP(2,1/(A$4:A236=A237),F$4:F236),0)+IF(ISNUMBER(C237),C237,0)-IF(ISNUMBER(E237),E237,0))</f>
         <v/>
@@ -5601,11 +5619,11 @@
       <c r="I237" s="7"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A238" s="4"/>
-      <c r="B238" s="5"/>
-      <c r="C238" s="6"/>
-      <c r="D238" s="7"/>
-      <c r="E238" s="6"/>
+      <c r="A238" s="12"/>
+      <c r="B238" s="13"/>
+      <c r="C238" s="14"/>
+      <c r="D238" s="15"/>
+      <c r="E238" s="14"/>
       <c r="F238" s="6" t="str">
         <f>IF(A238="","",IFERROR(LOOKUP(2,1/(A$4:A237=A238),F$4:F237),0)+IF(ISNUMBER(C238),C238,0)-IF(ISNUMBER(E238),E238,0))</f>
         <v/>
@@ -5617,11 +5635,11 @@
       <c r="I238" s="7"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A239" s="4"/>
-      <c r="B239" s="5"/>
-      <c r="C239" s="6"/>
-      <c r="D239" s="7"/>
-      <c r="E239" s="6"/>
+      <c r="A239" s="12"/>
+      <c r="B239" s="13"/>
+      <c r="C239" s="14"/>
+      <c r="D239" s="15"/>
+      <c r="E239" s="14"/>
       <c r="F239" s="6" t="str">
         <f>IF(A239="","",IFERROR(LOOKUP(2,1/(A$4:A238=A239),F$4:F238),0)+IF(ISNUMBER(C239),C239,0)-IF(ISNUMBER(E239),E239,0))</f>
         <v/>
@@ -5633,11 +5651,11 @@
       <c r="I239" s="7"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A240" s="4"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="6"/>
-      <c r="D240" s="7"/>
-      <c r="E240" s="6"/>
+      <c r="A240" s="12"/>
+      <c r="B240" s="13"/>
+      <c r="C240" s="14"/>
+      <c r="D240" s="15"/>
+      <c r="E240" s="14"/>
       <c r="F240" s="6" t="str">
         <f>IF(A240="","",IFERROR(LOOKUP(2,1/(A$4:A239=A240),F$4:F239),0)+IF(ISNUMBER(C240),C240,0)-IF(ISNUMBER(E240),E240,0))</f>
         <v/>
@@ -5649,11 +5667,11 @@
       <c r="I240" s="7"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A241" s="4"/>
-      <c r="B241" s="5"/>
-      <c r="C241" s="6"/>
-      <c r="D241" s="7"/>
-      <c r="E241" s="6"/>
+      <c r="A241" s="12"/>
+      <c r="B241" s="13"/>
+      <c r="C241" s="14"/>
+      <c r="D241" s="15"/>
+      <c r="E241" s="14"/>
       <c r="F241" s="6" t="str">
         <f>IF(A241="","",IFERROR(LOOKUP(2,1/(A$4:A240=A241),F$4:F240),0)+IF(ISNUMBER(C241),C241,0)-IF(ISNUMBER(E241),E241,0))</f>
         <v/>
@@ -5665,11 +5683,11 @@
       <c r="I241" s="7"/>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A242" s="4"/>
-      <c r="B242" s="5"/>
-      <c r="C242" s="6"/>
-      <c r="D242" s="7"/>
-      <c r="E242" s="6"/>
+      <c r="A242" s="12"/>
+      <c r="B242" s="13"/>
+      <c r="C242" s="14"/>
+      <c r="D242" s="15"/>
+      <c r="E242" s="14"/>
       <c r="F242" s="6" t="str">
         <f>IF(A242="","",IFERROR(LOOKUP(2,1/(A$4:A241=A242),F$4:F241),0)+IF(ISNUMBER(C242),C242,0)-IF(ISNUMBER(E242),E242,0))</f>
         <v/>
@@ -5681,11 +5699,11 @@
       <c r="I242" s="7"/>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A243" s="4"/>
-      <c r="B243" s="5"/>
-      <c r="C243" s="6"/>
-      <c r="D243" s="7"/>
-      <c r="E243" s="6"/>
+      <c r="A243" s="12"/>
+      <c r="B243" s="13"/>
+      <c r="C243" s="14"/>
+      <c r="D243" s="15"/>
+      <c r="E243" s="14"/>
       <c r="F243" s="6" t="str">
         <f>IF(A243="","",IFERROR(LOOKUP(2,1/(A$4:A242=A243),F$4:F242),0)+IF(ISNUMBER(C243),C243,0)-IF(ISNUMBER(E243),E243,0))</f>
         <v/>
@@ -5697,11 +5715,11 @@
       <c r="I243" s="7"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A244" s="4"/>
-      <c r="B244" s="5"/>
-      <c r="C244" s="6"/>
-      <c r="D244" s="7"/>
-      <c r="E244" s="6"/>
+      <c r="A244" s="12"/>
+      <c r="B244" s="13"/>
+      <c r="C244" s="14"/>
+      <c r="D244" s="15"/>
+      <c r="E244" s="14"/>
       <c r="F244" s="6" t="str">
         <f>IF(A244="","",IFERROR(LOOKUP(2,1/(A$4:A243=A244),F$4:F243),0)+IF(ISNUMBER(C244),C244,0)-IF(ISNUMBER(E244),E244,0))</f>
         <v/>
@@ -5713,11 +5731,11 @@
       <c r="I244" s="7"/>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A245" s="4"/>
-      <c r="B245" s="5"/>
-      <c r="C245" s="6"/>
-      <c r="D245" s="7"/>
-      <c r="E245" s="6"/>
+      <c r="A245" s="12"/>
+      <c r="B245" s="13"/>
+      <c r="C245" s="14"/>
+      <c r="D245" s="15"/>
+      <c r="E245" s="14"/>
       <c r="F245" s="6" t="str">
         <f>IF(A245="","",IFERROR(LOOKUP(2,1/(A$4:A244=A245),F$4:F244),0)+IF(ISNUMBER(C245),C245,0)-IF(ISNUMBER(E245),E245,0))</f>
         <v/>
@@ -5729,11 +5747,11 @@
       <c r="I245" s="7"/>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A246" s="4"/>
-      <c r="B246" s="5"/>
-      <c r="C246" s="6"/>
-      <c r="D246" s="7"/>
-      <c r="E246" s="6"/>
+      <c r="A246" s="12"/>
+      <c r="B246" s="13"/>
+      <c r="C246" s="14"/>
+      <c r="D246" s="15"/>
+      <c r="E246" s="14"/>
       <c r="F246" s="6" t="str">
         <f>IF(A246="","",IFERROR(LOOKUP(2,1/(A$4:A245=A246),F$4:F245),0)+IF(ISNUMBER(C246),C246,0)-IF(ISNUMBER(E246),E246,0))</f>
         <v/>
@@ -5745,11 +5763,11 @@
       <c r="I246" s="7"/>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A247" s="4"/>
-      <c r="B247" s="5"/>
-      <c r="C247" s="6"/>
-      <c r="D247" s="7"/>
-      <c r="E247" s="6"/>
+      <c r="A247" s="12"/>
+      <c r="B247" s="13"/>
+      <c r="C247" s="14"/>
+      <c r="D247" s="15"/>
+      <c r="E247" s="14"/>
       <c r="F247" s="6" t="str">
         <f>IF(A247="","",IFERROR(LOOKUP(2,1/(A$4:A246=A247),F$4:F246),0)+IF(ISNUMBER(C247),C247,0)-IF(ISNUMBER(E247),E247,0))</f>
         <v/>
@@ -5761,11 +5779,11 @@
       <c r="I247" s="7"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A248" s="4"/>
-      <c r="B248" s="5"/>
-      <c r="C248" s="6"/>
-      <c r="D248" s="7"/>
-      <c r="E248" s="6"/>
+      <c r="A248" s="12"/>
+      <c r="B248" s="13"/>
+      <c r="C248" s="14"/>
+      <c r="D248" s="15"/>
+      <c r="E248" s="14"/>
       <c r="F248" s="6" t="str">
         <f>IF(A248="","",IFERROR(LOOKUP(2,1/(A$4:A247=A248),F$4:F247),0)+IF(ISNUMBER(C248),C248,0)-IF(ISNUMBER(E248),E248,0))</f>
         <v/>
@@ -5777,11 +5795,11 @@
       <c r="I248" s="7"/>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A249" s="4"/>
-      <c r="B249" s="5"/>
-      <c r="C249" s="6"/>
-      <c r="D249" s="7"/>
-      <c r="E249" s="6"/>
+      <c r="A249" s="12"/>
+      <c r="B249" s="13"/>
+      <c r="C249" s="14"/>
+      <c r="D249" s="15"/>
+      <c r="E249" s="14"/>
       <c r="F249" s="6" t="str">
         <f>IF(A249="","",IFERROR(LOOKUP(2,1/(A$4:A248=A249),F$4:F248),0)+IF(ISNUMBER(C249),C249,0)-IF(ISNUMBER(E249),E249,0))</f>
         <v/>
@@ -5793,11 +5811,11 @@
       <c r="I249" s="7"/>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A250" s="4"/>
-      <c r="B250" s="5"/>
-      <c r="C250" s="6"/>
-      <c r="D250" s="7"/>
-      <c r="E250" s="6"/>
+      <c r="A250" s="12"/>
+      <c r="B250" s="13"/>
+      <c r="C250" s="14"/>
+      <c r="D250" s="15"/>
+      <c r="E250" s="14"/>
       <c r="F250" s="6" t="str">
         <f>IF(A250="","",IFERROR(LOOKUP(2,1/(A$4:A249=A250),F$4:F249),0)+IF(ISNUMBER(C250),C250,0)-IF(ISNUMBER(E250),E250,0))</f>
         <v/>
@@ -5809,11 +5827,11 @@
       <c r="I250" s="7"/>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A251" s="4"/>
-      <c r="B251" s="5"/>
-      <c r="C251" s="6"/>
-      <c r="D251" s="7"/>
-      <c r="E251" s="6"/>
+      <c r="A251" s="12"/>
+      <c r="B251" s="13"/>
+      <c r="C251" s="14"/>
+      <c r="D251" s="15"/>
+      <c r="E251" s="14"/>
       <c r="F251" s="6" t="str">
         <f>IF(A251="","",IFERROR(LOOKUP(2,1/(A$4:A250=A251),F$4:F250),0)+IF(ISNUMBER(C251),C251,0)-IF(ISNUMBER(E251),E251,0))</f>
         <v/>
@@ -5915,17 +5933,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="13">
         <v>45839</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7">
+      <c r="C4" s="14"/>
+      <c r="D4" s="15">
         <v>149.9</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="14"/>
       <c r="F4" s="6">
         <f>IF(A4="","",IF(ISNUMBER(C4),C4,0)-IF(ISNUMBER(E4),E4,0))</f>
         <v>0</v>
@@ -5937,19 +5955,19 @@
       <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="13">
         <v>46174</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="14">
         <v>84</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="15">
         <v>149.4</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="14">
         <v>37</v>
       </c>
       <c r="F5" s="6">
@@ -5963,19 +5981,19 @@
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="13">
         <v>46204</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="14">
         <v>213</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="15">
         <v>227</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="14">
         <v>10</v>
       </c>
       <c r="F6" s="6">
@@ -5989,19 +6007,19 @@
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="13">
         <v>46204</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="14">
         <v>10</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="15">
         <v>227</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="14"/>
       <c r="F7" s="6">
         <f>IF(A7="","",IFERROR(LOOKUP(2,1/(A$4:A6=A7),F$4:F6),0)+IF(ISNUMBER(C7),C7,0)-IF(ISNUMBER(E7),E7,0))</f>
         <v>260</v>
@@ -6013,19 +6031,19 @@
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="13">
         <v>46235</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="14">
         <v>37</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="15">
         <v>215.12</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="14">
         <v>10</v>
       </c>
       <c r="F8" s="6">
@@ -6039,17 +6057,17 @@
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="13">
         <v>46266</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7">
+      <c r="C9" s="14"/>
+      <c r="D9" s="15">
         <v>215.12</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="14"/>
       <c r="F9" s="6">
         <f>IF(A9="","",IFERROR(LOOKUP(2,1/(A$4:A8=A9),F$4:F8),0)+IF(ISNUMBER(C9),C9,0)-IF(ISNUMBER(E9),E9,0))</f>
         <v>287</v>
@@ -6061,17 +6079,17 @@
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="13">
         <v>46296</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7">
+      <c r="C10" s="14"/>
+      <c r="D10" s="15">
         <v>215.12</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="6">
         <f>IF(A10="","",IFERROR(LOOKUP(2,1/(A$4:A9=A10),F$4:F9),0)+IF(ISNUMBER(C10),C10,0)-IF(ISNUMBER(E10),E10,0))</f>
         <v>287</v>
@@ -6083,17 +6101,17 @@
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="13">
         <v>46327</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7">
+      <c r="C11" s="14"/>
+      <c r="D11" s="15">
         <v>215.12</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="14"/>
       <c r="F11" s="6">
         <f>IF(A11="","",IFERROR(LOOKUP(2,1/(A$4:A10=A11),F$4:F10),0)+IF(ISNUMBER(C11),C11,0)-IF(ISNUMBER(E11),E11,0))</f>
         <v>287</v>
@@ -6105,11 +6123,11 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="6"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="14"/>
       <c r="F12" s="6" t="str">
         <f>IF(A12="","",IFERROR(LOOKUP(2,1/(A$4:A11=A12),F$4:F11),0)+IF(ISNUMBER(C12),C12,0)-IF(ISNUMBER(E12),E12,0))</f>
         <v/>
@@ -6121,11 +6139,11 @@
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="6"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="6" t="str">
         <f>IF(A13="","",IFERROR(LOOKUP(2,1/(A$4:A12=A13),F$4:F12),0)+IF(ISNUMBER(C13),C13,0)-IF(ISNUMBER(E13),E13,0))</f>
         <v/>
@@ -6137,11 +6155,11 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="6"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="6" t="str">
         <f>IF(A14="","",IFERROR(LOOKUP(2,1/(A$4:A13=A14),F$4:F13),0)+IF(ISNUMBER(C14),C14,0)-IF(ISNUMBER(E14),E14,0))</f>
         <v/>
@@ -6153,11 +6171,11 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="6"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="6" t="str">
         <f>IF(A15="","",IFERROR(LOOKUP(2,1/(A$4:A14=A15),F$4:F14),0)+IF(ISNUMBER(C15),C15,0)-IF(ISNUMBER(E15),E15,0))</f>
         <v/>
@@ -6169,11 +6187,11 @@
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="6"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="14"/>
       <c r="F16" s="6" t="str">
         <f>IF(A16="","",IFERROR(LOOKUP(2,1/(A$4:A15=A16),F$4:F15),0)+IF(ISNUMBER(C16),C16,0)-IF(ISNUMBER(E16),E16,0))</f>
         <v/>
@@ -6185,11 +6203,11 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="6"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="14"/>
       <c r="F17" s="6" t="str">
         <f>IF(A17="","",IFERROR(LOOKUP(2,1/(A$4:A16=A17),F$4:F16),0)+IF(ISNUMBER(C17),C17,0)-IF(ISNUMBER(E17),E17,0))</f>
         <v/>
@@ -6201,11 +6219,11 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="6"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="14"/>
       <c r="F18" s="6" t="str">
         <f>IF(A18="","",IFERROR(LOOKUP(2,1/(A$4:A17=A18),F$4:F17),0)+IF(ISNUMBER(C18),C18,0)-IF(ISNUMBER(E18),E18,0))</f>
         <v/>
@@ -6217,11 +6235,11 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="6"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="14"/>
       <c r="F19" s="6" t="str">
         <f>IF(A19="","",IFERROR(LOOKUP(2,1/(A$4:A18=A19),F$4:F18),0)+IF(ISNUMBER(C19),C19,0)-IF(ISNUMBER(E19),E19,0))</f>
         <v/>
@@ -6233,11 +6251,11 @@
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="6"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="6" t="str">
         <f>IF(A20="","",IFERROR(LOOKUP(2,1/(A$4:A19=A20),F$4:F19),0)+IF(ISNUMBER(C20),C20,0)-IF(ISNUMBER(E20),E20,0))</f>
         <v/>
@@ -6249,11 +6267,11 @@
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="6"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="6" t="str">
         <f>IF(A21="","",IFERROR(LOOKUP(2,1/(A$4:A20=A21),F$4:F20),0)+IF(ISNUMBER(C21),C21,0)-IF(ISNUMBER(E21),E21,0))</f>
         <v/>
@@ -6265,11 +6283,11 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="6"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="14"/>
       <c r="F22" s="6" t="str">
         <f>IF(A22="","",IFERROR(LOOKUP(2,1/(A$4:A21=A22),F$4:F21),0)+IF(ISNUMBER(C22),C22,0)-IF(ISNUMBER(E22),E22,0))</f>
         <v/>
@@ -6281,11 +6299,11 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="6"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="6" t="str">
         <f>IF(A23="","",IFERROR(LOOKUP(2,1/(A$4:A22=A23),F$4:F22),0)+IF(ISNUMBER(C23),C23,0)-IF(ISNUMBER(E23),E23,0))</f>
         <v/>
@@ -6297,11 +6315,11 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="6"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="6" t="str">
         <f>IF(A24="","",IFERROR(LOOKUP(2,1/(A$4:A23=A24),F$4:F23),0)+IF(ISNUMBER(C24),C24,0)-IF(ISNUMBER(E24),E24,0))</f>
         <v/>
@@ -6313,11 +6331,11 @@
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="6"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="6" t="str">
         <f>IF(A25="","",IFERROR(LOOKUP(2,1/(A$4:A24=A25),F$4:F24),0)+IF(ISNUMBER(C25),C25,0)-IF(ISNUMBER(E25),E25,0))</f>
         <v/>
@@ -6329,11 +6347,11 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="6"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="6" t="str">
         <f>IF(A26="","",IFERROR(LOOKUP(2,1/(A$4:A25=A26),F$4:F25),0)+IF(ISNUMBER(C26),C26,0)-IF(ISNUMBER(E26),E26,0))</f>
         <v/>
@@ -6345,11 +6363,11 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="6"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="14"/>
       <c r="F27" s="6" t="str">
         <f>IF(A27="","",IFERROR(LOOKUP(2,1/(A$4:A26=A27),F$4:F26),0)+IF(ISNUMBER(C27),C27,0)-IF(ISNUMBER(E27),E27,0))</f>
         <v/>
@@ -6361,11 +6379,11 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="6"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="14"/>
       <c r="F28" s="6" t="str">
         <f>IF(A28="","",IFERROR(LOOKUP(2,1/(A$4:A27=A28),F$4:F27),0)+IF(ISNUMBER(C28),C28,0)-IF(ISNUMBER(E28),E28,0))</f>
         <v/>
@@ -6377,11 +6395,11 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="6"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="14"/>
       <c r="F29" s="6" t="str">
         <f>IF(A29="","",IFERROR(LOOKUP(2,1/(A$4:A28=A29),F$4:F28),0)+IF(ISNUMBER(C29),C29,0)-IF(ISNUMBER(E29),E29,0))</f>
         <v/>
@@ -6393,11 +6411,11 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="6"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="6" t="str">
         <f>IF(A30="","",IFERROR(LOOKUP(2,1/(A$4:A29=A30),F$4:F29),0)+IF(ISNUMBER(C30),C30,0)-IF(ISNUMBER(E30),E30,0))</f>
         <v/>
@@ -6409,11 +6427,11 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="6"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="14"/>
       <c r="F31" s="6" t="str">
         <f>IF(A31="","",IFERROR(LOOKUP(2,1/(A$4:A30=A31),F$4:F30),0)+IF(ISNUMBER(C31),C31,0)-IF(ISNUMBER(E31),E31,0))</f>
         <v/>
@@ -6425,11 +6443,11 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="6"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="14"/>
       <c r="F32" s="6" t="str">
         <f>IF(A32="","",IFERROR(LOOKUP(2,1/(A$4:A31=A32),F$4:F31),0)+IF(ISNUMBER(C32),C32,0)-IF(ISNUMBER(E32),E32,0))</f>
         <v/>
@@ -6441,11 +6459,11 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="6"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="14"/>
       <c r="F33" s="6" t="str">
         <f>IF(A33="","",IFERROR(LOOKUP(2,1/(A$4:A32=A33),F$4:F32),0)+IF(ISNUMBER(C33),C33,0)-IF(ISNUMBER(E33),E33,0))</f>
         <v/>
@@ -6457,11 +6475,11 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="6"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="14"/>
       <c r="F34" s="6" t="str">
         <f>IF(A34="","",IFERROR(LOOKUP(2,1/(A$4:A33=A34),F$4:F33),0)+IF(ISNUMBER(C34),C34,0)-IF(ISNUMBER(E34),E34,0))</f>
         <v/>
@@ -6473,11 +6491,11 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="6"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="14"/>
       <c r="F35" s="6" t="str">
         <f>IF(A35="","",IFERROR(LOOKUP(2,1/(A$4:A34=A35),F$4:F34),0)+IF(ISNUMBER(C35),C35,0)-IF(ISNUMBER(E35),E35,0))</f>
         <v/>
@@ -6489,11 +6507,11 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="6"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="14"/>
       <c r="F36" s="6" t="str">
         <f>IF(A36="","",IFERROR(LOOKUP(2,1/(A$4:A35=A36),F$4:F35),0)+IF(ISNUMBER(C36),C36,0)-IF(ISNUMBER(E36),E36,0))</f>
         <v/>
@@ -6505,11 +6523,11 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="6"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="14"/>
       <c r="F37" s="6" t="str">
         <f>IF(A37="","",IFERROR(LOOKUP(2,1/(A$4:A36=A37),F$4:F36),0)+IF(ISNUMBER(C37),C37,0)-IF(ISNUMBER(E37),E37,0))</f>
         <v/>
@@ -6521,11 +6539,11 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="6"/>
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="14"/>
       <c r="F38" s="6" t="str">
         <f>IF(A38="","",IFERROR(LOOKUP(2,1/(A$4:A37=A38),F$4:F37),0)+IF(ISNUMBER(C38),C38,0)-IF(ISNUMBER(E38),E38,0))</f>
         <v/>
@@ -6537,11 +6555,11 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="6"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="14"/>
       <c r="F39" s="6" t="str">
         <f>IF(A39="","",IFERROR(LOOKUP(2,1/(A$4:A38=A39),F$4:F38),0)+IF(ISNUMBER(C39),C39,0)-IF(ISNUMBER(E39),E39,0))</f>
         <v/>
@@ -6553,11 +6571,11 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="6"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="14"/>
       <c r="F40" s="6" t="str">
         <f>IF(A40="","",IFERROR(LOOKUP(2,1/(A$4:A39=A40),F$4:F39),0)+IF(ISNUMBER(C40),C40,0)-IF(ISNUMBER(E40),E40,0))</f>
         <v/>
@@ -6569,11 +6587,11 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="6"/>
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="14"/>
       <c r="F41" s="6" t="str">
         <f>IF(A41="","",IFERROR(LOOKUP(2,1/(A$4:A40=A41),F$4:F40),0)+IF(ISNUMBER(C41),C41,0)-IF(ISNUMBER(E41),E41,0))</f>
         <v/>
@@ -6675,19 +6693,19 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="13">
         <v>45839</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="14">
         <v>200</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="15">
         <v>85</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="14">
         <v>196</v>
       </c>
       <c r="F4" s="6">
@@ -6701,19 +6719,19 @@
       <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="13">
         <v>45870</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="14">
         <v>300</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="15">
         <v>92.5</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="14">
         <v>181</v>
       </c>
       <c r="F5" s="6">
@@ -6727,17 +6745,17 @@
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="13">
         <v>45870</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7">
+      <c r="C6" s="14"/>
+      <c r="D6" s="15">
         <v>92.4</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="14">
         <v>4</v>
       </c>
       <c r="F6" s="6">
@@ -6751,19 +6769,19 @@
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="13">
         <v>45901</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="14">
         <v>300</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="15">
         <v>99.2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="14">
         <v>34</v>
       </c>
       <c r="F7" s="6">
@@ -6777,17 +6795,17 @@
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="13">
         <v>45901</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7">
+      <c r="C8" s="14"/>
+      <c r="D8" s="15">
         <v>92.4</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="14">
         <v>119</v>
       </c>
       <c r="F8" s="6">
@@ -6801,19 +6819,19 @@
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="13">
         <v>45992</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="14">
         <v>300</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="15">
         <v>115</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="14"/>
       <c r="F9" s="6">
         <f>IF(A9="","",IFERROR(LOOKUP(2,1/(A$4:A8=A9),F$4:F8),0)+IF(ISNUMBER(C9),C9,0)-IF(ISNUMBER(E9),E9,0))</f>
         <v>566</v>
@@ -6825,17 +6843,17 @@
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="13">
         <v>45992</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7">
+      <c r="C10" s="14"/>
+      <c r="D10" s="15">
         <v>97.27</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="14">
         <v>266</v>
       </c>
       <c r="F10" s="6">
@@ -6849,17 +6867,17 @@
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="13">
         <v>46023</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7">
+      <c r="C11" s="14"/>
+      <c r="D11" s="15">
         <v>106.67</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="14">
         <v>56</v>
       </c>
       <c r="F11" s="6">
@@ -6873,17 +6891,17 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="13">
         <v>46054</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7">
+      <c r="C12" s="14"/>
+      <c r="D12" s="15">
         <v>106.67</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="14">
         <v>68</v>
       </c>
       <c r="F12" s="6">
@@ -6897,17 +6915,17 @@
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="13">
         <v>46082</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7">
+      <c r="C13" s="14"/>
+      <c r="D13" s="15">
         <v>106.67</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="6">
         <f>IF(A13="","",IFERROR(LOOKUP(2,1/(A$4:A12=A13),F$4:F12),0)+IF(ISNUMBER(C13),C13,0)-IF(ISNUMBER(E13),E13,0))</f>
         <v>176</v>
@@ -6919,17 +6937,17 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="13">
         <v>46113</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7">
+      <c r="C14" s="14"/>
+      <c r="D14" s="15">
         <v>106.67</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="14">
         <v>161</v>
       </c>
       <c r="F14" s="6">
@@ -6943,19 +6961,19 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="13">
         <v>46143</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="14">
         <v>400</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="15">
         <v>177</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="14">
         <v>150</v>
       </c>
       <c r="F15" s="6">
@@ -6969,17 +6987,17 @@
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="13">
         <v>46143</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7">
+      <c r="C16" s="14"/>
+      <c r="D16" s="15">
         <v>106.67</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="14">
         <v>15</v>
       </c>
       <c r="F16" s="6">
@@ -6993,17 +7011,17 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="13">
         <v>46174</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7">
+      <c r="C17" s="14"/>
+      <c r="D17" s="15">
         <v>174.46</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="14">
         <v>72</v>
       </c>
       <c r="F17" s="6">
@@ -7017,17 +7035,17 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="13">
         <v>46204</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7">
+      <c r="C18" s="14"/>
+      <c r="D18" s="15">
         <v>174.46</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="14">
         <v>10</v>
       </c>
       <c r="F18" s="6">
@@ -7041,17 +7059,17 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="13">
         <v>46235</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7">
+      <c r="C19" s="14"/>
+      <c r="D19" s="15">
         <v>174.46</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="14">
         <v>155</v>
       </c>
       <c r="F19" s="6">
@@ -7065,19 +7083,19 @@
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="13">
         <v>46266</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="14">
         <v>400</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="15">
         <v>188.4</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="6">
         <f>IF(A20="","",IFERROR(LOOKUP(2,1/(A$4:A19=A20),F$4:F19),0)+IF(ISNUMBER(C20),C20,0)-IF(ISNUMBER(E20),E20,0))</f>
         <v>413</v>
@@ -7089,17 +7107,17 @@
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="13">
         <v>46266</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7">
+      <c r="C21" s="14"/>
+      <c r="D21" s="15">
         <v>187.96</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="6">
         <f>IF(A21="","",IFERROR(LOOKUP(2,1/(A$4:A20=A21),F$4:F20),0)+IF(ISNUMBER(C21),C21,0)-IF(ISNUMBER(E21),E21,0))</f>
         <v>413</v>
@@ -7111,17 +7129,17 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="13">
         <v>46296</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7">
+      <c r="C22" s="14"/>
+      <c r="D22" s="15">
         <v>187.96</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="14">
         <v>60</v>
       </c>
       <c r="F22" s="6">
@@ -7135,11 +7153,11 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="6"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="6" t="str">
         <f>IF(A23="","",IFERROR(LOOKUP(2,1/(A$4:A22=A23),F$4:F22),0)+IF(ISNUMBER(C23),C23,0)-IF(ISNUMBER(E23),E23,0))</f>
         <v/>
@@ -7151,11 +7169,11 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="6"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="6" t="str">
         <f>IF(A24="","",IFERROR(LOOKUP(2,1/(A$4:A23=A24),F$4:F23),0)+IF(ISNUMBER(C24),C24,0)-IF(ISNUMBER(E24),E24,0))</f>
         <v/>
@@ -7167,11 +7185,11 @@
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="6"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="6" t="str">
         <f>IF(A25="","",IFERROR(LOOKUP(2,1/(A$4:A24=A25),F$4:F24),0)+IF(ISNUMBER(C25),C25,0)-IF(ISNUMBER(E25),E25,0))</f>
         <v/>
@@ -7183,11 +7201,11 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="6"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="6" t="str">
         <f>IF(A26="","",IFERROR(LOOKUP(2,1/(A$4:A25=A26),F$4:F25),0)+IF(ISNUMBER(C26),C26,0)-IF(ISNUMBER(E26),E26,0))</f>
         <v/>
@@ -7199,11 +7217,11 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="6"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="14"/>
       <c r="F27" s="6" t="str">
         <f>IF(A27="","",IFERROR(LOOKUP(2,1/(A$4:A26=A27),F$4:F26),0)+IF(ISNUMBER(C27),C27,0)-IF(ISNUMBER(E27),E27,0))</f>
         <v/>
@@ -7215,11 +7233,11 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="6"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="14"/>
       <c r="F28" s="6" t="str">
         <f>IF(A28="","",IFERROR(LOOKUP(2,1/(A$4:A27=A28),F$4:F27),0)+IF(ISNUMBER(C28),C28,0)-IF(ISNUMBER(E28),E28,0))</f>
         <v/>
@@ -7231,11 +7249,11 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="6"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="14"/>
       <c r="F29" s="6" t="str">
         <f>IF(A29="","",IFERROR(LOOKUP(2,1/(A$4:A28=A29),F$4:F28),0)+IF(ISNUMBER(C29),C29,0)-IF(ISNUMBER(E29),E29,0))</f>
         <v/>
@@ -7247,11 +7265,11 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="6"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="6" t="str">
         <f>IF(A30="","",IFERROR(LOOKUP(2,1/(A$4:A29=A30),F$4:F29),0)+IF(ISNUMBER(C30),C30,0)-IF(ISNUMBER(E30),E30,0))</f>
         <v/>
@@ -7263,11 +7281,11 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="6"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="14"/>
       <c r="F31" s="6" t="str">
         <f>IF(A31="","",IFERROR(LOOKUP(2,1/(A$4:A30=A31),F$4:F30),0)+IF(ISNUMBER(C31),C31,0)-IF(ISNUMBER(E31),E31,0))</f>
         <v/>
@@ -7279,11 +7297,11 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="6"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="14"/>
       <c r="F32" s="6" t="str">
         <f>IF(A32="","",IFERROR(LOOKUP(2,1/(A$4:A31=A32),F$4:F31),0)+IF(ISNUMBER(C32),C32,0)-IF(ISNUMBER(E32),E32,0))</f>
         <v/>
@@ -7295,11 +7313,11 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="6"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="14"/>
       <c r="F33" s="6" t="str">
         <f>IF(A33="","",IFERROR(LOOKUP(2,1/(A$4:A32=A33),F$4:F32),0)+IF(ISNUMBER(C33),C33,0)-IF(ISNUMBER(E33),E33,0))</f>
         <v/>
@@ -7311,11 +7329,11 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="6"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="14"/>
       <c r="F34" s="6" t="str">
         <f>IF(A34="","",IFERROR(LOOKUP(2,1/(A$4:A33=A34),F$4:F33),0)+IF(ISNUMBER(C34),C34,0)-IF(ISNUMBER(E34),E34,0))</f>
         <v/>
@@ -7327,11 +7345,11 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="6"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="14"/>
       <c r="F35" s="6" t="str">
         <f>IF(A35="","",IFERROR(LOOKUP(2,1/(A$4:A34=A35),F$4:F34),0)+IF(ISNUMBER(C35),C35,0)-IF(ISNUMBER(E35),E35,0))</f>
         <v/>
@@ -7343,11 +7361,11 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="6"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="14"/>
       <c r="F36" s="6" t="str">
         <f>IF(A36="","",IFERROR(LOOKUP(2,1/(A$4:A35=A36),F$4:F35),0)+IF(ISNUMBER(C36),C36,0)-IF(ISNUMBER(E36),E36,0))</f>
         <v/>
@@ -7359,11 +7377,11 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="6"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="14"/>
       <c r="F37" s="6" t="str">
         <f>IF(A37="","",IFERROR(LOOKUP(2,1/(A$4:A36=A37),F$4:F36),0)+IF(ISNUMBER(C37),C37,0)-IF(ISNUMBER(E37),E37,0))</f>
         <v/>
@@ -7375,11 +7393,11 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="6"/>
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="14"/>
       <c r="F38" s="6" t="str">
         <f>IF(A38="","",IFERROR(LOOKUP(2,1/(A$4:A37=A38),F$4:F37),0)+IF(ISNUMBER(C38),C38,0)-IF(ISNUMBER(E38),E38,0))</f>
         <v/>
@@ -7391,11 +7409,11 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="6"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="14"/>
       <c r="F39" s="6" t="str">
         <f>IF(A39="","",IFERROR(LOOKUP(2,1/(A$4:A38=A39),F$4:F38),0)+IF(ISNUMBER(C39),C39,0)-IF(ISNUMBER(E39),E39,0))</f>
         <v/>
@@ -7407,11 +7425,11 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="6"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="14"/>
       <c r="F40" s="6" t="str">
         <f>IF(A40="","",IFERROR(LOOKUP(2,1/(A$4:A39=A40),F$4:F39),0)+IF(ISNUMBER(C40),C40,0)-IF(ISNUMBER(E40),E40,0))</f>
         <v/>
@@ -7423,11 +7441,11 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="6"/>
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="14"/>
       <c r="F41" s="6" t="str">
         <f>IF(A41="","",IFERROR(LOOKUP(2,1/(A$4:A40=A41),F$4:F40),0)+IF(ISNUMBER(C41),C41,0)-IF(ISNUMBER(E41),E41,0))</f>
         <v/>
@@ -7439,11 +7457,11 @@
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="6"/>
+      <c r="A42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="14"/>
       <c r="F42" s="6" t="str">
         <f>IF(A42="","",IFERROR(LOOKUP(2,1/(A$4:A41=A42),F$4:F41),0)+IF(ISNUMBER(C42),C42,0)-IF(ISNUMBER(E42),E42,0))</f>
         <v/>
@@ -7455,11 +7473,11 @@
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="6"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="14"/>
       <c r="F43" s="6" t="str">
         <f>IF(A43="","",IFERROR(LOOKUP(2,1/(A$4:A42=A43),F$4:F42),0)+IF(ISNUMBER(C43),C43,0)-IF(ISNUMBER(E43),E43,0))</f>
         <v/>
@@ -7471,11 +7489,11 @@
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="6"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="14"/>
       <c r="F44" s="6" t="str">
         <f>IF(A44="","",IFERROR(LOOKUP(2,1/(A$4:A43=A44),F$4:F43),0)+IF(ISNUMBER(C44),C44,0)-IF(ISNUMBER(E44),E44,0))</f>
         <v/>
@@ -7487,11 +7505,11 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="6"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="14"/>
       <c r="F45" s="6" t="str">
         <f>IF(A45="","",IFERROR(LOOKUP(2,1/(A$4:A44=A45),F$4:F44),0)+IF(ISNUMBER(C45),C45,0)-IF(ISNUMBER(E45),E45,0))</f>
         <v/>
@@ -7503,11 +7521,11 @@
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="6"/>
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="14"/>
       <c r="F46" s="6" t="str">
         <f>IF(A46="","",IFERROR(LOOKUP(2,1/(A$4:A45=A46),F$4:F45),0)+IF(ISNUMBER(C46),C46,0)-IF(ISNUMBER(E46),E46,0))</f>
         <v/>
@@ -7519,11 +7537,11 @@
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="6"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="14"/>
       <c r="F47" s="6" t="str">
         <f>IF(A47="","",IFERROR(LOOKUP(2,1/(A$4:A46=A47),F$4:F46),0)+IF(ISNUMBER(C47),C47,0)-IF(ISNUMBER(E47),E47,0))</f>
         <v/>
@@ -7535,11 +7553,11 @@
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="6"/>
+      <c r="A48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="14"/>
       <c r="F48" s="6" t="str">
         <f>IF(A48="","",IFERROR(LOOKUP(2,1/(A$4:A47=A48),F$4:F47),0)+IF(ISNUMBER(C48),C48,0)-IF(ISNUMBER(E48),E48,0))</f>
         <v/>
@@ -7551,11 +7569,11 @@
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="6"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="14"/>
       <c r="F49" s="6" t="str">
         <f>IF(A49="","",IFERROR(LOOKUP(2,1/(A$4:A48=A49),F$4:F48),0)+IF(ISNUMBER(C49),C49,0)-IF(ISNUMBER(E49),E49,0))</f>
         <v/>
@@ -7567,11 +7585,11 @@
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="6"/>
+      <c r="A50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="14"/>
       <c r="F50" s="6" t="str">
         <f>IF(A50="","",IFERROR(LOOKUP(2,1/(A$4:A49=A50),F$4:F49),0)+IF(ISNUMBER(C50),C50,0)-IF(ISNUMBER(E50),E50,0))</f>
         <v/>
@@ -7583,11 +7601,11 @@
       <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="6"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="14"/>
       <c r="F51" s="6" t="str">
         <f>IF(A51="","",IFERROR(LOOKUP(2,1/(A$4:A50=A51),F$4:F50),0)+IF(ISNUMBER(C51),C51,0)-IF(ISNUMBER(E51),E51,0))</f>
         <v/>
@@ -7599,11 +7617,11 @@
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="6"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="14"/>
       <c r="F52" s="6" t="str">
         <f>IF(A52="","",IFERROR(LOOKUP(2,1/(A$4:A51=A52),F$4:F51),0)+IF(ISNUMBER(C52),C52,0)-IF(ISNUMBER(E52),E52,0))</f>
         <v/>
@@ -7705,19 +7723,19 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="13">
         <v>45992</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="14">
         <v>968</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="15">
         <v>10.5</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="14">
         <v>240</v>
       </c>
       <c r="F4" s="6">
@@ -7731,17 +7749,17 @@
       <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="13">
         <v>46023</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7">
+      <c r="C5" s="14"/>
+      <c r="D5" s="15">
         <v>10.5</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="14">
         <v>366</v>
       </c>
       <c r="F5" s="6">
@@ -7755,19 +7773,19 @@
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="13">
         <v>46054</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="14">
         <v>1000</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="15">
         <v>27</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="14">
         <v>104</v>
       </c>
       <c r="F6" s="6">
@@ -7781,17 +7799,17 @@
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="13">
         <v>46054</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7">
+      <c r="C7" s="14"/>
+      <c r="D7" s="15">
         <v>10.5</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="14">
         <v>165</v>
       </c>
       <c r="F7" s="6">
@@ -7805,17 +7823,17 @@
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="13">
         <v>46082</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7">
+      <c r="C8" s="14"/>
+      <c r="D8" s="15">
         <v>22.61</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="14">
         <v>268</v>
       </c>
       <c r="F8" s="6">
@@ -7829,17 +7847,17 @@
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="13">
         <v>46113</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7">
+      <c r="C9" s="14"/>
+      <c r="D9" s="15">
         <v>22.61</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="14">
         <v>280</v>
       </c>
       <c r="F9" s="6">
@@ -7853,19 +7871,19 @@
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="13">
         <v>46143</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="14">
         <v>1500</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="15">
         <v>38</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="6">
         <f>IF(A10="","",IFERROR(LOOKUP(2,1/(A$4:A9=A10),F$4:F9),0)+IF(ISNUMBER(C10),C10,0)-IF(ISNUMBER(E10),E10,0))</f>
         <v>2045</v>
@@ -7877,17 +7895,17 @@
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="13">
         <v>46143</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7">
+      <c r="C11" s="14"/>
+      <c r="D11" s="15">
         <v>22.61</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="14">
         <v>229</v>
       </c>
       <c r="F11" s="6">
@@ -7901,17 +7919,17 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="13">
         <v>46174</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7">
+      <c r="C12" s="14"/>
+      <c r="D12" s="15">
         <v>33.9</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="14">
         <v>531</v>
       </c>
       <c r="F12" s="6">
@@ -7925,17 +7943,17 @@
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="13">
         <v>46204</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7">
+      <c r="C13" s="14"/>
+      <c r="D13" s="15">
         <v>33.9</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="14">
         <v>245</v>
       </c>
       <c r="F13" s="6">
@@ -7949,17 +7967,17 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="13">
         <v>46235</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7">
+      <c r="C14" s="14"/>
+      <c r="D14" s="15">
         <v>33.9</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="14">
         <v>455</v>
       </c>
       <c r="F14" s="6">
@@ -7973,17 +7991,17 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="13">
         <v>46266</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7">
+      <c r="C15" s="14"/>
+      <c r="D15" s="15">
         <v>33.9</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="6">
         <f>IF(A15="","",IFERROR(LOOKUP(2,1/(A$4:A14=A15),F$4:F14),0)+IF(ISNUMBER(C15),C15,0)-IF(ISNUMBER(E15),E15,0))</f>
         <v>585</v>
@@ -7995,19 +8013,19 @@
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="13">
         <v>45992</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="14">
         <v>1749</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="15">
         <v>15.5</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="14">
         <v>634</v>
       </c>
       <c r="F16" s="6">
@@ -8021,17 +8039,17 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="13">
         <v>46023</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7">
+      <c r="C17" s="14"/>
+      <c r="D17" s="15">
         <v>15.5</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="14">
         <v>954</v>
       </c>
       <c r="F17" s="6">
@@ -8045,19 +8063,19 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="13">
         <v>46054</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="14">
         <v>2000</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="15">
         <v>50</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="14">
         <v>420</v>
       </c>
       <c r="F18" s="6">
@@ -8071,17 +8089,17 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="13">
         <v>46054</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7">
+      <c r="C19" s="14"/>
+      <c r="D19" s="15">
         <v>15.5</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="14">
         <v>161</v>
       </c>
       <c r="F19" s="6">
@@ -8095,19 +8113,19 @@
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="13">
         <v>46082</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="14">
         <v>500</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="15">
         <v>63</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="6">
         <f>IF(A20="","",IFERROR(LOOKUP(2,1/(A$4:A19=A20),F$4:F19),0)+IF(ISNUMBER(C20),C20,0)-IF(ISNUMBER(E20),E20,0))</f>
         <v>2080</v>
@@ -8119,19 +8137,19 @@
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="13">
         <v>46082</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="14">
         <v>1000</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="15">
         <v>58</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="6">
         <f>IF(A21="","",IFERROR(LOOKUP(2,1/(A$4:A20=A21),F$4:F20),0)+IF(ISNUMBER(C21),C21,0)-IF(ISNUMBER(E21),E21,0))</f>
         <v>3080</v>
@@ -8143,17 +8161,17 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="13">
         <v>46082</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7">
+      <c r="C22" s="14"/>
+      <c r="D22" s="15">
         <v>47.43</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="14">
         <v>1048</v>
       </c>
       <c r="F22" s="6">
@@ -8167,19 +8185,19 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="13">
         <v>46113</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="14">
         <v>2000</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="15">
         <v>68</v>
       </c>
-      <c r="E23" s="6"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="6">
         <f>IF(A23="","",IFERROR(LOOKUP(2,1/(A$4:A22=A23),F$4:F22),0)+IF(ISNUMBER(C23),C23,0)-IF(ISNUMBER(E23),E23,0))</f>
         <v>4032</v>
@@ -8191,17 +8209,17 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="13">
         <v>46113</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7">
+      <c r="C24" s="14"/>
+      <c r="D24" s="15">
         <v>53.39</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="14">
         <v>869</v>
       </c>
       <c r="F24" s="6">
@@ -8215,19 +8233,19 @@
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="13">
         <v>46143</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="14">
         <v>2000</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="15">
         <v>67</v>
       </c>
-      <c r="E25" s="6"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="6">
         <f>IF(A25="","",IFERROR(LOOKUP(2,1/(A$4:A24=A25),F$4:F24),0)+IF(ISNUMBER(C25),C25,0)-IF(ISNUMBER(E25),E25,0))</f>
         <v>5163</v>
@@ -8239,17 +8257,17 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="13">
         <v>46143</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7">
+      <c r="C26" s="14"/>
+      <c r="D26" s="15">
         <v>60.64</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="14">
         <v>623</v>
       </c>
       <c r="F26" s="6">
@@ -8263,17 +8281,17 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="13">
         <v>46174</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7">
+      <c r="C27" s="14"/>
+      <c r="D27" s="15">
         <v>63.1</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="14">
         <v>269</v>
       </c>
       <c r="F27" s="6">
@@ -8287,17 +8305,17 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="13">
         <v>46204</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7">
+      <c r="C28" s="14"/>
+      <c r="D28" s="15">
         <v>63.1</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="14">
         <v>282</v>
       </c>
       <c r="F28" s="6">
@@ -8311,17 +8329,17 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="13">
         <v>46235</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7">
+      <c r="C29" s="14"/>
+      <c r="D29" s="15">
         <v>63.1</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="14">
         <v>435</v>
       </c>
       <c r="F29" s="6">
@@ -8335,17 +8353,17 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="13">
         <v>46266</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7">
+      <c r="C30" s="14"/>
+      <c r="D30" s="15">
         <v>63.1</v>
       </c>
-      <c r="E30" s="6"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="6">
         <f>IF(A30="","",IFERROR(LOOKUP(2,1/(A$4:A29=A30),F$4:F29),0)+IF(ISNUMBER(C30),C30,0)-IF(ISNUMBER(E30),E30,0))</f>
         <v>3554</v>
@@ -8357,11 +8375,11 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="6"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="14"/>
       <c r="F31" s="6" t="str">
         <f>IF(A31="","",IFERROR(LOOKUP(2,1/(A$4:A30=A31),F$4:F30),0)+IF(ISNUMBER(C31),C31,0)-IF(ISNUMBER(E31),E31,0))</f>
         <v/>
@@ -8373,11 +8391,11 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="6"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="14"/>
       <c r="F32" s="6" t="str">
         <f>IF(A32="","",IFERROR(LOOKUP(2,1/(A$4:A31=A32),F$4:F31),0)+IF(ISNUMBER(C32),C32,0)-IF(ISNUMBER(E32),E32,0))</f>
         <v/>
@@ -8389,11 +8407,11 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="6"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="14"/>
       <c r="F33" s="6" t="str">
         <f>IF(A33="","",IFERROR(LOOKUP(2,1/(A$4:A32=A33),F$4:F32),0)+IF(ISNUMBER(C33),C33,0)-IF(ISNUMBER(E33),E33,0))</f>
         <v/>
@@ -8405,11 +8423,11 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="6"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="14"/>
       <c r="F34" s="6" t="str">
         <f>IF(A34="","",IFERROR(LOOKUP(2,1/(A$4:A33=A34),F$4:F33),0)+IF(ISNUMBER(C34),C34,0)-IF(ISNUMBER(E34),E34,0))</f>
         <v/>
@@ -8421,11 +8439,11 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="6"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="14"/>
       <c r="F35" s="6" t="str">
         <f>IF(A35="","",IFERROR(LOOKUP(2,1/(A$4:A34=A35),F$4:F34),0)+IF(ISNUMBER(C35),C35,0)-IF(ISNUMBER(E35),E35,0))</f>
         <v/>
@@ -8437,11 +8455,11 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="6"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="14"/>
       <c r="F36" s="6" t="str">
         <f>IF(A36="","",IFERROR(LOOKUP(2,1/(A$4:A35=A36),F$4:F35),0)+IF(ISNUMBER(C36),C36,0)-IF(ISNUMBER(E36),E36,0))</f>
         <v/>
@@ -8453,11 +8471,11 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="6"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="14"/>
       <c r="F37" s="6" t="str">
         <f>IF(A37="","",IFERROR(LOOKUP(2,1/(A$4:A36=A37),F$4:F36),0)+IF(ISNUMBER(C37),C37,0)-IF(ISNUMBER(E37),E37,0))</f>
         <v/>
@@ -8469,11 +8487,11 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="6"/>
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="14"/>
       <c r="F38" s="6" t="str">
         <f>IF(A38="","",IFERROR(LOOKUP(2,1/(A$4:A37=A38),F$4:F37),0)+IF(ISNUMBER(C38),C38,0)-IF(ISNUMBER(E38),E38,0))</f>
         <v/>
@@ -8485,11 +8503,11 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="6"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="14"/>
       <c r="F39" s="6" t="str">
         <f>IF(A39="","",IFERROR(LOOKUP(2,1/(A$4:A38=A39),F$4:F38),0)+IF(ISNUMBER(C39),C39,0)-IF(ISNUMBER(E39),E39,0))</f>
         <v/>
@@ -8501,11 +8519,11 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="6"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="14"/>
       <c r="F40" s="6" t="str">
         <f>IF(A40="","",IFERROR(LOOKUP(2,1/(A$4:A39=A40),F$4:F39),0)+IF(ISNUMBER(C40),C40,0)-IF(ISNUMBER(E40),E40,0))</f>
         <v/>
@@ -8517,11 +8535,11 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="6"/>
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="14"/>
       <c r="F41" s="6" t="str">
         <f>IF(A41="","",IFERROR(LOOKUP(2,1/(A$4:A40=A41),F$4:F40),0)+IF(ISNUMBER(C41),C41,0)-IF(ISNUMBER(E41),E41,0))</f>
         <v/>
@@ -8533,11 +8551,11 @@
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="6"/>
+      <c r="A42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="14"/>
       <c r="F42" s="6" t="str">
         <f>IF(A42="","",IFERROR(LOOKUP(2,1/(A$4:A41=A42),F$4:F41),0)+IF(ISNUMBER(C42),C42,0)-IF(ISNUMBER(E42),E42,0))</f>
         <v/>
@@ -8549,11 +8567,11 @@
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="6"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="14"/>
       <c r="F43" s="6" t="str">
         <f>IF(A43="","",IFERROR(LOOKUP(2,1/(A$4:A42=A43),F$4:F42),0)+IF(ISNUMBER(C43),C43,0)-IF(ISNUMBER(E43),E43,0))</f>
         <v/>
@@ -8565,11 +8583,11 @@
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="6"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="14"/>
       <c r="F44" s="6" t="str">
         <f>IF(A44="","",IFERROR(LOOKUP(2,1/(A$4:A43=A44),F$4:F43),0)+IF(ISNUMBER(C44),C44,0)-IF(ISNUMBER(E44),E44,0))</f>
         <v/>
@@ -8581,11 +8599,11 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="6"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="14"/>
       <c r="F45" s="6" t="str">
         <f>IF(A45="","",IFERROR(LOOKUP(2,1/(A$4:A44=A45),F$4:F44),0)+IF(ISNUMBER(C45),C45,0)-IF(ISNUMBER(E45),E45,0))</f>
         <v/>
@@ -8597,11 +8615,11 @@
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="6"/>
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="14"/>
       <c r="F46" s="6" t="str">
         <f>IF(A46="","",IFERROR(LOOKUP(2,1/(A$4:A45=A46),F$4:F45),0)+IF(ISNUMBER(C46),C46,0)-IF(ISNUMBER(E46),E46,0))</f>
         <v/>
@@ -8613,11 +8631,11 @@
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="6"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="14"/>
       <c r="F47" s="6" t="str">
         <f>IF(A47="","",IFERROR(LOOKUP(2,1/(A$4:A46=A47),F$4:F46),0)+IF(ISNUMBER(C47),C47,0)-IF(ISNUMBER(E47),E47,0))</f>
         <v/>
@@ -8629,11 +8647,11 @@
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="6"/>
+      <c r="A48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="14"/>
       <c r="F48" s="6" t="str">
         <f>IF(A48="","",IFERROR(LOOKUP(2,1/(A$4:A47=A48),F$4:F47),0)+IF(ISNUMBER(C48),C48,0)-IF(ISNUMBER(E48),E48,0))</f>
         <v/>
@@ -8645,11 +8663,11 @@
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="6"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="14"/>
       <c r="F49" s="6" t="str">
         <f>IF(A49="","",IFERROR(LOOKUP(2,1/(A$4:A48=A49),F$4:F48),0)+IF(ISNUMBER(C49),C49,0)-IF(ISNUMBER(E49),E49,0))</f>
         <v/>
@@ -8661,11 +8679,11 @@
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="6"/>
+      <c r="A50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="14"/>
       <c r="F50" s="6" t="str">
         <f>IF(A50="","",IFERROR(LOOKUP(2,1/(A$4:A49=A50),F$4:F49),0)+IF(ISNUMBER(C50),C50,0)-IF(ISNUMBER(E50),E50,0))</f>
         <v/>
@@ -8677,11 +8695,11 @@
       <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="6"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="14"/>
       <c r="F51" s="6" t="str">
         <f>IF(A51="","",IFERROR(LOOKUP(2,1/(A$4:A50=A51),F$4:F50),0)+IF(ISNUMBER(C51),C51,0)-IF(ISNUMBER(E51),E51,0))</f>
         <v/>
@@ -8693,11 +8711,11 @@
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="6"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="14"/>
       <c r="F52" s="6" t="str">
         <f>IF(A52="","",IFERROR(LOOKUP(2,1/(A$4:A51=A52),F$4:F51),0)+IF(ISNUMBER(C52),C52,0)-IF(ISNUMBER(E52),E52,0))</f>
         <v/>
@@ -8709,11 +8727,11 @@
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="6"/>
+      <c r="A53" s="12"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="14"/>
       <c r="F53" s="6" t="str">
         <f>IF(A53="","",IFERROR(LOOKUP(2,1/(A$4:A52=A53),F$4:F52),0)+IF(ISNUMBER(C53),C53,0)-IF(ISNUMBER(E53),E53,0))</f>
         <v/>
@@ -8725,11 +8743,11 @@
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="6"/>
+      <c r="A54" s="12"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="14"/>
       <c r="F54" s="6" t="str">
         <f>IF(A54="","",IFERROR(LOOKUP(2,1/(A$4:A53=A54),F$4:F53),0)+IF(ISNUMBER(C54),C54,0)-IF(ISNUMBER(E54),E54,0))</f>
         <v/>
@@ -8741,11 +8759,11 @@
       <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="6"/>
+      <c r="A55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="14"/>
       <c r="F55" s="6" t="str">
         <f>IF(A55="","",IFERROR(LOOKUP(2,1/(A$4:A54=A55),F$4:F54),0)+IF(ISNUMBER(C55),C55,0)-IF(ISNUMBER(E55),E55,0))</f>
         <v/>
@@ -8757,11 +8775,11 @@
       <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="6"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="14"/>
       <c r="F56" s="6" t="str">
         <f>IF(A56="","",IFERROR(LOOKUP(2,1/(A$4:A55=A56),F$4:F55),0)+IF(ISNUMBER(C56),C56,0)-IF(ISNUMBER(E56),E56,0))</f>
         <v/>
@@ -8773,11 +8791,11 @@
       <c r="I56" s="7"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="6"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="14"/>
       <c r="F57" s="6" t="str">
         <f>IF(A57="","",IFERROR(LOOKUP(2,1/(A$4:A56=A57),F$4:F56),0)+IF(ISNUMBER(C57),C57,0)-IF(ISNUMBER(E57),E57,0))</f>
         <v/>
@@ -8789,11 +8807,11 @@
       <c r="I57" s="7"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="6"/>
+      <c r="A58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="14"/>
       <c r="F58" s="6" t="str">
         <f>IF(A58="","",IFERROR(LOOKUP(2,1/(A$4:A57=A58),F$4:F57),0)+IF(ISNUMBER(C58),C58,0)-IF(ISNUMBER(E58),E58,0))</f>
         <v/>
@@ -8805,11 +8823,11 @@
       <c r="I58" s="7"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="6"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="14"/>
       <c r="F59" s="6" t="str">
         <f>IF(A59="","",IFERROR(LOOKUP(2,1/(A$4:A58=A59),F$4:F58),0)+IF(ISNUMBER(C59),C59,0)-IF(ISNUMBER(E59),E59,0))</f>
         <v/>
@@ -8821,11 +8839,11 @@
       <c r="I59" s="7"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="6"/>
+      <c r="A60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="14"/>
       <c r="F60" s="6" t="str">
         <f>IF(A60="","",IFERROR(LOOKUP(2,1/(A$4:A59=A60),F$4:F59),0)+IF(ISNUMBER(C60),C60,0)-IF(ISNUMBER(E60),E60,0))</f>
         <v/>
@@ -8887,7 +8905,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="23.69921875" customWidth="1"/>
@@ -9507,19 +9525,19 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="13">
         <v>46113</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="14">
         <v>9</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="15">
         <v>23</v>
       </c>
-      <c r="E28" s="6"/>
+      <c r="E28" s="14"/>
       <c r="F28" s="6">
         <f>IF(A28="","",IFERROR(LOOKUP(2,1/(A$4:A27=A28),F$4:F27),0)+IF(ISNUMBER(C28),C28,0)-IF(ISNUMBER(E28),E28,0))</f>
         <v>798</v>
@@ -9531,17 +9549,17 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="13">
         <v>46113</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7">
+      <c r="C29" s="14"/>
+      <c r="D29" s="15">
         <v>29.59</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="14">
         <v>474</v>
       </c>
       <c r="F29" s="6">
@@ -9555,17 +9573,17 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="13">
         <v>46143</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7">
+      <c r="C30" s="14"/>
+      <c r="D30" s="15">
         <v>29.52</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="14">
         <v>38</v>
       </c>
       <c r="F30" s="6">
@@ -9579,19 +9597,19 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="13">
         <v>46174</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="14">
         <v>500</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="15">
         <v>40.700000000000003</v>
       </c>
-      <c r="E31" s="6"/>
+      <c r="E31" s="14"/>
       <c r="F31" s="6">
         <f>IF(A31="","",IFERROR(LOOKUP(2,1/(A$4:A30=A31),F$4:F30),0)+IF(ISNUMBER(C31),C31,0)-IF(ISNUMBER(E31),E31,0))</f>
         <v>786</v>
@@ -9603,17 +9621,17 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="13">
         <v>46174</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7">
+      <c r="C32" s="14"/>
+      <c r="D32" s="15">
         <v>29.52</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="14">
         <v>37</v>
       </c>
       <c r="F32" s="6">
@@ -9627,19 +9645,19 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="13">
         <v>46204</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="14">
         <v>500</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="15">
         <v>42.2</v>
       </c>
-      <c r="E33" s="6"/>
+      <c r="E33" s="14"/>
       <c r="F33" s="6">
         <f>IF(A33="","",IFERROR(LOOKUP(2,1/(A$4:A32=A33),F$4:F32),0)+IF(ISNUMBER(C33),C33,0)-IF(ISNUMBER(E33),E33,0))</f>
         <v>1249</v>
@@ -9651,17 +9669,17 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="13">
         <v>46235</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7">
+      <c r="C34" s="14"/>
+      <c r="D34" s="15">
         <v>36.630000000000003</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="14">
         <v>200</v>
       </c>
       <c r="F34" s="6">
@@ -9675,17 +9693,17 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="13">
         <v>46235</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7">
+      <c r="C35" s="14"/>
+      <c r="D35" s="15">
         <v>38.86</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="14">
         <v>140</v>
       </c>
       <c r="F35" s="6">
@@ -9699,17 +9717,17 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="13">
         <v>46266</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7">
+      <c r="C36" s="14"/>
+      <c r="D36" s="15">
         <v>38.86</v>
       </c>
-      <c r="E36" s="6"/>
+      <c r="E36" s="14"/>
       <c r="F36" s="6">
         <f>IF(A36="","",IFERROR(LOOKUP(2,1/(A$4:A35=A36),F$4:F35),0)+IF(ISNUMBER(C36),C36,0)-IF(ISNUMBER(E36),E36,0))</f>
         <v>909</v>
@@ -9721,19 +9739,19 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="13">
         <v>45992</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="14">
         <v>108</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="14">
         <v>2</v>
       </c>
       <c r="F37" s="6">
@@ -9747,17 +9765,17 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="13">
         <v>46023</v>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7">
+      <c r="C38" s="14"/>
+      <c r="D38" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="14">
         <v>16</v>
       </c>
       <c r="F38" s="6">
@@ -9771,17 +9789,17 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="13">
         <v>46054</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7">
+      <c r="C39" s="14"/>
+      <c r="D39" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E39" s="6"/>
+      <c r="E39" s="14"/>
       <c r="F39" s="6">
         <f>IF(A39="","",IFERROR(LOOKUP(2,1/(A$4:A38=A39),F$4:F38),0)+IF(ISNUMBER(C39),C39,0)-IF(ISNUMBER(E39),E39,0))</f>
         <v>90</v>
@@ -9793,17 +9811,17 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="13">
         <v>46082</v>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7">
+      <c r="C40" s="14"/>
+      <c r="D40" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E40" s="6"/>
+      <c r="E40" s="14"/>
       <c r="F40" s="6">
         <f>IF(A40="","",IFERROR(LOOKUP(2,1/(A$4:A39=A40),F$4:F39),0)+IF(ISNUMBER(C40),C40,0)-IF(ISNUMBER(E40),E40,0))</f>
         <v>90</v>
@@ -9815,17 +9833,17 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="13">
         <v>46113</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7">
+      <c r="C41" s="14"/>
+      <c r="D41" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E41" s="6"/>
+      <c r="E41" s="14"/>
       <c r="F41" s="6">
         <f>IF(A41="","",IFERROR(LOOKUP(2,1/(A$4:A40=A41),F$4:F40),0)+IF(ISNUMBER(C41),C41,0)-IF(ISNUMBER(E41),E41,0))</f>
         <v>90</v>
@@ -9837,17 +9855,17 @@
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="13">
         <v>46143</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7">
+      <c r="C42" s="14"/>
+      <c r="D42" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="14">
         <v>18</v>
       </c>
       <c r="F42" s="6">
@@ -9861,17 +9879,17 @@
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="13">
         <v>46174</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7">
+      <c r="C43" s="14"/>
+      <c r="D43" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E43" s="6"/>
+      <c r="E43" s="14"/>
       <c r="F43" s="6">
         <f>IF(A43="","",IFERROR(LOOKUP(2,1/(A$4:A42=A43),F$4:F42),0)+IF(ISNUMBER(C43),C43,0)-IF(ISNUMBER(E43),E43,0))</f>
         <v>72</v>
@@ -9883,17 +9901,17 @@
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="13">
         <v>46204</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7">
+      <c r="C44" s="14"/>
+      <c r="D44" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E44" s="6"/>
+      <c r="E44" s="14"/>
       <c r="F44" s="6">
         <f>IF(A44="","",IFERROR(LOOKUP(2,1/(A$4:A43=A44),F$4:F43),0)+IF(ISNUMBER(C44),C44,0)-IF(ISNUMBER(E44),E44,0))</f>
         <v>72</v>
@@ -9905,17 +9923,17 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="13">
         <v>46235</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7">
+      <c r="C45" s="14"/>
+      <c r="D45" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E45" s="6"/>
+      <c r="E45" s="14"/>
       <c r="F45" s="6">
         <f>IF(A45="","",IFERROR(LOOKUP(2,1/(A$4:A44=A45),F$4:F44),0)+IF(ISNUMBER(C45),C45,0)-IF(ISNUMBER(E45),E45,0))</f>
         <v>72</v>
@@ -9927,17 +9945,17 @@
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="13">
         <v>46266</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7">
+      <c r="C46" s="14"/>
+      <c r="D46" s="15">
         <v>16.899999999999999</v>
       </c>
-      <c r="E46" s="6"/>
+      <c r="E46" s="14"/>
       <c r="F46" s="6">
         <f>IF(A46="","",IFERROR(LOOKUP(2,1/(A$4:A45=A46),F$4:F45),0)+IF(ISNUMBER(C46),C46,0)-IF(ISNUMBER(E46),E46,0))</f>
         <v>72</v>
@@ -9949,19 +9967,19 @@
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="13">
         <v>45992</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="14">
         <v>165</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="15">
         <v>24.5</v>
       </c>
-      <c r="E47" s="6"/>
+      <c r="E47" s="14"/>
       <c r="F47" s="6">
         <f>IF(A47="","",IFERROR(LOOKUP(2,1/(A$4:A46=A47),F$4:F46),0)+IF(ISNUMBER(C47),C47,0)-IF(ISNUMBER(E47),E47,0))</f>
         <v>165</v>
@@ -9973,17 +9991,17 @@
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="13">
         <v>46023</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7">
+      <c r="C48" s="14"/>
+      <c r="D48" s="15">
         <v>24.5</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="14">
         <v>1</v>
       </c>
       <c r="F48" s="6">
@@ -9997,17 +10015,17 @@
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="13">
         <v>46054</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7">
+      <c r="C49" s="14"/>
+      <c r="D49" s="15">
         <v>24.5</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="14">
         <v>125</v>
       </c>
       <c r="F49" s="6">
@@ -10021,19 +10039,19 @@
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="13">
         <v>46082</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="14">
         <v>250</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="15">
         <v>70</v>
       </c>
-      <c r="E50" s="6"/>
+      <c r="E50" s="14"/>
       <c r="F50" s="6">
         <f>IF(A50="","",IFERROR(LOOKUP(2,1/(A$4:A49=A50),F$4:F49),0)+IF(ISNUMBER(C50),C50,0)-IF(ISNUMBER(E50),E50,0))</f>
         <v>289</v>
@@ -10045,17 +10063,17 @@
       <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="13">
         <v>46113</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7">
+      <c r="C51" s="14"/>
+      <c r="D51" s="15">
         <v>63.86</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="14">
         <v>80</v>
       </c>
       <c r="F51" s="6">
@@ -10069,17 +10087,17 @@
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="13">
         <v>46143</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7">
+      <c r="C52" s="14"/>
+      <c r="D52" s="15">
         <v>63.86</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="14">
         <v>75</v>
       </c>
       <c r="F52" s="6">
@@ -10093,17 +10111,17 @@
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="13">
         <v>46174</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7">
+      <c r="C53" s="14"/>
+      <c r="D53" s="15">
         <v>63.86</v>
       </c>
-      <c r="E53" s="6"/>
+      <c r="E53" s="14"/>
       <c r="F53" s="6">
         <f>IF(A53="","",IFERROR(LOOKUP(2,1/(A$4:A52=A53),F$4:F52),0)+IF(ISNUMBER(C53),C53,0)-IF(ISNUMBER(E53),E53,0))</f>
         <v>134</v>
@@ -10115,19 +10133,19 @@
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="13">
         <v>46204</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="14">
         <v>100</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="15">
         <v>75</v>
       </c>
-      <c r="E54" s="6"/>
+      <c r="E54" s="14"/>
       <c r="F54" s="6">
         <f>IF(A54="","",IFERROR(LOOKUP(2,1/(A$4:A53=A54),F$4:F53),0)+IF(ISNUMBER(C54),C54,0)-IF(ISNUMBER(E54),E54,0))</f>
         <v>234</v>
@@ -10139,17 +10157,17 @@
       <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="13">
         <v>46204</v>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7">
+      <c r="C55" s="14"/>
+      <c r="D55" s="15">
         <v>68.620604501227334</v>
       </c>
-      <c r="E55" s="6"/>
+      <c r="E55" s="14"/>
       <c r="F55" s="6">
         <f>IF(A55="","",IFERROR(LOOKUP(2,1/(A$4:A54=A55),F$4:F54),0)+IF(ISNUMBER(C55),C55,0)-IF(ISNUMBER(E55),E55,0))</f>
         <v>234</v>
@@ -10161,17 +10179,17 @@
       <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="13">
         <v>46235</v>
       </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="7">
+      <c r="C56" s="14"/>
+      <c r="D56" s="15">
         <v>68.620604501227334</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E56" s="14">
         <v>185</v>
       </c>
       <c r="F56" s="6">
@@ -10185,17 +10203,17 @@
       <c r="I56" s="7"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="13">
         <v>46266</v>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="7">
+      <c r="C57" s="14"/>
+      <c r="D57" s="15">
         <v>68.620604501227334</v>
       </c>
-      <c r="E57" s="6"/>
+      <c r="E57" s="14"/>
       <c r="F57" s="6">
         <f>IF(A57="","",IFERROR(LOOKUP(2,1/(A$4:A56=A57),F$4:F56),0)+IF(ISNUMBER(C57),C57,0)-IF(ISNUMBER(E57),E57,0))</f>
         <v>49</v>
@@ -10207,17 +10225,17 @@
       <c r="I57" s="7"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58" s="13">
         <v>46266</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="7">
+      <c r="C58" s="14"/>
+      <c r="D58" s="15">
         <v>73.5</v>
       </c>
-      <c r="E58" s="6"/>
+      <c r="E58" s="14"/>
       <c r="F58" s="6">
         <f>IF(A58="","",IFERROR(LOOKUP(2,1/(A$4:A57=A58),F$4:F57),0)+IF(ISNUMBER(C58),C58,0)-IF(ISNUMBER(E58),E58,0))</f>
         <v>49</v>
@@ -10229,433 +10247,515 @@
       <c r="I58" s="7"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A59" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B59" s="5">
+      <c r="A59" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="13">
         <v>45992</v>
       </c>
-      <c r="C59" s="6">
-        <v>20</v>
-      </c>
-      <c r="D59" s="7">
-        <v>42</v>
-      </c>
-      <c r="E59" s="6"/>
+      <c r="C59" s="14">
+        <v>165</v>
+      </c>
+      <c r="D59" s="15">
+        <v>24.5</v>
+      </c>
+      <c r="E59" s="14"/>
       <c r="F59" s="6">
         <f>IF(A59="","",IFERROR(LOOKUP(2,1/(A$4:A58=A59),F$4:F58),0)+IF(ISNUMBER(C59),C59,0)-IF(ISNUMBER(E59),E59,0))</f>
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="G59" s="11">
         <f>IF(A59="","",IF(IF(ISNUMBER(C59),C59,0)=0,IFERROR(LOOKUP(2,1/(A$4:A58=A59),G$4:G58),IF(ISNUMBER(D59),D59,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A58=A59),F$4:F58),0)&lt;=0,D59,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A58=A59),F$4:F58),0))*IFERROR(LOOKUP(2,1/(A$4:A58=A59),G$4:G58),0)+C59*D59)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A58=A59),F$4:F58),0))+C59))))</f>
-        <v>42</v>
+        <v>24.5</v>
       </c>
       <c r="I59" s="7"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A60" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B60" s="5">
+      <c r="A60" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="13">
         <v>46023</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="7">
-        <v>42</v>
-      </c>
-      <c r="E60" s="6"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="15">
+        <v>24.5</v>
+      </c>
+      <c r="E60" s="14">
+        <v>1</v>
+      </c>
       <c r="F60" s="6">
         <f>IF(A60="","",IFERROR(LOOKUP(2,1/(A$4:A59=A60),F$4:F59),0)+IF(ISNUMBER(C60),C60,0)-IF(ISNUMBER(E60),E60,0))</f>
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="G60" s="11">
         <f>IF(A60="","",IF(IF(ISNUMBER(C60),C60,0)=0,IFERROR(LOOKUP(2,1/(A$4:A59=A60),G$4:G59),IF(ISNUMBER(D60),D60,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A59=A60),F$4:F59),0)&lt;=0,D60,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A59=A60),F$4:F59),0))*IFERROR(LOOKUP(2,1/(A$4:A59=A60),G$4:G59),0)+C60*D60)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A59=A60),F$4:F59),0))+C60))))</f>
-        <v>42</v>
+        <v>24.5</v>
       </c>
       <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A61" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B61" s="5">
+      <c r="A61" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="13">
         <v>46054</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="7">
-        <v>42</v>
-      </c>
-      <c r="E61" s="6"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="15">
+        <v>24.5</v>
+      </c>
+      <c r="E61" s="14">
+        <v>125</v>
+      </c>
       <c r="F61" s="6">
         <f>IF(A61="","",IFERROR(LOOKUP(2,1/(A$4:A60=A61),F$4:F60),0)+IF(ISNUMBER(C61),C61,0)-IF(ISNUMBER(E61),E61,0))</f>
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G61" s="11">
         <f>IF(A61="","",IF(IF(ISNUMBER(C61),C61,0)=0,IFERROR(LOOKUP(2,1/(A$4:A60=A61),G$4:G60),IF(ISNUMBER(D61),D61,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A60=A61),F$4:F60),0)&lt;=0,D61,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A60=A61),F$4:F60),0))*IFERROR(LOOKUP(2,1/(A$4:A60=A61),G$4:G60),0)+C61*D61)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A60=A61),F$4:F60),0))+C61))))</f>
-        <v>42</v>
+        <v>24.5</v>
       </c>
       <c r="I61" s="7"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A62" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B62" s="5">
+      <c r="A62" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="13">
         <v>46082</v>
       </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="7">
-        <v>42</v>
-      </c>
-      <c r="E62" s="6"/>
+      <c r="C62" s="14">
+        <v>250</v>
+      </c>
+      <c r="D62" s="15">
+        <v>70</v>
+      </c>
+      <c r="E62" s="14"/>
       <c r="F62" s="6">
         <f>IF(A62="","",IFERROR(LOOKUP(2,1/(A$4:A61=A62),F$4:F61),0)+IF(ISNUMBER(C62),C62,0)-IF(ISNUMBER(E62),E62,0))</f>
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="G62" s="11">
         <f>IF(A62="","",IF(IF(ISNUMBER(C62),C62,0)=0,IFERROR(LOOKUP(2,1/(A$4:A61=A62),G$4:G61),IF(ISNUMBER(D62),D62,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A61=A62),F$4:F61),0)&lt;=0,D62,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A61=A62),F$4:F61),0))*IFERROR(LOOKUP(2,1/(A$4:A61=A62),G$4:G61),0)+C62*D62)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A61=A62),F$4:F61),0))+C62))))</f>
-        <v>42</v>
+        <v>63.859861591695498</v>
       </c>
       <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A63" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B63" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="7">
-        <v>42</v>
-      </c>
-      <c r="E63" s="6"/>
+      <c r="A63" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C63" s="14"/>
+      <c r="D63" s="15">
+        <v>63.86</v>
+      </c>
+      <c r="E63" s="14"/>
       <c r="F63" s="6">
         <f>IF(A63="","",IFERROR(LOOKUP(2,1/(A$4:A62=A63),F$4:F62),0)+IF(ISNUMBER(C63),C63,0)-IF(ISNUMBER(E63),E63,0))</f>
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="G63" s="11">
         <f>IF(A63="","",IF(IF(ISNUMBER(C63),C63,0)=0,IFERROR(LOOKUP(2,1/(A$4:A62=A63),G$4:G62),IF(ISNUMBER(D63),D63,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A62=A63),F$4:F62),0)&lt;=0,D63,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A62=A63),F$4:F62),0))*IFERROR(LOOKUP(2,1/(A$4:A62=A63),G$4:G62),0)+C63*D63)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A62=A63),F$4:F62),0))+C63))))</f>
-        <v>42</v>
+        <v>63.859861591695498</v>
       </c>
       <c r="I63" s="7"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A64" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B64" s="5">
-        <v>46143</v>
-      </c>
-      <c r="C64" s="6">
-        <v>10</v>
-      </c>
-      <c r="D64" s="7">
-        <v>42</v>
-      </c>
-      <c r="E64" s="6"/>
+      <c r="A64" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="13">
+        <v>46113</v>
+      </c>
+      <c r="C64" s="14"/>
+      <c r="D64" s="15">
+        <v>63.86</v>
+      </c>
+      <c r="E64" s="14">
+        <v>80</v>
+      </c>
       <c r="F64" s="6">
         <f>IF(A64="","",IFERROR(LOOKUP(2,1/(A$4:A63=A64),F$4:F63),0)+IF(ISNUMBER(C64),C64,0)-IF(ISNUMBER(E64),E64,0))</f>
-        <v>30</v>
+        <v>209</v>
       </c>
       <c r="G64" s="11">
         <f>IF(A64="","",IF(IF(ISNUMBER(C64),C64,0)=0,IFERROR(LOOKUP(2,1/(A$4:A63=A64),G$4:G63),IF(ISNUMBER(D64),D64,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A63=A64),F$4:F63),0)&lt;=0,D64,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A63=A64),F$4:F63),0))*IFERROR(LOOKUP(2,1/(A$4:A63=A64),G$4:G63),0)+C64*D64)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A63=A64),F$4:F63),0))+C64))))</f>
-        <v>42</v>
+        <v>63.859861591695498</v>
       </c>
       <c r="I64" s="7"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A65" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B65" s="5">
+      <c r="A65" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="13">
         <v>46143</v>
       </c>
-      <c r="C65" s="6"/>
-      <c r="D65" s="7">
-        <v>42</v>
-      </c>
-      <c r="E65" s="6"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="15">
+        <v>63.86</v>
+      </c>
+      <c r="E65" s="14">
+        <v>75</v>
+      </c>
       <c r="F65" s="6">
         <f>IF(A65="","",IFERROR(LOOKUP(2,1/(A$4:A64=A65),F$4:F64),0)+IF(ISNUMBER(C65),C65,0)-IF(ISNUMBER(E65),E65,0))</f>
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="G65" s="11">
         <f>IF(A65="","",IF(IF(ISNUMBER(C65),C65,0)=0,IFERROR(LOOKUP(2,1/(A$4:A64=A65),G$4:G64),IF(ISNUMBER(D65),D65,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A64=A65),F$4:F64),0)&lt;=0,D65,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A64=A65),F$4:F64),0))*IFERROR(LOOKUP(2,1/(A$4:A64=A65),G$4:G64),0)+C65*D65)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A64=A65),F$4:F64),0))+C65))))</f>
-        <v>42</v>
+        <v>63.859861591695498</v>
       </c>
       <c r="I65" s="7"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A66" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B66" s="5">
+      <c r="A66" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="13">
         <v>46174</v>
       </c>
-      <c r="C66" s="6"/>
-      <c r="D66" s="7">
-        <v>42</v>
-      </c>
-      <c r="E66" s="6"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="15">
+        <v>63.86</v>
+      </c>
+      <c r="E66" s="14"/>
       <c r="F66" s="6">
         <f>IF(A66="","",IFERROR(LOOKUP(2,1/(A$4:A65=A66),F$4:F65),0)+IF(ISNUMBER(C66),C66,0)-IF(ISNUMBER(E66),E66,0))</f>
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="G66" s="11">
         <f>IF(A66="","",IF(IF(ISNUMBER(C66),C66,0)=0,IFERROR(LOOKUP(2,1/(A$4:A65=A66),G$4:G65),IF(ISNUMBER(D66),D66,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A65=A66),F$4:F65),0)&lt;=0,D66,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A65=A66),F$4:F65),0))*IFERROR(LOOKUP(2,1/(A$4:A65=A66),G$4:G65),0)+C66*D66)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A65=A66),F$4:F65),0))+C66))))</f>
-        <v>42</v>
+        <v>63.859861591695498</v>
       </c>
       <c r="I66" s="7"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A67" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B67" s="5">
+      <c r="A67" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="13">
         <v>46204</v>
       </c>
-      <c r="C67" s="6"/>
-      <c r="D67" s="7">
-        <v>42</v>
-      </c>
-      <c r="E67" s="6"/>
+      <c r="C67" s="14">
+        <v>100</v>
+      </c>
+      <c r="D67" s="15">
+        <v>75</v>
+      </c>
+      <c r="E67" s="14"/>
       <c r="F67" s="6">
         <f>IF(A67="","",IFERROR(LOOKUP(2,1/(A$4:A66=A67),F$4:F66),0)+IF(ISNUMBER(C67),C67,0)-IF(ISNUMBER(E67),E67,0))</f>
-        <v>30</v>
+        <v>234</v>
       </c>
       <c r="G67" s="11">
         <f>IF(A67="","",IF(IF(ISNUMBER(C67),C67,0)=0,IFERROR(LOOKUP(2,1/(A$4:A66=A67),G$4:G66),IF(ISNUMBER(D67),D67,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A66=A67),F$4:F66),0)&lt;=0,D67,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A66=A67),F$4:F66),0))*IFERROR(LOOKUP(2,1/(A$4:A66=A67),G$4:G66),0)+C67*D67)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A66=A67),F$4:F66),0))+C67))))</f>
-        <v>42</v>
+        <v>68.620604501227334</v>
       </c>
       <c r="I67" s="7"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A68" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B68" s="5">
+      <c r="A68" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="13">
         <v>46235</v>
       </c>
-      <c r="C68" s="6"/>
-      <c r="D68" s="7">
-        <v>42</v>
-      </c>
-      <c r="E68" s="6"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="15">
+        <v>68.62</v>
+      </c>
+      <c r="E68" s="14">
+        <v>185</v>
+      </c>
       <c r="F68" s="6">
         <f>IF(A68="","",IFERROR(LOOKUP(2,1/(A$4:A67=A68),F$4:F67),0)+IF(ISNUMBER(C68),C68,0)-IF(ISNUMBER(E68),E68,0))</f>
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="G68" s="11">
         <f>IF(A68="","",IF(IF(ISNUMBER(C68),C68,0)=0,IFERROR(LOOKUP(2,1/(A$4:A67=A68),G$4:G67),IF(ISNUMBER(D68),D68,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A67=A68),F$4:F67),0)&lt;=0,D68,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A67=A68),F$4:F67),0))*IFERROR(LOOKUP(2,1/(A$4:A67=A68),G$4:G67),0)+C68*D68)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A67=A68),F$4:F67),0))+C68))))</f>
-        <v>42</v>
+        <v>68.620604501227334</v>
       </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A69" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B69" s="5">
+      <c r="A69" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="13">
         <v>46266</v>
       </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="7">
-        <v>42</v>
-      </c>
-      <c r="E69" s="6"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="15">
+        <v>68.62</v>
+      </c>
+      <c r="E69" s="14"/>
       <c r="F69" s="6">
         <f>IF(A69="","",IFERROR(LOOKUP(2,1/(A$4:A68=A69),F$4:F68),0)+IF(ISNUMBER(C69),C69,0)-IF(ISNUMBER(E69),E69,0))</f>
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="G69" s="11">
         <f>IF(A69="","",IF(IF(ISNUMBER(C69),C69,0)=0,IFERROR(LOOKUP(2,1/(A$4:A68=A69),G$4:G68),IF(ISNUMBER(D69),D69,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A68=A69),F$4:F68),0)&lt;=0,D69,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A68=A69),F$4:F68),0))*IFERROR(LOOKUP(2,1/(A$4:A68=A69),G$4:G68),0)+C69*D69)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A68=A69),F$4:F68),0))+C69))))</f>
+        <v>68.620604501227334</v>
+      </c>
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A70" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" s="13">
+        <v>45992</v>
+      </c>
+      <c r="C70" s="14">
+        <v>20</v>
+      </c>
+      <c r="D70" s="15">
         <v>42</v>
       </c>
-      <c r="I69" s="7"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6" t="str">
+      <c r="E70" s="14"/>
+      <c r="F70" s="6">
         <f>IF(A70="","",IFERROR(LOOKUP(2,1/(A$4:A69=A70),F$4:F69),0)+IF(ISNUMBER(C70),C70,0)-IF(ISNUMBER(E70),E70,0))</f>
-        <v/>
-      </c>
-      <c r="G70" s="11" t="str">
+        <v>20</v>
+      </c>
+      <c r="G70" s="11">
         <f>IF(A70="","",IF(IF(ISNUMBER(C70),C70,0)=0,IFERROR(LOOKUP(2,1/(A$4:A69=A70),G$4:G69),IF(ISNUMBER(D70),D70,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A69=A70),F$4:F69),0)&lt;=0,D70,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A69=A70),F$4:F69),0))*IFERROR(LOOKUP(2,1/(A$4:A69=A70),G$4:G69),0)+C70*D70)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A69=A70),F$4:F69),0))+C70))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I70" s="7"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6" t="str">
+      <c r="A71" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" s="13">
+        <v>46023</v>
+      </c>
+      <c r="C71" s="14"/>
+      <c r="D71" s="15">
+        <v>42</v>
+      </c>
+      <c r="E71" s="14"/>
+      <c r="F71" s="6">
         <f>IF(A71="","",IFERROR(LOOKUP(2,1/(A$4:A70=A71),F$4:F70),0)+IF(ISNUMBER(C71),C71,0)-IF(ISNUMBER(E71),E71,0))</f>
-        <v/>
-      </c>
-      <c r="G71" s="11" t="str">
+        <v>20</v>
+      </c>
+      <c r="G71" s="11">
         <f>IF(A71="","",IF(IF(ISNUMBER(C71),C71,0)=0,IFERROR(LOOKUP(2,1/(A$4:A70=A71),G$4:G70),IF(ISNUMBER(D71),D71,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A70=A71),F$4:F70),0)&lt;=0,D71,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A70=A71),F$4:F70),0))*IFERROR(LOOKUP(2,1/(A$4:A70=A71),G$4:G70),0)+C71*D71)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A70=A71),F$4:F70),0))+C71))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I71" s="7"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6" t="str">
+      <c r="A72" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B72" s="13">
+        <v>46054</v>
+      </c>
+      <c r="C72" s="14"/>
+      <c r="D72" s="15">
+        <v>42</v>
+      </c>
+      <c r="E72" s="14"/>
+      <c r="F72" s="6">
         <f>IF(A72="","",IFERROR(LOOKUP(2,1/(A$4:A71=A72),F$4:F71),0)+IF(ISNUMBER(C72),C72,0)-IF(ISNUMBER(E72),E72,0))</f>
-        <v/>
-      </c>
-      <c r="G72" s="11" t="str">
+        <v>20</v>
+      </c>
+      <c r="G72" s="11">
         <f>IF(A72="","",IF(IF(ISNUMBER(C72),C72,0)=0,IFERROR(LOOKUP(2,1/(A$4:A71=A72),G$4:G71),IF(ISNUMBER(D72),D72,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A71=A72),F$4:F71),0)&lt;=0,D72,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A71=A72),F$4:F71),0))*IFERROR(LOOKUP(2,1/(A$4:A71=A72),G$4:G71),0)+C72*D72)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A71=A72),F$4:F71),0))+C72))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I72" s="7"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A73" s="4"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6" t="str">
+      <c r="A73" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C73" s="14"/>
+      <c r="D73" s="15">
+        <v>42</v>
+      </c>
+      <c r="E73" s="14"/>
+      <c r="F73" s="6">
         <f>IF(A73="","",IFERROR(LOOKUP(2,1/(A$4:A72=A73),F$4:F72),0)+IF(ISNUMBER(C73),C73,0)-IF(ISNUMBER(E73),E73,0))</f>
-        <v/>
-      </c>
-      <c r="G73" s="11" t="str">
+        <v>20</v>
+      </c>
+      <c r="G73" s="11">
         <f>IF(A73="","",IF(IF(ISNUMBER(C73),C73,0)=0,IFERROR(LOOKUP(2,1/(A$4:A72=A73),G$4:G72),IF(ISNUMBER(D73),D73,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A72=A73),F$4:F72),0)&lt;=0,D73,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A72=A73),F$4:F72),0))*IFERROR(LOOKUP(2,1/(A$4:A72=A73),G$4:G72),0)+C73*D73)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A72=A73),F$4:F72),0))+C73))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6" t="str">
+      <c r="A74" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" s="13">
+        <v>46113</v>
+      </c>
+      <c r="C74" s="14"/>
+      <c r="D74" s="15">
+        <v>42</v>
+      </c>
+      <c r="E74" s="14"/>
+      <c r="F74" s="6">
         <f>IF(A74="","",IFERROR(LOOKUP(2,1/(A$4:A73=A74),F$4:F73),0)+IF(ISNUMBER(C74),C74,0)-IF(ISNUMBER(E74),E74,0))</f>
-        <v/>
-      </c>
-      <c r="G74" s="11" t="str">
+        <v>20</v>
+      </c>
+      <c r="G74" s="11">
         <f>IF(A74="","",IF(IF(ISNUMBER(C74),C74,0)=0,IFERROR(LOOKUP(2,1/(A$4:A73=A74),G$4:G73),IF(ISNUMBER(D74),D74,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A73=A74),F$4:F73),0)&lt;=0,D74,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A73=A74),F$4:F73),0))*IFERROR(LOOKUP(2,1/(A$4:A73=A74),G$4:G73),0)+C74*D74)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A73=A74),F$4:F73),0))+C74))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6" t="str">
+      <c r="A75" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="13">
+        <v>46143</v>
+      </c>
+      <c r="C75" s="14">
+        <v>10</v>
+      </c>
+      <c r="D75" s="15">
+        <v>42</v>
+      </c>
+      <c r="E75" s="14"/>
+      <c r="F75" s="6">
         <f>IF(A75="","",IFERROR(LOOKUP(2,1/(A$4:A74=A75),F$4:F74),0)+IF(ISNUMBER(C75),C75,0)-IF(ISNUMBER(E75),E75,0))</f>
-        <v/>
-      </c>
-      <c r="G75" s="11" t="str">
+        <v>30</v>
+      </c>
+      <c r="G75" s="11">
         <f>IF(A75="","",IF(IF(ISNUMBER(C75),C75,0)=0,IFERROR(LOOKUP(2,1/(A$4:A74=A75),G$4:G74),IF(ISNUMBER(D75),D75,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A74=A75),F$4:F74),0)&lt;=0,D75,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A74=A75),F$4:F74),0))*IFERROR(LOOKUP(2,1/(A$4:A74=A75),G$4:G74),0)+C75*D75)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A74=A75),F$4:F74),0))+C75))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6" t="str">
+      <c r="A76" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B76" s="13">
+        <v>46143</v>
+      </c>
+      <c r="C76" s="14"/>
+      <c r="D76" s="15">
+        <v>42</v>
+      </c>
+      <c r="E76" s="14"/>
+      <c r="F76" s="6">
         <f>IF(A76="","",IFERROR(LOOKUP(2,1/(A$4:A75=A76),F$4:F75),0)+IF(ISNUMBER(C76),C76,0)-IF(ISNUMBER(E76),E76,0))</f>
-        <v/>
-      </c>
-      <c r="G76" s="11" t="str">
+        <v>30</v>
+      </c>
+      <c r="G76" s="11">
         <f>IF(A76="","",IF(IF(ISNUMBER(C76),C76,0)=0,IFERROR(LOOKUP(2,1/(A$4:A75=A76),G$4:G75),IF(ISNUMBER(D76),D76,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A75=A76),F$4:F75),0)&lt;=0,D76,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A75=A76),F$4:F75),0))*IFERROR(LOOKUP(2,1/(A$4:A75=A76),G$4:G75),0)+C76*D76)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A75=A76),F$4:F75),0))+C76))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I76" s="7"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6" t="str">
+      <c r="A77" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B77" s="13">
+        <v>46174</v>
+      </c>
+      <c r="C77" s="14"/>
+      <c r="D77" s="15">
+        <v>42</v>
+      </c>
+      <c r="E77" s="14"/>
+      <c r="F77" s="6">
         <f>IF(A77="","",IFERROR(LOOKUP(2,1/(A$4:A76=A77),F$4:F76),0)+IF(ISNUMBER(C77),C77,0)-IF(ISNUMBER(E77),E77,0))</f>
-        <v/>
-      </c>
-      <c r="G77" s="11" t="str">
+        <v>30</v>
+      </c>
+      <c r="G77" s="11">
         <f>IF(A77="","",IF(IF(ISNUMBER(C77),C77,0)=0,IFERROR(LOOKUP(2,1/(A$4:A76=A77),G$4:G76),IF(ISNUMBER(D77),D77,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A76=A77),F$4:F76),0)&lt;=0,D77,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A76=A77),F$4:F76),0))*IFERROR(LOOKUP(2,1/(A$4:A76=A77),G$4:G76),0)+C77*D77)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A76=A77),F$4:F76),0))+C77))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A78" s="4"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6" t="str">
+      <c r="A78" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" s="13">
+        <v>46204</v>
+      </c>
+      <c r="C78" s="14"/>
+      <c r="D78" s="15">
+        <v>42</v>
+      </c>
+      <c r="E78" s="14"/>
+      <c r="F78" s="6">
         <f>IF(A78="","",IFERROR(LOOKUP(2,1/(A$4:A77=A78),F$4:F77),0)+IF(ISNUMBER(C78),C78,0)-IF(ISNUMBER(E78),E78,0))</f>
-        <v/>
-      </c>
-      <c r="G78" s="11" t="str">
+        <v>30</v>
+      </c>
+      <c r="G78" s="11">
         <f>IF(A78="","",IF(IF(ISNUMBER(C78),C78,0)=0,IFERROR(LOOKUP(2,1/(A$4:A77=A78),G$4:G77),IF(ISNUMBER(D78),D78,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A77=A78),F$4:F77),0)&lt;=0,D78,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A77=A78),F$4:F77),0))*IFERROR(LOOKUP(2,1/(A$4:A77=A78),G$4:G77),0)+C78*D78)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A77=A78),F$4:F77),0))+C78))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A79" s="4"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6" t="str">
+      <c r="A79" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B79" s="13">
+        <v>46235</v>
+      </c>
+      <c r="C79" s="14"/>
+      <c r="D79" s="15">
+        <v>42</v>
+      </c>
+      <c r="E79" s="14"/>
+      <c r="F79" s="6">
         <f>IF(A79="","",IFERROR(LOOKUP(2,1/(A$4:A78=A79),F$4:F78),0)+IF(ISNUMBER(C79),C79,0)-IF(ISNUMBER(E79),E79,0))</f>
-        <v/>
-      </c>
-      <c r="G79" s="11" t="str">
+        <v>30</v>
+      </c>
+      <c r="G79" s="11">
         <f>IF(A79="","",IF(IF(ISNUMBER(C79),C79,0)=0,IFERROR(LOOKUP(2,1/(A$4:A78=A79),G$4:G78),IF(ISNUMBER(D79),D79,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A78=A79),F$4:F78),0)&lt;=0,D79,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A78=A79),F$4:F78),0))*IFERROR(LOOKUP(2,1/(A$4:A78=A79),G$4:G78),0)+C79*D79)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A78=A79),F$4:F78),0))+C79))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I79" s="7"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A80" s="4"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6" t="str">
+      <c r="A80" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B80" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C80" s="14"/>
+      <c r="D80" s="15">
+        <v>42</v>
+      </c>
+      <c r="E80" s="14"/>
+      <c r="F80" s="6">
         <f>IF(A80="","",IFERROR(LOOKUP(2,1/(A$4:A79=A80),F$4:F79),0)+IF(ISNUMBER(C80),C80,0)-IF(ISNUMBER(E80),E80,0))</f>
-        <v/>
-      </c>
-      <c r="G80" s="11" t="str">
+        <v>30</v>
+      </c>
+      <c r="G80" s="11">
         <f>IF(A80="","",IF(IF(ISNUMBER(C80),C80,0)=0,IFERROR(LOOKUP(2,1/(A$4:A79=A80),G$4:G79),IF(ISNUMBER(D80),D80,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A79=A80),F$4:F79),0)&lt;=0,D80,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A79=A80),F$4:F79),0))*IFERROR(LOOKUP(2,1/(A$4:A79=A80),G$4:G79),0)+C80*D80)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A79=A80),F$4:F79),0))+C80))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="I80" s="7"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A81" s="4"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="6"/>
+      <c r="A81" s="12"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="14"/>
       <c r="F81" s="6" t="str">
         <f>IF(A81="","",IFERROR(LOOKUP(2,1/(A$4:A80=A81),F$4:F80),0)+IF(ISNUMBER(C81),C81,0)-IF(ISNUMBER(E81),E81,0))</f>
         <v/>
@@ -10667,11 +10767,11 @@
       <c r="I81" s="7"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A82" s="4"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="6"/>
+      <c r="A82" s="12"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="14"/>
       <c r="F82" s="6" t="str">
         <f>IF(A82="","",IFERROR(LOOKUP(2,1/(A$4:A81=A82),F$4:F81),0)+IF(ISNUMBER(C82),C82,0)-IF(ISNUMBER(E82),E82,0))</f>
         <v/>
@@ -10683,11 +10783,11 @@
       <c r="I82" s="7"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A83" s="4"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="6"/>
+      <c r="A83" s="12"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="14"/>
       <c r="F83" s="6" t="str">
         <f>IF(A83="","",IFERROR(LOOKUP(2,1/(A$4:A82=A83),F$4:F82),0)+IF(ISNUMBER(C83),C83,0)-IF(ISNUMBER(E83),E83,0))</f>
         <v/>
@@ -10699,11 +10799,11 @@
       <c r="I83" s="7"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A84" s="4"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="6"/>
+      <c r="A84" s="12"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="14"/>
       <c r="F84" s="6" t="str">
         <f>IF(A84="","",IFERROR(LOOKUP(2,1/(A$4:A83=A84),F$4:F83),0)+IF(ISNUMBER(C84),C84,0)-IF(ISNUMBER(E84),E84,0))</f>
         <v/>
@@ -10715,11 +10815,11 @@
       <c r="I84" s="7"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A85" s="4"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="6"/>
+      <c r="A85" s="12"/>
+      <c r="B85" s="13"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="14"/>
       <c r="F85" s="6" t="str">
         <f>IF(A85="","",IFERROR(LOOKUP(2,1/(A$4:A84=A85),F$4:F84),0)+IF(ISNUMBER(C85),C85,0)-IF(ISNUMBER(E85),E85,0))</f>
         <v/>
@@ -10731,11 +10831,11 @@
       <c r="I85" s="7"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A86" s="4"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="6"/>
+      <c r="A86" s="12"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="14"/>
       <c r="F86" s="6" t="str">
         <f>IF(A86="","",IFERROR(LOOKUP(2,1/(A$4:A85=A86),F$4:F85),0)+IF(ISNUMBER(C86),C86,0)-IF(ISNUMBER(E86),E86,0))</f>
         <v/>
@@ -10747,11 +10847,11 @@
       <c r="I86" s="7"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A87" s="4"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="6"/>
+      <c r="A87" s="12"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="14"/>
       <c r="F87" s="6" t="str">
         <f>IF(A87="","",IFERROR(LOOKUP(2,1/(A$4:A86=A87),F$4:F86),0)+IF(ISNUMBER(C87),C87,0)-IF(ISNUMBER(E87),E87,0))</f>
         <v/>
@@ -10763,11 +10863,11 @@
       <c r="I87" s="7"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A88" s="4"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="6"/>
+      <c r="A88" s="12"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="14"/>
       <c r="F88" s="6" t="str">
         <f>IF(A88="","",IFERROR(LOOKUP(2,1/(A$4:A87=A88),F$4:F87),0)+IF(ISNUMBER(C88),C88,0)-IF(ISNUMBER(E88),E88,0))</f>
         <v/>
@@ -10779,11 +10879,11 @@
       <c r="I88" s="7"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A89" s="4"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="6"/>
+      <c r="A89" s="12"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="14"/>
       <c r="F89" s="6" t="str">
         <f>IF(A89="","",IFERROR(LOOKUP(2,1/(A$4:A88=A89),F$4:F88),0)+IF(ISNUMBER(C89),C89,0)-IF(ISNUMBER(E89),E89,0))</f>
         <v/>
@@ -10795,11 +10895,11 @@
       <c r="I89" s="7"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A90" s="4"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="6"/>
+      <c r="A90" s="12"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="14"/>
       <c r="F90" s="6" t="str">
         <f>IF(A90="","",IFERROR(LOOKUP(2,1/(A$4:A89=A90),F$4:F89),0)+IF(ISNUMBER(C90),C90,0)-IF(ISNUMBER(E90),E90,0))</f>
         <v/>
@@ -10811,11 +10911,11 @@
       <c r="I90" s="7"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A91" s="4"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="6"/>
+      <c r="A91" s="12"/>
+      <c r="B91" s="13"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="14"/>
       <c r="F91" s="6" t="str">
         <f>IF(A91="","",IFERROR(LOOKUP(2,1/(A$4:A90=A91),F$4:F90),0)+IF(ISNUMBER(C91),C91,0)-IF(ISNUMBER(E91),E91,0))</f>
         <v/>
@@ -10827,11 +10927,11 @@
       <c r="I91" s="7"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A92" s="4"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="6"/>
+      <c r="A92" s="12"/>
+      <c r="B92" s="13"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="14"/>
       <c r="F92" s="6" t="str">
         <f>IF(A92="","",IFERROR(LOOKUP(2,1/(A$4:A91=A92),F$4:F91),0)+IF(ISNUMBER(C92),C92,0)-IF(ISNUMBER(E92),E92,0))</f>
         <v/>
@@ -10843,11 +10943,11 @@
       <c r="I92" s="7"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A93" s="4"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="6"/>
+      <c r="A93" s="12"/>
+      <c r="B93" s="13"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="14"/>
       <c r="F93" s="6" t="str">
         <f>IF(A93="","",IFERROR(LOOKUP(2,1/(A$4:A92=A93),F$4:F92),0)+IF(ISNUMBER(C93),C93,0)-IF(ISNUMBER(E93),E93,0))</f>
         <v/>
@@ -10859,11 +10959,11 @@
       <c r="I93" s="7"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A94" s="4"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="6"/>
+      <c r="A94" s="12"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="14"/>
       <c r="F94" s="6" t="str">
         <f>IF(A94="","",IFERROR(LOOKUP(2,1/(A$4:A93=A94),F$4:F93),0)+IF(ISNUMBER(C94),C94,0)-IF(ISNUMBER(E94),E94,0))</f>
         <v/>
@@ -10875,11 +10975,11 @@
       <c r="I94" s="7"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A95" s="4"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="6"/>
+      <c r="A95" s="12"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="14"/>
       <c r="F95" s="6" t="str">
         <f>IF(A95="","",IFERROR(LOOKUP(2,1/(A$4:A94=A95),F$4:F94),0)+IF(ISNUMBER(C95),C95,0)-IF(ISNUMBER(E95),E95,0))</f>
         <v/>
@@ -10891,11 +10991,11 @@
       <c r="I95" s="7"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A96" s="4"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="6"/>
+      <c r="A96" s="12"/>
+      <c r="B96" s="13"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="14"/>
       <c r="F96" s="6" t="str">
         <f>IF(A96="","",IFERROR(LOOKUP(2,1/(A$4:A95=A96),F$4:F95),0)+IF(ISNUMBER(C96),C96,0)-IF(ISNUMBER(E96),E96,0))</f>
         <v/>
@@ -10907,11 +11007,11 @@
       <c r="I96" s="7"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A97" s="4"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="6"/>
+      <c r="A97" s="12"/>
+      <c r="B97" s="13"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="14"/>
       <c r="F97" s="6" t="str">
         <f>IF(A97="","",IFERROR(LOOKUP(2,1/(A$4:A96=A97),F$4:F96),0)+IF(ISNUMBER(C97),C97,0)-IF(ISNUMBER(E97),E97,0))</f>
         <v/>
@@ -10923,11 +11023,11 @@
       <c r="I97" s="7"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A98" s="4"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="6"/>
+      <c r="A98" s="12"/>
+      <c r="B98" s="13"/>
+      <c r="C98" s="14"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="14"/>
       <c r="F98" s="6" t="str">
         <f>IF(A98="","",IFERROR(LOOKUP(2,1/(A$4:A97=A98),F$4:F97),0)+IF(ISNUMBER(C98),C98,0)-IF(ISNUMBER(E98),E98,0))</f>
         <v/>
@@ -10939,11 +11039,11 @@
       <c r="I98" s="7"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A99" s="4"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="6"/>
+      <c r="A99" s="12"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="14"/>
+      <c r="D99" s="15"/>
+      <c r="E99" s="14"/>
       <c r="F99" s="6" t="str">
         <f>IF(A99="","",IFERROR(LOOKUP(2,1/(A$4:A98=A99),F$4:F98),0)+IF(ISNUMBER(C99),C99,0)-IF(ISNUMBER(E99),E99,0))</f>
         <v/>
@@ -10955,31 +11055,207 @@
       <c r="I99" s="7"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="12"/>
+      <c r="B100" s="13"/>
+      <c r="C100" s="14"/>
+      <c r="D100" s="15"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="6" t="str">
+        <f>IF(A100="","",IFERROR(LOOKUP(2,1/(A$4:A99=A100),F$4:F99),0)+IF(ISNUMBER(C100),C100,0)-IF(ISNUMBER(E100),E100,0))</f>
+        <v/>
+      </c>
+      <c r="G100" s="11" t="str">
+        <f>IF(A100="","",IF(IF(ISNUMBER(C100),C100,0)=0,IFERROR(LOOKUP(2,1/(A$4:A99=A100),G$4:G99),IF(ISNUMBER(D100),D100,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A99=A100),F$4:F99),0)&lt;=0,D100,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A99=A100),F$4:F99),0))*IFERROR(LOOKUP(2,1/(A$4:A99=A100),G$4:G99),0)+C100*D100)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A99=A100),F$4:F99),0))+C100))))</f>
+        <v/>
+      </c>
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A101" s="12"/>
+      <c r="B101" s="13"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="15"/>
+      <c r="E101" s="14"/>
+      <c r="F101" s="6" t="str">
+        <f>IF(A101="","",IFERROR(LOOKUP(2,1/(A$4:A100=A101),F$4:F100),0)+IF(ISNUMBER(C101),C101,0)-IF(ISNUMBER(E101),E101,0))</f>
+        <v/>
+      </c>
+      <c r="G101" s="11" t="str">
+        <f>IF(A101="","",IF(IF(ISNUMBER(C101),C101,0)=0,IFERROR(LOOKUP(2,1/(A$4:A100=A101),G$4:G100),IF(ISNUMBER(D101),D101,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A100=A101),F$4:F100),0)&lt;=0,D101,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A100=A101),F$4:F100),0))*IFERROR(LOOKUP(2,1/(A$4:A100=A101),G$4:G100),0)+C101*D101)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A100=A101),F$4:F100),0))+C101))))</f>
+        <v/>
+      </c>
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A102" s="12"/>
+      <c r="B102" s="13"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="15"/>
+      <c r="E102" s="14"/>
+      <c r="F102" s="6" t="str">
+        <f>IF(A102="","",IFERROR(LOOKUP(2,1/(A$4:A101=A102),F$4:F101),0)+IF(ISNUMBER(C102),C102,0)-IF(ISNUMBER(E102),E102,0))</f>
+        <v/>
+      </c>
+      <c r="G102" s="11" t="str">
+        <f>IF(A102="","",IF(IF(ISNUMBER(C102),C102,0)=0,IFERROR(LOOKUP(2,1/(A$4:A101=A102),G$4:G101),IF(ISNUMBER(D102),D102,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A101=A102),F$4:F101),0)&lt;=0,D102,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A101=A102),F$4:F101),0))*IFERROR(LOOKUP(2,1/(A$4:A101=A102),G$4:G101),0)+C102*D102)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A101=A102),F$4:F101),0))+C102))))</f>
+        <v/>
+      </c>
+      <c r="I102" s="7"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A103" s="12"/>
+      <c r="B103" s="13"/>
+      <c r="C103" s="14"/>
+      <c r="D103" s="15"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="6" t="str">
+        <f>IF(A103="","",IFERROR(LOOKUP(2,1/(A$4:A102=A103),F$4:F102),0)+IF(ISNUMBER(C103),C103,0)-IF(ISNUMBER(E103),E103,0))</f>
+        <v/>
+      </c>
+      <c r="G103" s="11" t="str">
+        <f>IF(A103="","",IF(IF(ISNUMBER(C103),C103,0)=0,IFERROR(LOOKUP(2,1/(A$4:A102=A103),G$4:G102),IF(ISNUMBER(D103),D103,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A102=A103),F$4:F102),0)&lt;=0,D103,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A102=A103),F$4:F102),0))*IFERROR(LOOKUP(2,1/(A$4:A102=A103),G$4:G102),0)+C103*D103)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A102=A103),F$4:F102),0))+C103))))</f>
+        <v/>
+      </c>
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A104" s="12"/>
+      <c r="B104" s="13"/>
+      <c r="C104" s="14"/>
+      <c r="D104" s="15"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="6" t="str">
+        <f>IF(A104="","",IFERROR(LOOKUP(2,1/(A$4:A103=A104),F$4:F103),0)+IF(ISNUMBER(C104),C104,0)-IF(ISNUMBER(E104),E104,0))</f>
+        <v/>
+      </c>
+      <c r="G104" s="11" t="str">
+        <f>IF(A104="","",IF(IF(ISNUMBER(C104),C104,0)=0,IFERROR(LOOKUP(2,1/(A$4:A103=A104),G$4:G103),IF(ISNUMBER(D104),D104,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A103=A104),F$4:F103),0)&lt;=0,D104,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A103=A104),F$4:F103),0))*IFERROR(LOOKUP(2,1/(A$4:A103=A104),G$4:G103),0)+C104*D104)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A103=A104),F$4:F103),0))+C104))))</f>
+        <v/>
+      </c>
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A105" s="12"/>
+      <c r="B105" s="13"/>
+      <c r="C105" s="14"/>
+      <c r="D105" s="15"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="6" t="str">
+        <f>IF(A105="","",IFERROR(LOOKUP(2,1/(A$4:A104=A105),F$4:F104),0)+IF(ISNUMBER(C105),C105,0)-IF(ISNUMBER(E105),E105,0))</f>
+        <v/>
+      </c>
+      <c r="G105" s="11" t="str">
+        <f>IF(A105="","",IF(IF(ISNUMBER(C105),C105,0)=0,IFERROR(LOOKUP(2,1/(A$4:A104=A105),G$4:G104),IF(ISNUMBER(D105),D105,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A104=A105),F$4:F104),0)&lt;=0,D105,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A104=A105),F$4:F104),0))*IFERROR(LOOKUP(2,1/(A$4:A104=A105),G$4:G104),0)+C105*D105)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A104=A105),F$4:F104),0))+C105))))</f>
+        <v/>
+      </c>
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A106" s="12"/>
+      <c r="B106" s="13"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="6" t="str">
+        <f>IF(A106="","",IFERROR(LOOKUP(2,1/(A$4:A105=A106),F$4:F105),0)+IF(ISNUMBER(C106),C106,0)-IF(ISNUMBER(E106),E106,0))</f>
+        <v/>
+      </c>
+      <c r="G106" s="11" t="str">
+        <f>IF(A106="","",IF(IF(ISNUMBER(C106),C106,0)=0,IFERROR(LOOKUP(2,1/(A$4:A105=A106),G$4:G105),IF(ISNUMBER(D106),D106,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A105=A106),F$4:F105),0)&lt;=0,D106,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A105=A106),F$4:F105),0))*IFERROR(LOOKUP(2,1/(A$4:A105=A106),G$4:G105),0)+C106*D106)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A105=A106),F$4:F105),0))+C106))))</f>
+        <v/>
+      </c>
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A107" s="12"/>
+      <c r="B107" s="13"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="15"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="6" t="str">
+        <f>IF(A107="","",IFERROR(LOOKUP(2,1/(A$4:A106=A107),F$4:F106),0)+IF(ISNUMBER(C107),C107,0)-IF(ISNUMBER(E107),E107,0))</f>
+        <v/>
+      </c>
+      <c r="G107" s="11" t="str">
+        <f>IF(A107="","",IF(IF(ISNUMBER(C107),C107,0)=0,IFERROR(LOOKUP(2,1/(A$4:A106=A107),G$4:G106),IF(ISNUMBER(D107),D107,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A106=A107),F$4:F106),0)&lt;=0,D107,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A106=A107),F$4:F106),0))*IFERROR(LOOKUP(2,1/(A$4:A106=A107),G$4:G106),0)+C107*D107)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A106=A107),F$4:F106),0))+C107))))</f>
+        <v/>
+      </c>
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A108" s="12"/>
+      <c r="B108" s="13"/>
+      <c r="C108" s="14"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="6" t="str">
+        <f>IF(A108="","",IFERROR(LOOKUP(2,1/(A$4:A107=A108),F$4:F107),0)+IF(ISNUMBER(C108),C108,0)-IF(ISNUMBER(E108),E108,0))</f>
+        <v/>
+      </c>
+      <c r="G108" s="11" t="str">
+        <f>IF(A108="","",IF(IF(ISNUMBER(C108),C108,0)=0,IFERROR(LOOKUP(2,1/(A$4:A107=A108),G$4:G107),IF(ISNUMBER(D108),D108,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A107=A108),F$4:F107),0)&lt;=0,D108,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A107=A108),F$4:F107),0))*IFERROR(LOOKUP(2,1/(A$4:A107=A108),G$4:G107),0)+C108*D108)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A107=A108),F$4:F107),0))+C108))))</f>
+        <v/>
+      </c>
+      <c r="I108" s="7"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A109" s="12"/>
+      <c r="B109" s="13"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="15"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="6" t="str">
+        <f>IF(A109="","",IFERROR(LOOKUP(2,1/(A$4:A108=A109),F$4:F108),0)+IF(ISNUMBER(C109),C109,0)-IF(ISNUMBER(E109),E109,0))</f>
+        <v/>
+      </c>
+      <c r="G109" s="11" t="str">
+        <f>IF(A109="","",IF(IF(ISNUMBER(C109),C109,0)=0,IFERROR(LOOKUP(2,1/(A$4:A108=A109),G$4:G108),IF(ISNUMBER(D109),D109,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A108=A109),F$4:F108),0)&lt;=0,D109,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A108=A109),F$4:F108),0))*IFERROR(LOOKUP(2,1/(A$4:A108=A109),G$4:G108),0)+C109*D109)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A108=A109),F$4:F108),0))+C109))))</f>
+        <v/>
+      </c>
+      <c r="I109" s="7"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A110" s="12"/>
+      <c r="B110" s="13"/>
+      <c r="C110" s="14"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="14"/>
+      <c r="F110" s="6" t="str">
+        <f>IF(A110="","",IFERROR(LOOKUP(2,1/(A$4:A109=A110),F$4:F109),0)+IF(ISNUMBER(C110),C110,0)-IF(ISNUMBER(E110),E110,0))</f>
+        <v/>
+      </c>
+      <c r="G110" s="11" t="str">
+        <f>IF(A110="","",IF(IF(ISNUMBER(C110),C110,0)=0,IFERROR(LOOKUP(2,1/(A$4:A109=A110),G$4:G109),IF(ISNUMBER(D110),D110,"")),IF(IFERROR(LOOKUP(2,1/(A$4:A109=A110),F$4:F109),0)&lt;=0,D110,(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A109=A110),F$4:F109),0))*IFERROR(LOOKUP(2,1/(A$4:A109=A110),G$4:G109),0)+C110*D110)/(MAX(0,IFERROR(LOOKUP(2,1/(A$4:A109=A110),F$4:F109),0))+C110))))</f>
+        <v/>
+      </c>
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A111" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="9">
-        <f>SUM(C4:C99)</f>
-        <v>10417</v>
-      </c>
-      <c r="D100" s="10">
-        <f>IF(SUM(C4:C99)=0,0,SUMPRODUCT(C4:C99,D4:D99)/SUM(C4:C99))</f>
-        <v>39.000595180954214</v>
-      </c>
-      <c r="E100" s="9">
-        <f>SUM(E4:E99)</f>
-        <v>6553</v>
-      </c>
-      <c r="F100" s="9">
-        <f>SUM(F4:F99)</f>
-        <v>74453</v>
-      </c>
-      <c r="G100" s="9">
-        <f>SUM(G4:G99)</f>
-        <v>2461.5312922124958</v>
-      </c>
-      <c r="I100" s="7"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="9">
+        <f>SUM(C4:C110)</f>
+        <v>10932</v>
+      </c>
+      <c r="D111" s="10">
+        <f>IF(SUM(C4:C110)=0,0,SUMPRODUCT(C4:C110,D4:D110)/SUM(C4:C110))</f>
+        <v>39.819950603732167</v>
+      </c>
+      <c r="E111" s="9">
+        <f>SUM(E4:E110)</f>
+        <v>7019</v>
+      </c>
+      <c r="F111" s="9">
+        <f>SUM(F4:F110)</f>
+        <v>76208</v>
+      </c>
+      <c r="G111" s="9">
+        <f>SUM(G4:G110)</f>
+        <v>3060.1924136746543</v>
+      </c>
+      <c r="I111" s="7"/>
     </row>
   </sheetData>
   <sortState ref="A4:G81">
@@ -10995,7 +11271,7 @@
           <x14:formula1>
             <xm:f>모델_마스터!$B$14:$B$19</xm:f>
           </x14:formula1>
-          <xm:sqref>A4:A99</xm:sqref>
+          <xm:sqref>A4:A110</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="57">
   <si>
     <t>시트구분</t>
   </si>
@@ -203,7 +203,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -251,7 +251,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -554,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -663,34 +663,34 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
@@ -698,7 +698,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
@@ -706,38 +706,70 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B27" t="s">
         <v>24</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH-\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\업무\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="57">
   <si>
     <t>시트구분</t>
   </si>
@@ -781,7 +781,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.19921875" customWidth="1"/>
@@ -1633,21 +1633,21 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C79">
-        <v>340</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.4">
@@ -1655,10 +1655,10 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C81">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.4">
@@ -1666,65 +1666,65 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C82">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C84">
-        <v>125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B85" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>80</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B86" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C86">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B87" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C87">
-        <v>185</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.4">
@@ -1732,54 +1732,54 @@
         <v>16</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C89">
-        <v>125</v>
+        <v>240</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C90">
-        <v>80</v>
+        <v>366</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B91" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C91">
-        <v>75</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C92">
-        <v>185</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.4">
@@ -1787,10 +1787,10 @@
         <v>19</v>
       </c>
       <c r="B93" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C93">
-        <v>240</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
@@ -1798,10 +1798,10 @@
         <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C94">
-        <v>366</v>
+        <v>229</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.4">
@@ -1809,10 +1809,10 @@
         <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C95">
-        <v>269</v>
+        <v>775</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.4">
@@ -1820,10 +1820,10 @@
         <v>19</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C96">
-        <v>268</v>
+        <v>245</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
@@ -1831,65 +1831,65 @@
         <v>19</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C97">
-        <v>280</v>
+        <v>455</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C98">
-        <v>229</v>
+        <v>634</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C99">
-        <v>531</v>
+        <v>954</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>245</v>
+        <v>581</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B101" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C101">
-        <v>455</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C102">
-        <v>500</v>
+        <v>869</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.4">
@@ -1897,10 +1897,10 @@
         <v>20</v>
       </c>
       <c r="B103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C103">
-        <v>634</v>
+        <v>623</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.4">
@@ -1908,10 +1908,10 @@
         <v>20</v>
       </c>
       <c r="B104" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C104">
-        <v>954</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.4">
@@ -1919,10 +1919,10 @@
         <v>20</v>
       </c>
       <c r="B105" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C105">
-        <v>581</v>
+        <v>282</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.4">
@@ -1930,65 +1930,65 @@
         <v>20</v>
       </c>
       <c r="B106" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C106">
-        <v>1048</v>
+        <v>435</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B107" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C107">
-        <v>869</v>
+        <v>196</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C108">
-        <v>623</v>
+        <v>185</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C109">
-        <v>269</v>
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C110">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C111">
-        <v>435</v>
+        <v>56</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.4">
@@ -1996,10 +1996,10 @@
         <v>22</v>
       </c>
       <c r="B112" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C112">
-        <v>196</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.4">
@@ -2007,10 +2007,10 @@
         <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C113">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.4">
@@ -2018,10 +2018,10 @@
         <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C114">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
@@ -2029,10 +2029,10 @@
         <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C115">
-        <v>266</v>
+        <v>72</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
@@ -2040,10 +2040,10 @@
         <v>22</v>
       </c>
       <c r="B116" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C116">
-        <v>56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
@@ -2051,10 +2051,10 @@
         <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C117">
-        <v>68</v>
+        <v>155</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
@@ -2062,97 +2062,42 @@
         <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C118">
-        <v>161</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B119" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C119">
-        <v>165</v>
+        <v>37</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C120">
-        <v>72</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B121" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C121">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A122" t="s">
-        <v>22</v>
-      </c>
-      <c r="B122" t="s">
-        <v>35</v>
-      </c>
-      <c r="C122">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
-        <v>22</v>
-      </c>
-      <c r="B123" t="s">
-        <v>33</v>
-      </c>
-      <c r="C123">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A124" t="s">
-        <v>24</v>
-      </c>
-      <c r="B124" t="s">
-        <v>32</v>
-      </c>
-      <c r="C124">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A125" t="s">
-        <v>24</v>
-      </c>
-      <c r="B125" t="s">
-        <v>34</v>
-      </c>
-      <c r="C125">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A126" t="s">
-        <v>24</v>
-      </c>
-      <c r="B126" t="s">
-        <v>35</v>
-      </c>
-      <c r="C126">
         <v>10</v>
       </c>
     </row>
@@ -2792,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.69921875" customWidth="1"/>
@@ -3030,7 +2975,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="2">
         <v>45992</v>
@@ -3044,7 +2989,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2">
         <v>46082</v>
@@ -3058,7 +3003,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>46204</v>
@@ -3072,71 +3017,29 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>45992</v>
       </c>
       <c r="C22">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="D22">
-        <v>24.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C23">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="2">
-        <v>46204</v>
-      </c>
-      <c r="C24">
-        <v>100</v>
-      </c>
-      <c r="D24">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="2">
-        <v>45992</v>
-      </c>
-      <c r="C25">
-        <v>20</v>
-      </c>
-      <c r="D25">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="2">
-        <v>46143</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-      <c r="D26">
         <v>42</v>
       </c>
     </row>
@@ -3473,39 +3376,17 @@
         <v>46204</v>
       </c>
       <c r="C5">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="D5">
         <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2">
-        <v>46204</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>227</v>
-      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46235</v>
-      </c>
-      <c r="C7">
-        <v>37</v>
-      </c>
-      <c r="D7">
-        <v>215.12</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="57">
   <si>
     <t>시트구분</t>
   </si>
@@ -2737,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.69921875" customWidth="1"/>
@@ -3041,6 +3041,20 @@
       </c>
       <c r="D23">
         <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C24">
+        <v>200</v>
+      </c>
+      <c r="D24">
+        <v>74.900000000000006</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="57">
   <si>
     <t>시트구분</t>
   </si>
@@ -3065,7 +3065,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
@@ -3214,6 +3214,20 @@
       </c>
       <c r="D12">
         <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C13">
+        <v>500</v>
+      </c>
+      <c r="D13">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="59">
   <si>
     <t>시트구분</t>
   </si>
@@ -196,6 +196,14 @@
   </si>
   <si>
     <t>TOPAZ Ultra5</t>
+  </si>
+  <si>
+    <t>16G</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16GB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -554,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -759,17 +767,25 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>24</v>
       </c>
     </row>
@@ -781,7 +797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.19921875" customWidth="1"/>
@@ -2099,6 +2115,17 @@
       </c>
       <c r="C121">
         <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>58</v>
+      </c>
+      <c r="B122" t="s">
+        <v>34</v>
+      </c>
+      <c r="C122">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3065,7 +3092,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
@@ -3228,6 +3255,20 @@
       </c>
       <c r="D13">
         <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2122,7 +2122,7 @@
         <v>58</v>
       </c>
       <c r="B122" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C122">
         <v>8</v>
@@ -3262,7 +3262,7 @@
         <v>57</v>
       </c>
       <c r="B14" s="2">
-        <v>46226</v>
+        <v>46204</v>
       </c>
       <c r="C14">
         <v>10</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1954,13 +1954,13 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B107" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C107">
-        <v>196</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.4">
@@ -1968,10 +1968,10 @@
         <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C108">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.4">
@@ -1979,10 +1979,10 @@
         <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C109">
-        <v>153</v>
+        <v>185</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.4">
@@ -1990,10 +1990,10 @@
         <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C110">
-        <v>266</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.4">
@@ -2001,10 +2001,10 @@
         <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C111">
-        <v>56</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.4">
@@ -2012,10 +2012,10 @@
         <v>22</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C112">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.4">
@@ -2023,10 +2023,10 @@
         <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C113">
-        <v>161</v>
+        <v>68</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.4">
@@ -2034,10 +2034,10 @@
         <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C114">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
@@ -2045,10 +2045,10 @@
         <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C115">
-        <v>72</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
@@ -2056,10 +2056,10 @@
         <v>22</v>
       </c>
       <c r="B116" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
@@ -2067,10 +2067,10 @@
         <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C117">
-        <v>155</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
@@ -2078,21 +2078,21 @@
         <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C118">
-        <v>60</v>
+        <v>155</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B119" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C119">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
@@ -2100,10 +2100,10 @@
         <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C120">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
@@ -2111,7 +2111,7 @@
         <v>24</v>
       </c>
       <c r="B121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C121">
         <v>10</v>
@@ -2119,13 +2119,13 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B122" t="s">
         <v>35</v>
       </c>
       <c r="C122">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
     <t>TOPAZ Ultra5</t>
   </si>
   <si>
-    <t>16G</t>
+    <t>16GB</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -770,7 +770,7 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C107">
         <v>8</v>
@@ -3259,7 +3259,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2">
         <v>46204</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -904,7 +904,7 @@
         <v>35</v>
       </c>
       <c r="C11">
-        <v>80</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
@@ -992,7 +992,7 @@
         <v>35</v>
       </c>
       <c r="C19">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
@@ -1003,7 +1003,7 @@
         <v>36</v>
       </c>
       <c r="C20">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
@@ -1058,7 +1058,7 @@
         <v>35</v>
       </c>
       <c r="C25">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
@@ -1069,7 +1069,7 @@
         <v>36</v>
       </c>
       <c r="C26">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
@@ -1190,7 +1190,7 @@
         <v>35</v>
       </c>
       <c r="C37">
-        <v>618</v>
+        <v>565</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
@@ -1201,7 +1201,7 @@
         <v>36</v>
       </c>
       <c r="C38">
-        <v>30</v>
+        <v>625</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
@@ -1267,7 +1267,7 @@
         <v>35</v>
       </c>
       <c r="C44">
-        <v>366</v>
+        <v>474</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
@@ -1278,7 +1278,7 @@
         <v>36</v>
       </c>
       <c r="C45">
-        <v>570</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
@@ -1388,7 +1388,7 @@
         <v>35</v>
       </c>
       <c r="C55">
-        <v>312</v>
+        <v>350</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
@@ -1399,7 +1399,7 @@
         <v>36</v>
       </c>
       <c r="C56">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
@@ -1454,7 +1454,7 @@
         <v>36</v>
       </c>
       <c r="C61">
-        <v>310</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
@@ -2092,7 +2092,7 @@
         <v>33</v>
       </c>
       <c r="C119">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
@@ -2114,7 +2114,7 @@
         <v>34</v>
       </c>
       <c r="C121">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,25 @@
     <sheet name="Android MB" sheetId="6" r:id="rId6"/>
     <sheet name="SAP-600 MB" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="59">
   <si>
     <t>시트구분</t>
   </si>
@@ -797,7 +810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.19921875" customWidth="1"/>
@@ -1569,24 +1582,24 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C72">
-        <v>31</v>
+        <v>675</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C73">
-        <v>42</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
@@ -1594,10 +1607,10 @@
         <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C74">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
@@ -1605,10 +1618,10 @@
         <v>13</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C75">
-        <v>212</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
@@ -1616,10 +1629,10 @@
         <v>13</v>
       </c>
       <c r="B76" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C76">
-        <v>474</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
@@ -1627,10 +1640,10 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C77">
-        <v>38</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
@@ -1638,10 +1651,10 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C78">
-        <v>37</v>
+        <v>474</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
@@ -1649,10 +1662,10 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C79">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
@@ -1660,175 +1673,175 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C80">
-        <v>140</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C81">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C82">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C83">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C85">
-        <v>125</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86">
         <v>16</v>
-      </c>
-      <c r="B86" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86">
-        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B87" t="s">
         <v>41</v>
       </c>
       <c r="C87">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C88">
-        <v>185</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B89" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C89">
-        <v>240</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>366</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C91">
-        <v>269</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C92">
-        <v>268</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B93" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C93">
-        <v>280</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C94">
-        <v>229</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C95">
-        <v>775</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.4">
@@ -1836,10 +1849,10 @@
         <v>19</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C96">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
@@ -1847,241 +1860,241 @@
         <v>19</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C97">
-        <v>455</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B98" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>634</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B99" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C99">
-        <v>954</v>
+        <v>268</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C100">
-        <v>581</v>
+        <v>280</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B101" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C101">
-        <v>1048</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B102" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C102">
-        <v>869</v>
+        <v>775</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B103" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C103">
-        <v>623</v>
+        <v>489</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B104" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C104">
-        <v>269</v>
+        <v>455</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C105">
-        <v>282</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B106" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C106">
-        <v>435</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="B107" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>634</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B108" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C108">
-        <v>196</v>
+        <v>954</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B109" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C109">
-        <v>185</v>
+        <v>581</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B110" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C110">
-        <v>153</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C111">
-        <v>266</v>
+        <v>869</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B112" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C112">
-        <v>56</v>
+        <v>623</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B113" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C113">
-        <v>68</v>
+        <v>269</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C114">
-        <v>161</v>
+        <v>282</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B115" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C115">
-        <v>165</v>
+        <v>420</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B116" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C116">
-        <v>72</v>
+        <v>725</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C117">
-        <v>10</v>
+        <v>600</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B118" t="s">
         <v>35</v>
       </c>
       <c r="C118">
-        <v>155</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
@@ -2089,42 +2102,163 @@
         <v>22</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>196</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B120" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C120">
-        <v>37</v>
+        <v>185</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B121" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C121">
-        <v>19</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
+        <v>22</v>
+      </c>
+      <c r="B122" t="s">
+        <v>40</v>
+      </c>
+      <c r="C122">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>22</v>
+      </c>
+      <c r="B123" t="s">
+        <v>37</v>
+      </c>
+      <c r="C123">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>22</v>
+      </c>
+      <c r="B124" t="s">
+        <v>29</v>
+      </c>
+      <c r="C124">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125" t="s">
+        <v>31</v>
+      </c>
+      <c r="C125">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>22</v>
+      </c>
+      <c r="B126" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>22</v>
+      </c>
+      <c r="B127" t="s">
+        <v>32</v>
+      </c>
+      <c r="C127">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>22</v>
+      </c>
+      <c r="B128" t="s">
+        <v>34</v>
+      </c>
+      <c r="C128">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129" t="s">
+        <v>35</v>
+      </c>
+      <c r="C129">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>22</v>
+      </c>
+      <c r="B130" t="s">
+        <v>33</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
         <v>24</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B131" t="s">
+        <v>32</v>
+      </c>
+      <c r="C131">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>24</v>
+      </c>
+      <c r="B132" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>24</v>
+      </c>
+      <c r="B133" t="s">
         <v>35</v>
       </c>
-      <c r="C122">
+      <c r="C133">
         <v>10</v>
       </c>
     </row>
@@ -3254,7 +3388,7 @@
         <v>500</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -3400,7 +3534,7 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="40.296875" customWidth="1"/>
+    <col min="1" max="1" width="40.19921875" customWidth="1"/>
     <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -20,7 +20,7 @@
     <sheet name="Android MB" sheetId="6" r:id="rId6"/>
     <sheet name="SAP-600 MB" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="59">
   <si>
     <t>시트구분</t>
   </si>
@@ -269,10 +269,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -810,7 +811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.19921875" customWidth="1"/>
@@ -939,7 +940,7 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
@@ -1214,7 +1215,7 @@
         <v>36</v>
       </c>
       <c r="C38">
-        <v>625</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
@@ -1225,7 +1226,7 @@
         <v>33</v>
       </c>
       <c r="C39">
-        <v>70</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
@@ -1302,7 +1303,7 @@
         <v>33</v>
       </c>
       <c r="C46">
-        <v>580</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
@@ -1423,7 +1424,7 @@
         <v>33</v>
       </c>
       <c r="C57">
-        <v>105</v>
+        <v>285</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
@@ -1474,11 +1475,11 @@
       <c r="A62" t="s">
         <v>10</v>
       </c>
-      <c r="B62" t="s">
-        <v>33</v>
+      <c r="B62" s="3">
+        <v>46327</v>
       </c>
       <c r="C62">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
@@ -2226,7 +2227,7 @@
         <v>33</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
@@ -2260,6 +2261,83 @@
       </c>
       <c r="C133">
         <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A134" t="s">
+        <v>22</v>
+      </c>
+      <c r="B134" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C134">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>24</v>
+      </c>
+      <c r="B135" t="s">
+        <v>36</v>
+      </c>
+      <c r="C135">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>4</v>
+      </c>
+      <c r="B136" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C136">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A137" t="s">
+        <v>5</v>
+      </c>
+      <c r="B137" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C137">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A138" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C138">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C139">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C140">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="1"/>
+    <workbookView xWindow="-4980" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="807" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="모델_마스터" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="65">
   <si>
     <t>시트구분</t>
   </si>
@@ -216,6 +216,30 @@
   </si>
   <si>
     <t>16GB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASTRA i3 11th (35F)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASTRA i5 11th (35G)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASTRA i3 12th (44A)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASTRA i5 12th (44B)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASTRA i5 12th (44B)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASTRA i5 12th (44B)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -576,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -801,6 +825,38 @@
       </c>
       <c r="B28" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -811,10 +867,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.19921875" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
@@ -2338,6 +2395,165 @@
       </c>
       <c r="C140">
         <v>120</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A141" t="s">
+        <v>59</v>
+      </c>
+      <c r="B141" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C141">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A142" t="s">
+        <v>60</v>
+      </c>
+      <c r="B142" s="3">
+        <v>45748</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>59</v>
+      </c>
+      <c r="B144" t="s">
+        <v>41</v>
+      </c>
+      <c r="C144">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>61</v>
+      </c>
+      <c r="B145" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>61</v>
+      </c>
+      <c r="B146" s="3">
+        <v>45962</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A147" t="s">
+        <v>61</v>
+      </c>
+      <c r="B147" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>61</v>
+      </c>
+      <c r="B148" t="s">
+        <v>32</v>
+      </c>
+      <c r="C148">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>61</v>
+      </c>
+      <c r="B149" t="s">
+        <v>34</v>
+      </c>
+      <c r="C149">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>60</v>
+      </c>
+      <c r="B150" s="3">
+        <v>45778</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>60</v>
+      </c>
+      <c r="B151" s="3">
+        <v>45809</v>
+      </c>
+      <c r="C151">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>60</v>
+      </c>
+      <c r="B152" s="3">
+        <v>45839</v>
+      </c>
+      <c r="C152">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>60</v>
+      </c>
+      <c r="B153" s="3">
+        <v>45870</v>
+      </c>
+      <c r="C153">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>60</v>
+      </c>
+      <c r="B154" s="3">
+        <v>45931</v>
+      </c>
+      <c r="C154">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
+        <v>60</v>
+      </c>
+      <c r="B155" s="3">
+        <v>45962</v>
+      </c>
+      <c r="C155">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2348,7 +2564,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30.8984375" customWidth="1"/>
@@ -2966,6 +3182,56 @@
       </c>
       <c r="B48" s="2">
         <v>46315</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46054</v>
+      </c>
+      <c r="C49">
+        <v>50</v>
+      </c>
+      <c r="D49">
+        <v>162.30000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" s="2">
+        <v>45292</v>
+      </c>
+      <c r="C50">
+        <v>23</v>
+      </c>
+      <c r="D50">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45870</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+      <c r="D51">
+        <v>164.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46266</v>
       </c>
     </row>
   </sheetData>
